--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -9,511 +9,396 @@
   <sheets>
     <sheet name="Opis parametrów" sheetId="2" r:id="rId2"/>
     <sheet name="Oddziały" sheetId="3" r:id="rId3"/>
-    <sheet name="Dyżury" sheetId="4" r:id="rId4"/>
+    <sheet name="Dzienniki zajeć innych" sheetId="4" r:id="rId4"/>
+    <sheet name="Dyżury" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Oddziały!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Dyżury!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dzienniki zajeć innych'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dyżury!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="164">
-  <si>
-    <t>Rok szkolny: 2026/2027</t>
-  </si>
-  <si>
-    <t>Okres: 07.09.2026 (pon.) - 13.09.2026 (niedz.)</t>
-  </si>
-  <si>
-    <t>Dzień</t>
-  </si>
-  <si>
-    <t>Lekcja</t>
-  </si>
-  <si>
-    <t>Nauczyciel/wakat</t>
-  </si>
-  <si>
-    <t>Oddział</t>
-  </si>
-  <si>
-    <t>Przedmiot</t>
-  </si>
-  <si>
-    <t>Sala</t>
-  </si>
-  <si>
-    <t>Zastępca</t>
-  </si>
-  <si>
-    <t>Uwagi</t>
-  </si>
-  <si>
-    <t>Forma płatności</t>
-  </si>
-  <si>
-    <t>07.09.2026</t>
-  </si>
-  <si>
-    <t>1, 08:00-08:45</t>
-  </si>
-  <si>
-    <t>Stępień Krystyna</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>Technika w produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>prs</t>
-  </si>
-  <si>
-    <t>Uczniowie przychodzą później</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>2, 08:50-09:35</t>
-  </si>
-  <si>
-    <t>3, 09:40-10:25</t>
-  </si>
-  <si>
-    <t>3CA</t>
-  </si>
-  <si>
-    <t>4, 10:35-11:20</t>
-  </si>
-  <si>
-    <t>Sobczak Anna</t>
-  </si>
-  <si>
-    <t>2FA</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Biezmienow Małgorzata</t>
-  </si>
-  <si>
-    <t>Dodatkowo płatne</t>
-  </si>
-  <si>
-    <t>Technologie produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>5, 11:25-12:10</t>
-  </si>
-  <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
-    <t>1TFA|gr1</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>Zajęcia biblioteczne</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>Wrzeszcz Barbara</t>
-  </si>
-  <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
-    <t>1CA</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Kaczorowski Waldemar</t>
-  </si>
-  <si>
-    <t>6, 12:25-13:10</t>
-  </si>
-  <si>
-    <t>1TFH|gr2</t>
-  </si>
-  <si>
-    <t>1FB</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>prF3</t>
-  </si>
-  <si>
-    <t>Uczniowie zwolnieni do domu</t>
-  </si>
-  <si>
-    <t>Zajęcia z wychowawcą</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Galert Anna</t>
-  </si>
-  <si>
-    <t>7, 13:15-14:00</t>
-  </si>
-  <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>Filusz Marzena</t>
-  </si>
-  <si>
-    <t>4TFB</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>1TFB|gr1</t>
-  </si>
-  <si>
-    <t>Zając Ewa</t>
-  </si>
-  <si>
-    <t>9, 14:55-15:40</t>
-  </si>
-  <si>
-    <t>4TFA</t>
-  </si>
-  <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>Filipiak Wiesław</t>
-  </si>
-  <si>
-    <t>11, 16:35-17:20</t>
-  </si>
-  <si>
-    <t>Krystek Krzysztof</t>
-  </si>
-  <si>
-    <t>1B</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>12, 17:25-18:10</t>
-  </si>
-  <si>
-    <t>13, 18:15-19:00</t>
-  </si>
-  <si>
-    <t>08.09.2026</t>
-  </si>
-  <si>
-    <t>1TFB|gr2</t>
-  </si>
-  <si>
-    <t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Jaworska Edyta</t>
-  </si>
-  <si>
-    <t>prf2</t>
-  </si>
-  <si>
-    <t>Leńczowska Iwona</t>
-  </si>
-  <si>
-    <t>10, 15:45-16:30</t>
-  </si>
-  <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>09.09.2026</t>
-  </si>
-  <si>
-    <t>Krycia Ewelina</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>Informatyka</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>1CB</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Zaleska Magdalena</t>
-  </si>
-  <si>
-    <t>1S</t>
-  </si>
-  <si>
-    <t>Biologia</t>
-  </si>
-  <si>
-    <t>Mucha Anna</t>
-  </si>
-  <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>Kruk Marcin</t>
-  </si>
-  <si>
-    <t>3TFB|gr2</t>
-  </si>
-  <si>
-    <t>10.09.2026</t>
-  </si>
-  <si>
-    <t>1CB|fryzjer</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Jastrzębska-Majtyka Agnieszka</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
-    <t>5TFB</t>
-  </si>
-  <si>
-    <t>2CA|CH</t>
-  </si>
-  <si>
-    <t>Wychowanie fizyczne</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Pietrycha Małgorzata</t>
-  </si>
-  <si>
-    <t>2CA|DZ</t>
-  </si>
-  <si>
-    <t>1FA|gr1</t>
-  </si>
-  <si>
-    <t>1FA|gr2</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2WA</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Wójcik Kamil</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>Filipek Anna</t>
-  </si>
-  <si>
-    <t>1TFB</t>
-  </si>
-  <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>Ostrowska Ewa</t>
-  </si>
-  <si>
-    <t>2CB</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>11.09.2026</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
-  </si>
-  <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Małecka Barbara</t>
-  </si>
-  <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
-    <t>Sałdyka Karolina</t>
-  </si>
-  <si>
-    <t>3FB</t>
-  </si>
-  <si>
-    <t>1TFH</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>Doradztwo zawodowe</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
-    <t>Godzina</t>
-  </si>
-  <si>
-    <t>Nauczyciel</t>
-  </si>
-  <si>
-    <t>Miejsce dyżuru</t>
-  </si>
-  <si>
-    <t>10:25-10:35</t>
-  </si>
-  <si>
-    <t>boisko - dziedziniec wejściowy/boisko</t>
-  </si>
-  <si>
-    <t>Nowak Magdalena</t>
-  </si>
-  <si>
-    <t>13:10-13:15</t>
-  </si>
-  <si>
-    <t>14:00-14:05</t>
-  </si>
-  <si>
-    <t>14:50-14:55</t>
-  </si>
-  <si>
-    <t>piętro_1</t>
-  </si>
-  <si>
-    <t>Ulanowska Magdalena</t>
-  </si>
-  <si>
-    <t>16:30-16:35</t>
-  </si>
-  <si>
-    <t>Smereka Alicja</t>
-  </si>
-  <si>
-    <t>09:35-09:40</t>
-  </si>
-  <si>
-    <t>piętro_3</t>
-  </si>
-  <si>
-    <t>07:55-08:00</t>
-  </si>
-  <si>
-    <t>parter</t>
-  </si>
-  <si>
-    <t>11:20-11:25</t>
-  </si>
-  <si>
-    <t>Marzec Renata</t>
-  </si>
-  <si>
-    <t>12:10-12:25</t>
-  </si>
-  <si>
-    <t>Piątek-Pawłowska Bożena</t>
-  </si>
-  <si>
-    <t>piętro_2</t>
-  </si>
-  <si>
-    <t>Świerzewicz Katarzyna</t>
-  </si>
-  <si>
-    <t>Karczmarz Aleksandra</t>
-  </si>
-  <si>
-    <t>Biczysko Wojciech</t>
-  </si>
-  <si>
-    <t>Misiąg Anna</t>
-  </si>
-  <si>
-    <t>Kopij Marcin</t>
-  </si>
-  <si>
-    <t>15:40-15:45</t>
-  </si>
-</sst>
+<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="125">
+  <ns0:si>
+    <ns0:t>Rok szkolny: 2026/2027</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Okres: 14.09.2026 (pon.) - 20.09.2026 (niedz.)</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Dzień</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Lekcja</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Nauczyciel/wakat</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Oddział</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Przedmiot</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Sala</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Zastępca</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Uwagi</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Forma płatności</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>14.09.2026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1, 08:00-08:45</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Stępień Krystyna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2CA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Technika w produkcji cukierniczej</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>prs</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kończyńska Małgorzata</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t/>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Dodatkowo płatne</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2, 08:50-09:35</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Krycia Ewelina</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1TFA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Biologia</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>31</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Sałdyka Karolina</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3, 09:40-10:25</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Język polski</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>33</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Zastępstwo</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>-</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3CA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4, 10:35-11:20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3WA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Zajęcia biblioteczne</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>bib</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Wrzeszcz Barbara</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bezpłatne</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Technologie produkcji cukierniczej</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5, 11:25-12:10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1FB</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Historia</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kaczorowski Waldemar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1CA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6, 12:25-13:10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2TFB</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7, 13:15-14:00</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Zajęcia z wychowawcą</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Galert Anna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8, 14:05-14:50</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Filusz Marzena</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4TFB</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Uczniowie zwolnieni do domu</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9, 14:55-15:40</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4TFA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Doradztwo zawodowe</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Krzemińska Beata</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>15.09.2026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Jaworska Edyta</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1TFB|gr1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bez konsekwencji (nieobecny oddział nauczyciela)</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Sobczak Anna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1TFB|gr2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>prf2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Misiąg Anna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2WA|gr1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Język niemiecki</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>44</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2TFA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3TFB|gr1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1TFA|gr1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1TFH|gr1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2TH</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Techniki fryzjerskie</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10, 15:45-16:30</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>16.09.2026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1CB</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1S</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Matematyka</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>17.09.2026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5TFB</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1FA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>18.09.2026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Świerzewicz Katarzyna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2K</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Technologia gastronomiczna z towaroznawstwem</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>29</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Okienko dla uczniów</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Godzina</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Nauczyciel</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Dziennik zajęć innych</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Opis zajęć</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>08:00-08:45</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t/>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>08:00-14:40</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bokuniewicz Sylwia</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t/>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>dyżur pedagoga</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>04</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>08:50-09:35</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Miejsce dyżuru</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>08:45-08:50</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>piętro_3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kosin Anna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>09:35-09:40</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>piętro_2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10:25-10:35</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>boisko - dziedziniec wejściowy/boisko</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Jastrzębska-Majtyka Agnieszka</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>07:55-08:00</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>parter</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>13:10-13:15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>14:00-14:05</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>14:50-14:55</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>piętro_1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>16:30-16:35</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>11:20-11:25</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>12:10-12:25</ns0:t>
+  </ns0:si>
+</ns0:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -961,7 +846,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7b69b720-263f-409a-8ace-71751a1182b4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{07798d68-ff35-4714-beca-c4f6135787b9}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -982,17 +867,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{65802c7f-f101-4504-9092-87d613bbd669}">
-  <dimension ref="A1:I94"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{df400fe4-3e65-42b8-b0b6-7605c1b5066c}">
+  <dimension ref="A1:I78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="11.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="21.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="68.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
-    <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="45.5714285714286" customWidth="1"/>
     <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
@@ -1063,19 +948,19 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -1089,13 +974,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -1118,28 +1003,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1147,16 +1032,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1176,28 +1061,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1205,28 +1090,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
@@ -1234,10 +1119,10 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
         <v>40</v>
@@ -1255,7 +1140,7 @@
         <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
@@ -1263,28 +1148,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
         <v>44</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -1292,28 +1177,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
         <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1321,28 +1206,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1350,19 +1235,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G13" t="s">
         <v>49</v>
@@ -1379,28 +1264,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s">
         <v>54</v>
       </c>
-      <c r="C14" t="s">
+      <c r="G14" t="s">
         <v>55</v>
       </c>
-      <c r="D14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" t="s">
-        <v>49</v>
-      </c>
       <c r="H14" t="s">
         <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1408,19 +1293,19 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" t="s">
         <v>59</v>
-      </c>
-      <c r="E15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" t="s">
-        <v>37</v>
       </c>
       <c r="G15" t="s">
         <v>60</v>
@@ -1429,1088 +1314,1088 @@
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" t="s">
         <v>66</v>
       </c>
-      <c r="D17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" t="s">
-        <v>64</v>
-      </c>
       <c r="H17" t="s">
         <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" t="s">
         <v>66</v>
       </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" t="s">
-        <v>64</v>
-      </c>
       <c r="H18" t="s">
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
         <v>70</v>
       </c>
-      <c r="C19" t="s">
-        <v>66</v>
-      </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="H20" t="s">
         <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
         <v>21</v>
       </c>
-      <c r="C22" t="s">
-        <v>24</v>
-      </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G22" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s">
         <v>72</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>73</v>
       </c>
-      <c r="F23" t="s">
-        <v>74</v>
-      </c>
       <c r="G23" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="H23" t="s">
         <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F24" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G24" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H24" t="s">
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F25" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
       <c r="A27" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E27" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="G27" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F28" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="G28" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F29" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G29" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E30" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F30" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="E31" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F31" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="E33" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="G33" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F34" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="G34" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E35" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="F35" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="G35" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E36" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F36" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="G36" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G37" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G38" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E39" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G39" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="G40" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D41" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="G41" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E42" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F42" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="G42" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C43" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D43" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="E43" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F43" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B44" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="E44" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="G44" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B45" t="s">
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F45" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="G45" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
         <v>21</v>
       </c>
-      <c r="C46" t="s">
-        <v>81</v>
-      </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E46" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F46" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="G46" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" t="s">
         <v>21</v>
       </c>
-      <c r="C47" t="s">
-        <v>24</v>
-      </c>
       <c r="D47" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E47" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F47" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="G47" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="E48" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F48" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="G48" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D49" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="E49" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F49" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="G49" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="E50" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F50" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G50" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="F51" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B52" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E52" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F52" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="G52" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
@@ -2519,1208 +2404,744 @@
         <v>14</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="F53" t="s">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="E54" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F54" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="G54" t="s">
-        <v>111</v>
+        <v>30</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E55" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F55" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="E56" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F56" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="G56" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B57" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="F57" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>114</v>
+        <v>30</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B58" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C58" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E58" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="F58" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C59" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F59" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B60" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="E60" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="F60" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G60" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C61" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D61" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E61" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="F61" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G61" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B62" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C62" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="D62" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="E62" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="F62" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="G62" t="s">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B63" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E63" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F63" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C64" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="D64" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="E64" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="F64" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="G64" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B65" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C65" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E65" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F65" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B66" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="C66" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="D66" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="E66" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="F66" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B67" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E67" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F67" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="G67" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="E68" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F68" t="s">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B69" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="D69" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="E69" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="F69" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="G69" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="C70" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="E70" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="F70" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="G70" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C71" t="s">
         <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E71" t="s">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="F71" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C72" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="D72" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E72" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="F72" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G72" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C73" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E73" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F73" t="s">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="G73" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C74" t="s">
         <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E74" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F74" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="G74" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="D75" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="E75" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="F75" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G75" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" t="s">
         <v>21</v>
       </c>
-      <c r="C76" t="s">
-        <v>81</v>
-      </c>
       <c r="D76" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E76" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F76" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="G76" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B77" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C77" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="E77" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F77" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B78" t="s">
+        <v>47</v>
+      </c>
+      <c r="C78" t="s">
         <v>21</v>
       </c>
-      <c r="C78" t="s">
-        <v>13</v>
-      </c>
       <c r="D78" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="E78" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F78" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="G78" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="15">
-      <c r="A79" t="s">
-        <v>122</v>
-      </c>
-      <c r="B79" t="s">
-        <v>23</v>
-      </c>
-      <c r="C79" t="s">
-        <v>81</v>
-      </c>
-      <c r="D79" t="s">
-        <v>46</v>
-      </c>
-      <c r="E79" t="s">
-        <v>36</v>
-      </c>
-      <c r="F79" t="s">
-        <v>37</v>
-      </c>
-      <c r="G79" t="s">
-        <v>60</v>
-      </c>
-      <c r="H79" t="s">
-        <v>18</v>
-      </c>
-      <c r="I79" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="15">
-      <c r="A80" t="s">
-        <v>122</v>
-      </c>
-      <c r="B80" t="s">
-        <v>23</v>
-      </c>
-      <c r="C80" t="s">
-        <v>24</v>
-      </c>
-      <c r="D80" t="s">
-        <v>96</v>
-      </c>
-      <c r="E80" t="s">
-        <v>47</v>
-      </c>
-      <c r="F80" t="s">
-        <v>125</v>
-      </c>
-      <c r="G80" t="s">
-        <v>98</v>
-      </c>
-      <c r="H80" t="s">
-        <v>18</v>
-      </c>
-      <c r="I80" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="15">
-      <c r="A81" t="s">
-        <v>122</v>
-      </c>
-      <c r="B81" t="s">
-        <v>23</v>
-      </c>
-      <c r="C81" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" t="s">
-        <v>40</v>
-      </c>
-      <c r="E81" t="s">
-        <v>30</v>
-      </c>
-      <c r="F81" t="s">
-        <v>68</v>
-      </c>
-      <c r="G81" t="s">
-        <v>99</v>
-      </c>
-      <c r="H81" t="s">
-        <v>18</v>
-      </c>
-      <c r="I81" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="15">
-      <c r="A82" t="s">
-        <v>122</v>
-      </c>
-      <c r="B82" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" t="s">
-        <v>124</v>
-      </c>
-      <c r="D82" t="s">
-        <v>127</v>
-      </c>
-      <c r="E82" t="s">
-        <v>117</v>
-      </c>
-      <c r="F82" t="s">
-        <v>112</v>
-      </c>
-      <c r="G82" t="s">
-        <v>17</v>
-      </c>
-      <c r="H82" t="s">
-        <v>18</v>
-      </c>
-      <c r="I82" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="15">
-      <c r="A83" t="s">
-        <v>122</v>
-      </c>
-      <c r="B83" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" t="s">
-        <v>81</v>
-      </c>
-      <c r="D83" t="s">
-        <v>128</v>
-      </c>
-      <c r="E83" t="s">
-        <v>89</v>
-      </c>
-      <c r="F83" t="s">
-        <v>68</v>
-      </c>
-      <c r="G83" t="s">
-        <v>129</v>
-      </c>
-      <c r="H83" t="s">
-        <v>18</v>
-      </c>
-      <c r="I83" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="15">
-      <c r="A84" t="s">
-        <v>122</v>
-      </c>
-      <c r="B84" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" t="s">
-        <v>24</v>
-      </c>
-      <c r="D84" t="s">
-        <v>91</v>
-      </c>
-      <c r="E84" t="s">
-        <v>47</v>
-      </c>
-      <c r="F84" t="s">
-        <v>48</v>
-      </c>
-      <c r="G84" t="s">
-        <v>17</v>
-      </c>
-      <c r="H84" t="s">
-        <v>18</v>
-      </c>
-      <c r="I84" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="15">
-      <c r="A85" t="s">
-        <v>122</v>
-      </c>
-      <c r="B85" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" t="s">
-        <v>40</v>
-      </c>
-      <c r="E85" t="s">
-        <v>30</v>
-      </c>
-      <c r="F85" t="s">
-        <v>112</v>
-      </c>
-      <c r="G85" t="s">
-        <v>99</v>
-      </c>
-      <c r="H85" t="s">
-        <v>18</v>
-      </c>
-      <c r="I85" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="15">
-      <c r="A86" t="s">
-        <v>122</v>
-      </c>
-      <c r="B86" t="s">
-        <v>44</v>
-      </c>
-      <c r="C86" t="s">
-        <v>124</v>
-      </c>
-      <c r="D86" t="s">
-        <v>130</v>
-      </c>
-      <c r="E86" t="s">
-        <v>36</v>
-      </c>
-      <c r="F86" t="s">
-        <v>37</v>
-      </c>
-      <c r="G86" t="s">
-        <v>38</v>
-      </c>
-      <c r="H86" t="s">
-        <v>18</v>
-      </c>
-      <c r="I86" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="15">
-      <c r="A87" t="s">
-        <v>122</v>
-      </c>
-      <c r="B87" t="s">
-        <v>44</v>
-      </c>
-      <c r="C87" t="s">
-        <v>81</v>
-      </c>
-      <c r="D87" t="s">
-        <v>85</v>
-      </c>
-      <c r="E87" t="s">
-        <v>89</v>
-      </c>
-      <c r="F87" t="s">
-        <v>68</v>
-      </c>
-      <c r="G87" t="s">
-        <v>126</v>
-      </c>
-      <c r="H87" t="s">
-        <v>18</v>
-      </c>
-      <c r="I87" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="15">
-      <c r="A88" t="s">
-        <v>122</v>
-      </c>
-      <c r="B88" t="s">
-        <v>44</v>
-      </c>
-      <c r="C88" t="s">
-        <v>24</v>
-      </c>
-      <c r="D88" t="s">
-        <v>91</v>
-      </c>
-      <c r="E88" t="s">
-        <v>47</v>
-      </c>
-      <c r="F88" t="s">
-        <v>48</v>
-      </c>
-      <c r="G88" t="s">
-        <v>17</v>
-      </c>
-      <c r="H88" t="s">
-        <v>18</v>
-      </c>
-      <c r="I88" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="15">
-      <c r="A89" t="s">
-        <v>122</v>
-      </c>
-      <c r="B89" t="s">
-        <v>44</v>
-      </c>
-      <c r="C89" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" t="s">
-        <v>40</v>
-      </c>
-      <c r="E89" t="s">
-        <v>50</v>
-      </c>
-      <c r="F89" t="s">
-        <v>112</v>
-      </c>
-      <c r="G89" t="s">
-        <v>99</v>
-      </c>
-      <c r="H89" t="s">
-        <v>18</v>
-      </c>
-      <c r="I89" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="15">
-      <c r="A90" t="s">
-        <v>122</v>
-      </c>
-      <c r="B90" t="s">
-        <v>53</v>
-      </c>
-      <c r="C90" t="s">
-        <v>124</v>
-      </c>
-      <c r="D90" t="s">
-        <v>131</v>
-      </c>
-      <c r="E90" t="s">
-        <v>36</v>
-      </c>
-      <c r="F90" t="s">
-        <v>37</v>
-      </c>
-      <c r="G90" t="s">
-        <v>38</v>
-      </c>
-      <c r="H90" t="s">
-        <v>18</v>
-      </c>
-      <c r="I90" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="15">
-      <c r="A91" t="s">
-        <v>122</v>
-      </c>
-      <c r="B91" t="s">
-        <v>53</v>
-      </c>
-      <c r="C91" t="s">
-        <v>81</v>
-      </c>
-      <c r="D91" t="s">
-        <v>113</v>
-      </c>
-      <c r="E91" t="s">
-        <v>89</v>
-      </c>
-      <c r="F91" t="s">
-        <v>68</v>
-      </c>
-      <c r="G91" t="s">
-        <v>129</v>
-      </c>
-      <c r="H91" t="s">
-        <v>18</v>
-      </c>
-      <c r="I91" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="15">
-      <c r="A92" t="s">
-        <v>122</v>
-      </c>
-      <c r="B92" t="s">
-        <v>53</v>
-      </c>
-      <c r="C92" t="s">
-        <v>24</v>
-      </c>
-      <c r="D92" t="s">
-        <v>115</v>
-      </c>
-      <c r="E92" t="s">
-        <v>50</v>
-      </c>
-      <c r="F92" t="s">
-        <v>132</v>
-      </c>
-      <c r="G92" t="s">
-        <v>35</v>
-      </c>
-      <c r="H92" t="s">
-        <v>18</v>
-      </c>
-      <c r="I92" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="15">
-      <c r="A93" t="s">
-        <v>122</v>
-      </c>
-      <c r="B93" t="s">
-        <v>54</v>
-      </c>
-      <c r="C93" t="s">
-        <v>24</v>
-      </c>
-      <c r="D93" t="s">
-        <v>115</v>
-      </c>
-      <c r="E93" t="s">
-        <v>133</v>
-      </c>
-      <c r="F93" t="s">
-        <v>134</v>
-      </c>
-      <c r="G93" t="s">
-        <v>135</v>
-      </c>
-      <c r="H93" t="s">
-        <v>18</v>
-      </c>
-      <c r="I93" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="15">
-      <c r="A94" t="s">
-        <v>122</v>
-      </c>
-      <c r="B94" t="s">
-        <v>61</v>
-      </c>
-      <c r="C94" t="s">
-        <v>24</v>
-      </c>
-      <c r="D94" t="s">
-        <v>115</v>
-      </c>
-      <c r="E94" t="s">
-        <v>133</v>
-      </c>
-      <c r="F94" t="s">
-        <v>134</v>
-      </c>
-      <c r="G94" t="s">
-        <v>135</v>
-      </c>
-      <c r="H94" t="s">
-        <v>18</v>
-      </c>
-      <c r="I94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3731,13 +3152,152 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5f4407a8-5b32-4469-94ef-9f5ffad6c2ad}">
-  <dimension ref="A1:F19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c43d19c3-00f8-43fd-bbf0-6a5019495413}">
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="17.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="18.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="36.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="15.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
+    <col min="7" max="7" width="45.5714285714286" customWidth="1"/>
+    <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
+    <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="56.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a7d12d72-5462-41e7-838e-42a1c7885cf9}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
@@ -3748,13 +3308,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -3768,16 +3328,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -3788,16 +3348,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -3808,16 +3368,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -3825,19 +3385,19 @@
     </row>
     <row r="5" spans="1:6" ht="15">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="E5" t="s">
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -3845,19 +3405,19 @@
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>148</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -3865,19 +3425,19 @@
     </row>
     <row r="7" spans="1:6" ht="15">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -3885,19 +3445,19 @@
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -3905,19 +3465,19 @@
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>154</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -3925,19 +3485,19 @@
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -3945,19 +3505,19 @@
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -3965,19 +3525,19 @@
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -3985,19 +3545,19 @@
     </row>
     <row r="13" spans="1:6" ht="15">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -4005,19 +3565,19 @@
     </row>
     <row r="14" spans="1:6" ht="15">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>159</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -4025,19 +3585,19 @@
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -4045,19 +3605,19 @@
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -4065,19 +3625,19 @@
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="E17" t="s">
-        <v>161</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -4085,41 +3645,21 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15">
-      <c r="A19" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" t="s">
-        <v>163</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>152</v>
-      </c>
-      <c r="E19" t="s">
-        <v>116</v>
-      </c>
-      <c r="F19" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="125">
+<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="153">
   <ns0:si>
     <ns0:t>Rok szkolny: 2026/2027</ns0:t>
   </ns0:si>
@@ -72,270 +72,390 @@
     <ns0:t>Technika w produkcji cukierniczej</ns0:t>
   </ns0:si>
   <ns0:si>
+    <ns0:t>33</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kończyńska Małgorzata</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t/>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Dodatkowo płatne</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2, 08:50-09:35</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Krycia Ewelina</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1TFA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Biologia</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>31</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Sałdyka Karolina</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3, 09:40-10:25</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Język polski</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Zastępstwo</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>-</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3CA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4, 10:35-11:20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3WA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Zajęcia biblioteczne</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>bib</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Wrzeszcz Barbara</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bezpłatne</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Technologie produkcji cukierniczej</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5, 11:25-12:10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1FB</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Historia</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kaczorowski Waldemar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1CA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6, 12:25-13:10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2TFB</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7, 13:15-14:00</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Zajęcia z wychowawcą</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Galert Anna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8, 14:05-14:50</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Filusz Marzena</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4TFB</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Uczniowie zwolnieni do domu</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9, 14:55-15:40</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4TFA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Doradztwo zawodowe</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Krzemińska Beata</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>11, 16:35-17:20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Krystek Krzysztof</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1B</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Matematyka</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>12, 17:25-18:10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>13, 18:15-19:00</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>15.09.2026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Antoszewska Joanna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3WA|ch1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Wychowanie fizyczne</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>sg1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Pietrycha Małgorzata</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Jaworska Edyta</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1TFB|gr1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bez konsekwencji (nieobecny oddział nauczyciela)</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Sobczak Anna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1TFB|gr2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>prf2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Misiąg Anna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2WA|gr1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Zając Ewa</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Leńczowska Iwona</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2TFA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Język niemiecki</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>44</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>p. Karczmarz, Zajęcia z wychowawcą za lekcję 2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>23</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Wójcik Kamil</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3TFB|gr1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Język angielski</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>29</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Wojciechowski Łukasz</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Techniki fryzjerskie</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1TFA|gr1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Fiodorów Małgorzata</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3CA|DZ</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>sg4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Dalach Krystyna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1TFH|gr1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Rejno Julita</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Edukacja dla bezpieczeństwa</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>40</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Płatek Krzysztof</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2TH</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Edukacja obywatelska</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kopij Marcin</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>42</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Młynarczyk Paweł</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10, 15:45-16:30</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>16.09.2026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Uczniowie przychodzą później</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1CB</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Zaleska Magdalena</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1S</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Mucha Anna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>17.09.2026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5TFB</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1FA|gr1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1FA|gr2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>26</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Projektowanie fryzur</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Danielewski Paweł</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3B</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>18.09.2026</ns0:t>
+  </ns0:si>
+  <ns0:si>
     <ns0:t>prs</ns0:t>
   </ns0:si>
   <ns0:si>
-    <ns0:t>Kończyńska Małgorzata</ns0:t>
+    <ns0:t>Świerzewicz Katarzyna</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2K</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Technologia gastronomiczna z towaroznawstwem</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Okienko dla uczniów</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1FA</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Godzina</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Nauczyciel</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Dziennik zajęć innych</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Opis zajęć</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>08:00-08:45</ns0:t>
   </ns0:si>
   <ns0:si>
     <ns0:t/>
   </ns0:si>
   <ns0:si>
-    <ns0:t>Dodatkowo płatne</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2, 08:50-09:35</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Krycia Ewelina</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1TFA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Biologia</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>31</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sałdyka Karolina</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3, 09:40-10:25</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Język polski</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>33</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Zastępstwo</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>-</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3CA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>4, 10:35-11:20</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3WA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Zajęcia biblioteczne</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>bib</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Wrzeszcz Barbara</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Bezpłatne</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Technologie produkcji cukierniczej</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>5, 11:25-12:10</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1FB</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Historia</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>18</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Kaczorowski Waldemar</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1CA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>6, 12:25-13:10</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2TFB</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>7, 13:15-14:00</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Zajęcia z wychowawcą</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Galert Anna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>8, 14:05-14:50</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Filusz Marzena</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>4TFB</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>17</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Uczniowie zwolnieni do domu</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>9, 14:55-15:40</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>4TFA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Doradztwo zawodowe</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>5</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Krzemińska Beata</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>15.09.2026</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Jaworska Edyta</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1TFB|gr1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>6</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Bez konsekwencji (nieobecny oddział nauczyciela)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sobczak Anna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1TFB|gr2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>prf2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Misiąg Anna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2WA|gr1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Język niemiecki</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>44</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2TFA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3TFB|gr1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1TFA|gr1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1TFH|gr1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2TH</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Techniki fryzjerskie</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>10, 15:45-16:30</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>16.09.2026</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1CB</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1S</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Matematyka</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>17.09.2026</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>5TFB</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1FA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>18.09.2026</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Świerzewicz Katarzyna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2K</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Technologia gastronomiczna z towaroznawstwem</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>29</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Okienko dla uczniów</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Godzina</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Nauczyciel</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Dziennik zajęć innych</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Opis zajęć</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>08:00-08:45</ns0:t>
+    <ns0:t>08:00-14:40</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bokuniewicz Sylwia</ns0:t>
   </ns0:si>
   <ns0:si>
     <ns0:t/>
   </ns0:si>
   <ns0:si>
-    <ns0:t>08:00-14:40</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Bokuniewicz Sylwia</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t/>
-  </ns0:si>
-  <ns0:si>
     <ns0:t>dyżur pedagoga</ns0:t>
   </ns0:si>
   <ns0:si>
@@ -348,55 +468,19 @@
     <ns0:t>Miejsce dyżuru</ns0:t>
   </ns0:si>
   <ns0:si>
-    <ns0:t>08:45-08:50</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>piętro_3</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Kosin Anna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>09:35-09:40</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>piętro_2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>10:25-10:35</ns0:t>
+    <ns0:t>11:20-11:25</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>piętro_1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Ulanowska Magdalena</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>12:10-12:25</ns0:t>
   </ns0:si>
   <ns0:si>
     <ns0:t>boisko - dziedziniec wejściowy/boisko</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Jastrzębska-Majtyka Agnieszka</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>07:55-08:00</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>parter</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>13:10-13:15</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>14:00-14:05</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>14:50-14:55</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>piętro_1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>16:30-16:35</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>11:20-11:25</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>12:10-12:25</ns0:t>
   </ns0:si>
 </ns0:sst>
 </file>
@@ -846,7 +930,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{07798d68-ff35-4714-beca-c4f6135787b9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{782acc36-1156-4a2b-a4cf-38ad7cb9947b}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -867,8 +951,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{df400fe4-3e65-42b8-b0b6-7605c1b5066c}">
-  <dimension ref="A1:I78"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{97268e35-8e15-4eeb-9953-a9ab59d323dd}">
+  <dimension ref="A1:I92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -878,7 +962,7 @@
     <col min="5" max="5" width="68.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="45.5714285714286" customWidth="1"/>
-    <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
+    <col min="8" max="8" width="42" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1015,16 +1099,16 @@
         <v>27</v>
       </c>
       <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
         <v>28</v>
       </c>
-      <c r="G5" t="s">
-        <v>29</v>
-      </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1038,7 +1122,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
@@ -1061,28 +1145,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
         <v>33</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>35</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
         <v>36</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1090,16 +1174,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -1119,22 +1203,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
       </c>
       <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>41</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>42</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
@@ -1148,13 +1232,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -1177,28 +1261,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>35</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
         <v>36</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1206,13 +1290,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -1235,22 +1319,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
         <v>48</v>
-      </c>
-      <c r="F13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" t="s">
-        <v>49</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
@@ -1264,28 +1348,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
         <v>50</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>51</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>52</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>53</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>54</v>
       </c>
-      <c r="G14" t="s">
-        <v>55</v>
-      </c>
       <c r="H14" t="s">
         <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1293,22 +1377,22 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
         <v>56</v>
       </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>57</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>58</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>59</v>
-      </c>
-      <c r="G15" t="s">
-        <v>60</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
@@ -1319,1829 +1403,2235 @@
     </row>
     <row r="16" spans="1:9" ht="15">
       <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" t="s">
         <v>61</v>
       </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>62</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>63</v>
       </c>
-      <c r="E16" t="s">
-        <v>64</v>
-      </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
         <v>61</v>
       </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" t="s">
-        <v>67</v>
-      </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H17" t="s">
         <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s">
         <v>61</v>
       </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>62</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>63</v>
       </c>
-      <c r="E18" t="s">
-        <v>64</v>
-      </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H18" t="s">
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" t="s">
         <v>70</v>
       </c>
-      <c r="D19" t="s">
+      <c r="G19" t="s">
         <v>71</v>
       </c>
-      <c r="E19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" t="s">
-        <v>29</v>
-      </c>
       <c r="H19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
         <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="H22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" t="s">
         <v>74</v>
       </c>
-      <c r="E23" t="s">
-        <v>72</v>
-      </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="H23" t="s">
         <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s">
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F25" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="G26" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" t="s">
         <v>75</v>
       </c>
-      <c r="E27" t="s">
-        <v>72</v>
-      </c>
-      <c r="F27" t="s">
-        <v>73</v>
-      </c>
       <c r="G27" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="H29" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="F31" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="s">
         <v>45</v>
       </c>
-      <c r="C33" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" t="s">
-        <v>63</v>
-      </c>
       <c r="E33" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E35" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F35" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E36" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F36" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E37" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="F37" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G37" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="E38" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="F38" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G38" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D39" t="s">
         <v>78</v>
       </c>
       <c r="E39" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F39" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
         <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="E40" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F40" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G40" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="E41" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F41" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E42" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G42" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" t="s">
         <v>80</v>
       </c>
-      <c r="C43" t="s">
-        <v>67</v>
-      </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="E43" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F43" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G43" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="F44" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B45" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="E45" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F45" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="D46" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E46" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="F46" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C47" t="s">
         <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="E47" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="F47" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="G47" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="E48" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="F48" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G48" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D49" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E49" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F49" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="E50" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F50" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E51" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D52" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="E52" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="F52" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="G52" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G53" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
         <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
       </c>
       <c r="F54" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E55" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C56" t="s">
         <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="E56" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F56" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="E57" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E58" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G58" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="B59" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E59" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G59" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="B60" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E60" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F60" t="s">
+        <v>53</v>
+      </c>
+      <c r="G60" t="s">
         <v>54</v>
       </c>
-      <c r="G60" t="s">
-        <v>30</v>
-      </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B61" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D61" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="F61" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="E62" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="F62" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
         <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B64" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C64" t="s">
         <v>21</v>
       </c>
       <c r="D64" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
       </c>
       <c r="F64" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B65" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E65" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="G65" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="E66" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F66" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="G66" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C67" t="s">
         <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="E67" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F67" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="G67" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C68" t="s">
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E68" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C69" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="F69" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="G69" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C70" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F70" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G70" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E71" t="s">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G71" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C72" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D72" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="E72" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="F72" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="G72" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D73" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E73" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F73" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G73" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B74" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C74" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="D74" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E74" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F74" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G74" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B75" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C75" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D75" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="E75" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="F75" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="G75" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B76" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D76" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="E76" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F76" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G76" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C77" t="s">
         <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E77" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="F77" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="G77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="B78" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="C78" t="s">
         <v>21</v>
       </c>
       <c r="D78" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
       </c>
       <c r="F78" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="15">
+      <c r="A79" t="s">
+        <v>128</v>
+      </c>
+      <c r="B79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>43</v>
+      </c>
+      <c r="E79" t="s">
+        <v>37</v>
+      </c>
+      <c r="F79" t="s">
+        <v>129</v>
+      </c>
+      <c r="G79" t="s">
+        <v>29</v>
+      </c>
+      <c r="H79" t="s">
+        <v>18</v>
+      </c>
+      <c r="I79" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="15">
+      <c r="A80" t="s">
+        <v>128</v>
+      </c>
+      <c r="B80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" t="s">
+        <v>130</v>
+      </c>
+      <c r="D80" t="s">
+        <v>131</v>
+      </c>
+      <c r="E80" t="s">
+        <v>132</v>
+      </c>
+      <c r="F80" t="s">
+        <v>93</v>
+      </c>
+      <c r="G80" t="s">
+        <v>133</v>
+      </c>
+      <c r="H80" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="15">
+      <c r="A81" t="s">
+        <v>128</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81" t="s">
+        <v>116</v>
+      </c>
+      <c r="E81" t="s">
+        <v>27</v>
+      </c>
+      <c r="F81" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" t="s">
+        <v>29</v>
+      </c>
+      <c r="H81" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="15">
+      <c r="A82" t="s">
+        <v>128</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>43</v>
+      </c>
+      <c r="E82" t="s">
+        <v>37</v>
+      </c>
+      <c r="F82" t="s">
+        <v>129</v>
+      </c>
+      <c r="G82" t="s">
+        <v>29</v>
+      </c>
+      <c r="H82" t="s">
+        <v>18</v>
+      </c>
+      <c r="I82" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="15">
+      <c r="A83" t="s">
+        <v>128</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" t="s">
+        <v>130</v>
+      </c>
+      <c r="D83" t="s">
+        <v>131</v>
+      </c>
+      <c r="E83" t="s">
+        <v>132</v>
+      </c>
+      <c r="F83" t="s">
+        <v>93</v>
+      </c>
+      <c r="G83" t="s">
+        <v>133</v>
+      </c>
+      <c r="H83" t="s">
+        <v>18</v>
+      </c>
+      <c r="I83" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="15">
+      <c r="A84" t="s">
+        <v>128</v>
+      </c>
+      <c r="B84" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" t="s">
+        <v>39</v>
+      </c>
+      <c r="E84" t="s">
+        <v>27</v>
+      </c>
+      <c r="F84" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" t="s">
+        <v>29</v>
+      </c>
+      <c r="H84" t="s">
+        <v>18</v>
+      </c>
+      <c r="I84" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="15">
+      <c r="A85" t="s">
+        <v>128</v>
+      </c>
+      <c r="B85" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" t="s">
+        <v>43</v>
+      </c>
+      <c r="E85" t="s">
+        <v>37</v>
+      </c>
+      <c r="F85" t="s">
+        <v>129</v>
+      </c>
+      <c r="G85" t="s">
+        <v>29</v>
+      </c>
+      <c r="H85" t="s">
+        <v>18</v>
+      </c>
+      <c r="I85" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="15">
+      <c r="A86" t="s">
+        <v>128</v>
+      </c>
+      <c r="B86" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" t="s">
+        <v>130</v>
+      </c>
+      <c r="D86" t="s">
+        <v>131</v>
+      </c>
+      <c r="E86" t="s">
+        <v>132</v>
+      </c>
+      <c r="F86" t="s">
+        <v>93</v>
+      </c>
+      <c r="G86" t="s">
+        <v>133</v>
+      </c>
+      <c r="H86" t="s">
+        <v>18</v>
+      </c>
+      <c r="I86" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="15">
+      <c r="A87" t="s">
+        <v>128</v>
+      </c>
+      <c r="B87" t="s">
+        <v>38</v>
+      </c>
+      <c r="C87" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" t="s">
+        <v>22</v>
+      </c>
+      <c r="E87" t="s">
+        <v>47</v>
+      </c>
+      <c r="F87" t="s">
+        <v>16</v>
+      </c>
+      <c r="G87" t="s">
+        <v>29</v>
+      </c>
+      <c r="H87" t="s">
+        <v>18</v>
+      </c>
+      <c r="I87" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="15">
+      <c r="A88" t="s">
+        <v>128</v>
+      </c>
+      <c r="B88" t="s">
+        <v>38</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" t="s">
+        <v>37</v>
+      </c>
+      <c r="F88" t="s">
+        <v>129</v>
+      </c>
+      <c r="G88" t="s">
+        <v>29</v>
+      </c>
+      <c r="H88" t="s">
+        <v>18</v>
+      </c>
+      <c r="I88" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="15">
+      <c r="A89" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" t="s">
+        <v>38</v>
+      </c>
+      <c r="C89" t="s">
+        <v>130</v>
+      </c>
+      <c r="D89" t="s">
+        <v>131</v>
+      </c>
+      <c r="E89" t="s">
+        <v>132</v>
+      </c>
+      <c r="F89" t="s">
+        <v>93</v>
+      </c>
+      <c r="G89" t="s">
+        <v>133</v>
+      </c>
+      <c r="H89" t="s">
+        <v>18</v>
+      </c>
+      <c r="I89" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="15">
+      <c r="A90" t="s">
+        <v>128</v>
+      </c>
+      <c r="B90" t="s">
+        <v>44</v>
+      </c>
+      <c r="C90" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" t="s">
+        <v>114</v>
+      </c>
+      <c r="E90" t="s">
+        <v>27</v>
+      </c>
+      <c r="F90" t="s">
+        <v>16</v>
+      </c>
+      <c r="G90" t="s">
+        <v>29</v>
+      </c>
+      <c r="H90" t="s">
+        <v>18</v>
+      </c>
+      <c r="I90" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="15">
+      <c r="A91" t="s">
+        <v>128</v>
+      </c>
+      <c r="B91" t="s">
+        <v>44</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
+        <v>43</v>
+      </c>
+      <c r="E91" t="s">
+        <v>47</v>
+      </c>
+      <c r="F91" t="s">
+        <v>129</v>
+      </c>
+      <c r="G91" t="s">
+        <v>29</v>
+      </c>
+      <c r="H91" t="s">
+        <v>18</v>
+      </c>
+      <c r="I91" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="15">
+      <c r="A92" t="s">
+        <v>128</v>
+      </c>
+      <c r="B92" t="s">
+        <v>46</v>
+      </c>
+      <c r="C92" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" t="s">
+        <v>134</v>
+      </c>
+      <c r="E92" t="s">
+        <v>27</v>
+      </c>
+      <c r="F92" t="s">
+        <v>16</v>
+      </c>
+      <c r="G92" t="s">
+        <v>29</v>
+      </c>
+      <c r="H92" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3152,7 +3642,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c43d19c3-00f8-43fd-bbf0-6a5019495413}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0209470e-7358-4afb-b1e4-d2f0ec6cbd0a}">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3172,16 +3662,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -3198,89 +3688,89 @@
     </row>
     <row r="2" spans="1:9" ht="15">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
         <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="F3" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3291,15 +3781,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a7d12d72-5462-41e7-838e-42a1c7885cf9}">
-  <dimension ref="A1:F18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8548b5d5-c576-4645-b65b-5137a1f0d303}">
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="21.7142857142857" customWidth="1"/>
     <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3308,13 +3798,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -3325,19 +3815,19 @@
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -3345,321 +3835,21 @@
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15">
-      <c r="A5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15">
-      <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15">
-      <c r="A7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15">
-      <c r="A8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15">
-      <c r="A9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15">
-      <c r="A10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15">
-      <c r="A11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>121</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15">
-      <c r="A12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15">
-      <c r="A13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15">
-      <c r="A14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15">
-      <c r="A15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15">
-      <c r="A16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15">
-      <c r="A17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15">
-      <c r="A18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,467 +22,587 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="153">
-  <ns0:si>
-    <ns0:t>Rok szkolny: 2026/2027</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Okres: 14.09.2026 (pon.) - 20.09.2026 (niedz.)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Dzień</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Lekcja</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Nauczyciel/wakat</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Oddział</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Przedmiot</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sala</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Zastępca</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Uwagi</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Forma płatności</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>14.09.2026</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1, 08:00-08:45</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Stępień Krystyna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2CA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Technika w produkcji cukierniczej</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>33</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Kończyńska Małgorzata</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t/>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Dodatkowo płatne</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2, 08:50-09:35</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Krycia Ewelina</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1TFA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Biologia</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>31</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sałdyka Karolina</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3, 09:40-10:25</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Język polski</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Zastępstwo</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>-</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3CA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>4, 10:35-11:20</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3WA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Zajęcia biblioteczne</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>bib</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Wrzeszcz Barbara</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Bezpłatne</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Technologie produkcji cukierniczej</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>5, 11:25-12:10</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1FB</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Historia</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>18</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Kaczorowski Waldemar</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1CA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>6, 12:25-13:10</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2TFB</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>7, 13:15-14:00</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Zajęcia z wychowawcą</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Galert Anna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>8, 14:05-14:50</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Filusz Marzena</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>4TFB</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>17</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Uczniowie zwolnieni do domu</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>9, 14:55-15:40</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>4TFA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Doradztwo zawodowe</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>5</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Krzemińska Beata</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>11, 16:35-17:20</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Krystek Krzysztof</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1B</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Matematyka</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>12, 17:25-18:10</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>13, 18:15-19:00</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>15.09.2026</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Antoszewska Joanna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3WA|ch1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Wychowanie fizyczne</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>sg1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Pietrycha Małgorzata</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Jaworska Edyta</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1TFB|gr1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>6</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Bez konsekwencji (nieobecny oddział nauczyciela)</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Sobczak Anna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1TFB|gr2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>prf2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Misiąg Anna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2WA|gr1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Zając Ewa</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Leńczowska Iwona</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2TFA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Język niemiecki</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>44</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>p. Karczmarz, Zajęcia z wychowawcą za lekcję 2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>23</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Wójcik Kamil</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3TFB|gr1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Język angielski</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>29</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Wojciechowski Łukasz</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Techniki fryzjerskie</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1TFA|gr1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Fiodorów Małgorzata</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3CA|DZ</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>sg4</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Dalach Krystyna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1TFH|gr1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Rejno Julita</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Edukacja dla bezpieczeństwa</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>40</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Płatek Krzysztof</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2TH</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Edukacja obywatelska</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Kopij Marcin</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>42</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Młynarczyk Paweł</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>10, 15:45-16:30</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>16.09.2026</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Uczniowie przychodzą później</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1CB</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Zaleska Magdalena</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1S</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Mucha Anna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>17.09.2026</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>5TFB</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1FA|gr1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1FA|gr2</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>26</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Projektowanie fryzur</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Danielewski Paweł</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>3B</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>18.09.2026</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>prs</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Świerzewicz Katarzyna</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>2K</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Technologia gastronomiczna z towaroznawstwem</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Okienko dla uczniów</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>1FA</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Godzina</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Nauczyciel</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Dziennik zajęć innych</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Opis zajęć</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>08:00-08:45</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t/>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>08:00-14:40</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Bokuniewicz Sylwia</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t/>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>dyżur pedagoga</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>04</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>08:50-09:35</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Miejsce dyżuru</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>11:20-11:25</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>piętro_1</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Ulanowska Magdalena</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>12:10-12:25</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>boisko - dziedziniec wejściowy/boisko</ns0:t>
-  </ns0:si>
-</ns0:sst>
+<s:sst xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="193">
+  <s:si>
+    <s:t>Rok szkolny: 2026/2027</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Okres: 14.09.2026 (pon.) - 20.09.2026 (niedz.)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Dzień</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Lekcja</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Nauczyciel/wakat</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Oddział</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Przedmiot</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Sala</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Zastępca</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Uwagi</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Forma płatności</s:t>
+  </s:si>
+  <s:si>
+    <s:t>14.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1, 08:00-08:45</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Stępień Krystyna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2CA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Technika w produkcji cukierniczej</s:t>
+  </s:si>
+  <s:si>
+    <s:t>33</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Kończyńska Małgorzata</s:t>
+  </s:si>
+  <s:si>
+    <s:t/>
+  </s:si>
+  <s:si>
+    <s:t>Dodatkowo płatne</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2, 08:50-09:35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Krycia Ewelina</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1TFA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Biologia</s:t>
+  </s:si>
+  <s:si>
+    <s:t>31</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Sałdyka Karolina</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3, 09:40-10:25</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Język polski</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Zastępstwo</s:t>
+  </s:si>
+  <s:si>
+    <s:t>-</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3CA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>4, 10:35-11:20</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3WA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Zajęcia biblioteczne</s:t>
+  </s:si>
+  <s:si>
+    <s:t>bib</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Wrzeszcz Barbara</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Bezpłatne</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Technologie produkcji cukierniczej</s:t>
+  </s:si>
+  <s:si>
+    <s:t>5, 11:25-12:10</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1FB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Historia</s:t>
+  </s:si>
+  <s:si>
+    <s:t>18</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Kaczorowski Waldemar</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1CA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>6, 12:25-13:10</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2TFB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>7, 13:15-14:00</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Zajęcia z wychowawcą</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Galert Anna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>8, 14:05-14:50</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Filusz Marzena</s:t>
+  </s:si>
+  <s:si>
+    <s:t>4TFB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</s:t>
+  </s:si>
+  <s:si>
+    <s:t>17</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Uczniowie zwolnieni do domu</s:t>
+  </s:si>
+  <s:si>
+    <s:t>9, 14:55-15:40</s:t>
+  </s:si>
+  <s:si>
+    <s:t>4TFA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Doradztwo zawodowe</s:t>
+  </s:si>
+  <s:si>
+    <s:t>5</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Krzemińska Beata</s:t>
+  </s:si>
+  <s:si>
+    <s:t>11, 16:35-17:20</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Krystek Krzysztof</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1B</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Matematyka</s:t>
+  </s:si>
+  <s:si>
+    <s:t>12, 17:25-18:10</s:t>
+  </s:si>
+  <s:si>
+    <s:t>13, 18:15-19:00</s:t>
+  </s:si>
+  <s:si>
+    <s:t>15.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Antoszewska Joanna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3WA|ch1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Wychowanie fizyczne</s:t>
+  </s:si>
+  <s:si>
+    <s:t>sg1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Pietrycha Małgorzata</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Jaworska Edyta</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1TFB|gr1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</s:t>
+  </s:si>
+  <s:si>
+    <s:t>6</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Bez konsekwencji (nieobecny oddział nauczyciela)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Sobczak Anna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1TFB|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>prf2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Misiąg Anna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2WA|gr1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Zając Ewa</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Leńczowska Iwona</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2TFA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Język niemiecki</s:t>
+  </s:si>
+  <s:si>
+    <s:t>44</s:t>
+  </s:si>
+  <s:si>
+    <s:t>p. Karczmarz, Zajęcia z wychowawcą za lekcję 2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>23</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Wójcik Kamil</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3TFB|gr1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Język angielski</s:t>
+  </s:si>
+  <s:si>
+    <s:t>29</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Wojciechowski Łukasz</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Techniki fryzjerskie</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1TFA|gr1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Fiodorów Małgorzata</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3CA|DZ</s:t>
+  </s:si>
+  <s:si>
+    <s:t>sg4</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Dalach Krystyna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1TFH|gr1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Rejno Julita</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Edukacja dla bezpieczeństwa</s:t>
+  </s:si>
+  <s:si>
+    <s:t>40</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Płatek Krzysztof</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2TH</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Edukacja obywatelska</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Kopij Marcin</s:t>
+  </s:si>
+  <s:si>
+    <s:t>42</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Młynarczyk Paweł</s:t>
+  </s:si>
+  <s:si>
+    <s:t>10, 15:45-16:30</s:t>
+  </s:si>
+  <s:si>
+    <s:t>16.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Uczniowie przychodzą później</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1CB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Zaleska Magdalena</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1S</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Mucha Anna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>17.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</s:t>
+  </s:si>
+  <s:si>
+    <s:t>5TFB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Biezmienow Małgorzata</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1K|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>43</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1FA|gr1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1FA|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Nestoruk Lidia</s:t>
+  </s:si>
+  <s:si>
+    <s:t>26</s:t>
+  </s:si>
+  <s:si>
+    <s:t>p. Jastrzębska, projektowanie fryzur za lekcję 10</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1CB|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Projektowanie fryzur</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Danielewski Paweł</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Okienko dla uczniów</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3B</s:t>
+  </s:si>
+  <s:si>
+    <s:t>18.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1FB|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>32</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Jastrzębska-Majtyka Agnieszka</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Świerzewicz Katarzyna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2K</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Technologia gastronomiczna z towaroznawstwem</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1TFH|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>28</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Małecka Barbara</s:t>
+  </s:si>
+  <s:si>
+    <s:t>37</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Najwer Maciej</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Chemia</s:t>
+  </s:si>
+  <s:si>
+    <s:t>30</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Hudziec Agnieszka</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3FB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Język angielski zawodowy</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1TH|gr1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Informatyka</s:t>
+  </s:si>
+  <s:si>
+    <s:t>41</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1FA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3TFB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>27</s:t>
+  </s:si>
+  <s:si>
+    <s:t>4</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Godzina</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Nauczyciel</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Dziennik zajęć innych</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Opis zajęć</s:t>
+  </s:si>
+  <s:si>
+    <s:t>08:00-08:45</s:t>
+  </s:si>
+  <s:si>
+    <s:t/>
+  </s:si>
+  <s:si>
+    <s:t>08:00-14:40</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Bokuniewicz Sylwia</s:t>
+  </s:si>
+  <s:si>
+    <s:t/>
+  </s:si>
+  <s:si>
+    <s:t>dyżur pedagoga</s:t>
+  </s:si>
+  <s:si>
+    <s:t>04</s:t>
+  </s:si>
+  <s:si>
+    <s:t>08:50-09:35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>08:00-12:35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Aszkiełowicz Aleksandra</s:t>
+  </s:si>
+  <s:si>
+    <s:t/>
+  </s:si>
+  <s:si>
+    <s:t>Dyżur psychologa szkolnego</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Miejsce dyżuru</s:t>
+  </s:si>
+  <s:si>
+    <s:t>11:20-11:25</s:t>
+  </s:si>
+  <s:si>
+    <s:t>piętro_1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Ulanowska Magdalena</s:t>
+  </s:si>
+  <s:si>
+    <s:t>12:10-12:25</s:t>
+  </s:si>
+  <s:si>
+    <s:t>boisko - dziedziniec wejściowy/boisko</s:t>
+  </s:si>
+  <s:si>
+    <s:t>09:35-09:40</s:t>
+  </s:si>
+  <s:si>
+    <s:t>piętro_3</s:t>
+  </s:si>
+  <s:si>
+    <s:t>10:25-10:35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>bramka wejściowa</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Taszycka Magdalena</s:t>
+  </s:si>
+  <s:si>
+    <s:t>13:10-13:15</s:t>
+  </s:si>
+  <s:si>
+    <s:t>08:45-08:50</s:t>
+  </s:si>
+  <s:si>
+    <s:t>piętro_2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Smereka Alicja</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Biczysko Wojciech</s:t>
+  </s:si>
+  <s:si>
+    <s:t>parter</s:t>
+  </s:si>
+  <s:si>
+    <s:t>14:00-14:05</s:t>
+  </s:si>
+</s:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -930,7 +1050,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{782acc36-1156-4a2b-a4cf-38ad7cb9947b}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{fd2c6218-4dec-4d3c-984f-803397d4c9f1}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -951,18 +1071,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{97268e35-8e15-4eeb-9953-a9ab59d323dd}">
-  <dimension ref="A1:I92"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{9a65fb0a-bbb4-4b44-8072-83c079624620}">
+  <dimension ref="A1:I110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="21.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="68.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="45.5714285714286" customWidth="1"/>
-    <col min="8" max="8" width="42" customWidth="1"/>
+    <col min="8" max="8" width="43.1428571428571" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2859,25 +2979,25 @@
         <v>31</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D66" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E66" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F66" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G66" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
@@ -2891,7 +3011,7 @@
         <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E67" t="s">
         <v>69</v>
@@ -2906,7 +3026,7 @@
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
@@ -2917,25 +3037,25 @@
         <v>31</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D68" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="E68" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F68" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="G68" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
@@ -2943,7 +3063,7 @@
         <v>118</v>
       </c>
       <c r="B69" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
@@ -2955,7 +3075,7 @@
         <v>37</v>
       </c>
       <c r="F69" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="G69" t="s">
         <v>17</v>
@@ -2972,22 +3092,22 @@
         <v>118</v>
       </c>
       <c r="B70" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C70" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="E70" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F70" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="G70" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
@@ -3001,22 +3121,22 @@
         <v>118</v>
       </c>
       <c r="B71" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C71" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E71" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="F71" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="G71" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
@@ -3030,28 +3150,28 @@
         <v>118</v>
       </c>
       <c r="B72" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C72" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="D72" t="s">
         <v>51</v>
       </c>
       <c r="E72" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="F72" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="G72" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="H72" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
@@ -3059,28 +3179,28 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="F73" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
@@ -3088,28 +3208,28 @@
         <v>118</v>
       </c>
       <c r="B74" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C74" t="s">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="D74" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="E74" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="F74" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="G74" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
@@ -3117,28 +3237,28 @@
         <v>118</v>
       </c>
       <c r="B75" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C75" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D75" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="E75" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="F75" t="s">
         <v>53</v>
       </c>
       <c r="G75" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
@@ -3146,51 +3266,51 @@
         <v>118</v>
       </c>
       <c r="B76" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C76" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D76" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="E76" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="F76" t="s">
         <v>53</v>
       </c>
       <c r="G76" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B77" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="C77" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D77" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E77" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="F77" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="G77" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
@@ -3201,25 +3321,25 @@
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D78" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E78" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F78" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G78" t="s">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
@@ -3230,25 +3350,25 @@
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="D79" t="s">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="E79" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F79" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="G79" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
@@ -3259,25 +3379,25 @@
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B80" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C80" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="D80" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E80" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="F80" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="G80" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
@@ -3288,54 +3408,54 @@
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="E81" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="F81" t="s">
         <v>16</v>
       </c>
       <c r="G81" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B82" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="D82" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E82" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="F82" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G82" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
@@ -3346,83 +3466,83 @@
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B83" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C83" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="D83" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="E83" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="F83" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="G83" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B84" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C84" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E84" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F84" t="s">
         <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B85" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C85" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="D85" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="E85" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="F85" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="G85" t="s">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
@@ -3433,68 +3553,68 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B86" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D86" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E86" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="F86" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="G86" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B87" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C87" t="s">
         <v>21</v>
       </c>
       <c r="D87" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="E87" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F87" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="G87" t="s">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C88" t="s">
         <v>13</v>
@@ -3506,33 +3626,33 @@
         <v>37</v>
       </c>
       <c r="F88" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="G88" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B89" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C89" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D89" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E89" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F89" t="s">
         <v>93</v>
@@ -3549,89 +3669,611 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B90" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C90" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D90" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="E90" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F90" t="s">
-        <v>16</v>
+        <v>145</v>
       </c>
       <c r="G90" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B91" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C91" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D91" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E91" t="s">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="F91" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="G91" t="s">
-        <v>29</v>
+        <v>149</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B92" t="s">
+        <v>31</v>
+      </c>
+      <c r="C92" t="s">
+        <v>59</v>
+      </c>
+      <c r="D92" t="s">
+        <v>150</v>
+      </c>
+      <c r="E92" t="s">
+        <v>151</v>
+      </c>
+      <c r="F92" t="s">
+        <v>109</v>
+      </c>
+      <c r="G92" t="s">
+        <v>94</v>
+      </c>
+      <c r="H92" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="15">
+      <c r="A93" t="s">
+        <v>135</v>
+      </c>
+      <c r="B93" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" t="s">
+        <v>144</v>
+      </c>
+      <c r="D93" t="s">
+        <v>56</v>
+      </c>
+      <c r="E93" t="s">
+        <v>23</v>
+      </c>
+      <c r="F93" t="s">
+        <v>143</v>
+      </c>
+      <c r="G93" t="s">
+        <v>28</v>
+      </c>
+      <c r="H93" t="s">
+        <v>18</v>
+      </c>
+      <c r="I93" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="15">
+      <c r="A94" t="s">
+        <v>135</v>
+      </c>
+      <c r="B94" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" t="s">
+        <v>43</v>
+      </c>
+      <c r="E94" t="s">
+        <v>37</v>
+      </c>
+      <c r="F94" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" t="s">
+        <v>17</v>
+      </c>
+      <c r="H94" t="s">
+        <v>18</v>
+      </c>
+      <c r="I94" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="15">
+      <c r="A95" t="s">
+        <v>135</v>
+      </c>
+      <c r="B95" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" t="s">
+        <v>139</v>
+      </c>
+      <c r="D95" t="s">
+        <v>140</v>
+      </c>
+      <c r="E95" t="s">
+        <v>141</v>
+      </c>
+      <c r="F95" t="s">
+        <v>93</v>
+      </c>
+      <c r="G95" t="s">
+        <v>133</v>
+      </c>
+      <c r="H95" t="s">
+        <v>18</v>
+      </c>
+      <c r="I95" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="15">
+      <c r="A96" t="s">
+        <v>135</v>
+      </c>
+      <c r="B96" t="s">
+        <v>38</v>
+      </c>
+      <c r="C96" t="s">
+        <v>122</v>
+      </c>
+      <c r="D96" t="s">
+        <v>51</v>
+      </c>
+      <c r="E96" t="s">
+        <v>33</v>
+      </c>
+      <c r="F96" t="s">
+        <v>34</v>
+      </c>
+      <c r="G96" t="s">
+        <v>82</v>
+      </c>
+      <c r="H96" t="s">
+        <v>18</v>
+      </c>
+      <c r="I96" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="15">
+      <c r="A97" t="s">
+        <v>135</v>
+      </c>
+      <c r="B97" t="s">
+        <v>38</v>
+      </c>
+      <c r="C97" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" t="s">
+        <v>22</v>
+      </c>
+      <c r="E97" t="s">
+        <v>47</v>
+      </c>
+      <c r="F97" t="s">
+        <v>104</v>
+      </c>
+      <c r="G97" t="s">
+        <v>146</v>
+      </c>
+      <c r="H97" t="s">
+        <v>18</v>
+      </c>
+      <c r="I97" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15">
+      <c r="A98" t="s">
+        <v>135</v>
+      </c>
+      <c r="B98" t="s">
+        <v>38</v>
+      </c>
+      <c r="C98" t="s">
+        <v>59</v>
+      </c>
+      <c r="D98" t="s">
+        <v>39</v>
+      </c>
+      <c r="E98" t="s">
+        <v>23</v>
+      </c>
+      <c r="F98" t="s">
+        <v>143</v>
+      </c>
+      <c r="G98" t="s">
+        <v>25</v>
+      </c>
+      <c r="H98" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15">
+      <c r="A99" t="s">
+        <v>135</v>
+      </c>
+      <c r="B99" t="s">
+        <v>38</v>
+      </c>
+      <c r="C99" t="s">
+        <v>144</v>
+      </c>
+      <c r="D99" t="s">
+        <v>56</v>
+      </c>
+      <c r="E99" t="s">
+        <v>23</v>
+      </c>
+      <c r="F99" t="s">
+        <v>143</v>
+      </c>
+      <c r="G99" t="s">
+        <v>28</v>
+      </c>
+      <c r="H99" t="s">
+        <v>18</v>
+      </c>
+      <c r="I99" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15">
+      <c r="A100" t="s">
+        <v>135</v>
+      </c>
+      <c r="B100" t="s">
+        <v>38</v>
+      </c>
+      <c r="C100" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" t="s">
+        <v>43</v>
+      </c>
+      <c r="E100" t="s">
+        <v>37</v>
+      </c>
+      <c r="F100" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" t="s">
+        <v>17</v>
+      </c>
+      <c r="H100" t="s">
+        <v>18</v>
+      </c>
+      <c r="I100" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="15">
+      <c r="A101" t="s">
+        <v>135</v>
+      </c>
+      <c r="B101" t="s">
+        <v>38</v>
+      </c>
+      <c r="C101" t="s">
+        <v>139</v>
+      </c>
+      <c r="D101" t="s">
+        <v>140</v>
+      </c>
+      <c r="E101" t="s">
+        <v>141</v>
+      </c>
+      <c r="F101" t="s">
+        <v>93</v>
+      </c>
+      <c r="G101" t="s">
+        <v>133</v>
+      </c>
+      <c r="H101" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="15">
+      <c r="A102" t="s">
+        <v>135</v>
+      </c>
+      <c r="B102" t="s">
+        <v>44</v>
+      </c>
+      <c r="C102" t="s">
+        <v>122</v>
+      </c>
+      <c r="D102" t="s">
+        <v>152</v>
+      </c>
+      <c r="E102" t="s">
+        <v>153</v>
+      </c>
+      <c r="F102" t="s">
+        <v>145</v>
+      </c>
+      <c r="G102" t="s">
+        <v>146</v>
+      </c>
+      <c r="H102" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="15">
+      <c r="A103" t="s">
+        <v>135</v>
+      </c>
+      <c r="B103" t="s">
+        <v>44</v>
+      </c>
+      <c r="C103" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" t="s">
+        <v>114</v>
+      </c>
+      <c r="E103" t="s">
+        <v>33</v>
+      </c>
+      <c r="F103" t="s">
+        <v>34</v>
+      </c>
+      <c r="G103" t="s">
+        <v>82</v>
+      </c>
+      <c r="H103" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15">
+      <c r="A104" t="s">
+        <v>135</v>
+      </c>
+      <c r="B104" t="s">
+        <v>44</v>
+      </c>
+      <c r="C104" t="s">
+        <v>59</v>
+      </c>
+      <c r="D104" t="s">
+        <v>56</v>
+      </c>
+      <c r="E104" t="s">
+        <v>131</v>
+      </c>
+      <c r="F104" t="s">
+        <v>58</v>
+      </c>
+      <c r="G104" t="s">
+        <v>28</v>
+      </c>
+      <c r="H104" t="s">
+        <v>18</v>
+      </c>
+      <c r="I104" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="15">
+      <c r="A105" t="s">
+        <v>135</v>
+      </c>
+      <c r="B105" t="s">
+        <v>44</v>
+      </c>
+      <c r="C105" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" t="s">
+        <v>43</v>
+      </c>
+      <c r="E105" t="s">
+        <v>47</v>
+      </c>
+      <c r="F105" t="s">
+        <v>16</v>
+      </c>
+      <c r="G105" t="s">
+        <v>17</v>
+      </c>
+      <c r="H105" t="s">
+        <v>18</v>
+      </c>
+      <c r="I105" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15">
+      <c r="A106" t="s">
+        <v>135</v>
+      </c>
+      <c r="B106" t="s">
         <v>46</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C106" t="s">
+        <v>122</v>
+      </c>
+      <c r="D106" t="s">
+        <v>96</v>
+      </c>
+      <c r="E106" t="s">
+        <v>153</v>
+      </c>
+      <c r="F106" t="s">
+        <v>154</v>
+      </c>
+      <c r="G106" t="s">
+        <v>146</v>
+      </c>
+      <c r="H106" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15">
+      <c r="A107" t="s">
+        <v>135</v>
+      </c>
+      <c r="B107" t="s">
+        <v>46</v>
+      </c>
+      <c r="C107" t="s">
         <v>21</v>
       </c>
-      <c r="D92" t="s">
-        <v>134</v>
-      </c>
-      <c r="E92" t="s">
-        <v>27</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="D107" t="s">
+        <v>155</v>
+      </c>
+      <c r="E107" t="s">
+        <v>23</v>
+      </c>
+      <c r="F107" t="s">
         <v>16</v>
       </c>
-      <c r="G92" t="s">
-        <v>29</v>
-      </c>
-      <c r="H92" t="s">
-        <v>18</v>
-      </c>
-      <c r="I92" t="s">
-        <v>29</v>
+      <c r="G107" t="s">
+        <v>25</v>
+      </c>
+      <c r="H107" t="s">
+        <v>18</v>
+      </c>
+      <c r="I107" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15">
+      <c r="A108" t="s">
+        <v>135</v>
+      </c>
+      <c r="B108" t="s">
+        <v>46</v>
+      </c>
+      <c r="C108" t="s">
+        <v>59</v>
+      </c>
+      <c r="D108" t="s">
+        <v>56</v>
+      </c>
+      <c r="E108" t="s">
+        <v>131</v>
+      </c>
+      <c r="F108" t="s">
+        <v>58</v>
+      </c>
+      <c r="G108" t="s">
+        <v>28</v>
+      </c>
+      <c r="H108" t="s">
+        <v>18</v>
+      </c>
+      <c r="I108" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15">
+      <c r="A109" t="s">
+        <v>135</v>
+      </c>
+      <c r="B109" t="s">
+        <v>46</v>
+      </c>
+      <c r="C109" t="s">
+        <v>144</v>
+      </c>
+      <c r="D109" t="s">
+        <v>156</v>
+      </c>
+      <c r="E109" t="s">
+        <v>23</v>
+      </c>
+      <c r="F109" t="s">
+        <v>157</v>
+      </c>
+      <c r="G109" t="s">
+        <v>54</v>
+      </c>
+      <c r="H109" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15">
+      <c r="A110" t="s">
+        <v>135</v>
+      </c>
+      <c r="B110" t="s">
+        <v>49</v>
+      </c>
+      <c r="C110" t="s">
+        <v>144</v>
+      </c>
+      <c r="D110" t="s">
+        <v>85</v>
+      </c>
+      <c r="E110" t="s">
+        <v>95</v>
+      </c>
+      <c r="F110" t="s">
+        <v>158</v>
+      </c>
+      <c r="G110" t="s">
+        <v>132</v>
+      </c>
+      <c r="H110" t="s">
+        <v>18</v>
+      </c>
+      <c r="I110" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3642,15 +4284,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0209470e-7358-4afb-b1e4-d2f0ec6cbd0a}">
-  <dimension ref="A1:I4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2f07d88a-71ae-4888-9449-454c68a67997}">
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="18.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="36.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="15.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="22.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="42.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="25.8571428571429" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="45.5714285714286" customWidth="1"/>
     <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
@@ -3662,16 +4304,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -3691,13 +4333,13 @@
         <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
         <v>27</v>
@@ -3720,19 +4362,19 @@
         <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="E3" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="F3" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="G3" t="s">
         <v>76</v>
@@ -3749,13 +4391,13 @@
         <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -3770,6 +4412,35 @@
         <v>18</v>
       </c>
       <c r="I4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3781,15 +4452,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8548b5d5-c576-4645-b65b-5137a1f0d303}">
-  <dimension ref="A1:F3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e5b05591-4c9b-4d22-8ba4-960c7e78a05d}">
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="21.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3798,13 +4469,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -3818,16 +4489,16 @@
         <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
         <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -3838,18 +4509,298 @@
         <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
         <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="E3" t="s">
         <v>42</v>
       </c>
       <c r="F3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15">
+      <c r="A5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15">
+      <c r="A6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15">
+      <c r="A7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15">
+      <c r="A8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15">
+      <c r="A9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15">
+      <c r="A10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15">
+      <c r="A11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15">
+      <c r="A13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>191</v>
+      </c>
+      <c r="E13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15">
+      <c r="A14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15">
+      <c r="A15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>180</v>
+      </c>
+      <c r="E15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15">
+      <c r="A16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15">
+      <c r="A17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,12 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<s:sst xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="193">
+<s:sst xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="225">
   <s:si>
     <s:t>Rok szkolny: 2026/2027</s:t>
   </s:si>
   <s:si>
-    <s:t>Okres: 14.09.2026 (pon.) - 20.09.2026 (niedz.)</s:t>
+    <s:t>Okres: 14.09.2026 (pon.) - 30.09.2026 (śr.)</s:t>
   </s:si>
   <s:si>
     <s:t>Dzień</s:t>
@@ -501,6 +501,87 @@
     <s:t>4</s:t>
   </s:si>
   <s:si>
+    <s:t>21.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3FA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3K|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>22.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3CB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>23.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Granatowska Mariola</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2K|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>05</s:t>
+  </s:si>
+  <s:si>
+    <s:t>4TH|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3TFA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2CB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>24.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Czukiewska Bożena</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Symulacyjna firma handlowa</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Smirnow-Zechman Eleonora</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Biznes i zarządzanie</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1K</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1WB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Pracownia sprzedaży</s:t>
+  </s:si>
+  <s:si>
+    <s:t>25.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Piątek-Pawłowska Bożena</s:t>
+  </s:si>
+  <s:si>
+    <s:t>30.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1TFB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Bujanowska Iwona</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2WA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1FC</s:t>
+  </s:si>
+  <s:si>
     <s:t>Godzina</s:t>
   </s:si>
   <s:si>
@@ -549,6 +630,9 @@
     <s:t>Dyżur psychologa szkolnego</s:t>
   </s:si>
   <s:si>
+    <s:t xml:space="preserve">Matematyka </s:t>
+  </s:si>
+  <s:si>
     <s:t>Miejsce dyżuru</s:t>
   </s:si>
   <s:si>
@@ -601,6 +685,18 @@
   </s:si>
   <s:si>
     <s:t>14:00-14:05</s:t>
+  </s:si>
+  <s:si>
+    <s:t>16:30-16:35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Staliś Donata</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Derezińska Katarzyna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>15:40-15:45</s:t>
   </s:si>
 </s:sst>
 </file>
@@ -1050,7 +1146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{fd2c6218-4dec-4d3c-984f-803397d4c9f1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{fa50b800-9567-4135-a9f7-c76c650b0a31}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1071,13 +1167,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{9a65fb0a-bbb4-4b44-8072-83c079624620}">
-  <dimension ref="A1:I110"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1c5b9002-c574-42cb-8730-6575dba92b7b}">
+  <dimension ref="A1:I180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="68.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
@@ -4276,6 +4372,2036 @@
         <v>19</v>
       </c>
     </row>
+    <row r="111" spans="1:9" ht="15">
+      <c r="A111" t="s">
+        <v>159</v>
+      </c>
+      <c r="B111" t="s">
+        <v>20</v>
+      </c>
+      <c r="C111" t="s">
+        <v>21</v>
+      </c>
+      <c r="D111" t="s">
+        <v>22</v>
+      </c>
+      <c r="E111" t="s">
+        <v>27</v>
+      </c>
+      <c r="F111" t="s">
+        <v>16</v>
+      </c>
+      <c r="G111" t="s">
+        <v>29</v>
+      </c>
+      <c r="H111" t="s">
+        <v>18</v>
+      </c>
+      <c r="I111" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="15">
+      <c r="A112" t="s">
+        <v>159</v>
+      </c>
+      <c r="B112" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" t="s">
+        <v>122</v>
+      </c>
+      <c r="D112" t="s">
+        <v>136</v>
+      </c>
+      <c r="E112" t="s">
+        <v>92</v>
+      </c>
+      <c r="F112" t="s">
+        <v>137</v>
+      </c>
+      <c r="G112" t="s">
+        <v>28</v>
+      </c>
+      <c r="H112" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15">
+      <c r="A113" t="s">
+        <v>159</v>
+      </c>
+      <c r="B113" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" t="s">
+        <v>21</v>
+      </c>
+      <c r="D113" t="s">
+        <v>22</v>
+      </c>
+      <c r="E113" t="s">
+        <v>27</v>
+      </c>
+      <c r="F113" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" t="s">
+        <v>29</v>
+      </c>
+      <c r="H113" t="s">
+        <v>18</v>
+      </c>
+      <c r="I113" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="15">
+      <c r="A114" t="s">
+        <v>159</v>
+      </c>
+      <c r="B114" t="s">
+        <v>31</v>
+      </c>
+      <c r="C114" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114" t="s">
+        <v>32</v>
+      </c>
+      <c r="E114" t="s">
+        <v>27</v>
+      </c>
+      <c r="F114" t="s">
+        <v>16</v>
+      </c>
+      <c r="G114" t="s">
+        <v>29</v>
+      </c>
+      <c r="H114" t="s">
+        <v>18</v>
+      </c>
+      <c r="I114" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="15">
+      <c r="A115" t="s">
+        <v>159</v>
+      </c>
+      <c r="B115" t="s">
+        <v>38</v>
+      </c>
+      <c r="C115" t="s">
+        <v>122</v>
+      </c>
+      <c r="D115" t="s">
+        <v>160</v>
+      </c>
+      <c r="E115" t="s">
+        <v>92</v>
+      </c>
+      <c r="F115" t="s">
+        <v>137</v>
+      </c>
+      <c r="G115" t="s">
+        <v>28</v>
+      </c>
+      <c r="H115" t="s">
+        <v>18</v>
+      </c>
+      <c r="I115" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15">
+      <c r="A116" t="s">
+        <v>159</v>
+      </c>
+      <c r="B116" t="s">
+        <v>38</v>
+      </c>
+      <c r="C116" t="s">
+        <v>21</v>
+      </c>
+      <c r="D116" t="s">
+        <v>39</v>
+      </c>
+      <c r="E116" t="s">
+        <v>27</v>
+      </c>
+      <c r="F116" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" t="s">
+        <v>29</v>
+      </c>
+      <c r="H116" t="s">
+        <v>18</v>
+      </c>
+      <c r="I116" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15">
+      <c r="A117" t="s">
+        <v>159</v>
+      </c>
+      <c r="B117" t="s">
+        <v>44</v>
+      </c>
+      <c r="C117" t="s">
+        <v>122</v>
+      </c>
+      <c r="D117" t="s">
+        <v>30</v>
+      </c>
+      <c r="E117" t="s">
+        <v>92</v>
+      </c>
+      <c r="F117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G117" t="s">
+        <v>28</v>
+      </c>
+      <c r="H117" t="s">
+        <v>18</v>
+      </c>
+      <c r="I117" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="15">
+      <c r="A118" t="s">
+        <v>159</v>
+      </c>
+      <c r="B118" t="s">
+        <v>44</v>
+      </c>
+      <c r="C118" t="s">
+        <v>21</v>
+      </c>
+      <c r="D118" t="s">
+        <v>45</v>
+      </c>
+      <c r="E118" t="s">
+        <v>27</v>
+      </c>
+      <c r="F118" t="s">
+        <v>16</v>
+      </c>
+      <c r="G118" t="s">
+        <v>29</v>
+      </c>
+      <c r="H118" t="s">
+        <v>18</v>
+      </c>
+      <c r="I118" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="15">
+      <c r="A119" t="s">
+        <v>159</v>
+      </c>
+      <c r="B119" t="s">
+        <v>46</v>
+      </c>
+      <c r="C119" t="s">
+        <v>122</v>
+      </c>
+      <c r="D119" t="s">
+        <v>161</v>
+      </c>
+      <c r="E119" t="s">
+        <v>92</v>
+      </c>
+      <c r="F119" t="s">
+        <v>137</v>
+      </c>
+      <c r="G119" t="s">
+        <v>28</v>
+      </c>
+      <c r="H119" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="15">
+      <c r="A120" t="s">
+        <v>159</v>
+      </c>
+      <c r="B120" t="s">
+        <v>46</v>
+      </c>
+      <c r="C120" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" t="s">
+        <v>43</v>
+      </c>
+      <c r="E120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F120" t="s">
+        <v>16</v>
+      </c>
+      <c r="G120" t="s">
+        <v>29</v>
+      </c>
+      <c r="H120" t="s">
+        <v>18</v>
+      </c>
+      <c r="I120" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="15">
+      <c r="A121" t="s">
+        <v>162</v>
+      </c>
+      <c r="B121" t="s">
+        <v>26</v>
+      </c>
+      <c r="C121" t="s">
+        <v>122</v>
+      </c>
+      <c r="D121" t="s">
+        <v>45</v>
+      </c>
+      <c r="E121" t="s">
+        <v>92</v>
+      </c>
+      <c r="F121" t="s">
+        <v>124</v>
+      </c>
+      <c r="G121" t="s">
+        <v>28</v>
+      </c>
+      <c r="H121" t="s">
+        <v>18</v>
+      </c>
+      <c r="I121" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15">
+      <c r="A122" t="s">
+        <v>162</v>
+      </c>
+      <c r="B122" t="s">
+        <v>26</v>
+      </c>
+      <c r="C122" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122" t="s">
+        <v>22</v>
+      </c>
+      <c r="E122" t="s">
+        <v>27</v>
+      </c>
+      <c r="F122" t="s">
+        <v>16</v>
+      </c>
+      <c r="G122" t="s">
+        <v>29</v>
+      </c>
+      <c r="H122" t="s">
+        <v>18</v>
+      </c>
+      <c r="I122" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15">
+      <c r="A123" t="s">
+        <v>162</v>
+      </c>
+      <c r="B123" t="s">
+        <v>31</v>
+      </c>
+      <c r="C123" t="s">
+        <v>122</v>
+      </c>
+      <c r="D123" t="s">
+        <v>163</v>
+      </c>
+      <c r="E123" t="s">
+        <v>92</v>
+      </c>
+      <c r="F123" t="s">
+        <v>124</v>
+      </c>
+      <c r="G123" t="s">
+        <v>28</v>
+      </c>
+      <c r="H123" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15">
+      <c r="A124" t="s">
+        <v>162</v>
+      </c>
+      <c r="B124" t="s">
+        <v>31</v>
+      </c>
+      <c r="C124" t="s">
+        <v>21</v>
+      </c>
+      <c r="D124" t="s">
+        <v>45</v>
+      </c>
+      <c r="E124" t="s">
+        <v>27</v>
+      </c>
+      <c r="F124" t="s">
+        <v>16</v>
+      </c>
+      <c r="G124" t="s">
+        <v>29</v>
+      </c>
+      <c r="H124" t="s">
+        <v>18</v>
+      </c>
+      <c r="I124" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15">
+      <c r="A125" t="s">
+        <v>162</v>
+      </c>
+      <c r="B125" t="s">
+        <v>38</v>
+      </c>
+      <c r="C125" t="s">
+        <v>122</v>
+      </c>
+      <c r="D125" t="s">
+        <v>30</v>
+      </c>
+      <c r="E125" t="s">
+        <v>47</v>
+      </c>
+      <c r="F125" t="s">
+        <v>124</v>
+      </c>
+      <c r="G125" t="s">
+        <v>28</v>
+      </c>
+      <c r="H125" t="s">
+        <v>18</v>
+      </c>
+      <c r="I125" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="15">
+      <c r="A126" t="s">
+        <v>162</v>
+      </c>
+      <c r="B126" t="s">
+        <v>38</v>
+      </c>
+      <c r="C126" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" t="s">
+        <v>45</v>
+      </c>
+      <c r="E126" t="s">
+        <v>27</v>
+      </c>
+      <c r="F126" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" t="s">
+        <v>29</v>
+      </c>
+      <c r="H126" t="s">
+        <v>18</v>
+      </c>
+      <c r="I126" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="15">
+      <c r="A127" t="s">
+        <v>162</v>
+      </c>
+      <c r="B127" t="s">
+        <v>44</v>
+      </c>
+      <c r="C127" t="s">
+        <v>122</v>
+      </c>
+      <c r="D127" t="s">
+        <v>150</v>
+      </c>
+      <c r="E127" t="s">
+        <v>92</v>
+      </c>
+      <c r="F127" t="s">
+        <v>124</v>
+      </c>
+      <c r="G127" t="s">
+        <v>28</v>
+      </c>
+      <c r="H127" t="s">
+        <v>18</v>
+      </c>
+      <c r="I127" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="15">
+      <c r="A128" t="s">
+        <v>162</v>
+      </c>
+      <c r="B128" t="s">
+        <v>44</v>
+      </c>
+      <c r="C128" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" t="s">
+        <v>32</v>
+      </c>
+      <c r="E128" t="s">
+        <v>27</v>
+      </c>
+      <c r="F128" t="s">
+        <v>16</v>
+      </c>
+      <c r="G128" t="s">
+        <v>29</v>
+      </c>
+      <c r="H128" t="s">
+        <v>18</v>
+      </c>
+      <c r="I128" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="15">
+      <c r="A129" t="s">
+        <v>162</v>
+      </c>
+      <c r="B129" t="s">
+        <v>46</v>
+      </c>
+      <c r="C129" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" t="s">
+        <v>43</v>
+      </c>
+      <c r="E129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F129" t="s">
+        <v>16</v>
+      </c>
+      <c r="G129" t="s">
+        <v>29</v>
+      </c>
+      <c r="H129" t="s">
+        <v>18</v>
+      </c>
+      <c r="I129" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="15">
+      <c r="A130" t="s">
+        <v>164</v>
+      </c>
+      <c r="B130" t="s">
+        <v>20</v>
+      </c>
+      <c r="C130" t="s">
+        <v>122</v>
+      </c>
+      <c r="D130" t="s">
+        <v>142</v>
+      </c>
+      <c r="E130" t="s">
+        <v>92</v>
+      </c>
+      <c r="F130" t="s">
+        <v>124</v>
+      </c>
+      <c r="G130" t="s">
+        <v>28</v>
+      </c>
+      <c r="H130" t="s">
+        <v>18</v>
+      </c>
+      <c r="I130" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="15">
+      <c r="A131" t="s">
+        <v>164</v>
+      </c>
+      <c r="B131" t="s">
+        <v>26</v>
+      </c>
+      <c r="C131" t="s">
+        <v>122</v>
+      </c>
+      <c r="D131" t="s">
+        <v>45</v>
+      </c>
+      <c r="E131" t="s">
+        <v>92</v>
+      </c>
+      <c r="F131" t="s">
+        <v>124</v>
+      </c>
+      <c r="G131" t="s">
+        <v>28</v>
+      </c>
+      <c r="H131" t="s">
+        <v>18</v>
+      </c>
+      <c r="I131" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="15">
+      <c r="A132" t="s">
+        <v>164</v>
+      </c>
+      <c r="B132" t="s">
+        <v>26</v>
+      </c>
+      <c r="C132" t="s">
+        <v>165</v>
+      </c>
+      <c r="D132" t="s">
+        <v>166</v>
+      </c>
+      <c r="E132" t="s">
+        <v>92</v>
+      </c>
+      <c r="F132" t="s">
+        <v>167</v>
+      </c>
+      <c r="G132" t="s">
+        <v>28</v>
+      </c>
+      <c r="H132" t="s">
+        <v>18</v>
+      </c>
+      <c r="I132" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="15">
+      <c r="A133" t="s">
+        <v>164</v>
+      </c>
+      <c r="B133" t="s">
+        <v>31</v>
+      </c>
+      <c r="C133" t="s">
+        <v>165</v>
+      </c>
+      <c r="D133" t="s">
+        <v>168</v>
+      </c>
+      <c r="E133" t="s">
+        <v>92</v>
+      </c>
+      <c r="F133" t="s">
+        <v>167</v>
+      </c>
+      <c r="G133" t="s">
+        <v>28</v>
+      </c>
+      <c r="H133" t="s">
+        <v>18</v>
+      </c>
+      <c r="I133" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="15">
+      <c r="A134" t="s">
+        <v>164</v>
+      </c>
+      <c r="B134" t="s">
+        <v>38</v>
+      </c>
+      <c r="C134" t="s">
+        <v>122</v>
+      </c>
+      <c r="D134" t="s">
+        <v>130</v>
+      </c>
+      <c r="E134" t="s">
+        <v>92</v>
+      </c>
+      <c r="F134" t="s">
+        <v>157</v>
+      </c>
+      <c r="G134" t="s">
+        <v>28</v>
+      </c>
+      <c r="H134" t="s">
+        <v>18</v>
+      </c>
+      <c r="I134" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="15">
+      <c r="A135" t="s">
+        <v>164</v>
+      </c>
+      <c r="B135" t="s">
+        <v>38</v>
+      </c>
+      <c r="C135" t="s">
+        <v>165</v>
+      </c>
+      <c r="D135" t="s">
+        <v>168</v>
+      </c>
+      <c r="E135" t="s">
+        <v>92</v>
+      </c>
+      <c r="F135" t="s">
+        <v>167</v>
+      </c>
+      <c r="G135" t="s">
+        <v>28</v>
+      </c>
+      <c r="H135" t="s">
+        <v>18</v>
+      </c>
+      <c r="I135" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="15">
+      <c r="A136" t="s">
+        <v>164</v>
+      </c>
+      <c r="B136" t="s">
+        <v>44</v>
+      </c>
+      <c r="C136" t="s">
+        <v>122</v>
+      </c>
+      <c r="D136" t="s">
+        <v>123</v>
+      </c>
+      <c r="E136" t="s">
+        <v>92</v>
+      </c>
+      <c r="F136" t="s">
+        <v>157</v>
+      </c>
+      <c r="G136" t="s">
+        <v>28</v>
+      </c>
+      <c r="H136" t="s">
+        <v>18</v>
+      </c>
+      <c r="I136" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="15">
+      <c r="A137" t="s">
+        <v>164</v>
+      </c>
+      <c r="B137" t="s">
+        <v>44</v>
+      </c>
+      <c r="C137" t="s">
+        <v>165</v>
+      </c>
+      <c r="D137" t="s">
+        <v>169</v>
+      </c>
+      <c r="E137" t="s">
+        <v>92</v>
+      </c>
+      <c r="F137" t="s">
+        <v>167</v>
+      </c>
+      <c r="G137" t="s">
+        <v>28</v>
+      </c>
+      <c r="H137" t="s">
+        <v>18</v>
+      </c>
+      <c r="I137" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="15">
+      <c r="A138" t="s">
+        <v>164</v>
+      </c>
+      <c r="B138" t="s">
+        <v>46</v>
+      </c>
+      <c r="C138" t="s">
+        <v>122</v>
+      </c>
+      <c r="D138" t="s">
+        <v>152</v>
+      </c>
+      <c r="E138" t="s">
+        <v>92</v>
+      </c>
+      <c r="F138" t="s">
+        <v>157</v>
+      </c>
+      <c r="G138" t="s">
+        <v>28</v>
+      </c>
+      <c r="H138" t="s">
+        <v>18</v>
+      </c>
+      <c r="I138" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="15">
+      <c r="A139" t="s">
+        <v>164</v>
+      </c>
+      <c r="B139" t="s">
+        <v>46</v>
+      </c>
+      <c r="C139" t="s">
+        <v>165</v>
+      </c>
+      <c r="D139" t="s">
+        <v>170</v>
+      </c>
+      <c r="E139" t="s">
+        <v>92</v>
+      </c>
+      <c r="F139" t="s">
+        <v>167</v>
+      </c>
+      <c r="G139" t="s">
+        <v>28</v>
+      </c>
+      <c r="H139" t="s">
+        <v>18</v>
+      </c>
+      <c r="I139" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="15">
+      <c r="A140" t="s">
+        <v>171</v>
+      </c>
+      <c r="B140" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" t="s">
+        <v>122</v>
+      </c>
+      <c r="D140" t="s">
+        <v>123</v>
+      </c>
+      <c r="E140" t="s">
+        <v>92</v>
+      </c>
+      <c r="F140" t="s">
+        <v>124</v>
+      </c>
+      <c r="G140" t="s">
+        <v>28</v>
+      </c>
+      <c r="H140" t="s">
+        <v>18</v>
+      </c>
+      <c r="I140" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="15">
+      <c r="A141" t="s">
+        <v>171</v>
+      </c>
+      <c r="B141" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" t="s">
+        <v>172</v>
+      </c>
+      <c r="D141" t="s">
+        <v>168</v>
+      </c>
+      <c r="E141" t="s">
+        <v>173</v>
+      </c>
+      <c r="F141" t="s">
+        <v>145</v>
+      </c>
+      <c r="G141" t="s">
+        <v>28</v>
+      </c>
+      <c r="H141" t="s">
+        <v>18</v>
+      </c>
+      <c r="I141" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="15">
+      <c r="A142" t="s">
+        <v>171</v>
+      </c>
+      <c r="B142" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" t="s">
+        <v>174</v>
+      </c>
+      <c r="D142" t="s">
+        <v>106</v>
+      </c>
+      <c r="E142" t="s">
+        <v>175</v>
+      </c>
+      <c r="F142" t="s">
+        <v>89</v>
+      </c>
+      <c r="G142" t="s">
+        <v>28</v>
+      </c>
+      <c r="H142" t="s">
+        <v>18</v>
+      </c>
+      <c r="I142" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="15">
+      <c r="A143" t="s">
+        <v>171</v>
+      </c>
+      <c r="B143" t="s">
+        <v>38</v>
+      </c>
+      <c r="C143" t="s">
+        <v>122</v>
+      </c>
+      <c r="D143" t="s">
+        <v>96</v>
+      </c>
+      <c r="E143" t="s">
+        <v>92</v>
+      </c>
+      <c r="F143" t="s">
+        <v>124</v>
+      </c>
+      <c r="G143" t="s">
+        <v>28</v>
+      </c>
+      <c r="H143" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="15">
+      <c r="A144" t="s">
+        <v>171</v>
+      </c>
+      <c r="B144" t="s">
+        <v>38</v>
+      </c>
+      <c r="C144" t="s">
+        <v>172</v>
+      </c>
+      <c r="D144" t="s">
+        <v>168</v>
+      </c>
+      <c r="E144" t="s">
+        <v>173</v>
+      </c>
+      <c r="F144" t="s">
+        <v>145</v>
+      </c>
+      <c r="G144" t="s">
+        <v>28</v>
+      </c>
+      <c r="H144" t="s">
+        <v>18</v>
+      </c>
+      <c r="I144" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="15">
+      <c r="A145" t="s">
+        <v>171</v>
+      </c>
+      <c r="B145" t="s">
+        <v>38</v>
+      </c>
+      <c r="C145" t="s">
+        <v>174</v>
+      </c>
+      <c r="D145" t="s">
+        <v>176</v>
+      </c>
+      <c r="E145" t="s">
+        <v>175</v>
+      </c>
+      <c r="F145" t="s">
+        <v>89</v>
+      </c>
+      <c r="G145" t="s">
+        <v>28</v>
+      </c>
+      <c r="H145" t="s">
+        <v>18</v>
+      </c>
+      <c r="I145" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="15">
+      <c r="A146" t="s">
+        <v>171</v>
+      </c>
+      <c r="B146" t="s">
+        <v>44</v>
+      </c>
+      <c r="C146" t="s">
+        <v>122</v>
+      </c>
+      <c r="D146" t="s">
+        <v>51</v>
+      </c>
+      <c r="E146" t="s">
+        <v>92</v>
+      </c>
+      <c r="F146" t="s">
+        <v>124</v>
+      </c>
+      <c r="G146" t="s">
+        <v>28</v>
+      </c>
+      <c r="H146" t="s">
+        <v>18</v>
+      </c>
+      <c r="I146" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="15">
+      <c r="A147" t="s">
+        <v>171</v>
+      </c>
+      <c r="B147" t="s">
+        <v>44</v>
+      </c>
+      <c r="C147" t="s">
+        <v>174</v>
+      </c>
+      <c r="D147" t="s">
+        <v>177</v>
+      </c>
+      <c r="E147" t="s">
+        <v>175</v>
+      </c>
+      <c r="F147" t="s">
+        <v>89</v>
+      </c>
+      <c r="G147" t="s">
+        <v>28</v>
+      </c>
+      <c r="H147" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="15">
+      <c r="A148" t="s">
+        <v>171</v>
+      </c>
+      <c r="B148" t="s">
+        <v>46</v>
+      </c>
+      <c r="C148" t="s">
+        <v>122</v>
+      </c>
+      <c r="D148" t="s">
+        <v>130</v>
+      </c>
+      <c r="E148" t="s">
+        <v>92</v>
+      </c>
+      <c r="F148" t="s">
+        <v>124</v>
+      </c>
+      <c r="G148" t="s">
+        <v>28</v>
+      </c>
+      <c r="H148" t="s">
+        <v>18</v>
+      </c>
+      <c r="I148" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="15">
+      <c r="A149" t="s">
+        <v>171</v>
+      </c>
+      <c r="B149" t="s">
+        <v>46</v>
+      </c>
+      <c r="C149" t="s">
+        <v>172</v>
+      </c>
+      <c r="D149" t="s">
+        <v>106</v>
+      </c>
+      <c r="E149" t="s">
+        <v>178</v>
+      </c>
+      <c r="F149" t="s">
+        <v>154</v>
+      </c>
+      <c r="G149" t="s">
+        <v>28</v>
+      </c>
+      <c r="H149" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="15">
+      <c r="A150" t="s">
+        <v>171</v>
+      </c>
+      <c r="B150" t="s">
+        <v>46</v>
+      </c>
+      <c r="C150" t="s">
+        <v>174</v>
+      </c>
+      <c r="D150" t="s">
+        <v>177</v>
+      </c>
+      <c r="E150" t="s">
+        <v>175</v>
+      </c>
+      <c r="F150" t="s">
+        <v>89</v>
+      </c>
+      <c r="G150" t="s">
+        <v>28</v>
+      </c>
+      <c r="H150" t="s">
+        <v>18</v>
+      </c>
+      <c r="I150" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="15">
+      <c r="A151" t="s">
+        <v>171</v>
+      </c>
+      <c r="B151" t="s">
+        <v>49</v>
+      </c>
+      <c r="C151" t="s">
+        <v>172</v>
+      </c>
+      <c r="D151" t="s">
+        <v>106</v>
+      </c>
+      <c r="E151" t="s">
+        <v>178</v>
+      </c>
+      <c r="F151" t="s">
+        <v>154</v>
+      </c>
+      <c r="G151" t="s">
+        <v>28</v>
+      </c>
+      <c r="H151" t="s">
+        <v>18</v>
+      </c>
+      <c r="I151" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="15">
+      <c r="A152" t="s">
+        <v>171</v>
+      </c>
+      <c r="B152" t="s">
+        <v>55</v>
+      </c>
+      <c r="C152" t="s">
+        <v>172</v>
+      </c>
+      <c r="D152" t="s">
+        <v>106</v>
+      </c>
+      <c r="E152" t="s">
+        <v>178</v>
+      </c>
+      <c r="F152" t="s">
+        <v>154</v>
+      </c>
+      <c r="G152" t="s">
+        <v>28</v>
+      </c>
+      <c r="H152" t="s">
+        <v>18</v>
+      </c>
+      <c r="I152" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="15">
+      <c r="A153" t="s">
+        <v>171</v>
+      </c>
+      <c r="B153" t="s">
+        <v>111</v>
+      </c>
+      <c r="C153" t="s">
+        <v>172</v>
+      </c>
+      <c r="D153" t="s">
+        <v>106</v>
+      </c>
+      <c r="E153" t="s">
+        <v>47</v>
+      </c>
+      <c r="F153" t="s">
+        <v>154</v>
+      </c>
+      <c r="G153" t="s">
+        <v>28</v>
+      </c>
+      <c r="H153" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="15">
+      <c r="A154" t="s">
+        <v>179</v>
+      </c>
+      <c r="B154" t="s">
+        <v>20</v>
+      </c>
+      <c r="C154" t="s">
+        <v>122</v>
+      </c>
+      <c r="D154" t="s">
+        <v>136</v>
+      </c>
+      <c r="E154" t="s">
+        <v>92</v>
+      </c>
+      <c r="F154" t="s">
+        <v>137</v>
+      </c>
+      <c r="G154" t="s">
+        <v>28</v>
+      </c>
+      <c r="H154" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="15">
+      <c r="A155" t="s">
+        <v>179</v>
+      </c>
+      <c r="B155" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" t="s">
+        <v>122</v>
+      </c>
+      <c r="D155" t="s">
+        <v>142</v>
+      </c>
+      <c r="E155" t="s">
+        <v>92</v>
+      </c>
+      <c r="F155" t="s">
+        <v>137</v>
+      </c>
+      <c r="G155" t="s">
+        <v>28</v>
+      </c>
+      <c r="H155" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="15">
+      <c r="A156" t="s">
+        <v>179</v>
+      </c>
+      <c r="B156" t="s">
+        <v>31</v>
+      </c>
+      <c r="C156" t="s">
+        <v>122</v>
+      </c>
+      <c r="D156" t="s">
+        <v>51</v>
+      </c>
+      <c r="E156" t="s">
+        <v>92</v>
+      </c>
+      <c r="F156" t="s">
+        <v>137</v>
+      </c>
+      <c r="G156" t="s">
+        <v>28</v>
+      </c>
+      <c r="H156" t="s">
+        <v>18</v>
+      </c>
+      <c r="I156" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="15">
+      <c r="A157" t="s">
+        <v>179</v>
+      </c>
+      <c r="B157" t="s">
+        <v>38</v>
+      </c>
+      <c r="C157" t="s">
+        <v>122</v>
+      </c>
+      <c r="D157" t="s">
+        <v>51</v>
+      </c>
+      <c r="E157" t="s">
+        <v>92</v>
+      </c>
+      <c r="F157" t="s">
+        <v>137</v>
+      </c>
+      <c r="G157" t="s">
+        <v>28</v>
+      </c>
+      <c r="H157" t="s">
+        <v>18</v>
+      </c>
+      <c r="I157" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="15">
+      <c r="A158" t="s">
+        <v>179</v>
+      </c>
+      <c r="B158" t="s">
+        <v>38</v>
+      </c>
+      <c r="C158" t="s">
+        <v>180</v>
+      </c>
+      <c r="D158" t="s">
+        <v>169</v>
+      </c>
+      <c r="E158" t="s">
+        <v>27</v>
+      </c>
+      <c r="F158" t="s">
+        <v>41</v>
+      </c>
+      <c r="G158" t="s">
+        <v>133</v>
+      </c>
+      <c r="H158" t="s">
+        <v>18</v>
+      </c>
+      <c r="I158" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="15">
+      <c r="A159" t="s">
+        <v>179</v>
+      </c>
+      <c r="B159" t="s">
+        <v>44</v>
+      </c>
+      <c r="C159" t="s">
+        <v>122</v>
+      </c>
+      <c r="D159" t="s">
+        <v>152</v>
+      </c>
+      <c r="E159" t="s">
+        <v>92</v>
+      </c>
+      <c r="F159" t="s">
+        <v>137</v>
+      </c>
+      <c r="G159" t="s">
+        <v>28</v>
+      </c>
+      <c r="H159" t="s">
+        <v>18</v>
+      </c>
+      <c r="I159" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="15">
+      <c r="A160" t="s">
+        <v>179</v>
+      </c>
+      <c r="B160" t="s">
+        <v>44</v>
+      </c>
+      <c r="C160" t="s">
+        <v>180</v>
+      </c>
+      <c r="D160" t="s">
+        <v>169</v>
+      </c>
+      <c r="E160" t="s">
+        <v>27</v>
+      </c>
+      <c r="F160" t="s">
+        <v>41</v>
+      </c>
+      <c r="G160" t="s">
+        <v>133</v>
+      </c>
+      <c r="H160" t="s">
+        <v>18</v>
+      </c>
+      <c r="I160" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="15">
+      <c r="A161" t="s">
+        <v>179</v>
+      </c>
+      <c r="B161" t="s">
+        <v>46</v>
+      </c>
+      <c r="C161" t="s">
+        <v>122</v>
+      </c>
+      <c r="D161" t="s">
+        <v>96</v>
+      </c>
+      <c r="E161" t="s">
+        <v>92</v>
+      </c>
+      <c r="F161" t="s">
+        <v>137</v>
+      </c>
+      <c r="G161" t="s">
+        <v>28</v>
+      </c>
+      <c r="H161" t="s">
+        <v>18</v>
+      </c>
+      <c r="I161" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="15">
+      <c r="A162" t="s">
+        <v>179</v>
+      </c>
+      <c r="B162" t="s">
+        <v>46</v>
+      </c>
+      <c r="C162" t="s">
+        <v>180</v>
+      </c>
+      <c r="D162" t="s">
+        <v>150</v>
+      </c>
+      <c r="E162" t="s">
+        <v>27</v>
+      </c>
+      <c r="F162" t="s">
+        <v>41</v>
+      </c>
+      <c r="G162" t="s">
+        <v>133</v>
+      </c>
+      <c r="H162" t="s">
+        <v>18</v>
+      </c>
+      <c r="I162" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="15">
+      <c r="A163" t="s">
+        <v>179</v>
+      </c>
+      <c r="B163" t="s">
+        <v>49</v>
+      </c>
+      <c r="C163" t="s">
+        <v>180</v>
+      </c>
+      <c r="D163" t="s">
+        <v>150</v>
+      </c>
+      <c r="E163" t="s">
+        <v>27</v>
+      </c>
+      <c r="F163" t="s">
+        <v>41</v>
+      </c>
+      <c r="G163" t="s">
+        <v>133</v>
+      </c>
+      <c r="H163" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="15">
+      <c r="A164" t="s">
+        <v>179</v>
+      </c>
+      <c r="B164" t="s">
+        <v>55</v>
+      </c>
+      <c r="C164" t="s">
+        <v>180</v>
+      </c>
+      <c r="D164" t="s">
+        <v>56</v>
+      </c>
+      <c r="E164" t="s">
+        <v>27</v>
+      </c>
+      <c r="F164" t="s">
+        <v>41</v>
+      </c>
+      <c r="G164" t="s">
+        <v>54</v>
+      </c>
+      <c r="H164" t="s">
+        <v>18</v>
+      </c>
+      <c r="I164" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="15">
+      <c r="A165" t="s">
+        <v>181</v>
+      </c>
+      <c r="B165" t="s">
+        <v>12</v>
+      </c>
+      <c r="C165" t="s">
+        <v>174</v>
+      </c>
+      <c r="D165" t="s">
+        <v>182</v>
+      </c>
+      <c r="E165" t="s">
+        <v>175</v>
+      </c>
+      <c r="F165" t="s">
+        <v>89</v>
+      </c>
+      <c r="G165" t="s">
+        <v>28</v>
+      </c>
+      <c r="H165" t="s">
+        <v>18</v>
+      </c>
+      <c r="I165" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="15">
+      <c r="A166" t="s">
+        <v>181</v>
+      </c>
+      <c r="B166" t="s">
+        <v>20</v>
+      </c>
+      <c r="C166" t="s">
+        <v>183</v>
+      </c>
+      <c r="D166" t="s">
+        <v>184</v>
+      </c>
+      <c r="E166" t="s">
+        <v>63</v>
+      </c>
+      <c r="F166" t="s">
+        <v>93</v>
+      </c>
+      <c r="G166" t="s">
+        <v>28</v>
+      </c>
+      <c r="H166" t="s">
+        <v>18</v>
+      </c>
+      <c r="I166" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="15">
+      <c r="A167" t="s">
+        <v>181</v>
+      </c>
+      <c r="B167" t="s">
+        <v>20</v>
+      </c>
+      <c r="C167" t="s">
+        <v>174</v>
+      </c>
+      <c r="D167" t="s">
+        <v>45</v>
+      </c>
+      <c r="E167" t="s">
+        <v>175</v>
+      </c>
+      <c r="F167" t="s">
+        <v>89</v>
+      </c>
+      <c r="G167" t="s">
+        <v>28</v>
+      </c>
+      <c r="H167" t="s">
+        <v>18</v>
+      </c>
+      <c r="I167" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="15">
+      <c r="A168" t="s">
+        <v>181</v>
+      </c>
+      <c r="B168" t="s">
+        <v>26</v>
+      </c>
+      <c r="C168" t="s">
+        <v>183</v>
+      </c>
+      <c r="D168" t="s">
+        <v>116</v>
+      </c>
+      <c r="E168" t="s">
+        <v>63</v>
+      </c>
+      <c r="F168" t="s">
+        <v>93</v>
+      </c>
+      <c r="G168" t="s">
+        <v>28</v>
+      </c>
+      <c r="H168" t="s">
+        <v>18</v>
+      </c>
+      <c r="I168" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="15">
+      <c r="A169" t="s">
+        <v>181</v>
+      </c>
+      <c r="B169" t="s">
+        <v>31</v>
+      </c>
+      <c r="C169" t="s">
+        <v>183</v>
+      </c>
+      <c r="D169" t="s">
+        <v>45</v>
+      </c>
+      <c r="E169" t="s">
+        <v>63</v>
+      </c>
+      <c r="F169" t="s">
+        <v>93</v>
+      </c>
+      <c r="G169" t="s">
+        <v>28</v>
+      </c>
+      <c r="H169" t="s">
+        <v>18</v>
+      </c>
+      <c r="I169" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="15">
+      <c r="A170" t="s">
+        <v>181</v>
+      </c>
+      <c r="B170" t="s">
+        <v>31</v>
+      </c>
+      <c r="C170" t="s">
+        <v>174</v>
+      </c>
+      <c r="D170" t="s">
+        <v>114</v>
+      </c>
+      <c r="E170" t="s">
+        <v>175</v>
+      </c>
+      <c r="F170" t="s">
+        <v>89</v>
+      </c>
+      <c r="G170" t="s">
+        <v>28</v>
+      </c>
+      <c r="H170" t="s">
+        <v>18</v>
+      </c>
+      <c r="I170" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="15">
+      <c r="A171" t="s">
+        <v>181</v>
+      </c>
+      <c r="B171" t="s">
+        <v>38</v>
+      </c>
+      <c r="C171" t="s">
+        <v>183</v>
+      </c>
+      <c r="D171" t="s">
+        <v>45</v>
+      </c>
+      <c r="E171" t="s">
+        <v>63</v>
+      </c>
+      <c r="F171" t="s">
+        <v>93</v>
+      </c>
+      <c r="G171" t="s">
+        <v>28</v>
+      </c>
+      <c r="H171" t="s">
+        <v>18</v>
+      </c>
+      <c r="I171" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="15">
+      <c r="A172" t="s">
+        <v>181</v>
+      </c>
+      <c r="B172" t="s">
+        <v>38</v>
+      </c>
+      <c r="C172" t="s">
+        <v>174</v>
+      </c>
+      <c r="D172" t="s">
+        <v>185</v>
+      </c>
+      <c r="E172" t="s">
+        <v>175</v>
+      </c>
+      <c r="F172" t="s">
+        <v>89</v>
+      </c>
+      <c r="G172" t="s">
+        <v>28</v>
+      </c>
+      <c r="H172" t="s">
+        <v>18</v>
+      </c>
+      <c r="I172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="15">
+      <c r="A173" t="s">
+        <v>181</v>
+      </c>
+      <c r="B173" t="s">
+        <v>44</v>
+      </c>
+      <c r="C173" t="s">
+        <v>183</v>
+      </c>
+      <c r="D173" t="s">
+        <v>156</v>
+      </c>
+      <c r="E173" t="s">
+        <v>63</v>
+      </c>
+      <c r="F173" t="s">
+        <v>93</v>
+      </c>
+      <c r="G173" t="s">
+        <v>28</v>
+      </c>
+      <c r="H173" t="s">
+        <v>18</v>
+      </c>
+      <c r="I173" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="15">
+      <c r="A174" t="s">
+        <v>181</v>
+      </c>
+      <c r="B174" t="s">
+        <v>44</v>
+      </c>
+      <c r="C174" t="s">
+        <v>174</v>
+      </c>
+      <c r="D174" t="s">
+        <v>116</v>
+      </c>
+      <c r="E174" t="s">
+        <v>175</v>
+      </c>
+      <c r="F174" t="s">
+        <v>89</v>
+      </c>
+      <c r="G174" t="s">
+        <v>28</v>
+      </c>
+      <c r="H174" t="s">
+        <v>18</v>
+      </c>
+      <c r="I174" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="15">
+      <c r="A175" t="s">
+        <v>181</v>
+      </c>
+      <c r="B175" t="s">
+        <v>46</v>
+      </c>
+      <c r="C175" t="s">
+        <v>183</v>
+      </c>
+      <c r="D175" t="s">
+        <v>140</v>
+      </c>
+      <c r="E175" t="s">
+        <v>63</v>
+      </c>
+      <c r="F175" t="s">
+        <v>93</v>
+      </c>
+      <c r="G175" t="s">
+        <v>28</v>
+      </c>
+      <c r="H175" t="s">
+        <v>18</v>
+      </c>
+      <c r="I175" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="15">
+      <c r="A176" t="s">
+        <v>181</v>
+      </c>
+      <c r="B176" t="s">
+        <v>46</v>
+      </c>
+      <c r="C176" t="s">
+        <v>174</v>
+      </c>
+      <c r="D176" t="s">
+        <v>176</v>
+      </c>
+      <c r="E176" t="s">
+        <v>175</v>
+      </c>
+      <c r="F176" t="s">
+        <v>89</v>
+      </c>
+      <c r="G176" t="s">
+        <v>28</v>
+      </c>
+      <c r="H176" t="s">
+        <v>18</v>
+      </c>
+      <c r="I176" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="15">
+      <c r="A177" t="s">
+        <v>181</v>
+      </c>
+      <c r="B177" t="s">
+        <v>49</v>
+      </c>
+      <c r="C177" t="s">
+        <v>183</v>
+      </c>
+      <c r="D177" t="s">
+        <v>106</v>
+      </c>
+      <c r="E177" t="s">
+        <v>63</v>
+      </c>
+      <c r="F177" t="s">
+        <v>93</v>
+      </c>
+      <c r="G177" t="s">
+        <v>28</v>
+      </c>
+      <c r="H177" t="s">
+        <v>18</v>
+      </c>
+      <c r="I177" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="15">
+      <c r="A178" t="s">
+        <v>181</v>
+      </c>
+      <c r="B178" t="s">
+        <v>49</v>
+      </c>
+      <c r="C178" t="s">
+        <v>174</v>
+      </c>
+      <c r="D178" t="s">
+        <v>155</v>
+      </c>
+      <c r="E178" t="s">
+        <v>175</v>
+      </c>
+      <c r="F178" t="s">
+        <v>89</v>
+      </c>
+      <c r="G178" t="s">
+        <v>28</v>
+      </c>
+      <c r="H178" t="s">
+        <v>18</v>
+      </c>
+      <c r="I178" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="15">
+      <c r="A179" t="s">
+        <v>181</v>
+      </c>
+      <c r="B179" t="s">
+        <v>55</v>
+      </c>
+      <c r="C179" t="s">
+        <v>183</v>
+      </c>
+      <c r="D179" t="s">
+        <v>106</v>
+      </c>
+      <c r="E179" t="s">
+        <v>63</v>
+      </c>
+      <c r="F179" t="s">
+        <v>93</v>
+      </c>
+      <c r="G179" t="s">
+        <v>28</v>
+      </c>
+      <c r="H179" t="s">
+        <v>18</v>
+      </c>
+      <c r="I179" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="15">
+      <c r="A180" t="s">
+        <v>181</v>
+      </c>
+      <c r="B180" t="s">
+        <v>55</v>
+      </c>
+      <c r="C180" t="s">
+        <v>174</v>
+      </c>
+      <c r="D180" t="s">
+        <v>85</v>
+      </c>
+      <c r="E180" t="s">
+        <v>175</v>
+      </c>
+      <c r="F180" t="s">
+        <v>89</v>
+      </c>
+      <c r="G180" t="s">
+        <v>28</v>
+      </c>
+      <c r="H180" t="s">
+        <v>18</v>
+      </c>
+      <c r="I180" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4284,8 +6410,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2f07d88a-71ae-4888-9449-454c68a67997}">
-  <dimension ref="A1:I5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6a8900d8-3782-4001-9da3-cfb534853d23}">
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -4304,16 +6430,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -4333,13 +6459,13 @@
         <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="E2" t="s">
         <v>27</v>
@@ -4362,19 +6488,19 @@
         <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="D3" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="F3" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="G3" t="s">
         <v>76</v>
@@ -4391,13 +6517,13 @@
         <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -4420,19 +6546,19 @@
         <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="F5" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="G5" t="s">
         <v>113</v>
@@ -4441,6 +6567,93 @@
         <v>18</v>
       </c>
       <c r="I5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15">
+      <c r="A6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15">
+      <c r="A7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15">
+      <c r="A8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4452,13 +6665,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e5b05591-4c9b-4d22-8ba4-960c7e78a05d}">
-  <dimension ref="A1:F17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{df5b2c11-046a-496e-8074-d14a98b5a2fa}">
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
@@ -4469,13 +6682,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -4489,16 +6702,16 @@
         <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C2" t="s">
         <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -4509,13 +6722,13 @@
         <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="C3" t="s">
         <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="E3" t="s">
         <v>42</v>
@@ -4529,13 +6742,13 @@
         <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="E4" t="s">
         <v>80</v>
@@ -4549,13 +6762,13 @@
         <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="C5" t="s">
         <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="E5" t="s">
         <v>90</v>
@@ -4569,16 +6782,16 @@
         <v>118</v>
       </c>
       <c r="B6" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -4589,13 +6802,13 @@
         <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -4609,16 +6822,16 @@
         <v>118</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C8" t="s">
         <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>172</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -4629,16 +6842,16 @@
         <v>135</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C9" t="s">
         <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -4649,13 +6862,13 @@
         <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C10" t="s">
         <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="E10" t="s">
         <v>146</v>
@@ -4669,16 +6882,16 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="E11" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -4689,16 +6902,16 @@
         <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="E12" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -4709,13 +6922,13 @@
         <v>135</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="C13" t="s">
         <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="E13" t="s">
         <v>138</v>
@@ -4729,13 +6942,13 @@
         <v>135</v>
       </c>
       <c r="B14" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="C14" t="s">
         <v>144</v>
       </c>
       <c r="D14" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="E14" t="s">
         <v>42</v>
@@ -4749,13 +6962,13 @@
         <v>135</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="E15" t="s">
         <v>77</v>
@@ -4769,13 +6982,13 @@
         <v>135</v>
       </c>
       <c r="B16" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C16" t="s">
         <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="E16" t="s">
         <v>132</v>
@@ -4789,18 +7002,298 @@
         <v>135</v>
       </c>
       <c r="B17" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="C17" t="s">
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="E17" t="s">
         <v>80</v>
       </c>
       <c r="F17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15">
+      <c r="A18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" t="s">
+        <v>221</v>
+      </c>
+      <c r="C18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D18" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" t="s">
+        <v>223</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15">
+      <c r="A19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15">
+      <c r="A20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15">
+      <c r="A21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B21" t="s">
+        <v>214</v>
+      </c>
+      <c r="C21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" t="s">
+        <v>216</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15">
+      <c r="A22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22" t="s">
+        <v>211</v>
+      </c>
+      <c r="C22" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15">
+      <c r="A23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" t="s">
+        <v>210</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15">
+      <c r="A24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" t="s">
+        <v>165</v>
+      </c>
+      <c r="D24" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15">
+      <c r="A25" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D25" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15">
+      <c r="A26" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" t="s">
+        <v>214</v>
+      </c>
+      <c r="C26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" t="s">
+        <v>210</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15">
+      <c r="A27" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" t="s">
+        <v>210</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15">
+      <c r="A28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" t="s">
+        <v>210</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15">
+      <c r="A29" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" t="s">
+        <v>209</v>
+      </c>
+      <c r="C29" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" t="s">
+        <v>205</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" t="s">
+        <v>181</v>
+      </c>
+      <c r="B30" t="s">
+        <v>211</v>
+      </c>
+      <c r="C30" t="s">
+        <v>183</v>
+      </c>
+      <c r="D30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15">
+      <c r="A31" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" t="s">
+        <v>224</v>
+      </c>
+      <c r="C31" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<s:sst xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="225">
+<s:sst xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="232">
   <s:si>
     <s:t>Rok szkolny: 2026/2027</s:t>
   </s:si>
@@ -432,6 +432,15 @@
     <s:t>18.09.2026</s:t>
   </s:si>
   <s:si>
+    <s:t>Świerzewicz Katarzyna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2K</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Technologia gastronomiczna z towaroznawstwem</s:t>
+  </s:si>
+  <s:si>
     <s:t>1FB|gr2</s:t>
   </s:si>
   <s:si>
@@ -441,15 +450,6 @@
     <s:t>Jastrzębska-Majtyka Agnieszka</s:t>
   </s:si>
   <s:si>
-    <s:t>Świerzewicz Katarzyna</s:t>
-  </s:si>
-  <s:si>
-    <s:t>2K</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Technologia gastronomiczna z towaroznawstwem</s:t>
-  </s:si>
-  <s:si>
     <s:t>1TFH|gr2</s:t>
   </s:si>
   <s:si>
@@ -486,6 +486,12 @@
     <s:t>Informatyka</s:t>
   </s:si>
   <s:si>
+    <s:t>1K</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Mocarski Arkadiusz</s:t>
+  </s:si>
+  <s:si>
     <s:t>41</s:t>
   </s:si>
   <s:si>
@@ -498,6 +504,9 @@
     <s:t>27</s:t>
   </s:si>
   <s:si>
+    <s:t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</s:t>
+  </s:si>
+  <s:si>
     <s:t>4</s:t>
   </s:si>
   <s:si>
@@ -552,9 +561,6 @@
     <s:t>Biznes i zarządzanie</s:t>
   </s:si>
   <s:si>
-    <s:t>1K</s:t>
-  </s:si>
-  <s:si>
     <s:t>1WB</s:t>
   </s:si>
   <s:si>
@@ -630,6 +636,18 @@
     <s:t>Dyżur psychologa szkolnego</s:t>
   </s:si>
   <s:si>
+    <s:t>09:00-13:00</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Kaszak Maria</s:t>
+  </s:si>
+  <s:si>
+    <s:t/>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">dyżur pedagoga specjalnego </s:t>
+  </s:si>
+  <s:si>
     <s:t xml:space="preserve">Matematyka </s:t>
   </s:si>
   <s:si>
@@ -667,6 +685,9 @@
   </s:si>
   <s:si>
     <s:t>13:10-13:15</s:t>
+  </s:si>
+  <s:si>
+    <s:t>07:55-08:00</s:t>
   </s:si>
   <s:si>
     <s:t>08:45-08:50</s:t>
@@ -1146,7 +1167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{fa50b800-9567-4135-a9f7-c76c650b0a31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7acacd02-a3f5-4dae-9df1-d08e1d54cfba}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1167,8 +1188,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1c5b9002-c574-42cb-8730-6575dba92b7b}">
-  <dimension ref="A1:I180"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{05501696-feab-4fce-affd-2617c323f72e}">
+  <dimension ref="A1:I183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -3536,19 +3557,19 @@
         <v>135</v>
       </c>
       <c r="B82" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D82" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E82" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="F82" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="G82" t="s">
         <v>113</v>
@@ -3568,25 +3589,25 @@
         <v>20</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D83" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="E83" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="F83" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="G83" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
@@ -3597,19 +3618,19 @@
         <v>20</v>
       </c>
       <c r="C84" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D84" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E84" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F84" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="G84" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
@@ -3626,25 +3647,25 @@
         <v>20</v>
       </c>
       <c r="C85" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="E85" t="s">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="F85" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G85" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
@@ -3652,28 +3673,28 @@
         <v>135</v>
       </c>
       <c r="B86" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C86" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D86" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E86" t="s">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="F86" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="G86" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
@@ -3684,19 +3705,19 @@
         <v>26</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D87" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="E87" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F87" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="G87" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
@@ -3713,19 +3734,19 @@
         <v>26</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D88" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="E88" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F88" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="G88" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
@@ -3742,25 +3763,25 @@
         <v>26</v>
       </c>
       <c r="C89" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="E89" t="s">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="F89" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G89" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
@@ -3768,28 +3789,28 @@
         <v>135</v>
       </c>
       <c r="B90" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D90" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="E90" t="s">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="F90" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="G90" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
@@ -3800,19 +3821,19 @@
         <v>31</v>
       </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D91" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E91" t="s">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="F91" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G91" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
@@ -3829,19 +3850,19 @@
         <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="D92" t="s">
-        <v>150</v>
+        <v>39</v>
       </c>
       <c r="E92" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F92" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="G92" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
@@ -3858,25 +3879,25 @@
         <v>31</v>
       </c>
       <c r="C93" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="E93" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="F93" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="G93" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
@@ -3887,25 +3908,25 @@
         <v>31</v>
       </c>
       <c r="C94" t="s">
-        <v>13</v>
+        <v>144</v>
       </c>
       <c r="D94" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E94" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F94" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="G94" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
@@ -3916,25 +3937,25 @@
         <v>31</v>
       </c>
       <c r="C95" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="E95" t="s">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="F95" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
@@ -3942,28 +3963,28 @@
         <v>135</v>
       </c>
       <c r="B96" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C96" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D96" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="E96" t="s">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="F96" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="G96" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
@@ -3974,25 +3995,25 @@
         <v>38</v>
       </c>
       <c r="C97" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D97" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="E97" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F97" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="G97" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
@@ -4003,19 +4024,19 @@
         <v>38</v>
       </c>
       <c r="C98" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="D98" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="E98" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="F98" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="G98" t="s">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
@@ -4032,10 +4053,10 @@
         <v>38</v>
       </c>
       <c r="C99" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="D99" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="E99" t="s">
         <v>23</v>
@@ -4044,13 +4065,13 @@
         <v>143</v>
       </c>
       <c r="G99" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
@@ -4061,25 +4082,25 @@
         <v>38</v>
       </c>
       <c r="C100" t="s">
-        <v>13</v>
+        <v>144</v>
       </c>
       <c r="D100" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E100" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="G100" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
@@ -4090,25 +4111,25 @@
         <v>38</v>
       </c>
       <c r="C101" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="D101" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="E101" t="s">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="F101" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G101" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
@@ -4116,28 +4137,28 @@
         <v>135</v>
       </c>
       <c r="B102" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C102" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D102" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="E102" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="F102" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="G102" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
@@ -4148,25 +4169,25 @@
         <v>44</v>
       </c>
       <c r="C103" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D103" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="E103" t="s">
-        <v>33</v>
+        <v>153</v>
       </c>
       <c r="F103" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="G103" t="s">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
@@ -4177,25 +4198,25 @@
         <v>44</v>
       </c>
       <c r="C104" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="D104" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="E104" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="F104" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="G104" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="H104" t="s">
         <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
@@ -4206,25 +4227,25 @@
         <v>44</v>
       </c>
       <c r="C105" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D105" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E105" t="s">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="F105" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G105" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
@@ -4232,22 +4253,22 @@
         <v>135</v>
       </c>
       <c r="B106" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C106" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="E106" t="s">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="F106" t="s">
-        <v>154</v>
+        <v>16</v>
       </c>
       <c r="G106" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
@@ -4261,22 +4282,22 @@
         <v>135</v>
       </c>
       <c r="B107" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C107" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="D107" t="s">
+        <v>154</v>
+      </c>
+      <c r="E107" t="s">
+        <v>138</v>
+      </c>
+      <c r="F107" t="s">
+        <v>104</v>
+      </c>
+      <c r="G107" t="s">
         <v>155</v>
-      </c>
-      <c r="E107" t="s">
-        <v>23</v>
-      </c>
-      <c r="F107" t="s">
-        <v>16</v>
-      </c>
-      <c r="G107" t="s">
-        <v>25</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
@@ -4293,25 +4314,25 @@
         <v>46</v>
       </c>
       <c r="C108" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="D108" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="E108" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="F108" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="G108" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
@@ -4322,25 +4343,25 @@
         <v>46</v>
       </c>
       <c r="C109" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="D109" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E109" t="s">
         <v>23</v>
       </c>
       <c r="F109" t="s">
-        <v>157</v>
+        <v>16</v>
       </c>
       <c r="G109" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
@@ -4348,51 +4369,51 @@
         <v>135</v>
       </c>
       <c r="B110" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C110" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="D110" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="E110" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="F110" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="G110" t="s">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="H110" t="s">
         <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
+        <v>135</v>
+      </c>
+      <c r="B111" t="s">
+        <v>46</v>
+      </c>
+      <c r="C111" t="s">
+        <v>144</v>
+      </c>
+      <c r="D111" t="s">
+        <v>158</v>
+      </c>
+      <c r="E111" t="s">
+        <v>23</v>
+      </c>
+      <c r="F111" t="s">
         <v>159</v>
       </c>
-      <c r="B111" t="s">
-        <v>20</v>
-      </c>
-      <c r="C111" t="s">
-        <v>21</v>
-      </c>
-      <c r="D111" t="s">
-        <v>22</v>
-      </c>
-      <c r="E111" t="s">
-        <v>27</v>
-      </c>
-      <c r="F111" t="s">
-        <v>16</v>
-      </c>
       <c r="G111" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
@@ -4403,74 +4424,74 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="B112" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C112" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D112" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="E112" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="F112" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="G112" t="s">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="B113" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C113" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="D113" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="E113" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="F113" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="G113" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B114" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C114" t="s">
         <v>21</v>
       </c>
       <c r="D114" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E114" t="s">
         <v>27</v>
@@ -4490,22 +4511,22 @@
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B115" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C115" t="s">
         <v>122</v>
       </c>
       <c r="D115" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="E115" t="s">
         <v>92</v>
       </c>
       <c r="F115" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G115" t="s">
         <v>28</v>
@@ -4519,16 +4540,16 @@
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B116" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C116" t="s">
         <v>21</v>
       </c>
       <c r="D116" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="E116" t="s">
         <v>27</v>
@@ -4548,25 +4569,25 @@
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B117" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C117" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D117" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E117" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="F117" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="G117" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
@@ -4577,25 +4598,25 @@
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B118" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C118" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D118" t="s">
-        <v>45</v>
+        <v>163</v>
       </c>
       <c r="E118" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F118" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="G118" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
@@ -4606,25 +4627,25 @@
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B119" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C119" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D119" t="s">
-        <v>161</v>
+        <v>39</v>
       </c>
       <c r="E119" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="F119" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="G119" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
@@ -4635,25 +4656,25 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B120" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C120" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D120" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E120" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F120" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="G120" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
@@ -4667,22 +4688,22 @@
         <v>162</v>
       </c>
       <c r="B121" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C121" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D121" t="s">
         <v>45</v>
       </c>
       <c r="E121" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="F121" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="G121" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
@@ -4696,22 +4717,22 @@
         <v>162</v>
       </c>
       <c r="B122" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C122" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D122" t="s">
-        <v>22</v>
+        <v>164</v>
       </c>
       <c r="E122" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F122" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="G122" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
@@ -4725,22 +4746,22 @@
         <v>162</v>
       </c>
       <c r="B123" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C123" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D123" t="s">
-        <v>163</v>
+        <v>43</v>
       </c>
       <c r="E123" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="F123" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="G123" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
@@ -4751,25 +4772,25 @@
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B124" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C124" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D124" t="s">
         <v>45</v>
       </c>
       <c r="E124" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F124" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="G124" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
@@ -4780,25 +4801,25 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B125" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C125" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D125" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E125" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F125" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="G125" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
@@ -4809,25 +4830,25 @@
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B126" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C126" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D126" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="E126" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F126" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="G126" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
@@ -4838,25 +4859,25 @@
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B127" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C127" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D127" t="s">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="E127" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="F127" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="G127" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
@@ -4867,25 +4888,25 @@
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B128" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C128" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D128" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E128" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F128" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="G128" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
@@ -4896,16 +4917,16 @@
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B129" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C129" t="s">
         <v>21</v>
       </c>
       <c r="D129" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E129" t="s">
         <v>27</v>
@@ -4925,16 +4946,16 @@
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B130" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C130" t="s">
         <v>122</v>
       </c>
       <c r="D130" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E130" t="s">
         <v>92</v>
@@ -4954,25 +4975,25 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B131" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C131" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D131" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E131" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="F131" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="G131" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
@@ -4983,25 +5004,25 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B132" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C132" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="D132" t="s">
-        <v>166</v>
+        <v>43</v>
       </c>
       <c r="E132" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="F132" t="s">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="G132" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
@@ -5012,22 +5033,22 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B133" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C133" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="D133" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="E133" t="s">
         <v>92</v>
       </c>
       <c r="F133" t="s">
-        <v>167</v>
+        <v>124</v>
       </c>
       <c r="G133" t="s">
         <v>28</v>
@@ -5041,22 +5062,22 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B134" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C134" t="s">
         <v>122</v>
       </c>
       <c r="D134" t="s">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="E134" t="s">
         <v>92</v>
       </c>
       <c r="F134" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="G134" t="s">
         <v>28</v>
@@ -5070,22 +5091,22 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B135" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C135" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D135" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E135" t="s">
         <v>92</v>
       </c>
       <c r="F135" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G135" t="s">
         <v>28</v>
@@ -5099,22 +5120,22 @@
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B136" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C136" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="D136" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="E136" t="s">
         <v>92</v>
       </c>
       <c r="F136" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="G136" t="s">
         <v>28</v>
@@ -5128,22 +5149,22 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B137" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C137" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="D137" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="E137" t="s">
         <v>92</v>
       </c>
       <c r="F137" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="G137" t="s">
         <v>28</v>
@@ -5157,22 +5178,22 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B138" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C138" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="D138" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="E138" t="s">
         <v>92</v>
       </c>
       <c r="F138" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="G138" t="s">
         <v>28</v>
@@ -5186,22 +5207,22 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B139" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C139" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="D139" t="s">
-        <v>170</v>
+        <v>123</v>
       </c>
       <c r="E139" t="s">
         <v>92</v>
       </c>
       <c r="F139" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="G139" t="s">
         <v>28</v>
@@ -5215,22 +5236,22 @@
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B140" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C140" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="D140" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="E140" t="s">
         <v>92</v>
       </c>
       <c r="F140" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="G140" t="s">
         <v>28</v>
@@ -5244,22 +5265,22 @@
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B141" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C141" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="D141" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E141" t="s">
-        <v>173</v>
+        <v>92</v>
       </c>
       <c r="F141" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="G141" t="s">
         <v>28</v>
@@ -5273,22 +5294,22 @@
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B142" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C142" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D142" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="E142" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="F142" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="G142" t="s">
         <v>28</v>
@@ -5302,16 +5323,16 @@
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B143" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C143" t="s">
         <v>122</v>
       </c>
       <c r="D143" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="E143" t="s">
         <v>92</v>
@@ -5331,19 +5352,19 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
+        <v>174</v>
+      </c>
+      <c r="B144" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" t="s">
+        <v>175</v>
+      </c>
+      <c r="D144" t="s">
         <v>171</v>
       </c>
-      <c r="B144" t="s">
-        <v>38</v>
-      </c>
-      <c r="C144" t="s">
-        <v>172</v>
-      </c>
-      <c r="D144" t="s">
-        <v>168</v>
-      </c>
       <c r="E144" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F144" t="s">
         <v>145</v>
@@ -5360,19 +5381,19 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B145" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C145" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D145" t="s">
-        <v>176</v>
+        <v>106</v>
       </c>
       <c r="E145" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F145" t="s">
         <v>89</v>
@@ -5389,16 +5410,16 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B146" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C146" t="s">
         <v>122</v>
       </c>
       <c r="D146" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="E146" t="s">
         <v>92</v>
@@ -5418,22 +5439,22 @@
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
+        <v>174</v>
+      </c>
+      <c r="B147" t="s">
+        <v>38</v>
+      </c>
+      <c r="C147" t="s">
+        <v>175</v>
+      </c>
+      <c r="D147" t="s">
         <v>171</v>
       </c>
-      <c r="B147" t="s">
-        <v>44</v>
-      </c>
-      <c r="C147" t="s">
-        <v>174</v>
-      </c>
-      <c r="D147" t="s">
-        <v>177</v>
-      </c>
       <c r="E147" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F147" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="G147" t="s">
         <v>28</v>
@@ -5447,22 +5468,22 @@
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B148" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C148" t="s">
-        <v>122</v>
+        <v>177</v>
       </c>
       <c r="D148" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="E148" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F148" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="G148" t="s">
         <v>28</v>
@@ -5476,22 +5497,22 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B149" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C149" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="D149" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="E149" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="F149" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="G149" t="s">
         <v>28</v>
@@ -5505,19 +5526,19 @@
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B150" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C150" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D150" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E150" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F150" t="s">
         <v>89</v>
@@ -5534,22 +5555,22 @@
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B151" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C151" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="D151" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="E151" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="F151" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="G151" t="s">
         <v>28</v>
@@ -5563,22 +5584,22 @@
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B152" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C152" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D152" t="s">
         <v>106</v>
       </c>
       <c r="E152" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F152" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G152" t="s">
         <v>28</v>
@@ -5592,22 +5613,22 @@
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B153" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="C153" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D153" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="E153" t="s">
-        <v>47</v>
+        <v>178</v>
       </c>
       <c r="F153" t="s">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="G153" t="s">
         <v>28</v>
@@ -5621,22 +5642,22 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B154" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C154" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="D154" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E154" t="s">
-        <v>92</v>
+        <v>180</v>
       </c>
       <c r="F154" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="G154" t="s">
         <v>28</v>
@@ -5650,22 +5671,22 @@
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B155" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C155" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="D155" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="E155" t="s">
-        <v>92</v>
+        <v>180</v>
       </c>
       <c r="F155" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="G155" t="s">
         <v>28</v>
@@ -5679,22 +5700,22 @@
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B156" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="C156" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="D156" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="E156" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="F156" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="G156" t="s">
         <v>28</v>
@@ -5708,22 +5729,22 @@
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B157" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C157" t="s">
         <v>122</v>
       </c>
       <c r="D157" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="E157" t="s">
         <v>92</v>
       </c>
       <c r="F157" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G157" t="s">
         <v>28</v>
@@ -5737,25 +5758,25 @@
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B158" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C158" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="D158" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="E158" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F158" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="G158" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
@@ -5766,22 +5787,22 @@
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B159" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C159" t="s">
         <v>122</v>
       </c>
       <c r="D159" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="E159" t="s">
         <v>92</v>
       </c>
       <c r="F159" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G159" t="s">
         <v>28</v>
@@ -5795,25 +5816,25 @@
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B160" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C160" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="D160" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="E160" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F160" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="G160" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
@@ -5824,25 +5845,25 @@
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B161" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C161" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D161" t="s">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="E161" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="F161" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G161" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="H161" t="s">
         <v>18</v>
@@ -5853,25 +5874,25 @@
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B162" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C162" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="D162" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E162" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F162" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="G162" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="H162" t="s">
         <v>18</v>
@@ -5882,16 +5903,16 @@
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B163" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C163" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D163" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="E163" t="s">
         <v>27</v>
@@ -5911,25 +5932,25 @@
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B164" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C164" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="D164" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="E164" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F164" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="G164" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="H164" t="s">
         <v>18</v>
@@ -5943,22 +5964,22 @@
         <v>181</v>
       </c>
       <c r="B165" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C165" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D165" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="E165" t="s">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c r="F165" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="G165" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
@@ -5972,22 +5993,22 @@
         <v>181</v>
       </c>
       <c r="B166" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C166" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D166" t="s">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="E166" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="F166" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="G166" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
@@ -6001,22 +6022,22 @@
         <v>181</v>
       </c>
       <c r="B167" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="C167" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D167" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E167" t="s">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c r="F167" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="G167" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="H167" t="s">
         <v>18</v>
@@ -6027,22 +6048,22 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B168" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C168" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D168" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="E168" t="s">
-        <v>63</v>
+        <v>178</v>
       </c>
       <c r="F168" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G168" t="s">
         <v>28</v>
@@ -6056,16 +6077,16 @@
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B169" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C169" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D169" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="E169" t="s">
         <v>63</v>
@@ -6085,19 +6106,19 @@
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B170" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C170" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D170" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="E170" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F170" t="s">
         <v>89</v>
@@ -6114,16 +6135,16 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B171" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C171" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D171" t="s">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="E171" t="s">
         <v>63</v>
@@ -6143,22 +6164,22 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B172" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C172" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D172" t="s">
-        <v>185</v>
+        <v>45</v>
       </c>
       <c r="E172" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="F172" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G172" t="s">
         <v>28</v>
@@ -6172,22 +6193,22 @@
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B173" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C173" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D173" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="E173" t="s">
-        <v>63</v>
+        <v>178</v>
       </c>
       <c r="F173" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G173" t="s">
         <v>28</v>
@@ -6201,22 +6222,22 @@
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B174" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C174" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D174" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="E174" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="F174" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G174" t="s">
         <v>28</v>
@@ -6230,22 +6251,22 @@
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B175" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C175" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D175" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="E175" t="s">
-        <v>63</v>
+        <v>178</v>
       </c>
       <c r="F175" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G175" t="s">
         <v>28</v>
@@ -6259,22 +6280,22 @@
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B176" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C176" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D176" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="E176" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="F176" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G176" t="s">
         <v>28</v>
@@ -6288,22 +6309,22 @@
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B177" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C177" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D177" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E177" t="s">
-        <v>63</v>
+        <v>178</v>
       </c>
       <c r="F177" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G177" t="s">
         <v>28</v>
@@ -6317,22 +6338,22 @@
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B178" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C178" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D178" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="E178" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="F178" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G178" t="s">
         <v>28</v>
@@ -6346,22 +6367,22 @@
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B179" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C179" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D179" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="E179" t="s">
-        <v>63</v>
+        <v>178</v>
       </c>
       <c r="F179" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G179" t="s">
         <v>28</v>
@@ -6375,22 +6396,22 @@
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B180" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C180" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D180" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="E180" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="F180" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G180" t="s">
         <v>28</v>
@@ -6399,6 +6420,93 @@
         <v>18</v>
       </c>
       <c r="I180" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="15">
+      <c r="A181" t="s">
+        <v>183</v>
+      </c>
+      <c r="B181" t="s">
+        <v>49</v>
+      </c>
+      <c r="C181" t="s">
+        <v>177</v>
+      </c>
+      <c r="D181" t="s">
+        <v>157</v>
+      </c>
+      <c r="E181" t="s">
+        <v>178</v>
+      </c>
+      <c r="F181" t="s">
+        <v>89</v>
+      </c>
+      <c r="G181" t="s">
+        <v>28</v>
+      </c>
+      <c r="H181" t="s">
+        <v>18</v>
+      </c>
+      <c r="I181" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="15">
+      <c r="A182" t="s">
+        <v>183</v>
+      </c>
+      <c r="B182" t="s">
+        <v>55</v>
+      </c>
+      <c r="C182" t="s">
+        <v>185</v>
+      </c>
+      <c r="D182" t="s">
+        <v>106</v>
+      </c>
+      <c r="E182" t="s">
+        <v>63</v>
+      </c>
+      <c r="F182" t="s">
+        <v>93</v>
+      </c>
+      <c r="G182" t="s">
+        <v>28</v>
+      </c>
+      <c r="H182" t="s">
+        <v>18</v>
+      </c>
+      <c r="I182" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="15">
+      <c r="A183" t="s">
+        <v>183</v>
+      </c>
+      <c r="B183" t="s">
+        <v>55</v>
+      </c>
+      <c r="C183" t="s">
+        <v>177</v>
+      </c>
+      <c r="D183" t="s">
+        <v>85</v>
+      </c>
+      <c r="E183" t="s">
+        <v>178</v>
+      </c>
+      <c r="F183" t="s">
+        <v>89</v>
+      </c>
+      <c r="G183" t="s">
+        <v>28</v>
+      </c>
+      <c r="H183" t="s">
+        <v>18</v>
+      </c>
+      <c r="I183" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6410,15 +6518,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6a8900d8-3782-4001-9da3-cfb534853d23}">
-  <dimension ref="A1:I8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d569cde3-c7c6-4a19-b502-290fab4762fc}">
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="22.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="42.2857142857143" customWidth="1"/>
-    <col min="5" max="5" width="25.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="26.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="45.5714285714286" customWidth="1"/>
     <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
@@ -6430,16 +6538,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6459,13 +6567,13 @@
         <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E2" t="s">
         <v>27</v>
@@ -6488,19 +6596,19 @@
         <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G3" t="s">
         <v>76</v>
@@ -6517,13 +6625,13 @@
         <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -6546,19 +6654,19 @@
         <v>135</v>
       </c>
       <c r="B5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F5" t="s">
         <v>198</v>
-      </c>
-      <c r="C5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D5" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" t="s">
-        <v>196</v>
       </c>
       <c r="G5" t="s">
         <v>113</v>
@@ -6572,25 +6680,25 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="D6" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>207</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -6601,16 +6709,16 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
@@ -6630,30 +6738,59 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15">
+      <c r="A9" t="s">
         <v>183</v>
       </c>
-      <c r="D8" t="s">
-        <v>191</v>
-      </c>
-      <c r="E8" t="s">
-        <v>202</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="B9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F9" t="s">
         <v>93</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G9" t="s">
         <v>28</v>
       </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6665,8 +6802,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{df5b2c11-046a-496e-8074-d14a98b5a2fa}">
-  <dimension ref="A1:F31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f5ed6959-bd6f-46dd-8e1f-815ee48c626e}">
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6682,13 +6819,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6702,16 +6839,16 @@
         <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C2" t="s">
         <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -6722,13 +6859,13 @@
         <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C3" t="s">
         <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E3" t="s">
         <v>42</v>
@@ -6742,13 +6879,13 @@
         <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E4" t="s">
         <v>80</v>
@@ -6762,13 +6899,13 @@
         <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C5" t="s">
         <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
         <v>90</v>
@@ -6782,16 +6919,16 @@
         <v>118</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E6" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -6802,13 +6939,13 @@
         <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -6822,16 +6959,16 @@
         <v>118</v>
       </c>
       <c r="B8" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C8" t="s">
         <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -6842,16 +6979,16 @@
         <v>135</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E9" t="s">
-        <v>213</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -6862,16 +6999,16 @@
         <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C10" t="s">
         <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E10" t="s">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -6882,16 +7019,16 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
         <v>216</v>
       </c>
       <c r="E11" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -6902,16 +7039,16 @@
         <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="E12" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -6922,16 +7059,16 @@
         <v>135</v>
       </c>
       <c r="B13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E13" t="s">
-        <v>138</v>
+        <v>225</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -6942,16 +7079,16 @@
         <v>135</v>
       </c>
       <c r="B14" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C14" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -6962,16 +7099,16 @@
         <v>135</v>
       </c>
       <c r="B15" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>144</v>
       </c>
       <c r="D15" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -6982,16 +7119,16 @@
         <v>135</v>
       </c>
       <c r="B16" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
         <v>214</v>
       </c>
-      <c r="C16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" t="s">
-        <v>219</v>
-      </c>
       <c r="E16" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -7005,13 +7142,13 @@
         <v>220</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -7022,16 +7159,16 @@
         <v>135</v>
       </c>
       <c r="B18" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C18" t="s">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E18" t="s">
-        <v>223</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -7039,19 +7176,19 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>229</v>
       </c>
       <c r="D19" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>230</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -7059,16 +7196,16 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C20" t="s">
         <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
@@ -7082,7 +7219,7 @@
         <v>162</v>
       </c>
       <c r="B21" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C21" t="s">
         <v>122</v>
@@ -7099,16 +7236,16 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B22" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C22" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
@@ -7119,16 +7256,16 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B23" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="D23" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
@@ -7139,16 +7276,16 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B24" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C24" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
@@ -7159,16 +7296,16 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B25" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C25" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D25" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
@@ -7179,16 +7316,16 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B26" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="D26" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -7199,16 +7336,16 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B27" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C27" t="s">
         <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E27" t="s">
         <v>29</v>
@@ -7219,16 +7356,16 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C28" t="s">
         <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
@@ -7242,13 +7379,13 @@
         <v>181</v>
       </c>
       <c r="B29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C29" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="E29" t="s">
         <v>29</v>
@@ -7259,16 +7396,16 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C30" t="s">
+        <v>177</v>
+      </c>
+      <c r="D30" t="s">
         <v>211</v>
-      </c>
-      <c r="C30" t="s">
-        <v>183</v>
-      </c>
-      <c r="D30" t="s">
-        <v>216</v>
       </c>
       <c r="E30" t="s">
         <v>29</v>
@@ -7279,21 +7416,41 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C31" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" t="s">
+        <v>223</v>
+      </c>
+      <c r="E31" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15">
+      <c r="A32" t="s">
         <v>183</v>
       </c>
-      <c r="D31" t="s">
-        <v>216</v>
-      </c>
-      <c r="E31" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="B32" t="s">
+        <v>231</v>
+      </c>
+      <c r="C32" t="s">
+        <v>185</v>
+      </c>
+      <c r="D32" t="s">
+        <v>223</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -429,7 +429,7 @@
     <s:t>17:25-18:10</s:t>
   </s:si>
   <s:si>
-    <s:t/>
+    <s:t>IND</s:t>
   </s:si>
   <s:si>
     <s:t xml:space="preserve">Matematyka </s:t>
@@ -438,7 +438,7 @@
     <s:t>08:00-08:45</s:t>
   </s:si>
   <s:si>
-    <s:t/>
+    <s:t>IND</s:t>
   </s:si>
   <s:si>
     <s:t>08:50-09:35</s:t>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,12 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<s:sst xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="175">
+<s:sst xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="197">
   <s:si>
     <s:t>Rok szkolny: 2026/2027</s:t>
   </s:si>
   <s:si>
-    <s:t>Okres: 21.09.2026 (pon.) - 27.09.2026 (niedz.)</s:t>
+    <s:t>Okres: 21.09.2026 (pon.) - 30.09.2026 (śr.)</s:t>
   </s:si>
   <s:si>
     <s:t>Dzień</s:t>
@@ -291,6 +291,18 @@
     <s:t>Leńczowska Iwona</s:t>
   </s:si>
   <s:si>
+    <s:t>Mucha Anna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2TH</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Edukacja zdrowotna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>31</s:t>
+  </s:si>
+  <s:si>
     <s:t>Zajęcia z wychowawcą</s:t>
   </s:si>
   <s:si>
@@ -300,6 +312,9 @@
     <s:t>3CB</s:t>
   </s:si>
   <s:si>
+    <s:t>3FB</s:t>
+  </s:si>
+  <s:si>
     <s:t>p. Filipek, przeniesienie na lekcję 5, j. polski sala 30</s:t>
   </s:si>
   <s:si>
@@ -315,9 +330,6 @@
     <s:t>Dalach Krystyna</s:t>
   </s:si>
   <s:si>
-    <s:t>3FB</s:t>
-  </s:si>
-  <s:si>
     <s:t>Biologia</s:t>
   </s:si>
   <s:si>
@@ -327,6 +339,9 @@
     <s:t>Sałdyka Karolina</s:t>
   </s:si>
   <s:si>
+    <s:t>42</s:t>
+  </s:si>
+  <s:si>
     <s:t>Płatek Krzysztof</s:t>
   </s:si>
   <s:si>
@@ -336,6 +351,9 @@
     <s:t>3FB|CH</s:t>
   </s:si>
   <s:si>
+    <s:t>1TFH|t.usfryz</s:t>
+  </s:si>
+  <s:si>
     <s:t>23.09.2026</s:t>
   </s:si>
   <s:si>
@@ -405,9 +423,6 @@
     <s:t>Smirnow-Zechman Eleonora</s:t>
   </s:si>
   <s:si>
-    <s:t>2TH</s:t>
-  </s:si>
-  <s:si>
     <s:t>Biznes i zarządzanie</s:t>
   </s:si>
   <s:si>
@@ -441,6 +456,54 @@
     <s:t>1FB|DZ</s:t>
   </s:si>
   <s:si>
+    <s:t>28.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Mocarski Arkadiusz</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3K|kucharz</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Technologia gastronomiczna z towaroznawstwem</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</s:t>
+  </s:si>
+  <s:si>
+    <s:t>40</s:t>
+  </s:si>
+  <s:si>
+    <s:t>29.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Technika w produkcji gastronomicznej</s:t>
+  </s:si>
+  <s:si>
+    <s:t>30.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2WA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2FA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>26</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1S</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1CB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1FC</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1FA</s:t>
+  </s:si>
+  <s:si>
     <s:t>Godzina</s:t>
   </s:si>
   <s:si>
@@ -504,9 +567,6 @@
     <s:t>11:20-11:25</s:t>
   </s:si>
   <s:si>
-    <s:t>Mucha Anna</s:t>
-  </s:si>
-  <s:si>
     <s:t>13:10-13:15</s:t>
   </s:si>
   <s:si>
@@ -519,10 +579,16 @@
     <s:t>17:20-17:25</s:t>
   </s:si>
   <s:si>
+    <s:t>Misiąg Anna</s:t>
+  </s:si>
+  <s:si>
     <s:t>piętro_1</s:t>
   </s:si>
   <s:si>
     <s:t>Ulanowska Magdalena</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Socha Dariusz</s:t>
   </s:si>
   <s:si>
     <s:t>12:10-12:25</s:t>
@@ -996,7 +1062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{904a7cb9-ae2d-40dd-84ce-ed989fbb1af2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{aa5b084d-c628-44de-a4a8-db75be982c95}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1017,15 +1083,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{00dbf6c6-4421-4ae0-a36f-59e5f7588c74}">
-  <dimension ref="A1:I105"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{507f6b95-31f6-4ad0-87b3-70340dd7ba7b}">
+  <dimension ref="A1:I136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="13.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="31.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="27.8571428571429" customWidth="1"/>
     <col min="8" max="8" width="47.7142857142857" customWidth="1"/>
@@ -1994,28 +2060,28 @@
         <v>81</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D34" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F34" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G34" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
@@ -2026,19 +2092,19 @@
         <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="E35" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="G35" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
@@ -2055,25 +2121,25 @@
         <v>29</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -2081,25 +2147,25 @@
         <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E37" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F37" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="I37" t="s">
         <v>19</v>
@@ -2110,28 +2176,28 @@
         <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="E38" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G38" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
@@ -2139,28 +2205,28 @@
         <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="E39" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F39" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="G39" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="H39" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="I39" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
@@ -2168,22 +2234,22 @@
         <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="E40" t="s">
         <v>98</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
@@ -2197,28 +2263,28 @@
         <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="D41" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="F41" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="G41" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
@@ -2226,19 +2292,19 @@
         <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C42" t="s">
         <v>83</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E42" t="s">
         <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -2255,28 +2321,28 @@
         <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="E43" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="H43" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
@@ -2284,28 +2350,28 @@
         <v>81</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="E44" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F44" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
@@ -2313,22 +2379,22 @@
         <v>81</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D45" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="F45" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="G45" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
@@ -2342,28 +2408,28 @@
         <v>81</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D46" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E46" t="s">
         <v>75</v>
       </c>
       <c r="F46" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G46" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
@@ -2371,25 +2437,25 @@
         <v>81</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="E47" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="H47" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
@@ -2397,74 +2463,74 @@
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B48" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D48" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="F48" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B49" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C49" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="E49" t="s">
+        <v>75</v>
+      </c>
+      <c r="F49" t="s">
+        <v>100</v>
+      </c>
+      <c r="G49" t="s">
         <v>106</v>
       </c>
-      <c r="F49" t="s">
-        <v>107</v>
-      </c>
-      <c r="G49" t="s">
-        <v>27</v>
-      </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C50" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E50" t="s">
         <v>75</v>
@@ -2473,7 +2539,7 @@
         <v>76</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
@@ -2484,25 +2550,25 @@
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="D51" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="E51" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="F51" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="G51" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
@@ -2513,16 +2579,16 @@
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D52" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E52" t="s">
         <v>75</v>
@@ -2531,7 +2597,7 @@
         <v>76</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
@@ -2542,25 +2608,25 @@
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="D53" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="E53" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F53" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="G53" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
@@ -2571,22 +2637,22 @@
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B54" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C54" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D54" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E54" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F54" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s">
         <v>27</v>
@@ -2600,22 +2666,22 @@
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B55" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C55" t="s">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="D55" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="E55" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="F55" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="G55" t="s">
         <v>27</v>
@@ -2629,16 +2695,16 @@
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
         <v>83</v>
       </c>
       <c r="D56" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E56" t="s">
         <v>75</v>
@@ -2658,22 +2724,22 @@
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="E57" t="s">
         <v>45</v>
       </c>
       <c r="F57" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="G57" t="s">
         <v>27</v>
@@ -2687,22 +2753,22 @@
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C58" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="D58" t="s">
         <v>111</v>
       </c>
       <c r="E58" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F58" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s">
         <v>27</v>
@@ -2716,22 +2782,22 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C59" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="E59" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F59" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="G59" t="s">
         <v>27</v>
@@ -2745,13 +2811,13 @@
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D60" t="s">
         <v>114</v>
@@ -2760,7 +2826,7 @@
         <v>45</v>
       </c>
       <c r="F60" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -2774,22 +2840,22 @@
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B61" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C61" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E61" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F61" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -2803,22 +2869,22 @@
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="D62" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E62" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F62" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -2832,22 +2898,22 @@
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C63" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="D63" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E63" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F63" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="G63" t="s">
         <v>27</v>
@@ -2861,22 +2927,22 @@
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B64" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C64" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="D64" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E64" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="F64" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="G64" t="s">
         <v>27</v>
@@ -2890,22 +2956,22 @@
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B65" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="D65" t="s">
         <v>118</v>
       </c>
       <c r="E65" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F65" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s">
         <v>27</v>
@@ -2919,22 +2985,22 @@
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B66" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C66" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E66" t="s">
         <v>45</v>
       </c>
       <c r="F66" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -2948,22 +3014,22 @@
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B67" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C67" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D67" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="E67" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="F67" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>27</v>
@@ -2977,22 +3043,22 @@
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B68" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C68" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E68" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="F68" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="G68" t="s">
         <v>27</v>
@@ -3006,22 +3072,22 @@
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B69" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C69" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="D69" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E69" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F69" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="G69" t="s">
         <v>27</v>
@@ -3035,22 +3101,22 @@
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C70" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="D70" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E70" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F70" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="G70" t="s">
         <v>27</v>
@@ -3064,22 +3130,22 @@
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B71" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C71" t="s">
         <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E71" t="s">
         <v>45</v>
       </c>
       <c r="F71" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="G71" t="s">
         <v>27</v>
@@ -3093,22 +3159,22 @@
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C72" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="D72" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E72" t="s">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="F72" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G72" t="s">
         <v>27</v>
@@ -3122,22 +3188,22 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B73" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C73" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="D73" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="E73" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F73" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="G73" t="s">
         <v>27</v>
@@ -3151,22 +3217,22 @@
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B74" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C74" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" t="s">
         <v>126</v>
       </c>
-      <c r="D74" t="s">
-        <v>127</v>
-      </c>
       <c r="E74" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="F74" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G74" t="s">
         <v>27</v>
@@ -3180,22 +3246,22 @@
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C75" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D75" t="s">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="E75" t="s">
         <v>45</v>
       </c>
       <c r="F75" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="G75" t="s">
         <v>27</v>
@@ -3209,22 +3275,22 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B76" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C76" t="s">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E76" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="F76" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G76" t="s">
         <v>27</v>
@@ -3238,22 +3304,22 @@
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B77" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C77" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D77" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E77" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F77" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="G77" t="s">
         <v>27</v>
@@ -3267,22 +3333,22 @@
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B78" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D78" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E78" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F78" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G78" t="s">
         <v>27</v>
@@ -3296,22 +3362,22 @@
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C79" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="D79" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E79" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F79" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="G79" t="s">
         <v>27</v>
@@ -3325,22 +3391,22 @@
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B80" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C80" t="s">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="D80" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="E80" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="F80" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="G80" t="s">
         <v>27</v>
@@ -3354,22 +3420,22 @@
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B81" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C81" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="D81" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="E81" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="F81" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="G81" t="s">
         <v>27</v>
@@ -3383,22 +3449,22 @@
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B82" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C82" t="s">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="D82" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E82" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F82" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G82" t="s">
         <v>27</v>
@@ -3412,22 +3478,22 @@
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B83" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="D83" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E83" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F83" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="G83" t="s">
         <v>27</v>
@@ -3441,22 +3507,22 @@
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B84" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C84" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D84" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E84" t="s">
         <v>133</v>
       </c>
       <c r="F84" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="G84" t="s">
         <v>27</v>
@@ -3470,22 +3536,22 @@
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C85" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="D85" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E85" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="F85" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="G85" t="s">
         <v>27</v>
@@ -3499,22 +3565,22 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B86" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C86" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E86" t="s">
         <v>75</v>
       </c>
       <c r="F86" t="s">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s">
         <v>27</v>
@@ -3528,22 +3594,22 @@
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B87" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C87" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D87" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E87" t="s">
         <v>133</v>
       </c>
       <c r="F87" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="G87" t="s">
         <v>27</v>
@@ -3557,22 +3623,22 @@
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B88" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C88" t="s">
         <v>83</v>
       </c>
       <c r="D88" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E88" t="s">
         <v>75</v>
       </c>
       <c r="F88" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G88" t="s">
         <v>27</v>
@@ -3586,22 +3652,22 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C89" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="D89" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E89" t="s">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="F89" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="G89" t="s">
         <v>27</v>
@@ -3615,22 +3681,22 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C90" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D90" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="E90" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="F90" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G90" t="s">
         <v>27</v>
@@ -3644,22 +3710,22 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B91" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="C91" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="D91" t="s">
         <v>136</v>
       </c>
       <c r="E91" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="F91" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G91" t="s">
         <v>27</v>
@@ -3673,22 +3739,22 @@
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B92" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C92" t="s">
         <v>83</v>
       </c>
       <c r="D92" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E92" t="s">
         <v>75</v>
       </c>
       <c r="F92" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="G92" t="s">
         <v>27</v>
@@ -3702,22 +3768,22 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="D93" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E93" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="F93" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="G93" t="s">
         <v>27</v>
@@ -3731,22 +3797,22 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B94" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C94" t="s">
         <v>83</v>
       </c>
       <c r="D94" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E94" t="s">
         <v>75</v>
       </c>
       <c r="F94" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="G94" t="s">
         <v>27</v>
@@ -3760,22 +3826,22 @@
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B95" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="D95" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="E95" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="F95" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="G95" t="s">
         <v>27</v>
@@ -3789,22 +3855,22 @@
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B96" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="C96" t="s">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="D96" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="E96" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F96" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="G96" t="s">
         <v>27</v>
@@ -3818,22 +3884,22 @@
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B97" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="D97" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="E97" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F97" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="G97" t="s">
         <v>27</v>
@@ -3847,16 +3913,16 @@
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B98" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C98" t="s">
         <v>83</v>
       </c>
       <c r="D98" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E98" t="s">
         <v>75</v>
@@ -3876,16 +3942,16 @@
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B99" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C99" t="s">
         <v>21</v>
       </c>
       <c r="D99" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="E99" t="s">
         <v>45</v>
@@ -3905,16 +3971,16 @@
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B100" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="C100" t="s">
         <v>83</v>
       </c>
       <c r="D100" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E100" t="s">
         <v>75</v>
@@ -3934,16 +4000,16 @@
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B101" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="C101" t="s">
         <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="E101" t="s">
         <v>45</v>
@@ -3963,16 +4029,16 @@
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B102" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C102" t="s">
         <v>83</v>
       </c>
       <c r="D102" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E102" t="s">
         <v>75</v>
@@ -3992,16 +4058,16 @@
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B103" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C103" t="s">
         <v>21</v>
       </c>
       <c r="D103" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="E103" t="s">
         <v>45</v>
@@ -4021,16 +4087,16 @@
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B104" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="C104" t="s">
         <v>83</v>
       </c>
       <c r="D104" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E104" t="s">
         <v>75</v>
@@ -4050,30 +4116,929 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
+        <v>140</v>
+      </c>
+      <c r="B105" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" t="s">
         <v>135</v>
       </c>
-      <c r="B105" t="s">
+      <c r="E105" t="s">
+        <v>45</v>
+      </c>
+      <c r="F105" t="s">
+        <v>46</v>
+      </c>
+      <c r="G105" t="s">
+        <v>27</v>
+      </c>
+      <c r="H105" t="s">
+        <v>18</v>
+      </c>
+      <c r="I105" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15">
+      <c r="A106" t="s">
+        <v>140</v>
+      </c>
+      <c r="B106" t="s">
+        <v>48</v>
+      </c>
+      <c r="C106" t="s">
+        <v>83</v>
+      </c>
+      <c r="D106" t="s">
+        <v>142</v>
+      </c>
+      <c r="E106" t="s">
+        <v>75</v>
+      </c>
+      <c r="F106" t="s">
+        <v>85</v>
+      </c>
+      <c r="G106" t="s">
+        <v>27</v>
+      </c>
+      <c r="H106" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15">
+      <c r="A107" t="s">
+        <v>140</v>
+      </c>
+      <c r="B107" t="s">
+        <v>48</v>
+      </c>
+      <c r="C107" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" t="s">
+        <v>126</v>
+      </c>
+      <c r="E107" t="s">
+        <v>45</v>
+      </c>
+      <c r="F107" t="s">
+        <v>46</v>
+      </c>
+      <c r="G107" t="s">
+        <v>27</v>
+      </c>
+      <c r="H107" t="s">
+        <v>18</v>
+      </c>
+      <c r="I107" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15">
+      <c r="A108" t="s">
+        <v>140</v>
+      </c>
+      <c r="B108" t="s">
+        <v>58</v>
+      </c>
+      <c r="C108" t="s">
+        <v>83</v>
+      </c>
+      <c r="D108" t="s">
+        <v>143</v>
+      </c>
+      <c r="E108" t="s">
+        <v>75</v>
+      </c>
+      <c r="F108" t="s">
+        <v>85</v>
+      </c>
+      <c r="G108" t="s">
+        <v>27</v>
+      </c>
+      <c r="H108" t="s">
+        <v>18</v>
+      </c>
+      <c r="I108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15">
+      <c r="A109" t="s">
+        <v>140</v>
+      </c>
+      <c r="B109" t="s">
+        <v>58</v>
+      </c>
+      <c r="C109" t="s">
+        <v>21</v>
+      </c>
+      <c r="D109" t="s">
+        <v>44</v>
+      </c>
+      <c r="E109" t="s">
+        <v>45</v>
+      </c>
+      <c r="F109" t="s">
+        <v>46</v>
+      </c>
+      <c r="G109" t="s">
+        <v>27</v>
+      </c>
+      <c r="H109" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15">
+      <c r="A110" t="s">
+        <v>140</v>
+      </c>
+      <c r="B110" t="s">
+        <v>64</v>
+      </c>
+      <c r="C110" t="s">
+        <v>83</v>
+      </c>
+      <c r="D110" t="s">
+        <v>143</v>
+      </c>
+      <c r="E110" t="s">
+        <v>75</v>
+      </c>
+      <c r="F110" t="s">
+        <v>85</v>
+      </c>
+      <c r="G110" t="s">
+        <v>27</v>
+      </c>
+      <c r="H110" t="s">
+        <v>18</v>
+      </c>
+      <c r="I110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="15">
+      <c r="A111" t="s">
+        <v>140</v>
+      </c>
+      <c r="B111" t="s">
         <v>71</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C111" t="s">
         <v>83</v>
       </c>
-      <c r="D105" t="s">
-        <v>138</v>
-      </c>
-      <c r="E105" t="s">
+      <c r="D111" t="s">
+        <v>143</v>
+      </c>
+      <c r="E111" t="s">
         <v>75</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F111" t="s">
         <v>85</v>
       </c>
-      <c r="G105" t="s">
-        <v>27</v>
-      </c>
-      <c r="H105" t="s">
-        <v>18</v>
-      </c>
-      <c r="I105" t="s">
+      <c r="G111" t="s">
+        <v>27</v>
+      </c>
+      <c r="H111" t="s">
+        <v>18</v>
+      </c>
+      <c r="I111" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="15">
+      <c r="A112" t="s">
+        <v>144</v>
+      </c>
+      <c r="B112" t="s">
+        <v>82</v>
+      </c>
+      <c r="C112" t="s">
+        <v>145</v>
+      </c>
+      <c r="D112" t="s">
+        <v>146</v>
+      </c>
+      <c r="E112" t="s">
+        <v>147</v>
+      </c>
+      <c r="F112" t="s">
+        <v>52</v>
+      </c>
+      <c r="G112" t="s">
+        <v>27</v>
+      </c>
+      <c r="H112" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15">
+      <c r="A113" t="s">
+        <v>144</v>
+      </c>
+      <c r="B113" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" t="s">
+        <v>145</v>
+      </c>
+      <c r="D113" t="s">
+        <v>146</v>
+      </c>
+      <c r="E113" t="s">
+        <v>147</v>
+      </c>
+      <c r="F113" t="s">
+        <v>52</v>
+      </c>
+      <c r="G113" t="s">
+        <v>27</v>
+      </c>
+      <c r="H113" t="s">
+        <v>18</v>
+      </c>
+      <c r="I113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="15">
+      <c r="A114" t="s">
+        <v>144</v>
+      </c>
+      <c r="B114" t="s">
+        <v>29</v>
+      </c>
+      <c r="C114" t="s">
+        <v>145</v>
+      </c>
+      <c r="D114" t="s">
+        <v>65</v>
+      </c>
+      <c r="E114" t="s">
+        <v>148</v>
+      </c>
+      <c r="F114" t="s">
+        <v>149</v>
+      </c>
+      <c r="G114" t="s">
+        <v>27</v>
+      </c>
+      <c r="H114" t="s">
+        <v>18</v>
+      </c>
+      <c r="I114" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="15">
+      <c r="A115" t="s">
+        <v>144</v>
+      </c>
+      <c r="B115" t="s">
+        <v>37</v>
+      </c>
+      <c r="C115" t="s">
+        <v>145</v>
+      </c>
+      <c r="D115" t="s">
+        <v>65</v>
+      </c>
+      <c r="E115" t="s">
+        <v>148</v>
+      </c>
+      <c r="F115" t="s">
+        <v>149</v>
+      </c>
+      <c r="G115" t="s">
+        <v>27</v>
+      </c>
+      <c r="H115" t="s">
+        <v>18</v>
+      </c>
+      <c r="I115" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15">
+      <c r="A116" t="s">
+        <v>150</v>
+      </c>
+      <c r="B116" t="s">
+        <v>37</v>
+      </c>
+      <c r="C116" t="s">
+        <v>145</v>
+      </c>
+      <c r="D116" t="s">
+        <v>146</v>
+      </c>
+      <c r="E116" t="s">
+        <v>151</v>
+      </c>
+      <c r="F116" t="s">
+        <v>61</v>
+      </c>
+      <c r="G116" t="s">
+        <v>27</v>
+      </c>
+      <c r="H116" t="s">
+        <v>18</v>
+      </c>
+      <c r="I116" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15">
+      <c r="A117" t="s">
+        <v>152</v>
+      </c>
+      <c r="B117" t="s">
+        <v>82</v>
+      </c>
+      <c r="C117" t="s">
+        <v>132</v>
+      </c>
+      <c r="D117" t="s">
+        <v>80</v>
+      </c>
+      <c r="E117" t="s">
+        <v>133</v>
+      </c>
+      <c r="F117" t="s">
+        <v>94</v>
+      </c>
+      <c r="G117" t="s">
+        <v>27</v>
+      </c>
+      <c r="H117" t="s">
+        <v>18</v>
+      </c>
+      <c r="I117" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="15">
+      <c r="A118" t="s">
+        <v>152</v>
+      </c>
+      <c r="B118" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" t="s">
+        <v>30</v>
+      </c>
+      <c r="D118" t="s">
+        <v>153</v>
+      </c>
+      <c r="E118" t="s">
+        <v>32</v>
+      </c>
+      <c r="F118" t="s">
+        <v>33</v>
+      </c>
+      <c r="G118" t="s">
+        <v>27</v>
+      </c>
+      <c r="H118" t="s">
+        <v>18</v>
+      </c>
+      <c r="I118" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="15">
+      <c r="A119" t="s">
+        <v>152</v>
+      </c>
+      <c r="B119" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" t="s">
+        <v>89</v>
+      </c>
+      <c r="D119" t="s">
+        <v>154</v>
+      </c>
+      <c r="E119" t="s">
+        <v>102</v>
+      </c>
+      <c r="F119" t="s">
+        <v>155</v>
+      </c>
+      <c r="G119" t="s">
+        <v>27</v>
+      </c>
+      <c r="H119" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="15">
+      <c r="A120" t="s">
+        <v>152</v>
+      </c>
+      <c r="B120" t="s">
+        <v>12</v>
+      </c>
+      <c r="C120" t="s">
+        <v>132</v>
+      </c>
+      <c r="D120" t="s">
+        <v>54</v>
+      </c>
+      <c r="E120" t="s">
+        <v>133</v>
+      </c>
+      <c r="F120" t="s">
+        <v>94</v>
+      </c>
+      <c r="G120" t="s">
+        <v>27</v>
+      </c>
+      <c r="H120" t="s">
+        <v>18</v>
+      </c>
+      <c r="I120" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="15">
+      <c r="A121" t="s">
+        <v>152</v>
+      </c>
+      <c r="B121" t="s">
+        <v>20</v>
+      </c>
+      <c r="C121" t="s">
+        <v>30</v>
+      </c>
+      <c r="D121" t="s">
+        <v>156</v>
+      </c>
+      <c r="E121" t="s">
+        <v>32</v>
+      </c>
+      <c r="F121" t="s">
+        <v>33</v>
+      </c>
+      <c r="G121" t="s">
+        <v>27</v>
+      </c>
+      <c r="H121" t="s">
+        <v>18</v>
+      </c>
+      <c r="I121" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15">
+      <c r="A122" t="s">
+        <v>152</v>
+      </c>
+      <c r="B122" t="s">
+        <v>20</v>
+      </c>
+      <c r="C122" t="s">
+        <v>89</v>
+      </c>
+      <c r="D122" t="s">
+        <v>154</v>
+      </c>
+      <c r="E122" t="s">
+        <v>91</v>
+      </c>
+      <c r="F122" t="s">
+        <v>155</v>
+      </c>
+      <c r="G122" t="s">
+        <v>27</v>
+      </c>
+      <c r="H122" t="s">
+        <v>18</v>
+      </c>
+      <c r="I122" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15">
+      <c r="A123" t="s">
+        <v>152</v>
+      </c>
+      <c r="B123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C123" t="s">
+        <v>30</v>
+      </c>
+      <c r="D123" t="s">
+        <v>54</v>
+      </c>
+      <c r="E123" t="s">
+        <v>32</v>
+      </c>
+      <c r="F123" t="s">
+        <v>33</v>
+      </c>
+      <c r="G123" t="s">
+        <v>27</v>
+      </c>
+      <c r="H123" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15">
+      <c r="A124" t="s">
+        <v>152</v>
+      </c>
+      <c r="B124" t="s">
+        <v>29</v>
+      </c>
+      <c r="C124" t="s">
+        <v>132</v>
+      </c>
+      <c r="D124" t="s">
+        <v>157</v>
+      </c>
+      <c r="E124" t="s">
+        <v>133</v>
+      </c>
+      <c r="F124" t="s">
+        <v>94</v>
+      </c>
+      <c r="G124" t="s">
+        <v>27</v>
+      </c>
+      <c r="H124" t="s">
+        <v>18</v>
+      </c>
+      <c r="I124" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15">
+      <c r="A125" t="s">
+        <v>152</v>
+      </c>
+      <c r="B125" t="s">
+        <v>37</v>
+      </c>
+      <c r="C125" t="s">
+        <v>30</v>
+      </c>
+      <c r="D125" t="s">
+        <v>54</v>
+      </c>
+      <c r="E125" t="s">
+        <v>32</v>
+      </c>
+      <c r="F125" t="s">
+        <v>33</v>
+      </c>
+      <c r="G125" t="s">
+        <v>27</v>
+      </c>
+      <c r="H125" t="s">
+        <v>18</v>
+      </c>
+      <c r="I125" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="15">
+      <c r="A126" t="s">
+        <v>152</v>
+      </c>
+      <c r="B126" t="s">
+        <v>37</v>
+      </c>
+      <c r="C126" t="s">
+        <v>89</v>
+      </c>
+      <c r="D126" t="s">
+        <v>154</v>
+      </c>
+      <c r="E126" t="s">
+        <v>98</v>
+      </c>
+      <c r="F126" t="s">
+        <v>155</v>
+      </c>
+      <c r="G126" t="s">
+        <v>27</v>
+      </c>
+      <c r="H126" t="s">
+        <v>18</v>
+      </c>
+      <c r="I126" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="15">
+      <c r="A127" t="s">
+        <v>152</v>
+      </c>
+      <c r="B127" t="s">
+        <v>37</v>
+      </c>
+      <c r="C127" t="s">
+        <v>132</v>
+      </c>
+      <c r="D127" t="s">
+        <v>158</v>
+      </c>
+      <c r="E127" t="s">
+        <v>133</v>
+      </c>
+      <c r="F127" t="s">
+        <v>94</v>
+      </c>
+      <c r="G127" t="s">
+        <v>27</v>
+      </c>
+      <c r="H127" t="s">
+        <v>18</v>
+      </c>
+      <c r="I127" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="15">
+      <c r="A128" t="s">
+        <v>152</v>
+      </c>
+      <c r="B128" t="s">
+        <v>48</v>
+      </c>
+      <c r="C128" t="s">
+        <v>30</v>
+      </c>
+      <c r="D128" t="s">
+        <v>31</v>
+      </c>
+      <c r="E128" t="s">
+        <v>32</v>
+      </c>
+      <c r="F128" t="s">
+        <v>33</v>
+      </c>
+      <c r="G128" t="s">
+        <v>27</v>
+      </c>
+      <c r="H128" t="s">
+        <v>18</v>
+      </c>
+      <c r="I128" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="15">
+      <c r="A129" t="s">
+        <v>152</v>
+      </c>
+      <c r="B129" t="s">
+        <v>48</v>
+      </c>
+      <c r="C129" t="s">
+        <v>132</v>
+      </c>
+      <c r="D129" t="s">
+        <v>156</v>
+      </c>
+      <c r="E129" t="s">
+        <v>133</v>
+      </c>
+      <c r="F129" t="s">
+        <v>94</v>
+      </c>
+      <c r="G129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H129" t="s">
+        <v>18</v>
+      </c>
+      <c r="I129" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="15">
+      <c r="A130" t="s">
+        <v>152</v>
+      </c>
+      <c r="B130" t="s">
+        <v>58</v>
+      </c>
+      <c r="C130" t="s">
+        <v>30</v>
+      </c>
+      <c r="D130" t="s">
+        <v>65</v>
+      </c>
+      <c r="E130" t="s">
+        <v>32</v>
+      </c>
+      <c r="F130" t="s">
+        <v>33</v>
+      </c>
+      <c r="G130" t="s">
+        <v>27</v>
+      </c>
+      <c r="H130" t="s">
+        <v>18</v>
+      </c>
+      <c r="I130" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="15">
+      <c r="A131" t="s">
+        <v>152</v>
+      </c>
+      <c r="B131" t="s">
+        <v>58</v>
+      </c>
+      <c r="C131" t="s">
+        <v>89</v>
+      </c>
+      <c r="D131" t="s">
+        <v>90</v>
+      </c>
+      <c r="E131" t="s">
+        <v>102</v>
+      </c>
+      <c r="F131" t="s">
+        <v>61</v>
+      </c>
+      <c r="G131" t="s">
+        <v>27</v>
+      </c>
+      <c r="H131" t="s">
+        <v>18</v>
+      </c>
+      <c r="I131" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="15">
+      <c r="A132" t="s">
+        <v>152</v>
+      </c>
+      <c r="B132" t="s">
+        <v>58</v>
+      </c>
+      <c r="C132" t="s">
+        <v>132</v>
+      </c>
+      <c r="D132" t="s">
+        <v>134</v>
+      </c>
+      <c r="E132" t="s">
+        <v>133</v>
+      </c>
+      <c r="F132" t="s">
+        <v>94</v>
+      </c>
+      <c r="G132" t="s">
+        <v>27</v>
+      </c>
+      <c r="H132" t="s">
+        <v>18</v>
+      </c>
+      <c r="I132" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="15">
+      <c r="A133" t="s">
+        <v>152</v>
+      </c>
+      <c r="B133" t="s">
+        <v>64</v>
+      </c>
+      <c r="C133" t="s">
+        <v>30</v>
+      </c>
+      <c r="D133" t="s">
+        <v>90</v>
+      </c>
+      <c r="E133" t="s">
+        <v>32</v>
+      </c>
+      <c r="F133" t="s">
+        <v>33</v>
+      </c>
+      <c r="G133" t="s">
+        <v>27</v>
+      </c>
+      <c r="H133" t="s">
+        <v>18</v>
+      </c>
+      <c r="I133" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="15">
+      <c r="A134" t="s">
+        <v>152</v>
+      </c>
+      <c r="B134" t="s">
+        <v>64</v>
+      </c>
+      <c r="C134" t="s">
+        <v>132</v>
+      </c>
+      <c r="D134" t="s">
+        <v>159</v>
+      </c>
+      <c r="E134" t="s">
+        <v>133</v>
+      </c>
+      <c r="F134" t="s">
+        <v>94</v>
+      </c>
+      <c r="G134" t="s">
+        <v>27</v>
+      </c>
+      <c r="H134" t="s">
+        <v>18</v>
+      </c>
+      <c r="I134" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="15">
+      <c r="A135" t="s">
+        <v>152</v>
+      </c>
+      <c r="B135" t="s">
+        <v>71</v>
+      </c>
+      <c r="C135" t="s">
+        <v>30</v>
+      </c>
+      <c r="D135" t="s">
+        <v>90</v>
+      </c>
+      <c r="E135" t="s">
+        <v>32</v>
+      </c>
+      <c r="F135" t="s">
+        <v>33</v>
+      </c>
+      <c r="G135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H135" t="s">
+        <v>18</v>
+      </c>
+      <c r="I135" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="15">
+      <c r="A136" t="s">
+        <v>152</v>
+      </c>
+      <c r="B136" t="s">
+        <v>71</v>
+      </c>
+      <c r="C136" t="s">
+        <v>132</v>
+      </c>
+      <c r="D136" t="s">
+        <v>121</v>
+      </c>
+      <c r="E136" t="s">
+        <v>133</v>
+      </c>
+      <c r="F136" t="s">
+        <v>94</v>
+      </c>
+      <c r="G136" t="s">
+        <v>27</v>
+      </c>
+      <c r="H136" t="s">
+        <v>18</v>
+      </c>
+      <c r="I136" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4085,8 +5050,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f55de81d-8224-4b09-9cd2-fdb89088f006}">
-  <dimension ref="A1:I5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{9c7efcd2-950a-4cd6-a80c-f2b3ee7897fd}">
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -4105,16 +5070,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -4134,16 +5099,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s">
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F2" t="s">
         <v>33</v>
@@ -4163,13 +5128,13 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -4192,13 +5157,13 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -4218,19 +5183,19 @@
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -4242,6 +5207,35 @@
         <v>18</v>
       </c>
       <c r="I5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15">
+      <c r="A6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4253,13 +5247,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{41415fc1-4f52-4973-89d6-47e97f5e744d}">
-  <dimension ref="A1:F23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{3dd2ae8a-becc-4195-997c-53455cc8ebf1}">
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
@@ -4270,13 +5264,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -4290,16 +5284,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -4310,16 +5304,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -4330,16 +5324,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="E4" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -4350,16 +5344,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="E5" t="s">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -4370,16 +5364,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -4390,13 +5384,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
         <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
@@ -4410,13 +5404,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -4430,16 +5424,16 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -4450,16 +5444,16 @@
         <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C10" t="s">
         <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -4470,16 +5464,16 @@
         <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -4490,16 +5484,16 @@
         <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="E12" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -4507,19 +5501,19 @@
     </row>
     <row r="13" spans="1:6" ht="15">
       <c r="A13" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -4527,19 +5521,19 @@
     </row>
     <row r="14" spans="1:6" ht="15">
       <c r="A14" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -4547,16 +5541,16 @@
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="C15" t="s">
         <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -4567,16 +5561,16 @@
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B16" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
@@ -4587,16 +5581,16 @@
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B17" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
@@ -4607,16 +5601,16 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
@@ -4627,16 +5621,16 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" t="s">
         <v>174</v>
-      </c>
-      <c r="C19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" t="s">
-        <v>168</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -4647,16 +5641,16 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -4667,16 +5661,16 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B21" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C21" t="s">
         <v>83</v>
       </c>
       <c r="D21" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -4687,16 +5681,16 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B22" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -4707,21 +5701,141 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="C23" t="s">
         <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
       </c>
       <c r="F23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15">
+      <c r="A24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15">
+      <c r="A25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15">
+      <c r="A26" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15">
+      <c r="A27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" t="s">
+        <v>186</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15">
+      <c r="A28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" t="s">
+        <v>193</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15">
+      <c r="A29" t="s">
+        <v>152</v>
+      </c>
+      <c r="B29" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -580,7 +580,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>-</t>
@@ -623,7 +622,6 @@
           <t>Wrzeszcz Barbara</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -713,7 +711,6 @@
           <t>Filipiak Wiesław</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -756,7 +753,6 @@
           <t>Wrzeszcz Barbara</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -799,7 +795,6 @@
           <t>Wrzeszcz Barbara</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -842,7 +837,6 @@
           <t>Filipiak Wiesław</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -885,7 +879,6 @@
           <t>Kaczorowski Waldemar</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -928,7 +921,6 @@
           <t>Granatowska Mariola</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -971,7 +963,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1014,7 +1005,6 @@
           <t>Nowak Magdalena</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1057,7 +1047,6 @@
           <t>Wrzeszcz Barbara</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -1100,7 +1089,6 @@
           <t>Galert Anna</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1143,7 +1131,6 @@
           <t>Wojciechowski Łukasz</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -1186,7 +1173,6 @@
           <t>Filipek Anna</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1229,7 +1215,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1272,7 +1257,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>-</t>
@@ -1315,7 +1299,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>-</t>
@@ -1358,7 +1341,6 @@
           <t>Zając Ewa</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -1401,7 +1383,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>-</t>
@@ -1444,7 +1425,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1487,7 +1467,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>-</t>
@@ -1530,7 +1509,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>-</t>
@@ -1573,7 +1551,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1616,7 +1593,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>-</t>
@@ -1659,7 +1635,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>-</t>
@@ -1702,7 +1677,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1745,7 +1719,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1788,7 +1761,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1831,7 +1803,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1874,7 +1845,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>-</t>
@@ -1917,7 +1887,6 @@
           <t>Leńczowska Iwona</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1960,7 +1929,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>-</t>
@@ -2003,7 +1971,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2046,7 +2013,6 @@
           <t>Wojciechowski Łukasz</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2089,7 +2055,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>-</t>
@@ -2132,7 +2097,6 @@
           <t>Zając Ewa</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2222,7 +2186,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2265,7 +2228,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>-</t>
@@ -2308,7 +2270,6 @@
           <t>Dalach Krystyna</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2351,7 +2312,6 @@
           <t>Sałdyka Karolina</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2394,7 +2354,6 @@
           <t>Zając Ewa</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -2437,7 +2396,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>-</t>
@@ -2480,7 +2438,6 @@
           <t>Płatek Krzysztof</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2570,7 +2527,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2613,7 +2569,6 @@
           <t>Płatek Krzysztof</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2656,7 +2611,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>-</t>
@@ -2699,7 +2653,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>-</t>
@@ -2742,7 +2695,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>-</t>
@@ -2785,7 +2737,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>-</t>
@@ -2828,7 +2779,6 @@
           <t>Dalach Krystyna</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2871,7 +2821,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>-</t>
@@ -2914,7 +2863,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>-</t>
@@ -2957,7 +2905,6 @@
           <t>Dalach Krystyna</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3000,7 +2947,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>-</t>
@@ -3043,7 +2989,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>-</t>
@@ -3086,7 +3031,6 @@
           <t>Dalach Krystyna</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3176,7 +3120,6 @@
           <t>Wrzeszcz Barbara</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -3219,7 +3162,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>-</t>
@@ -3262,7 +3204,6 @@
           <t>Marzec Renata</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3305,7 +3246,6 @@
           <t>Dalach Krystyna</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3348,7 +3288,6 @@
           <t>Wojciechowski Łukasz</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3391,7 +3330,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>-</t>
@@ -3434,7 +3372,6 @@
           <t>Marzec Renata</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3477,7 +3414,6 @@
           <t>Nestoruk Lidia</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3520,7 +3456,6 @@
           <t>Marzec Renata</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3563,7 +3498,6 @@
           <t>Kruk Marcin</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3593,23 +3527,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Język polski</t>
+          <t>Zajęcia biblioteczne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>bib</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ulanowska Magdalena</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Wrzeszcz Barbara</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Dodatkowo płatne</t>
+          <t>Bezpłatne</t>
         </is>
       </c>
     </row>
@@ -3639,13 +3572,11 @@
           <t>Język polski</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>-</t>
@@ -3688,7 +3619,6 @@
           <t>Krzemińska Beata</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3731,7 +3661,6 @@
           <t>Nestoruk Lidia</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3774,7 +3703,6 @@
           <t>Marzec Renata</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3817,7 +3745,6 @@
           <t>Mucha Anna</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3860,7 +3787,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>-</t>
@@ -3903,7 +3829,6 @@
           <t>Galert Anna</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3946,7 +3871,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>-</t>
@@ -3989,7 +3913,6 @@
           <t>Misiąg Anna</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -4032,7 +3955,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>-</t>
@@ -4075,7 +3997,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>-</t>
@@ -4118,7 +4039,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>-</t>
@@ -4161,7 +4081,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>-</t>
@@ -4204,7 +4123,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>-</t>
@@ -4247,7 +4165,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>-</t>
@@ -4290,7 +4207,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>-</t>
@@ -4333,7 +4249,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>-</t>
@@ -4376,7 +4291,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>-</t>
@@ -4419,7 +4333,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>-</t>
@@ -4462,7 +4375,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>-</t>
@@ -4505,7 +4417,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>-</t>
@@ -4548,7 +4459,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>-</t>
@@ -4591,7 +4501,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>-</t>
@@ -4634,7 +4543,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>-</t>
@@ -4677,7 +4585,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>-</t>
@@ -4720,7 +4627,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>-</t>
@@ -4763,7 +4669,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>-</t>
@@ -4806,7 +4711,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>-</t>
@@ -4849,7 +4753,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>-</t>
@@ -4892,7 +4795,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>-</t>
@@ -4935,7 +4837,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>-</t>
@@ -4978,7 +4879,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>-</t>
@@ -5021,7 +4921,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>-</t>
@@ -5064,7 +4963,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>-</t>
@@ -5107,7 +5005,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>-</t>
@@ -5150,7 +5047,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>-</t>
@@ -5193,7 +5089,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>-</t>
@@ -5236,7 +5131,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>-</t>
@@ -5279,7 +5173,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>-</t>
@@ -5322,7 +5215,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>-</t>
@@ -5365,7 +5257,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>-</t>
@@ -5408,7 +5299,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>-</t>
@@ -5451,7 +5341,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>-</t>
@@ -5494,7 +5383,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>-</t>
@@ -5537,7 +5425,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>-</t>
@@ -5580,7 +5467,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>-</t>
@@ -5623,7 +5509,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>-</t>
@@ -5666,7 +5551,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>-</t>
@@ -5709,7 +5593,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>-</t>
@@ -5752,7 +5635,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>-</t>
@@ -5795,7 +5677,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>-</t>
@@ -5838,7 +5719,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>-</t>
@@ -5881,7 +5761,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>-</t>
@@ -5924,7 +5803,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>-</t>
@@ -5967,7 +5845,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>-</t>
@@ -6010,7 +5887,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>-</t>
@@ -6053,7 +5929,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>-</t>
@@ -6096,7 +5971,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>-</t>
@@ -6139,7 +6013,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>-</t>
@@ -6182,7 +6055,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>-</t>
@@ -6225,7 +6097,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>-</t>
@@ -6268,7 +6139,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>-</t>
@@ -6311,7 +6181,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>-</t>
@@ -6354,7 +6223,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>-</t>
@@ -6397,7 +6265,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>-</t>
@@ -6440,7 +6307,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>-</t>
@@ -6483,7 +6349,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>-</t>
@@ -6526,7 +6391,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>-</t>
@@ -6569,7 +6433,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>-</t>
@@ -6612,7 +6475,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>-</t>
@@ -6655,7 +6517,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>-</t>
@@ -6698,7 +6559,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>-</t>
@@ -6741,7 +6601,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>-</t>
@@ -6784,7 +6643,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>-</t>
@@ -6827,7 +6685,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>-</t>
@@ -6870,7 +6727,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>-</t>
@@ -6987,7 +6843,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>-</t>
@@ -7030,7 +6885,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>-</t>
@@ -7073,7 +6927,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>-</t>
@@ -7106,13 +6959,11 @@
           <t>język polski</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>-</t>
@@ -7155,7 +7006,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>-</t>
@@ -7244,7 +7094,6 @@
           <t>Ostrowska Ewa</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -7272,7 +7121,6 @@
           <t>Kosin Anna</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -7300,7 +7148,6 @@
           <t>Małecka Barbara</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -7328,7 +7175,6 @@
           <t>Mucha Anna</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -7356,7 +7202,6 @@
           <t>Skarupa Agnieszka</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -7384,7 +7229,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -7412,7 +7256,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -7440,7 +7283,6 @@
           <t>Misiąg Anna</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -7468,7 +7310,6 @@
           <t>Ulanowska Magdalena</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -7496,7 +7337,6 @@
           <t>Socha Dariusz</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -7524,7 +7364,6 @@
           <t>Cieśla Marcin</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -7552,7 +7391,6 @@
           <t>Małecka Barbara</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -7580,7 +7418,6 @@
           <t>Kruk Marcin</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -7608,7 +7445,6 @@
           <t>Krycia Ewelina</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -7636,7 +7472,6 @@
           <t>Danielewski Paweł</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -7664,7 +7499,6 @@
           <t>Skarupa Agnieszka</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -7692,7 +7526,6 @@
           <t>Zaleska Magdalena</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -7720,7 +7553,6 @@
           <t>Krzemińska Beata</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -7748,7 +7580,6 @@
           <t>Płatek Krzysztof</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -7776,7 +7607,6 @@
           <t>Smirnow-Zechman Eleonora</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -7804,7 +7634,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -7832,7 +7661,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -7860,7 +7688,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
@@ -7888,7 +7715,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
@@ -7916,7 +7742,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -7944,7 +7769,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
@@ -7972,7 +7796,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -8000,7 +7823,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
@@ -8028,7 +7850,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
@@ -8056,7 +7877,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8084,7 +7904,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8112,7 +7931,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8140,7 +7958,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8168,7 +7985,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<s:sst xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3182" uniqueCount="294">
+<s:sst xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3620" uniqueCount="304">
   <s:si>
     <s:t>Rok szkolny: 2026/2027</s:t>
   </s:si>
@@ -525,108 +525,117 @@
     <s:t>Techniki fryzjerskie</s:t>
   </s:si>
   <s:si>
+    <s:t>Danielewski Paweł</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Rozwój kompetencji zawodowych - życie jako rozwój osobisty</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Sobczak Anna</s:t>
+  </s:si>
+  <s:si>
+    <s:t>25.09.2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3TFB|DZ</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2FB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Rozwój kompetencji zawodowych - fryzjerstwo wellness</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Jaworska Edyta</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2TFB|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</s:t>
+  </s:si>
+  <s:si>
+    <s:t>6</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Marketing w działalności handlowej</s:t>
+  </s:si>
+  <s:si>
+    <s:t>17</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2S</s:t>
+  </s:si>
+  <s:si>
+    <s:t>5TFB|DZ</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Fizyka</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Biczysko Wojciech</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1TFH</s:t>
+  </s:si>
+  <s:si>
+    <s:t>22</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2FC</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1TFB|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>szkolenie Eramsus+ - delegacja na szkolenie</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1S</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Organizacja sprzedaży</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1CB</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Taszycka Magdalena</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1WA</s:t>
+  </s:si>
+  <s:si>
+    <s:t>28</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1FB|DZ</s:t>
+  </s:si>
+  <s:si>
+    <s:t>5TH</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2TFB|gr1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1CB|gr1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>prf2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Kopij Marcin</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Edukacja obywatelska</s:t>
+  </s:si>
+  <s:si>
     <s:t>4</s:t>
   </s:si>
   <s:si>
-    <s:t>Danielewski Paweł</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Rozwój kompetencji zawodowych - życie jako rozwój osobisty</s:t>
-  </s:si>
-  <s:si>
-    <s:t>3</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Sobczak Anna</s:t>
-  </s:si>
-  <s:si>
-    <s:t>25.09.2026</s:t>
-  </s:si>
-  <s:si>
-    <s:t>3TFB|DZ</s:t>
-  </s:si>
-  <s:si>
-    <s:t>2FB</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Rozwój kompetencji zawodowych - fryzjerstwo wellness</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Jaworska Edyta</s:t>
-  </s:si>
-  <s:si>
-    <s:t>2TFB|gr2</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</s:t>
-  </s:si>
-  <s:si>
-    <s:t>6</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Marketing w działalności handlowej</s:t>
-  </s:si>
-  <s:si>
-    <s:t>17</s:t>
-  </s:si>
-  <s:si>
-    <s:t>2S</s:t>
-  </s:si>
-  <s:si>
-    <s:t>5TFB|DZ</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Fizyka</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Biczysko Wojciech</s:t>
-  </s:si>
-  <s:si>
-    <s:t>1TFH</s:t>
-  </s:si>
-  <s:si>
-    <s:t>2FC</s:t>
-  </s:si>
-  <s:si>
-    <s:t>1S</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Organizacja sprzedaży</s:t>
-  </s:si>
-  <s:si>
-    <s:t>1CB</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Taszycka Magdalena</s:t>
-  </s:si>
-  <s:si>
-    <s:t>1WA</s:t>
-  </s:si>
-  <s:si>
-    <s:t>28</s:t>
-  </s:si>
-  <s:si>
-    <s:t>1FB|DZ</s:t>
-  </s:si>
-  <s:si>
-    <s:t>5TH</s:t>
-  </s:si>
-  <s:si>
-    <s:t>2TFB|gr1</s:t>
-  </s:si>
-  <s:si>
-    <s:t>1CB|gr1</s:t>
-  </s:si>
-  <s:si>
-    <s:t>prf2</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Kopij Marcin</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Edukacja obywatelska</s:t>
-  </s:si>
-  <s:si>
     <s:t>Projektowanie fryzur</s:t>
   </s:si>
   <s:si>
@@ -654,9 +663,6 @@
     <s:t>Geografia</s:t>
   </s:si>
   <s:si>
-    <s:t>22</s:t>
-  </s:si>
-  <s:si>
     <s:t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</s:t>
   </s:si>
   <s:si>
@@ -765,18 +771,39 @@
     <s:t>28.09.2026</s:t>
   </s:si>
   <s:si>
+    <s:t>prF3</s:t>
+  </s:si>
+  <s:si>
     <s:t>Mocarski Arkadiusz</s:t>
   </s:si>
   <s:si>
     <s:t>3K|kucharz</s:t>
   </s:si>
   <s:si>
+    <s:t>2TFB|DZ</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Rejno Julita</s:t>
+  </s:si>
+  <s:si>
+    <s:t>zajęcia profilaktyczne - sala gimnastyczna</s:t>
+  </s:si>
+  <s:si>
     <s:t>3K</s:t>
   </s:si>
   <s:si>
+    <s:t>2TFA|gr2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>4TFB|DZ</s:t>
+  </s:si>
+  <s:si>
     <s:t>2CA</s:t>
   </s:si>
   <s:si>
+    <s:t>2FA</s:t>
+  </s:si>
+  <s:si>
     <s:t>29.09.2026</s:t>
   </s:si>
   <s:si>
@@ -789,7 +816,13 @@
     <s:t>30.09.2026</s:t>
   </s:si>
   <s:si>
-    <s:t>2FA</s:t>
+    <s:t>3TFB|t.hand.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Cieśla Marcin</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1TFB|CH</s:t>
   </s:si>
   <s:si>
     <s:t>Fiodorów Małgorzata</s:t>
@@ -798,7 +831,7 @@
     <s:t>1WB|gr1</s:t>
   </s:si>
   <s:si>
-    <s:t>1TFB|gr2</s:t>
+    <s:t>2WA|ch2</s:t>
   </s:si>
   <s:si>
     <s:t>1WB|gr2</s:t>
@@ -880,9 +913,6 @@
   </s:si>
   <s:si>
     <s:t>boisko - dziedziniec wejściowy/boisko</s:t>
-  </s:si>
-  <s:si>
-    <s:t>Cieśla Marcin</s:t>
   </s:si>
   <s:si>
     <s:t>07:55-08:00</s:t>
@@ -1353,7 +1383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4935c8d1-3a09-4ca2-9ba8-f35c0d751752}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{59a580c9-d433-42f3-88c2-9bd9c4297c3c}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1374,8 +1404,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{be2c640a-d21f-4323-a4ac-942114b2f450}">
-  <dimension ref="A1:I316"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{efa6cfce-6c77-4b82-9b78-5816adbbbc29}">
+  <dimension ref="A1:I358"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1384,7 +1414,7 @@
     <col min="4" max="4" width="13.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
-    <col min="7" max="7" width="27.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
     <col min="8" max="8" width="47.7142857142857" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
@@ -4248,10 +4278,10 @@
         <v>166</v>
       </c>
       <c r="F99" t="s">
+        <v>33</v>
+      </c>
+      <c r="G99" t="s">
         <v>167</v>
-      </c>
-      <c r="G99" t="s">
-        <v>168</v>
       </c>
       <c r="H99" t="s">
         <v>151</v>
@@ -4274,13 +4304,13 @@
         <v>150</v>
       </c>
       <c r="E100" t="s">
+        <v>168</v>
+      </c>
+      <c r="F100" t="s">
         <v>169</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>170</v>
-      </c>
-      <c r="G100" t="s">
-        <v>171</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
@@ -4364,10 +4394,10 @@
         <v>166</v>
       </c>
       <c r="F103" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103" t="s">
         <v>167</v>
-      </c>
-      <c r="G103" t="s">
-        <v>168</v>
       </c>
       <c r="H103" t="s">
         <v>151</v>
@@ -4465,7 +4495,7 @@
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B107" t="s">
         <v>82</v>
@@ -4474,7 +4504,7 @@
         <v>83</v>
       </c>
       <c r="D107" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E107" t="s">
         <v>75</v>
@@ -4494,7 +4524,7 @@
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B108" t="s">
         <v>82</v>
@@ -4503,13 +4533,13 @@
         <v>164</v>
       </c>
       <c r="D108" t="s">
+        <v>173</v>
+      </c>
+      <c r="E108" t="s">
         <v>174</v>
       </c>
-      <c r="E108" t="s">
-        <v>175</v>
-      </c>
       <c r="F108" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G108" t="s">
         <v>17</v>
@@ -4523,25 +4553,25 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B109" t="s">
         <v>82</v>
       </c>
       <c r="C109" t="s">
+        <v>175</v>
+      </c>
+      <c r="D109" t="s">
         <v>176</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>177</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>178</v>
       </c>
-      <c r="F109" t="s">
-        <v>179</v>
-      </c>
       <c r="G109" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H109" t="s">
         <v>151</v>
@@ -4552,7 +4582,7 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B110" t="s">
         <v>82</v>
@@ -4581,7 +4611,7 @@
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B111" t="s">
         <v>82</v>
@@ -4610,7 +4640,7 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B112" t="s">
         <v>12</v>
@@ -4619,7 +4649,7 @@
         <v>83</v>
       </c>
       <c r="D112" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E112" t="s">
         <v>75</v>
@@ -4639,7 +4669,7 @@
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B113" t="s">
         <v>12</v>
@@ -4668,25 +4698,25 @@
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B114" t="s">
         <v>12</v>
       </c>
       <c r="C114" t="s">
+        <v>175</v>
+      </c>
+      <c r="D114" t="s">
         <v>176</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>177</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>178</v>
       </c>
-      <c r="F114" t="s">
-        <v>179</v>
-      </c>
       <c r="G114" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H114" t="s">
         <v>151</v>
@@ -4697,7 +4727,7 @@
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B115" t="s">
         <v>12</v>
@@ -4709,7 +4739,7 @@
         <v>72</v>
       </c>
       <c r="E115" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F115" t="s">
         <v>163</v>
@@ -4726,7 +4756,7 @@
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B116" t="s">
         <v>12</v>
@@ -4755,7 +4785,7 @@
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B117" t="s">
         <v>20</v>
@@ -4764,7 +4794,7 @@
         <v>83</v>
       </c>
       <c r="D117" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E117" t="s">
         <v>75</v>
@@ -4784,7 +4814,7 @@
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B118" t="s">
         <v>20</v>
@@ -4799,7 +4829,7 @@
         <v>75</v>
       </c>
       <c r="F118" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G118" t="s">
         <v>125</v>
@@ -4813,25 +4843,25 @@
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B119" t="s">
         <v>20</v>
       </c>
       <c r="C119" t="s">
+        <v>175</v>
+      </c>
+      <c r="D119" t="s">
         <v>176</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>177</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>178</v>
       </c>
-      <c r="F119" t="s">
-        <v>179</v>
-      </c>
       <c r="G119" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H119" t="s">
         <v>151</v>
@@ -4842,7 +4872,7 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B120" t="s">
         <v>20</v>
@@ -4854,7 +4884,7 @@
         <v>72</v>
       </c>
       <c r="E120" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F120" t="s">
         <v>163</v>
@@ -4871,7 +4901,7 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B121" t="s">
         <v>20</v>
@@ -4880,7 +4910,7 @@
         <v>53</v>
       </c>
       <c r="D121" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E121" t="s">
         <v>32</v>
@@ -4900,7 +4930,7 @@
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B122" t="s">
         <v>20</v>
@@ -4929,7 +4959,7 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B123" t="s">
         <v>29</v>
@@ -4938,7 +4968,7 @@
         <v>83</v>
       </c>
       <c r="D123" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E123" t="s">
         <v>75</v>
@@ -4958,7 +4988,7 @@
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B124" t="s">
         <v>29</v>
@@ -4987,25 +5017,25 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B125" t="s">
         <v>29</v>
       </c>
       <c r="C125" t="s">
+        <v>175</v>
+      </c>
+      <c r="D125" t="s">
         <v>176</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>177</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>178</v>
       </c>
-      <c r="F125" t="s">
-        <v>179</v>
-      </c>
       <c r="G125" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H125" t="s">
         <v>151</v>
@@ -5016,7 +5046,7 @@
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B126" t="s">
         <v>29</v>
@@ -5028,13 +5058,13 @@
         <v>72</v>
       </c>
       <c r="E126" t="s">
+        <v>183</v>
+      </c>
+      <c r="F126" t="s">
+        <v>180</v>
+      </c>
+      <c r="G126" t="s">
         <v>184</v>
-      </c>
-      <c r="F126" t="s">
-        <v>181</v>
-      </c>
-      <c r="G126" t="s">
-        <v>185</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
@@ -5045,7 +5075,7 @@
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B127" t="s">
         <v>29</v>
@@ -5054,27 +5084,27 @@
         <v>53</v>
       </c>
       <c r="D127" t="s">
+        <v>185</v>
+      </c>
+      <c r="E127" t="s">
+        <v>40</v>
+      </c>
+      <c r="F127" t="s">
         <v>186</v>
       </c>
-      <c r="E127" t="s">
-        <v>23</v>
-      </c>
-      <c r="F127" t="s">
-        <v>24</v>
-      </c>
       <c r="G127" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B128" t="s">
         <v>29</v>
@@ -5103,7 +5133,7 @@
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B129" t="s">
         <v>37</v>
@@ -5112,7 +5142,7 @@
         <v>83</v>
       </c>
       <c r="D129" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E129" t="s">
         <v>75</v>
@@ -5132,7 +5162,7 @@
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B130" t="s">
         <v>37</v>
@@ -5161,7 +5191,7 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B131" t="s">
         <v>37</v>
@@ -5190,170 +5220,170 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B132" t="s">
         <v>37</v>
       </c>
       <c r="C132" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="D132" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E132" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="F132" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G132" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H132" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="I132" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B133" t="s">
         <v>37</v>
       </c>
       <c r="C133" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D133" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E133" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="F133" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G133" t="s">
-        <v>168</v>
+        <v>66</v>
       </c>
       <c r="H133" t="s">
         <v>151</v>
       </c>
       <c r="I133" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B134" t="s">
         <v>37</v>
       </c>
       <c r="C134" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D134" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E134" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F134" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="G134" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="H134" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
       <c r="I134" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B135" t="s">
         <v>37</v>
       </c>
       <c r="C135" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="D135" t="s">
         <v>190</v>
       </c>
       <c r="E135" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="F135" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="G135" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H135" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B136" t="s">
         <v>37</v>
       </c>
       <c r="C136" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="D136" t="s">
-        <v>65</v>
+        <v>192</v>
       </c>
       <c r="E136" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="F136" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G136" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H136" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
       <c r="I136" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B137" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C137" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="E137" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="F137" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="G137" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
@@ -5364,144 +5394,144 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B138" t="s">
         <v>48</v>
       </c>
       <c r="C138" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="D138" t="s">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="E138" t="s">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="F138" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="G138" t="s">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B139" t="s">
         <v>48</v>
       </c>
       <c r="C139" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D139" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="E139" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="F139" t="s">
-        <v>181</v>
+        <v>113</v>
       </c>
       <c r="G139" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="H139" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B140" t="s">
         <v>48</v>
       </c>
       <c r="C140" t="s">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="D140" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="E140" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="F140" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G140" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="H140" t="s">
         <v>151</v>
       </c>
       <c r="I140" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B141" t="s">
         <v>48</v>
       </c>
       <c r="C141" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="D141" t="s">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="E141" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="F141" t="s">
-        <v>179</v>
+        <v>56</v>
       </c>
       <c r="G141" t="s">
-        <v>168</v>
+        <v>66</v>
       </c>
       <c r="H141" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="I141" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B142" t="s">
         <v>48</v>
       </c>
       <c r="C142" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D142" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E142" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="F142" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G142" t="s">
         <v>66</v>
       </c>
       <c r="H142" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
       <c r="I142" t="s">
         <v>19</v>
@@ -5509,51 +5539,51 @@
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B143" t="s">
         <v>48</v>
       </c>
       <c r="C143" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="D143" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E143" t="s">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="F143" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G143" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="H143" t="s">
         <v>151</v>
       </c>
       <c r="I143" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B144" t="s">
         <v>48</v>
       </c>
       <c r="C144" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="D144" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E144" t="s">
-        <v>32</v>
+        <v>191</v>
       </c>
       <c r="F144" t="s">
-        <v>52</v>
+        <v>163</v>
       </c>
       <c r="G144" t="s">
         <v>66</v>
@@ -5567,28 +5597,28 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B145" t="s">
         <v>48</v>
       </c>
       <c r="C145" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="D145" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="E145" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F145" t="s">
-        <v>33</v>
+        <v>195</v>
       </c>
       <c r="G145" t="s">
         <v>66</v>
       </c>
       <c r="H145" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
       <c r="I145" t="s">
         <v>19</v>
@@ -5596,22 +5626,22 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B146" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C146" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="D146" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E146" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="F146" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="G146" t="s">
         <v>66</v>
@@ -5625,22 +5655,22 @@
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C147" t="s">
-        <v>185</v>
+        <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="E147" t="s">
-        <v>184</v>
+        <v>93</v>
       </c>
       <c r="F147" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="G147" t="s">
         <v>66</v>
@@ -5654,22 +5684,22 @@
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B148" t="s">
         <v>58</v>
       </c>
       <c r="C148" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="D148" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="E148" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F148" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="G148" t="s">
         <v>66</v>
@@ -5683,22 +5713,22 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B149" t="s">
         <v>58</v>
       </c>
       <c r="C149" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="D149" t="s">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="E149" t="s">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="F149" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="G149" t="s">
         <v>66</v>
@@ -5712,22 +5742,22 @@
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B150" t="s">
         <v>58</v>
       </c>
       <c r="C150" t="s">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="D150" t="s">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="E150" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="F150" t="s">
-        <v>179</v>
+        <v>46</v>
       </c>
       <c r="G150" t="s">
         <v>66</v>
@@ -5741,22 +5771,22 @@
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B151" t="s">
         <v>58</v>
       </c>
       <c r="C151" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D151" t="s">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="E151" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F151" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="G151" t="s">
         <v>66</v>
@@ -5770,22 +5800,22 @@
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B152" t="s">
         <v>58</v>
       </c>
       <c r="C152" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="D152" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E152" t="s">
-        <v>45</v>
+        <v>177</v>
       </c>
       <c r="F152" t="s">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="G152" t="s">
         <v>66</v>
@@ -5799,22 +5829,22 @@
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B153" t="s">
         <v>58</v>
       </c>
       <c r="C153" t="s">
-        <v>154</v>
+        <v>62</v>
       </c>
       <c r="D153" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="E153" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="F153" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="G153" t="s">
         <v>66</v>
@@ -5828,22 +5858,22 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B154" t="s">
         <v>58</v>
       </c>
       <c r="C154" t="s">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="D154" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="E154" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="F154" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="G154" t="s">
         <v>66</v>
@@ -5857,22 +5887,22 @@
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B155" t="s">
         <v>58</v>
       </c>
       <c r="C155" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="D155" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E155" t="s">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="F155" t="s">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="G155" t="s">
         <v>66</v>
@@ -5886,22 +5916,22 @@
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B156" t="s">
         <v>58</v>
       </c>
       <c r="C156" t="s">
-        <v>42</v>
+        <v>164</v>
       </c>
       <c r="D156" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E156" t="s">
-        <v>40</v>
+        <v>166</v>
       </c>
       <c r="F156" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G156" t="s">
         <v>66</v>
@@ -5915,22 +5945,22 @@
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B157" t="s">
         <v>58</v>
       </c>
       <c r="C157" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D157" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E157" t="s">
+        <v>177</v>
+      </c>
+      <c r="F157" t="s">
         <v>200</v>
-      </c>
-      <c r="F157" t="s">
-        <v>167</v>
       </c>
       <c r="G157" t="s">
         <v>66</v>
@@ -5944,22 +5974,22 @@
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B158" t="s">
         <v>58</v>
       </c>
       <c r="C158" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="D158" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="E158" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F158" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="G158" t="s">
         <v>66</v>
@@ -5973,22 +6003,22 @@
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B159" t="s">
         <v>58</v>
       </c>
       <c r="C159" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="D159" t="s">
-        <v>120</v>
+        <v>181</v>
       </c>
       <c r="E159" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F159" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="G159" t="s">
         <v>66</v>
@@ -6002,22 +6032,22 @@
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B160" t="s">
         <v>58</v>
       </c>
       <c r="C160" t="s">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="D160" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
       <c r="E160" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F160" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="G160" t="s">
         <v>66</v>
@@ -6031,22 +6061,22 @@
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B161" t="s">
         <v>58</v>
       </c>
       <c r="C161" t="s">
-        <v>203</v>
+        <v>132</v>
       </c>
       <c r="D161" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E161" t="s">
-        <v>112</v>
+        <v>204</v>
       </c>
       <c r="F161" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G161" t="s">
         <v>66</v>
@@ -6060,22 +6090,22 @@
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B162" t="s">
         <v>58</v>
       </c>
       <c r="C162" t="s">
-        <v>89</v>
+        <v>205</v>
       </c>
       <c r="D162" t="s">
-        <v>187</v>
+        <v>31</v>
       </c>
       <c r="E162" t="s">
         <v>102</v>
       </c>
       <c r="F162" t="s">
-        <v>193</v>
+        <v>103</v>
       </c>
       <c r="G162" t="s">
         <v>66</v>
@@ -6089,22 +6119,22 @@
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B163" t="s">
         <v>58</v>
       </c>
       <c r="C163" t="s">
-        <v>125</v>
+        <v>206</v>
       </c>
       <c r="D163" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E163" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F163" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="G163" t="s">
         <v>66</v>
@@ -6118,22 +6148,22 @@
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B164" t="s">
         <v>58</v>
       </c>
       <c r="C164" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="D164" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="E164" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="F164" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="G164" t="s">
         <v>66</v>
@@ -6147,22 +6177,22 @@
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B165" t="s">
         <v>58</v>
       </c>
       <c r="C165" t="s">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="D165" t="s">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="E165" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F165" t="s">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="G165" t="s">
         <v>66</v>
@@ -6176,22 +6206,22 @@
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B166" t="s">
         <v>58</v>
       </c>
       <c r="C166" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="D166" t="s">
-        <v>96</v>
+        <v>207</v>
       </c>
       <c r="E166" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F166" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G166" t="s">
         <v>66</v>
@@ -6205,22 +6235,22 @@
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B167" t="s">
         <v>58</v>
       </c>
       <c r="C167" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="D167" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E167" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="F167" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G167" t="s">
         <v>66</v>
@@ -6234,22 +6264,22 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B168" t="s">
         <v>58</v>
       </c>
       <c r="C168" t="s">
-        <v>207</v>
+        <v>119</v>
       </c>
       <c r="D168" t="s">
-        <v>208</v>
+        <v>96</v>
       </c>
       <c r="E168" t="s">
-        <v>209</v>
+        <v>15</v>
       </c>
       <c r="F168" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="G168" t="s">
         <v>66</v>
@@ -6263,22 +6293,22 @@
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B169" t="s">
         <v>58</v>
       </c>
       <c r="C169" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="D169" t="s">
-        <v>63</v>
+        <v>209</v>
       </c>
       <c r="E169" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="F169" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="G169" t="s">
         <v>66</v>
@@ -6292,22 +6322,22 @@
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B170" t="s">
         <v>58</v>
       </c>
       <c r="C170" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="D170" t="s">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="E170" t="s">
-        <v>166</v>
+        <v>212</v>
       </c>
       <c r="F170" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G170" t="s">
         <v>66</v>
@@ -6321,22 +6351,22 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B171" t="s">
         <v>58</v>
       </c>
       <c r="C171" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="D171" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="E171" t="s">
-        <v>211</v>
+        <v>148</v>
       </c>
       <c r="F171" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="G171" t="s">
         <v>66</v>
@@ -6350,22 +6380,22 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B172" t="s">
         <v>58</v>
       </c>
       <c r="C172" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="D172" t="s">
-        <v>213</v>
+        <v>80</v>
       </c>
       <c r="E172" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="F172" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="G172" t="s">
         <v>66</v>
@@ -6379,22 +6409,22 @@
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B173" t="s">
         <v>58</v>
       </c>
       <c r="C173" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="D173" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="E173" t="s">
+        <v>213</v>
+      </c>
+      <c r="F173" t="s">
         <v>214</v>
-      </c>
-      <c r="F173" t="s">
-        <v>105</v>
       </c>
       <c r="G173" t="s">
         <v>66</v>
@@ -6408,22 +6438,22 @@
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B174" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C174" t="s">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="D174" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="E174" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F174" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="G174" t="s">
         <v>66</v>
@@ -6437,22 +6467,22 @@
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B175" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C175" t="s">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="D175" t="s">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="E175" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="F175" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G175" t="s">
         <v>66</v>
@@ -6466,22 +6496,22 @@
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B176" t="s">
         <v>64</v>
       </c>
       <c r="C176" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="D176" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E176" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F176" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="G176" t="s">
         <v>66</v>
@@ -6495,22 +6525,22 @@
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B177" t="s">
         <v>64</v>
       </c>
       <c r="C177" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D177" t="s">
-        <v>120</v>
+        <v>194</v>
       </c>
       <c r="E177" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="F177" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G177" t="s">
         <v>66</v>
@@ -6524,22 +6554,22 @@
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B178" t="s">
         <v>64</v>
       </c>
       <c r="C178" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D178" t="s">
-        <v>68</v>
+        <v>197</v>
       </c>
       <c r="E178" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F178" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G178" t="s">
         <v>66</v>
@@ -6553,22 +6583,22 @@
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B179" t="s">
         <v>64</v>
       </c>
       <c r="C179" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="D179" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E179" t="s">
         <v>93</v>
       </c>
       <c r="F179" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="G179" t="s">
         <v>66</v>
@@ -6582,22 +6612,22 @@
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B180" t="s">
         <v>64</v>
       </c>
       <c r="C180" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D180" t="s">
-        <v>215</v>
+        <v>68</v>
       </c>
       <c r="E180" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F180" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="G180" t="s">
         <v>66</v>
@@ -6611,22 +6641,22 @@
     </row>
     <row r="181" spans="1:9" ht="15">
       <c r="A181" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B181" t="s">
         <v>64</v>
       </c>
       <c r="C181" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D181" t="s">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="E181" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="F181" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G181" t="s">
         <v>66</v>
@@ -6640,22 +6670,22 @@
     </row>
     <row r="182" spans="1:9" ht="15">
       <c r="A182" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B182" t="s">
         <v>64</v>
       </c>
       <c r="C182" t="s">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="D182" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="E182" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="F182" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="G182" t="s">
         <v>66</v>
@@ -6669,22 +6699,22 @@
     </row>
     <row r="183" spans="1:9" ht="15">
       <c r="A183" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B183" t="s">
         <v>64</v>
       </c>
       <c r="C183" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D183" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="E183" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F183" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="G183" t="s">
         <v>66</v>
@@ -6698,22 +6728,22 @@
     </row>
     <row r="184" spans="1:9" ht="15">
       <c r="A184" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B184" t="s">
         <v>64</v>
       </c>
       <c r="C184" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="D184" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E184" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="F184" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="G184" t="s">
         <v>66</v>
@@ -6727,22 +6757,22 @@
     </row>
     <row r="185" spans="1:9" ht="15">
       <c r="A185" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B185" t="s">
         <v>64</v>
       </c>
       <c r="C185" t="s">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="D185" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="E185" t="s">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="F185" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="G185" t="s">
         <v>66</v>
@@ -6756,22 +6786,22 @@
     </row>
     <row r="186" spans="1:9" ht="15">
       <c r="A186" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B186" t="s">
         <v>64</v>
       </c>
       <c r="C186" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D186" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E186" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F186" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="G186" t="s">
         <v>66</v>
@@ -6785,22 +6815,22 @@
     </row>
     <row r="187" spans="1:9" ht="15">
       <c r="A187" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B187" t="s">
         <v>64</v>
       </c>
       <c r="C187" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="D187" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="E187" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="F187" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="G187" t="s">
         <v>66</v>
@@ -6814,22 +6844,22 @@
     </row>
     <row r="188" spans="1:9" ht="15">
       <c r="A188" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B188" t="s">
         <v>64</v>
       </c>
       <c r="C188" t="s">
-        <v>125</v>
+        <v>206</v>
       </c>
       <c r="D188" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E188" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F188" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="G188" t="s">
         <v>66</v>
@@ -6843,22 +6873,22 @@
     </row>
     <row r="189" spans="1:9" ht="15">
       <c r="A189" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B189" t="s">
         <v>64</v>
       </c>
       <c r="C189" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="D189" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="E189" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="F189" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="G189" t="s">
         <v>66</v>
@@ -6872,22 +6902,22 @@
     </row>
     <row r="190" spans="1:9" ht="15">
       <c r="A190" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B190" t="s">
         <v>64</v>
       </c>
       <c r="C190" t="s">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="D190" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="E190" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F190" t="s">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="G190" t="s">
         <v>66</v>
@@ -6901,22 +6931,22 @@
     </row>
     <row r="191" spans="1:9" ht="15">
       <c r="A191" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B191" t="s">
         <v>64</v>
       </c>
       <c r="C191" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="D191" t="s">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="E191" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F191" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G191" t="s">
         <v>66</v>
@@ -6930,22 +6960,22 @@
     </row>
     <row r="192" spans="1:9" ht="15">
       <c r="A192" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B192" t="s">
         <v>64</v>
       </c>
       <c r="C192" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="D192" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="E192" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="F192" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G192" t="s">
         <v>66</v>
@@ -6959,22 +6989,22 @@
     </row>
     <row r="193" spans="1:9" ht="15">
       <c r="A193" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B193" t="s">
         <v>64</v>
       </c>
       <c r="C193" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D193" t="s">
-        <v>188</v>
+        <v>96</v>
       </c>
       <c r="E193" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F193" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="G193" t="s">
         <v>66</v>
@@ -6988,22 +7018,22 @@
     </row>
     <row r="194" spans="1:9" ht="15">
       <c r="A194" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B194" t="s">
         <v>64</v>
       </c>
       <c r="C194" t="s">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="D194" t="s">
-        <v>14</v>
+        <v>209</v>
       </c>
       <c r="E194" t="s">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="F194" t="s">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="G194" t="s">
         <v>66</v>
@@ -7017,22 +7047,22 @@
     </row>
     <row r="195" spans="1:9" ht="15">
       <c r="A195" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B195" t="s">
         <v>64</v>
       </c>
       <c r="C195" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="D195" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E195" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="F195" t="s">
-        <v>210</v>
+        <v>153</v>
       </c>
       <c r="G195" t="s">
         <v>66</v>
@@ -7046,22 +7076,22 @@
     </row>
     <row r="196" spans="1:9" ht="15">
       <c r="A196" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B196" t="s">
         <v>64</v>
       </c>
       <c r="C196" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="D196" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="E196" t="s">
-        <v>166</v>
+        <v>212</v>
       </c>
       <c r="F196" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G196" t="s">
         <v>66</v>
@@ -7075,22 +7105,22 @@
     </row>
     <row r="197" spans="1:9" ht="15">
       <c r="A197" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B197" t="s">
         <v>64</v>
       </c>
       <c r="C197" t="s">
-        <v>191</v>
+        <v>147</v>
       </c>
       <c r="D197" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="E197" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="F197" t="s">
-        <v>113</v>
+        <v>186</v>
       </c>
       <c r="G197" t="s">
         <v>66</v>
@@ -7104,22 +7134,22 @@
     </row>
     <row r="198" spans="1:9" ht="15">
       <c r="A198" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B198" t="s">
         <v>64</v>
       </c>
       <c r="C198" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="D198" t="s">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="E198" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="F198" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="G198" t="s">
         <v>66</v>
@@ -7133,22 +7163,22 @@
     </row>
     <row r="199" spans="1:9" ht="15">
       <c r="A199" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B199" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C199" t="s">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="D199" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="E199" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F199" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="G199" t="s">
         <v>66</v>
@@ -7162,22 +7192,22 @@
     </row>
     <row r="200" spans="1:9" ht="15">
       <c r="A200" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B200" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C200" t="s">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="D200" t="s">
-        <v>14</v>
+        <v>220</v>
       </c>
       <c r="E200" t="s">
-        <v>184</v>
+        <v>45</v>
       </c>
       <c r="F200" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="G200" t="s">
         <v>66</v>
@@ -7191,22 +7221,22 @@
     </row>
     <row r="201" spans="1:9" ht="15">
       <c r="A201" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B201" t="s">
         <v>71</v>
       </c>
       <c r="C201" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="D201" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E201" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F201" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="G201" t="s">
         <v>66</v>
@@ -7220,22 +7250,22 @@
     </row>
     <row r="202" spans="1:9" ht="15">
       <c r="A202" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B202" t="s">
         <v>71</v>
       </c>
       <c r="C202" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D202" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="E202" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="F202" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G202" t="s">
         <v>66</v>
@@ -7249,22 +7279,22 @@
     </row>
     <row r="203" spans="1:9" ht="15">
       <c r="A203" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B203" t="s">
         <v>71</v>
       </c>
       <c r="C203" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D203" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="E203" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="F203" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G203" t="s">
         <v>66</v>
@@ -7278,22 +7308,22 @@
     </row>
     <row r="204" spans="1:9" ht="15">
       <c r="A204" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B204" t="s">
         <v>71</v>
       </c>
       <c r="C204" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="D204" t="s">
-        <v>208</v>
+        <v>109</v>
       </c>
       <c r="E204" t="s">
-        <v>15</v>
+        <v>166</v>
       </c>
       <c r="F204" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="G204" t="s">
         <v>66</v>
@@ -7307,22 +7337,22 @@
     </row>
     <row r="205" spans="1:9" ht="15">
       <c r="A205" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B205" t="s">
         <v>71</v>
       </c>
       <c r="C205" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D205" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E205" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F205" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="G205" t="s">
         <v>66</v>
@@ -7336,22 +7366,22 @@
     </row>
     <row r="206" spans="1:9" ht="15">
       <c r="A206" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B206" t="s">
         <v>71</v>
       </c>
       <c r="C206" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D206" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E206" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F206" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G206" t="s">
         <v>66</v>
@@ -7365,22 +7395,22 @@
     </row>
     <row r="207" spans="1:9" ht="15">
       <c r="A207" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B207" t="s">
         <v>71</v>
       </c>
       <c r="C207" t="s">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="D207" t="s">
-        <v>165</v>
+        <v>219</v>
       </c>
       <c r="E207" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="F207" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="G207" t="s">
         <v>66</v>
@@ -7394,22 +7424,22 @@
     </row>
     <row r="208" spans="1:9" ht="15">
       <c r="A208" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B208" t="s">
         <v>71</v>
       </c>
       <c r="C208" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D208" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="E208" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F208" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="G208" t="s">
         <v>66</v>
@@ -7423,22 +7453,22 @@
     </row>
     <row r="209" spans="1:9" ht="15">
       <c r="A209" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B209" t="s">
         <v>71</v>
       </c>
       <c r="C209" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="D209" t="s">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="E209" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="F209" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G209" t="s">
         <v>66</v>
@@ -7452,22 +7482,22 @@
     </row>
     <row r="210" spans="1:9" ht="15">
       <c r="A210" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B210" t="s">
         <v>71</v>
       </c>
       <c r="C210" t="s">
-        <v>203</v>
+        <v>42</v>
       </c>
       <c r="D210" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E210" t="s">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="F210" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="G210" t="s">
         <v>66</v>
@@ -7481,22 +7511,22 @@
     </row>
     <row r="211" spans="1:9" ht="15">
       <c r="A211" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B211" t="s">
         <v>71</v>
       </c>
       <c r="C211" t="s">
-        <v>89</v>
+        <v>201</v>
       </c>
       <c r="D211" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="E211" t="s">
-        <v>98</v>
+        <v>202</v>
       </c>
       <c r="F211" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G211" t="s">
         <v>66</v>
@@ -7510,22 +7540,22 @@
     </row>
     <row r="212" spans="1:9" ht="15">
       <c r="A212" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B212" t="s">
         <v>71</v>
       </c>
       <c r="C212" t="s">
-        <v>125</v>
+        <v>206</v>
       </c>
       <c r="D212" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E212" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F212" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="G212" t="s">
         <v>66</v>
@@ -7539,22 +7569,22 @@
     </row>
     <row r="213" spans="1:9" ht="15">
       <c r="A213" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B213" t="s">
         <v>71</v>
       </c>
       <c r="C213" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="D213" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="E213" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="F213" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="G213" t="s">
         <v>66</v>
@@ -7568,22 +7598,22 @@
     </row>
     <row r="214" spans="1:9" ht="15">
       <c r="A214" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B214" t="s">
         <v>71</v>
       </c>
       <c r="C214" t="s">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="D214" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="E214" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F214" t="s">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="G214" t="s">
         <v>66</v>
@@ -7597,22 +7627,22 @@
     </row>
     <row r="215" spans="1:9" ht="15">
       <c r="A215" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B215" t="s">
         <v>71</v>
       </c>
       <c r="C215" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="D215" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E215" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F215" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G215" t="s">
         <v>66</v>
@@ -7626,22 +7656,22 @@
     </row>
     <row r="216" spans="1:9" ht="15">
       <c r="A216" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B216" t="s">
         <v>71</v>
       </c>
       <c r="C216" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="D216" t="s">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="E216" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="F216" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G216" t="s">
         <v>66</v>
@@ -7655,22 +7685,22 @@
     </row>
     <row r="217" spans="1:9" ht="15">
       <c r="A217" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B217" t="s">
         <v>71</v>
       </c>
       <c r="C217" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D217" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E217" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F217" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="G217" t="s">
         <v>66</v>
@@ -7684,22 +7714,22 @@
     </row>
     <row r="218" spans="1:9" ht="15">
       <c r="A218" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B218" t="s">
         <v>71</v>
       </c>
       <c r="C218" t="s">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="D218" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="E218" t="s">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="F218" t="s">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="G218" t="s">
         <v>66</v>
@@ -7713,22 +7743,22 @@
     </row>
     <row r="219" spans="1:9" ht="15">
       <c r="A219" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B219" t="s">
         <v>71</v>
       </c>
       <c r="C219" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="D219" t="s">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="E219" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="F219" t="s">
-        <v>210</v>
+        <v>153</v>
       </c>
       <c r="G219" t="s">
         <v>66</v>
@@ -7742,22 +7772,22 @@
     </row>
     <row r="220" spans="1:9" ht="15">
       <c r="A220" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B220" t="s">
         <v>71</v>
       </c>
       <c r="C220" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="D220" t="s">
-        <v>80</v>
+        <v>223</v>
       </c>
       <c r="E220" t="s">
-        <v>93</v>
+        <v>212</v>
       </c>
       <c r="F220" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G220" t="s">
         <v>66</v>
@@ -7771,22 +7801,22 @@
     </row>
     <row r="221" spans="1:9" ht="15">
       <c r="A221" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B221" t="s">
         <v>71</v>
       </c>
       <c r="C221" t="s">
-        <v>222</v>
+        <v>147</v>
       </c>
       <c r="D221" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="E221" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="F221" t="s">
-        <v>141</v>
+        <v>186</v>
       </c>
       <c r="G221" t="s">
         <v>66</v>
@@ -7800,22 +7830,22 @@
     </row>
     <row r="222" spans="1:9" ht="15">
       <c r="A222" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B222" t="s">
         <v>71</v>
       </c>
       <c r="C222" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="D222" t="s">
-        <v>224</v>
+        <v>80</v>
       </c>
       <c r="E222" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="F222" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="G222" t="s">
         <v>66</v>
@@ -7829,13 +7859,13 @@
     </row>
     <row r="223" spans="1:9" ht="15">
       <c r="A223" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B223" t="s">
         <v>71</v>
       </c>
       <c r="C223" t="s">
-        <v>60</v>
+        <v>224</v>
       </c>
       <c r="D223" t="s">
         <v>225</v>
@@ -7844,7 +7874,7 @@
         <v>45</v>
       </c>
       <c r="F223" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="G223" t="s">
         <v>66</v>
@@ -7858,22 +7888,22 @@
     </row>
     <row r="224" spans="1:9" ht="15">
       <c r="A224" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B224" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C224" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D224" t="s">
-        <v>186</v>
+        <v>226</v>
       </c>
       <c r="E224" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="F224" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="G224" t="s">
         <v>66</v>
@@ -7887,22 +7917,22 @@
     </row>
     <row r="225" spans="1:9" ht="15">
       <c r="A225" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B225" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C225" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D225" t="s">
-        <v>96</v>
+        <v>227</v>
       </c>
       <c r="E225" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F225" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G225" t="s">
         <v>66</v>
@@ -7916,22 +7946,22 @@
     </row>
     <row r="226" spans="1:9" ht="15">
       <c r="A226" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B226" t="s">
         <v>78</v>
       </c>
       <c r="C226" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D226" t="s">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="E226" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="F226" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G226" t="s">
         <v>66</v>
@@ -7945,22 +7975,22 @@
     </row>
     <row r="227" spans="1:9" ht="15">
       <c r="A227" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B227" t="s">
         <v>78</v>
       </c>
       <c r="C227" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D227" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="E227" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F227" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G227" t="s">
         <v>66</v>
@@ -7974,22 +8004,22 @@
     </row>
     <row r="228" spans="1:9" ht="15">
       <c r="A228" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B228" t="s">
         <v>78</v>
       </c>
       <c r="C228" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="D228" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="E228" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="F228" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="G228" t="s">
         <v>66</v>
@@ -8003,22 +8033,22 @@
     </row>
     <row r="229" spans="1:9" ht="15">
       <c r="A229" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B229" t="s">
         <v>78</v>
       </c>
       <c r="C229" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D229" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E229" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F229" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="G229" t="s">
         <v>66</v>
@@ -8032,22 +8062,22 @@
     </row>
     <row r="230" spans="1:9" ht="15">
       <c r="A230" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B230" t="s">
         <v>78</v>
       </c>
       <c r="C230" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D230" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E230" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F230" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G230" t="s">
         <v>66</v>
@@ -8061,22 +8091,22 @@
     </row>
     <row r="231" spans="1:9" ht="15">
       <c r="A231" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B231" t="s">
         <v>78</v>
       </c>
       <c r="C231" t="s">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="D231" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="E231" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="F231" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="G231" t="s">
         <v>66</v>
@@ -8090,22 +8120,22 @@
     </row>
     <row r="232" spans="1:9" ht="15">
       <c r="A232" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B232" t="s">
         <v>78</v>
       </c>
       <c r="C232" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D232" t="s">
-        <v>150</v>
+        <v>222</v>
       </c>
       <c r="E232" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F232" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="G232" t="s">
         <v>66</v>
@@ -8119,22 +8149,22 @@
     </row>
     <row r="233" spans="1:9" ht="15">
       <c r="A233" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B233" t="s">
         <v>78</v>
       </c>
       <c r="C233" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="D233" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="E233" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="F233" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G233" t="s">
         <v>66</v>
@@ -8148,22 +8178,22 @@
     </row>
     <row r="234" spans="1:9" ht="15">
       <c r="A234" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B234" t="s">
         <v>78</v>
       </c>
       <c r="C234" t="s">
-        <v>203</v>
+        <v>42</v>
       </c>
       <c r="D234" t="s">
-        <v>227</v>
+        <v>150</v>
       </c>
       <c r="E234" t="s">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="F234" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="G234" t="s">
         <v>66</v>
@@ -8177,22 +8207,22 @@
     </row>
     <row r="235" spans="1:9" ht="15">
       <c r="A235" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B235" t="s">
         <v>78</v>
       </c>
       <c r="C235" t="s">
-        <v>89</v>
+        <v>201</v>
       </c>
       <c r="D235" t="s">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="E235" t="s">
-        <v>102</v>
+        <v>202</v>
       </c>
       <c r="F235" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G235" t="s">
         <v>66</v>
@@ -8206,22 +8236,22 @@
     </row>
     <row r="236" spans="1:9" ht="15">
       <c r="A236" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B236" t="s">
         <v>78</v>
       </c>
       <c r="C236" t="s">
-        <v>53</v>
+        <v>206</v>
       </c>
       <c r="D236" t="s">
-        <v>14</v>
+        <v>229</v>
       </c>
       <c r="E236" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="F236" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="G236" t="s">
         <v>66</v>
@@ -8235,22 +8265,22 @@
     </row>
     <row r="237" spans="1:9" ht="15">
       <c r="A237" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B237" t="s">
         <v>78</v>
       </c>
       <c r="C237" t="s">
-        <v>205</v>
+        <v>89</v>
       </c>
       <c r="D237" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="E237" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="F237" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="G237" t="s">
         <v>66</v>
@@ -8264,22 +8294,22 @@
     </row>
     <row r="238" spans="1:9" ht="15">
       <c r="A238" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B238" t="s">
         <v>78</v>
       </c>
       <c r="C238" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="D238" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="E238" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F238" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G238" t="s">
         <v>66</v>
@@ -8293,22 +8323,22 @@
     </row>
     <row r="239" spans="1:9" ht="15">
       <c r="A239" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B239" t="s">
         <v>78</v>
       </c>
       <c r="C239" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="D239" t="s">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="E239" t="s">
-        <v>228</v>
+        <v>32</v>
       </c>
       <c r="F239" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="G239" t="s">
         <v>66</v>
@@ -8322,22 +8352,22 @@
     </row>
     <row r="240" spans="1:9" ht="15">
       <c r="A240" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B240" t="s">
         <v>78</v>
       </c>
       <c r="C240" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D240" t="s">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="E240" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F240" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="G240" t="s">
         <v>66</v>
@@ -8351,22 +8381,22 @@
     </row>
     <row r="241" spans="1:9" ht="15">
       <c r="A241" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B241" t="s">
         <v>78</v>
       </c>
       <c r="C241" t="s">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="D241" t="s">
         <v>192</v>
       </c>
       <c r="E241" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="F241" t="s">
-        <v>92</v>
+        <v>186</v>
       </c>
       <c r="G241" t="s">
         <v>66</v>
@@ -8380,22 +8410,22 @@
     </row>
     <row r="242" spans="1:9" ht="15">
       <c r="A242" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B242" t="s">
         <v>78</v>
       </c>
       <c r="C242" t="s">
-        <v>222</v>
+        <v>104</v>
       </c>
       <c r="D242" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="E242" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="F242" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="G242" t="s">
         <v>66</v>
@@ -8409,22 +8439,22 @@
     </row>
     <row r="243" spans="1:9" ht="15">
       <c r="A243" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B243" t="s">
         <v>78</v>
       </c>
       <c r="C243" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="D243" t="s">
-        <v>22</v>
+        <v>194</v>
       </c>
       <c r="E243" t="s">
-        <v>112</v>
+        <v>212</v>
       </c>
       <c r="F243" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="G243" t="s">
         <v>66</v>
@@ -8438,22 +8468,22 @@
     </row>
     <row r="244" spans="1:9" ht="15">
       <c r="A244" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B244" t="s">
         <v>78</v>
       </c>
       <c r="C244" t="s">
-        <v>60</v>
+        <v>224</v>
       </c>
       <c r="D244" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E244" t="s">
         <v>45</v>
       </c>
       <c r="F244" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="G244" t="s">
         <v>66</v>
@@ -8467,22 +8497,22 @@
     </row>
     <row r="245" spans="1:9" ht="15">
       <c r="A245" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B245" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C245" t="s">
-        <v>67</v>
+        <v>193</v>
       </c>
       <c r="D245" t="s">
-        <v>219</v>
+        <v>22</v>
       </c>
       <c r="E245" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="F245" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G245" t="s">
         <v>66</v>
@@ -8496,22 +8526,22 @@
     </row>
     <row r="246" spans="1:9" ht="15">
       <c r="A246" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B246" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C246" t="s">
-        <v>207</v>
+        <v>60</v>
       </c>
       <c r="D246" t="s">
-        <v>128</v>
+        <v>231</v>
       </c>
       <c r="E246" t="s">
-        <v>209</v>
+        <v>45</v>
       </c>
       <c r="F246" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="G246" t="s">
         <v>66</v>
@@ -8525,22 +8555,22 @@
     </row>
     <row r="247" spans="1:9" ht="15">
       <c r="A247" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B247" t="s">
         <v>79</v>
       </c>
       <c r="C247" t="s">
-        <v>222</v>
+        <v>67</v>
       </c>
       <c r="D247" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E247" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F247" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="G247" t="s">
         <v>66</v>
@@ -8554,22 +8584,22 @@
     </row>
     <row r="248" spans="1:9" ht="15">
       <c r="A248" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B248" t="s">
         <v>79</v>
       </c>
       <c r="C248" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="D248" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="E248" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="F248" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="G248" t="s">
         <v>66</v>
@@ -8583,22 +8613,22 @@
     </row>
     <row r="249" spans="1:9" ht="15">
       <c r="A249" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B249" t="s">
         <v>79</v>
       </c>
       <c r="C249" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D249" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="E249" t="s">
-        <v>232</v>
+        <v>45</v>
       </c>
       <c r="F249" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="G249" t="s">
         <v>66</v>
@@ -8612,19 +8642,19 @@
     </row>
     <row r="250" spans="1:9" ht="15">
       <c r="A250" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B250" t="s">
         <v>79</v>
       </c>
       <c r="C250" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D250" t="s">
+        <v>233</v>
+      </c>
+      <c r="E250" t="s">
         <v>234</v>
-      </c>
-      <c r="E250" t="s">
-        <v>232</v>
       </c>
       <c r="F250" t="s">
         <v>41</v>
@@ -8641,19 +8671,19 @@
     </row>
     <row r="251" spans="1:9" ht="15">
       <c r="A251" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B251" t="s">
         <v>79</v>
       </c>
       <c r="C251" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D251" t="s">
         <v>235</v>
       </c>
       <c r="E251" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F251" t="s">
         <v>41</v>
@@ -8670,19 +8700,19 @@
     </row>
     <row r="252" spans="1:9" ht="15">
       <c r="A252" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B252" t="s">
         <v>79</v>
       </c>
       <c r="C252" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D252" t="s">
         <v>236</v>
       </c>
       <c r="E252" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F252" t="s">
         <v>41</v>
@@ -8699,19 +8729,19 @@
     </row>
     <row r="253" spans="1:9" ht="15">
       <c r="A253" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B253" t="s">
         <v>79</v>
       </c>
       <c r="C253" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D253" t="s">
         <v>237</v>
       </c>
       <c r="E253" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F253" t="s">
         <v>41</v>
@@ -8728,19 +8758,19 @@
     </row>
     <row r="254" spans="1:9" ht="15">
       <c r="A254" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B254" t="s">
         <v>79</v>
       </c>
       <c r="C254" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D254" t="s">
         <v>238</v>
       </c>
       <c r="E254" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F254" t="s">
         <v>41</v>
@@ -8757,19 +8787,19 @@
     </row>
     <row r="255" spans="1:9" ht="15">
       <c r="A255" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B255" t="s">
         <v>79</v>
       </c>
       <c r="C255" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D255" t="s">
         <v>239</v>
       </c>
       <c r="E255" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F255" t="s">
         <v>41</v>
@@ -8786,19 +8816,19 @@
     </row>
     <row r="256" spans="1:9" ht="15">
       <c r="A256" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B256" t="s">
         <v>79</v>
       </c>
       <c r="C256" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D256" t="s">
         <v>240</v>
       </c>
       <c r="E256" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F256" t="s">
         <v>41</v>
@@ -8815,19 +8845,19 @@
     </row>
     <row r="257" spans="1:9" ht="15">
       <c r="A257" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B257" t="s">
         <v>79</v>
       </c>
       <c r="C257" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D257" t="s">
         <v>241</v>
       </c>
       <c r="E257" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F257" t="s">
         <v>41</v>
@@ -8844,19 +8874,19 @@
     </row>
     <row r="258" spans="1:9" ht="15">
       <c r="A258" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B258" t="s">
         <v>79</v>
       </c>
       <c r="C258" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D258" t="s">
         <v>242</v>
       </c>
       <c r="E258" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F258" t="s">
         <v>41</v>
@@ -8873,19 +8903,19 @@
     </row>
     <row r="259" spans="1:9" ht="15">
       <c r="A259" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B259" t="s">
         <v>79</v>
       </c>
       <c r="C259" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D259" t="s">
         <v>243</v>
       </c>
       <c r="E259" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F259" t="s">
         <v>41</v>
@@ -8902,19 +8932,19 @@
     </row>
     <row r="260" spans="1:9" ht="15">
       <c r="A260" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B260" t="s">
         <v>79</v>
       </c>
       <c r="C260" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D260" t="s">
         <v>244</v>
       </c>
       <c r="E260" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F260" t="s">
         <v>41</v>
@@ -8931,22 +8961,22 @@
     </row>
     <row r="261" spans="1:9" ht="15">
       <c r="A261" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B261" t="s">
+        <v>79</v>
+      </c>
+      <c r="C261" t="s">
+        <v>232</v>
+      </c>
+      <c r="D261" t="s">
         <v>245</v>
       </c>
-      <c r="C261" t="s">
-        <v>203</v>
-      </c>
-      <c r="D261" t="s">
-        <v>219</v>
-      </c>
       <c r="E261" t="s">
-        <v>112</v>
+        <v>234</v>
       </c>
       <c r="F261" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="G261" t="s">
         <v>66</v>
@@ -8960,25 +8990,25 @@
     </row>
     <row r="262" spans="1:9" ht="15">
       <c r="A262" t="s">
+        <v>171</v>
+      </c>
+      <c r="B262" t="s">
+        <v>79</v>
+      </c>
+      <c r="C262" t="s">
+        <v>232</v>
+      </c>
+      <c r="D262" t="s">
         <v>246</v>
       </c>
-      <c r="B262" t="s">
-        <v>82</v>
-      </c>
-      <c r="C262" t="s">
-        <v>247</v>
-      </c>
-      <c r="D262" t="s">
-        <v>248</v>
-      </c>
       <c r="E262" t="s">
-        <v>116</v>
+        <v>234</v>
       </c>
       <c r="F262" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G262" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H262" t="s">
         <v>18</v>
@@ -8989,25 +9019,25 @@
     </row>
     <row r="263" spans="1:9" ht="15">
       <c r="A263" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="B263" t="s">
-        <v>12</v>
+        <v>247</v>
       </c>
       <c r="C263" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
       <c r="D263" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="E263" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F263" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="G263" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H263" t="s">
         <v>18</v>
@@ -9018,25 +9048,25 @@
     </row>
     <row r="264" spans="1:9" ht="15">
       <c r="A264" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B264" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C264" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="D264" t="s">
+        <v>38</v>
+      </c>
+      <c r="E264" t="s">
+        <v>166</v>
+      </c>
+      <c r="F264" t="s">
         <v>249</v>
       </c>
-      <c r="E264" t="s">
-        <v>32</v>
-      </c>
-      <c r="F264" t="s">
-        <v>52</v>
-      </c>
       <c r="G264" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H264" t="s">
         <v>18</v>
@@ -9047,25 +9077,25 @@
     </row>
     <row r="265" spans="1:9" ht="15">
       <c r="A265" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B265" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C265" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D265" t="s">
-        <v>65</v>
+        <v>251</v>
       </c>
       <c r="E265" t="s">
-        <v>211</v>
+        <v>116</v>
       </c>
       <c r="F265" t="s">
-        <v>212</v>
+        <v>52</v>
       </c>
       <c r="G265" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H265" t="s">
         <v>18</v>
@@ -9076,83 +9106,83 @@
     </row>
     <row r="266" spans="1:9" ht="15">
       <c r="A266" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B266" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C266" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="D266" t="s">
-        <v>14</v>
+        <v>252</v>
       </c>
       <c r="E266" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F266" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G266" t="s">
-        <v>27</v>
+        <v>253</v>
       </c>
       <c r="H266" t="s">
         <v>18</v>
       </c>
       <c r="I266" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="267" spans="1:9" ht="15">
       <c r="A267" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B267" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C267" t="s">
-        <v>247</v>
+        <v>88</v>
       </c>
       <c r="D267" t="s">
-        <v>65</v>
+        <v>187</v>
       </c>
       <c r="E267" t="s">
-        <v>211</v>
+        <v>93</v>
       </c>
       <c r="F267" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="G267" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="H267" t="s">
-        <v>18</v>
+        <v>254</v>
       </c>
       <c r="I267" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="268" spans="1:9" ht="15">
       <c r="A268" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B268" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C268" t="s">
-        <v>53</v>
+        <v>250</v>
       </c>
       <c r="D268" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E268" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="F268" t="s">
         <v>52</v>
       </c>
       <c r="G268" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H268" t="s">
         <v>18</v>
@@ -9163,190 +9193,190 @@
     </row>
     <row r="269" spans="1:9" ht="15">
       <c r="A269" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B269" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C269" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="D269" t="s">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="E269" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F269" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G269" t="s">
-        <v>27</v>
+        <v>253</v>
       </c>
       <c r="H269" t="s">
         <v>18</v>
       </c>
       <c r="I269" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="270" spans="1:9" ht="15">
       <c r="A270" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B270" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C270" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="D270" t="s">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="E270" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="F270" t="s">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="G270" t="s">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="H270" t="s">
-        <v>18</v>
+        <v>254</v>
       </c>
       <c r="I270" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="271" spans="1:9" ht="15">
       <c r="A271" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B271" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="C271" t="s">
         <v>53</v>
       </c>
       <c r="D271" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="E271" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="F271" t="s">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="G271" t="s">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="H271" t="s">
-        <v>18</v>
+        <v>254</v>
       </c>
       <c r="I271" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="272" spans="1:9" ht="15">
       <c r="A272" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B272" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C272" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="D272" t="s">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="E272" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F272" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G272" t="s">
-        <v>27</v>
+        <v>253</v>
       </c>
       <c r="H272" t="s">
         <v>18</v>
       </c>
       <c r="I272" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="273" spans="1:9" ht="15">
       <c r="A273" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B273" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="C273" t="s">
-        <v>252</v>
+        <v>88</v>
       </c>
       <c r="D273" t="s">
-        <v>152</v>
+        <v>256</v>
       </c>
       <c r="E273" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="F273" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G273" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="H273" t="s">
         <v>18</v>
       </c>
       <c r="I273" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="274" spans="1:9" ht="15">
       <c r="A274" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B274" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C274" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D274" t="s">
-        <v>186</v>
+        <v>65</v>
       </c>
       <c r="E274" t="s">
-        <v>15</v>
+        <v>213</v>
       </c>
       <c r="F274" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G274" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="H274" t="s">
         <v>18</v>
       </c>
       <c r="I274" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="275" spans="1:9" ht="15">
       <c r="A275" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B275" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C275" t="s">
         <v>53</v>
       </c>
       <c r="D275" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E275" t="s">
         <v>32</v>
@@ -9355,250 +9385,250 @@
         <v>52</v>
       </c>
       <c r="G275" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H275" t="s">
         <v>18</v>
       </c>
       <c r="I275" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="276" spans="1:9" ht="15">
       <c r="A276" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B276" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C276" t="s">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="D276" t="s">
-        <v>31</v>
+        <v>257</v>
       </c>
       <c r="E276" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F276" t="s">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="G276" t="s">
-        <v>27</v>
+        <v>253</v>
       </c>
       <c r="H276" t="s">
         <v>18</v>
       </c>
       <c r="I276" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="277" spans="1:9" ht="15">
       <c r="A277" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B277" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C277" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="D277" t="s">
-        <v>49</v>
+        <v>256</v>
       </c>
       <c r="E277" t="s">
-        <v>32</v>
+        <v>177</v>
       </c>
       <c r="F277" t="s">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="G277" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="H277" t="s">
         <v>18</v>
       </c>
       <c r="I277" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="278" spans="1:9" ht="15">
       <c r="A278" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B278" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C278" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D278" t="s">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="E278" t="s">
-        <v>15</v>
+        <v>213</v>
       </c>
       <c r="F278" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G278" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="H278" t="s">
         <v>18</v>
       </c>
       <c r="I278" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="279" spans="1:9" ht="15">
       <c r="A279" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B279" t="s">
         <v>37</v>
       </c>
       <c r="C279" t="s">
-        <v>247</v>
+        <v>53</v>
       </c>
       <c r="D279" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E279" t="s">
-        <v>253</v>
+        <v>32</v>
       </c>
       <c r="F279" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G279" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H279" t="s">
         <v>18</v>
       </c>
       <c r="I279" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="280" spans="1:9" ht="15">
       <c r="A280" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B280" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C280" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="D280" t="s">
-        <v>156</v>
+        <v>257</v>
       </c>
       <c r="E280" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F280" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G280" t="s">
-        <v>27</v>
+        <v>253</v>
       </c>
       <c r="H280" t="s">
         <v>18</v>
       </c>
       <c r="I280" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="281" spans="1:9" ht="15">
       <c r="A281" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B281" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C281" t="s">
-        <v>252</v>
+        <v>88</v>
       </c>
       <c r="D281" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E281" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="F281" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G281" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="H281" t="s">
         <v>18</v>
       </c>
       <c r="I281" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="282" spans="1:9" ht="15">
       <c r="A282" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B282" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C282" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="D282" t="s">
-        <v>156</v>
+        <v>257</v>
       </c>
       <c r="E282" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F282" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G282" t="s">
-        <v>27</v>
+        <v>253</v>
       </c>
       <c r="H282" t="s">
         <v>18</v>
       </c>
       <c r="I282" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="283" spans="1:9" ht="15">
       <c r="A283" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B283" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C283" t="s">
-        <v>252</v>
+        <v>88</v>
       </c>
       <c r="D283" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E283" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="F283" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G283" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="H283" t="s">
         <v>18</v>
       </c>
       <c r="I283" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="284" spans="1:9" ht="15">
       <c r="A284" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B284" t="s">
         <v>58</v>
@@ -9607,7 +9637,7 @@
         <v>53</v>
       </c>
       <c r="D284" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E284" t="s">
         <v>32</v>
@@ -9616,7 +9646,7 @@
         <v>52</v>
       </c>
       <c r="G284" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H284" t="s">
         <v>18</v>
@@ -9627,54 +9657,54 @@
     </row>
     <row r="285" spans="1:9" ht="15">
       <c r="A285" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B285" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C285" t="s">
-        <v>252</v>
+        <v>88</v>
       </c>
       <c r="D285" t="s">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E285" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="F285" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G285" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="H285" t="s">
         <v>18</v>
       </c>
       <c r="I285" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="286" spans="1:9" ht="15">
       <c r="A286" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B286" t="s">
         <v>64</v>
       </c>
       <c r="C286" t="s">
-        <v>252</v>
+        <v>53</v>
       </c>
       <c r="D286" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E286" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F286" t="s">
-        <v>210</v>
+        <v>52</v>
       </c>
       <c r="G286" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H286" t="s">
         <v>18</v>
@@ -9685,54 +9715,54 @@
     </row>
     <row r="287" spans="1:9" ht="15">
       <c r="A287" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B287" t="s">
         <v>71</v>
       </c>
       <c r="C287" t="s">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="D287" t="s">
-        <v>31</v>
+        <v>259</v>
       </c>
       <c r="E287" t="s">
         <v>93</v>
       </c>
       <c r="F287" t="s">
-        <v>210</v>
+        <v>131</v>
       </c>
       <c r="G287" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="H287" t="s">
         <v>18</v>
       </c>
       <c r="I287" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="288" spans="1:9" ht="15">
       <c r="A288" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B288" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C288" t="s">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="D288" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E288" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="F288" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G288" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H288" t="s">
         <v>18</v>
@@ -9743,54 +9773,54 @@
     </row>
     <row r="289" spans="1:9" ht="15">
       <c r="A289" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B289" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="C289" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="D289" t="s">
-        <v>152</v>
+        <v>256</v>
       </c>
       <c r="E289" t="s">
-        <v>32</v>
+        <v>177</v>
       </c>
       <c r="F289" t="s">
-        <v>33</v>
+        <v>178</v>
       </c>
       <c r="G289" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="H289" t="s">
         <v>18</v>
       </c>
       <c r="I289" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="290" spans="1:9" ht="15">
       <c r="A290" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B290" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="C290" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="D290" t="s">
-        <v>255</v>
+        <v>134</v>
       </c>
       <c r="E290" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="F290" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G290" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H290" t="s">
         <v>18</v>
@@ -9801,25 +9831,25 @@
     </row>
     <row r="291" spans="1:9" ht="15">
       <c r="A291" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B291" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="C291" t="s">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="D291" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E291" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="F291" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G291" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H291" t="s">
         <v>18</v>
@@ -9830,54 +9860,54 @@
     </row>
     <row r="292" spans="1:9" ht="15">
       <c r="A292" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B292" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="C292" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="D292" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="E292" t="s">
-        <v>32</v>
+        <v>177</v>
       </c>
       <c r="F292" t="s">
-        <v>33</v>
+        <v>178</v>
       </c>
       <c r="G292" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="H292" t="s">
         <v>18</v>
       </c>
       <c r="I292" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="293" spans="1:9" ht="15">
       <c r="A293" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B293" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="C293" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="D293" t="s">
-        <v>255</v>
+        <v>211</v>
       </c>
       <c r="E293" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="F293" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G293" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H293" t="s">
         <v>18</v>
@@ -9888,25 +9918,25 @@
     </row>
     <row r="294" spans="1:9" ht="15">
       <c r="A294" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B294" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="C294" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="D294" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E294" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F294" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="G294" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H294" t="s">
         <v>18</v>
@@ -9917,22 +9947,22 @@
     </row>
     <row r="295" spans="1:9" ht="15">
       <c r="A295" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B295" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C295" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D295" t="s">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="E295" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="F295" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G295" t="s">
         <v>27</v>
@@ -9946,22 +9976,22 @@
     </row>
     <row r="296" spans="1:9" ht="15">
       <c r="A296" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B296" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C296" t="s">
-        <v>147</v>
+        <v>261</v>
       </c>
       <c r="D296" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E296" t="s">
-        <v>148</v>
+        <v>15</v>
       </c>
       <c r="F296" t="s">
-        <v>94</v>
+        <v>186</v>
       </c>
       <c r="G296" t="s">
         <v>27</v>
@@ -9975,22 +10005,22 @@
     </row>
     <row r="297" spans="1:9" ht="15">
       <c r="A297" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B297" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C297" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D297" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="E297" t="s">
         <v>32</v>
       </c>
       <c r="F297" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G297" t="s">
         <v>27</v>
@@ -10004,22 +10034,22 @@
     </row>
     <row r="298" spans="1:9" ht="15">
       <c r="A298" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B298" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C298" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D298" t="s">
-        <v>257</v>
+        <v>31</v>
       </c>
       <c r="E298" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="F298" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G298" t="s">
         <v>27</v>
@@ -10033,22 +10063,22 @@
     </row>
     <row r="299" spans="1:9" ht="15">
       <c r="A299" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B299" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C299" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="D299" t="s">
-        <v>255</v>
+        <v>49</v>
       </c>
       <c r="E299" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="F299" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G299" t="s">
         <v>27</v>
@@ -10062,22 +10092,22 @@
     </row>
     <row r="300" spans="1:9" ht="15">
       <c r="A300" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B300" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C300" t="s">
-        <v>53</v>
+        <v>261</v>
       </c>
       <c r="D300" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E300" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F300" t="s">
-        <v>52</v>
+        <v>186</v>
       </c>
       <c r="G300" t="s">
         <v>27</v>
@@ -10091,22 +10121,22 @@
     </row>
     <row r="301" spans="1:9" ht="15">
       <c r="A301" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B301" t="s">
         <v>37</v>
       </c>
       <c r="C301" t="s">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="D301" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="E301" t="s">
-        <v>148</v>
+        <v>262</v>
       </c>
       <c r="F301" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="G301" t="s">
         <v>27</v>
@@ -10120,22 +10150,22 @@
     </row>
     <row r="302" spans="1:9" ht="15">
       <c r="A302" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B302" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C302" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D302" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="E302" t="s">
         <v>32</v>
       </c>
       <c r="F302" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G302" t="s">
         <v>27</v>
@@ -10149,22 +10179,22 @@
     </row>
     <row r="303" spans="1:9" ht="15">
       <c r="A303" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B303" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C303" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D303" t="s">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="E303" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="F303" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G303" t="s">
         <v>27</v>
@@ -10178,7 +10208,7 @@
     </row>
     <row r="304" spans="1:9" ht="15">
       <c r="A304" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B304" t="s">
         <v>48</v>
@@ -10187,7 +10217,7 @@
         <v>53</v>
       </c>
       <c r="D304" t="s">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="E304" t="s">
         <v>32</v>
@@ -10207,22 +10237,22 @@
     </row>
     <row r="305" spans="1:9" ht="15">
       <c r="A305" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B305" t="s">
         <v>48</v>
       </c>
       <c r="C305" t="s">
-        <v>147</v>
+        <v>261</v>
       </c>
       <c r="D305" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="E305" t="s">
-        <v>148</v>
+        <v>15</v>
       </c>
       <c r="F305" t="s">
-        <v>94</v>
+        <v>186</v>
       </c>
       <c r="G305" t="s">
         <v>27</v>
@@ -10236,22 +10266,22 @@
     </row>
     <row r="306" spans="1:9" ht="15">
       <c r="A306" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B306" t="s">
         <v>58</v>
       </c>
       <c r="C306" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D306" t="s">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="E306" t="s">
         <v>32</v>
       </c>
       <c r="F306" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G306" t="s">
         <v>27</v>
@@ -10265,22 +10295,22 @@
     </row>
     <row r="307" spans="1:9" ht="15">
       <c r="A307" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B307" t="s">
         <v>58</v>
       </c>
       <c r="C307" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D307" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="E307" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="F307" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="G307" t="s">
         <v>27</v>
@@ -10294,22 +10324,22 @@
     </row>
     <row r="308" spans="1:9" ht="15">
       <c r="A308" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B308" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C308" t="s">
-        <v>89</v>
+        <v>261</v>
       </c>
       <c r="D308" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="E308" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F308" t="s">
-        <v>61</v>
+        <v>186</v>
       </c>
       <c r="G308" t="s">
         <v>27</v>
@@ -10323,22 +10353,22 @@
     </row>
     <row r="309" spans="1:9" ht="15">
       <c r="A309" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B309" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C309" t="s">
-        <v>53</v>
+        <v>261</v>
       </c>
       <c r="D309" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="E309" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="F309" t="s">
-        <v>52</v>
+        <v>186</v>
       </c>
       <c r="G309" t="s">
         <v>27</v>
@@ -10352,22 +10382,22 @@
     </row>
     <row r="310" spans="1:9" ht="15">
       <c r="A310" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B310" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C310" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D310" t="s">
-        <v>115</v>
+        <v>264</v>
       </c>
       <c r="E310" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="F310" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G310" t="s">
         <v>27</v>
@@ -10381,22 +10411,22 @@
     </row>
     <row r="311" spans="1:9" ht="15">
       <c r="A311" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B311" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C311" t="s">
-        <v>30</v>
+        <v>147</v>
       </c>
       <c r="D311" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E311" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="F311" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="G311" t="s">
         <v>27</v>
@@ -10410,22 +10440,22 @@
     </row>
     <row r="312" spans="1:9" ht="15">
       <c r="A312" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B312" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C312" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D312" t="s">
-        <v>250</v>
+        <v>152</v>
       </c>
       <c r="E312" t="s">
         <v>32</v>
       </c>
       <c r="F312" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="G312" t="s">
         <v>27</v>
@@ -10439,22 +10469,22 @@
     </row>
     <row r="313" spans="1:9" ht="15">
       <c r="A313" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B313" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C313" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="D313" t="s">
-        <v>165</v>
+        <v>266</v>
       </c>
       <c r="E313" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="F313" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="G313" t="s">
         <v>27</v>
@@ -10468,22 +10498,22 @@
     </row>
     <row r="314" spans="1:9" ht="15">
       <c r="A314" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B314" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="C314" t="s">
-        <v>30</v>
+        <v>146</v>
       </c>
       <c r="D314" t="s">
-        <v>90</v>
+        <v>264</v>
       </c>
       <c r="E314" t="s">
-        <v>32</v>
+        <v>162</v>
       </c>
       <c r="F314" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="G314" t="s">
         <v>27</v>
@@ -10497,22 +10527,22 @@
     </row>
     <row r="315" spans="1:9" ht="15">
       <c r="A315" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B315" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="C315" t="s">
-        <v>256</v>
+        <v>89</v>
       </c>
       <c r="D315" t="s">
         <v>259</v>
       </c>
       <c r="E315" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="F315" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G315" t="s">
         <v>27</v>
@@ -10526,16 +10556,16 @@
     </row>
     <row r="316" spans="1:9" ht="15">
       <c r="A316" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B316" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="C316" t="s">
         <v>147</v>
       </c>
       <c r="D316" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="E316" t="s">
         <v>148</v>
@@ -10550,6 +10580,1224 @@
         <v>18</v>
       </c>
       <c r="I316" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" ht="15">
+      <c r="A317" t="s">
+        <v>263</v>
+      </c>
+      <c r="B317" t="s">
+        <v>20</v>
+      </c>
+      <c r="C317" t="s">
+        <v>30</v>
+      </c>
+      <c r="D317" t="s">
+        <v>190</v>
+      </c>
+      <c r="E317" t="s">
+        <v>32</v>
+      </c>
+      <c r="F317" t="s">
+        <v>33</v>
+      </c>
+      <c r="G317" t="s">
+        <v>27</v>
+      </c>
+      <c r="H317" t="s">
+        <v>18</v>
+      </c>
+      <c r="I317" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" ht="15">
+      <c r="A318" t="s">
+        <v>263</v>
+      </c>
+      <c r="B318" t="s">
+        <v>20</v>
+      </c>
+      <c r="C318" t="s">
+        <v>265</v>
+      </c>
+      <c r="D318" t="s">
+        <v>266</v>
+      </c>
+      <c r="E318" t="s">
+        <v>75</v>
+      </c>
+      <c r="F318" t="s">
+        <v>161</v>
+      </c>
+      <c r="G318" t="s">
+        <v>27</v>
+      </c>
+      <c r="H318" t="s">
+        <v>18</v>
+      </c>
+      <c r="I318" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" ht="15">
+      <c r="A319" t="s">
+        <v>263</v>
+      </c>
+      <c r="B319" t="s">
+        <v>20</v>
+      </c>
+      <c r="C319" t="s">
+        <v>47</v>
+      </c>
+      <c r="D319" t="s">
+        <v>118</v>
+      </c>
+      <c r="E319" t="s">
+        <v>45</v>
+      </c>
+      <c r="F319" t="s">
+        <v>138</v>
+      </c>
+      <c r="G319" t="s">
+        <v>27</v>
+      </c>
+      <c r="H319" t="s">
+        <v>18</v>
+      </c>
+      <c r="I319" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" ht="15">
+      <c r="A320" t="s">
+        <v>263</v>
+      </c>
+      <c r="B320" t="s">
+        <v>20</v>
+      </c>
+      <c r="C320" t="s">
+        <v>146</v>
+      </c>
+      <c r="D320" t="s">
+        <v>264</v>
+      </c>
+      <c r="E320" t="s">
+        <v>162</v>
+      </c>
+      <c r="F320" t="s">
+        <v>105</v>
+      </c>
+      <c r="G320" t="s">
+        <v>27</v>
+      </c>
+      <c r="H320" t="s">
+        <v>18</v>
+      </c>
+      <c r="I320" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" ht="15">
+      <c r="A321" t="s">
+        <v>263</v>
+      </c>
+      <c r="B321" t="s">
+        <v>20</v>
+      </c>
+      <c r="C321" t="s">
+        <v>89</v>
+      </c>
+      <c r="D321" t="s">
+        <v>259</v>
+      </c>
+      <c r="E321" t="s">
+        <v>91</v>
+      </c>
+      <c r="F321" t="s">
+        <v>153</v>
+      </c>
+      <c r="G321" t="s">
+        <v>27</v>
+      </c>
+      <c r="H321" t="s">
+        <v>18</v>
+      </c>
+      <c r="I321" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" ht="15">
+      <c r="A322" t="s">
+        <v>263</v>
+      </c>
+      <c r="B322" t="s">
+        <v>29</v>
+      </c>
+      <c r="C322" t="s">
+        <v>30</v>
+      </c>
+      <c r="D322" t="s">
+        <v>54</v>
+      </c>
+      <c r="E322" t="s">
+        <v>32</v>
+      </c>
+      <c r="F322" t="s">
+        <v>33</v>
+      </c>
+      <c r="G322" t="s">
+        <v>27</v>
+      </c>
+      <c r="H322" t="s">
+        <v>18</v>
+      </c>
+      <c r="I322" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" ht="15">
+      <c r="A323" t="s">
+        <v>263</v>
+      </c>
+      <c r="B323" t="s">
+        <v>29</v>
+      </c>
+      <c r="C323" t="s">
+        <v>265</v>
+      </c>
+      <c r="D323" t="s">
+        <v>266</v>
+      </c>
+      <c r="E323" t="s">
+        <v>75</v>
+      </c>
+      <c r="F323" t="s">
+        <v>161</v>
+      </c>
+      <c r="G323" t="s">
+        <v>27</v>
+      </c>
+      <c r="H323" t="s">
+        <v>18</v>
+      </c>
+      <c r="I323" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" ht="15">
+      <c r="A324" t="s">
+        <v>263</v>
+      </c>
+      <c r="B324" t="s">
+        <v>29</v>
+      </c>
+      <c r="C324" t="s">
+        <v>267</v>
+      </c>
+      <c r="D324" t="s">
+        <v>218</v>
+      </c>
+      <c r="E324" t="s">
+        <v>140</v>
+      </c>
+      <c r="F324" t="s">
+        <v>180</v>
+      </c>
+      <c r="G324" t="s">
+        <v>27</v>
+      </c>
+      <c r="H324" t="s">
+        <v>18</v>
+      </c>
+      <c r="I324" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" ht="15">
+      <c r="A325" t="s">
+        <v>263</v>
+      </c>
+      <c r="B325" t="s">
+        <v>29</v>
+      </c>
+      <c r="C325" t="s">
+        <v>47</v>
+      </c>
+      <c r="D325" t="s">
+        <v>124</v>
+      </c>
+      <c r="E325" t="s">
+        <v>45</v>
+      </c>
+      <c r="F325" t="s">
+        <v>138</v>
+      </c>
+      <c r="G325" t="s">
+        <v>27</v>
+      </c>
+      <c r="H325" t="s">
+        <v>18</v>
+      </c>
+      <c r="I325" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" ht="15">
+      <c r="A326" t="s">
+        <v>263</v>
+      </c>
+      <c r="B326" t="s">
+        <v>29</v>
+      </c>
+      <c r="C326" t="s">
+        <v>154</v>
+      </c>
+      <c r="D326" t="s">
+        <v>165</v>
+      </c>
+      <c r="E326" t="s">
+        <v>98</v>
+      </c>
+      <c r="F326" t="s">
+        <v>153</v>
+      </c>
+      <c r="G326" t="s">
+        <v>27</v>
+      </c>
+      <c r="H326" t="s">
+        <v>18</v>
+      </c>
+      <c r="I326" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" ht="15">
+      <c r="A327" t="s">
+        <v>263</v>
+      </c>
+      <c r="B327" t="s">
+        <v>29</v>
+      </c>
+      <c r="C327" t="s">
+        <v>146</v>
+      </c>
+      <c r="D327" t="s">
+        <v>264</v>
+      </c>
+      <c r="E327" t="s">
+        <v>162</v>
+      </c>
+      <c r="F327" t="s">
+        <v>105</v>
+      </c>
+      <c r="G327" t="s">
+        <v>27</v>
+      </c>
+      <c r="H327" t="s">
+        <v>18</v>
+      </c>
+      <c r="I327" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" ht="15">
+      <c r="A328" t="s">
+        <v>263</v>
+      </c>
+      <c r="B328" t="s">
+        <v>29</v>
+      </c>
+      <c r="C328" t="s">
+        <v>147</v>
+      </c>
+      <c r="D328" t="s">
+        <v>192</v>
+      </c>
+      <c r="E328" t="s">
+        <v>148</v>
+      </c>
+      <c r="F328" t="s">
+        <v>94</v>
+      </c>
+      <c r="G328" t="s">
+        <v>27</v>
+      </c>
+      <c r="H328" t="s">
+        <v>18</v>
+      </c>
+      <c r="I328" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" ht="15">
+      <c r="A329" t="s">
+        <v>263</v>
+      </c>
+      <c r="B329" t="s">
+        <v>37</v>
+      </c>
+      <c r="C329" t="s">
+        <v>30</v>
+      </c>
+      <c r="D329" t="s">
+        <v>54</v>
+      </c>
+      <c r="E329" t="s">
+        <v>32</v>
+      </c>
+      <c r="F329" t="s">
+        <v>33</v>
+      </c>
+      <c r="G329" t="s">
+        <v>27</v>
+      </c>
+      <c r="H329" t="s">
+        <v>18</v>
+      </c>
+      <c r="I329" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" ht="15">
+      <c r="A330" t="s">
+        <v>263</v>
+      </c>
+      <c r="B330" t="s">
+        <v>37</v>
+      </c>
+      <c r="C330" t="s">
+        <v>267</v>
+      </c>
+      <c r="D330" t="s">
+        <v>268</v>
+      </c>
+      <c r="E330" t="s">
+        <v>140</v>
+      </c>
+      <c r="F330" t="s">
+        <v>180</v>
+      </c>
+      <c r="G330" t="s">
+        <v>27</v>
+      </c>
+      <c r="H330" t="s">
+        <v>18</v>
+      </c>
+      <c r="I330" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" ht="15">
+      <c r="A331" t="s">
+        <v>263</v>
+      </c>
+      <c r="B331" t="s">
+        <v>37</v>
+      </c>
+      <c r="C331" t="s">
+        <v>47</v>
+      </c>
+      <c r="D331" t="s">
+        <v>124</v>
+      </c>
+      <c r="E331" t="s">
+        <v>45</v>
+      </c>
+      <c r="F331" t="s">
+        <v>138</v>
+      </c>
+      <c r="G331" t="s">
+        <v>27</v>
+      </c>
+      <c r="H331" t="s">
+        <v>18</v>
+      </c>
+      <c r="I331" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" ht="15">
+      <c r="A332" t="s">
+        <v>263</v>
+      </c>
+      <c r="B332" t="s">
+        <v>37</v>
+      </c>
+      <c r="C332" t="s">
+        <v>154</v>
+      </c>
+      <c r="D332" t="s">
+        <v>258</v>
+      </c>
+      <c r="E332" t="s">
+        <v>93</v>
+      </c>
+      <c r="F332" t="s">
+        <v>61</v>
+      </c>
+      <c r="G332" t="s">
+        <v>27</v>
+      </c>
+      <c r="H332" t="s">
+        <v>18</v>
+      </c>
+      <c r="I332" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" ht="15">
+      <c r="A333" t="s">
+        <v>263</v>
+      </c>
+      <c r="B333" t="s">
+        <v>37</v>
+      </c>
+      <c r="C333" t="s">
+        <v>146</v>
+      </c>
+      <c r="D333" t="s">
+        <v>264</v>
+      </c>
+      <c r="E333" t="s">
+        <v>162</v>
+      </c>
+      <c r="F333" t="s">
+        <v>105</v>
+      </c>
+      <c r="G333" t="s">
+        <v>27</v>
+      </c>
+      <c r="H333" t="s">
+        <v>18</v>
+      </c>
+      <c r="I333" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" ht="15">
+      <c r="A334" t="s">
+        <v>263</v>
+      </c>
+      <c r="B334" t="s">
+        <v>37</v>
+      </c>
+      <c r="C334" t="s">
+        <v>89</v>
+      </c>
+      <c r="D334" t="s">
+        <v>259</v>
+      </c>
+      <c r="E334" t="s">
+        <v>98</v>
+      </c>
+      <c r="F334" t="s">
+        <v>153</v>
+      </c>
+      <c r="G334" t="s">
+        <v>27</v>
+      </c>
+      <c r="H334" t="s">
+        <v>18</v>
+      </c>
+      <c r="I334" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" ht="15">
+      <c r="A335" t="s">
+        <v>263</v>
+      </c>
+      <c r="B335" t="s">
+        <v>37</v>
+      </c>
+      <c r="C335" t="s">
+        <v>53</v>
+      </c>
+      <c r="D335" t="s">
+        <v>181</v>
+      </c>
+      <c r="E335" t="s">
+        <v>32</v>
+      </c>
+      <c r="F335" t="s">
+        <v>52</v>
+      </c>
+      <c r="G335" t="s">
+        <v>27</v>
+      </c>
+      <c r="H335" t="s">
+        <v>18</v>
+      </c>
+      <c r="I335" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" ht="15">
+      <c r="A336" t="s">
+        <v>263</v>
+      </c>
+      <c r="B336" t="s">
+        <v>37</v>
+      </c>
+      <c r="C336" t="s">
+        <v>147</v>
+      </c>
+      <c r="D336" t="s">
+        <v>207</v>
+      </c>
+      <c r="E336" t="s">
+        <v>148</v>
+      </c>
+      <c r="F336" t="s">
+        <v>94</v>
+      </c>
+      <c r="G336" t="s">
+        <v>27</v>
+      </c>
+      <c r="H336" t="s">
+        <v>18</v>
+      </c>
+      <c r="I336" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" ht="15">
+      <c r="A337" t="s">
+        <v>263</v>
+      </c>
+      <c r="B337" t="s">
+        <v>48</v>
+      </c>
+      <c r="C337" t="s">
+        <v>30</v>
+      </c>
+      <c r="D337" t="s">
+        <v>31</v>
+      </c>
+      <c r="E337" t="s">
+        <v>32</v>
+      </c>
+      <c r="F337" t="s">
+        <v>33</v>
+      </c>
+      <c r="G337" t="s">
+        <v>27</v>
+      </c>
+      <c r="H337" t="s">
+        <v>18</v>
+      </c>
+      <c r="I337" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" ht="15">
+      <c r="A338" t="s">
+        <v>263</v>
+      </c>
+      <c r="B338" t="s">
+        <v>48</v>
+      </c>
+      <c r="C338" t="s">
+        <v>265</v>
+      </c>
+      <c r="D338" t="s">
+        <v>269</v>
+      </c>
+      <c r="E338" t="s">
+        <v>75</v>
+      </c>
+      <c r="F338" t="s">
+        <v>161</v>
+      </c>
+      <c r="G338" t="s">
+        <v>27</v>
+      </c>
+      <c r="H338" t="s">
+        <v>18</v>
+      </c>
+      <c r="I338" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" ht="15">
+      <c r="A339" t="s">
+        <v>263</v>
+      </c>
+      <c r="B339" t="s">
+        <v>48</v>
+      </c>
+      <c r="C339" t="s">
+        <v>267</v>
+      </c>
+      <c r="D339" t="s">
+        <v>188</v>
+      </c>
+      <c r="E339" t="s">
+        <v>140</v>
+      </c>
+      <c r="F339" t="s">
+        <v>180</v>
+      </c>
+      <c r="G339" t="s">
+        <v>27</v>
+      </c>
+      <c r="H339" t="s">
+        <v>18</v>
+      </c>
+      <c r="I339" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" ht="15">
+      <c r="A340" t="s">
+        <v>263</v>
+      </c>
+      <c r="B340" t="s">
+        <v>48</v>
+      </c>
+      <c r="C340" t="s">
+        <v>47</v>
+      </c>
+      <c r="D340" t="s">
+        <v>134</v>
+      </c>
+      <c r="E340" t="s">
+        <v>45</v>
+      </c>
+      <c r="F340" t="s">
+        <v>138</v>
+      </c>
+      <c r="G340" t="s">
+        <v>27</v>
+      </c>
+      <c r="H340" t="s">
+        <v>18</v>
+      </c>
+      <c r="I340" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" ht="15">
+      <c r="A341" t="s">
+        <v>263</v>
+      </c>
+      <c r="B341" t="s">
+        <v>48</v>
+      </c>
+      <c r="C341" t="s">
+        <v>146</v>
+      </c>
+      <c r="D341" t="s">
+        <v>181</v>
+      </c>
+      <c r="E341" t="s">
+        <v>191</v>
+      </c>
+      <c r="F341" t="s">
+        <v>105</v>
+      </c>
+      <c r="G341" t="s">
+        <v>27</v>
+      </c>
+      <c r="H341" t="s">
+        <v>18</v>
+      </c>
+      <c r="I341" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" ht="15">
+      <c r="A342" t="s">
+        <v>263</v>
+      </c>
+      <c r="B342" t="s">
+        <v>48</v>
+      </c>
+      <c r="C342" t="s">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>207</v>
+      </c>
+      <c r="E342" t="s">
+        <v>32</v>
+      </c>
+      <c r="F342" t="s">
+        <v>52</v>
+      </c>
+      <c r="G342" t="s">
+        <v>27</v>
+      </c>
+      <c r="H342" t="s">
+        <v>18</v>
+      </c>
+      <c r="I342" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" ht="15">
+      <c r="A343" t="s">
+        <v>263</v>
+      </c>
+      <c r="B343" t="s">
+        <v>48</v>
+      </c>
+      <c r="C343" t="s">
+        <v>147</v>
+      </c>
+      <c r="D343" t="s">
+        <v>190</v>
+      </c>
+      <c r="E343" t="s">
+        <v>148</v>
+      </c>
+      <c r="F343" t="s">
+        <v>94</v>
+      </c>
+      <c r="G343" t="s">
+        <v>27</v>
+      </c>
+      <c r="H343" t="s">
+        <v>18</v>
+      </c>
+      <c r="I343" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" ht="15">
+      <c r="A344" t="s">
+        <v>263</v>
+      </c>
+      <c r="B344" t="s">
+        <v>58</v>
+      </c>
+      <c r="C344" t="s">
+        <v>30</v>
+      </c>
+      <c r="D344" t="s">
+        <v>65</v>
+      </c>
+      <c r="E344" t="s">
+        <v>32</v>
+      </c>
+      <c r="F344" t="s">
+        <v>33</v>
+      </c>
+      <c r="G344" t="s">
+        <v>27</v>
+      </c>
+      <c r="H344" t="s">
+        <v>18</v>
+      </c>
+      <c r="I344" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" ht="15">
+      <c r="A345" t="s">
+        <v>263</v>
+      </c>
+      <c r="B345" t="s">
+        <v>58</v>
+      </c>
+      <c r="C345" t="s">
+        <v>265</v>
+      </c>
+      <c r="D345" t="s">
+        <v>269</v>
+      </c>
+      <c r="E345" t="s">
+        <v>75</v>
+      </c>
+      <c r="F345" t="s">
+        <v>161</v>
+      </c>
+      <c r="G345" t="s">
+        <v>27</v>
+      </c>
+      <c r="H345" t="s">
+        <v>18</v>
+      </c>
+      <c r="I345" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" ht="15">
+      <c r="A346" t="s">
+        <v>263</v>
+      </c>
+      <c r="B346" t="s">
+        <v>58</v>
+      </c>
+      <c r="C346" t="s">
+        <v>267</v>
+      </c>
+      <c r="D346" t="s">
+        <v>54</v>
+      </c>
+      <c r="E346" t="s">
+        <v>140</v>
+      </c>
+      <c r="F346" t="s">
+        <v>16</v>
+      </c>
+      <c r="G346" t="s">
+        <v>27</v>
+      </c>
+      <c r="H346" t="s">
+        <v>18</v>
+      </c>
+      <c r="I346" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" ht="15">
+      <c r="A347" t="s">
+        <v>263</v>
+      </c>
+      <c r="B347" t="s">
+        <v>58</v>
+      </c>
+      <c r="C347" t="s">
+        <v>47</v>
+      </c>
+      <c r="D347" t="s">
+        <v>137</v>
+      </c>
+      <c r="E347" t="s">
+        <v>45</v>
+      </c>
+      <c r="F347" t="s">
+        <v>138</v>
+      </c>
+      <c r="G347" t="s">
+        <v>27</v>
+      </c>
+      <c r="H347" t="s">
+        <v>18</v>
+      </c>
+      <c r="I347" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" ht="15">
+      <c r="A348" t="s">
+        <v>263</v>
+      </c>
+      <c r="B348" t="s">
+        <v>58</v>
+      </c>
+      <c r="C348" t="s">
+        <v>146</v>
+      </c>
+      <c r="D348" t="s">
+        <v>181</v>
+      </c>
+      <c r="E348" t="s">
+        <v>191</v>
+      </c>
+      <c r="F348" t="s">
+        <v>105</v>
+      </c>
+      <c r="G348" t="s">
+        <v>27</v>
+      </c>
+      <c r="H348" t="s">
+        <v>18</v>
+      </c>
+      <c r="I348" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" ht="15">
+      <c r="A349" t="s">
+        <v>263</v>
+      </c>
+      <c r="B349" t="s">
+        <v>58</v>
+      </c>
+      <c r="C349" t="s">
+        <v>89</v>
+      </c>
+      <c r="D349" t="s">
+        <v>90</v>
+      </c>
+      <c r="E349" t="s">
+        <v>102</v>
+      </c>
+      <c r="F349" t="s">
+        <v>61</v>
+      </c>
+      <c r="G349" t="s">
+        <v>27</v>
+      </c>
+      <c r="H349" t="s">
+        <v>18</v>
+      </c>
+      <c r="I349" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" ht="15">
+      <c r="A350" t="s">
+        <v>263</v>
+      </c>
+      <c r="B350" t="s">
+        <v>58</v>
+      </c>
+      <c r="C350" t="s">
+        <v>53</v>
+      </c>
+      <c r="D350" t="s">
+        <v>165</v>
+      </c>
+      <c r="E350" t="s">
+        <v>32</v>
+      </c>
+      <c r="F350" t="s">
+        <v>52</v>
+      </c>
+      <c r="G350" t="s">
+        <v>27</v>
+      </c>
+      <c r="H350" t="s">
+        <v>18</v>
+      </c>
+      <c r="I350" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" ht="15">
+      <c r="A351" t="s">
+        <v>263</v>
+      </c>
+      <c r="B351" t="s">
+        <v>58</v>
+      </c>
+      <c r="C351" t="s">
+        <v>147</v>
+      </c>
+      <c r="D351" t="s">
+        <v>115</v>
+      </c>
+      <c r="E351" t="s">
+        <v>148</v>
+      </c>
+      <c r="F351" t="s">
+        <v>94</v>
+      </c>
+      <c r="G351" t="s">
+        <v>27</v>
+      </c>
+      <c r="H351" t="s">
+        <v>18</v>
+      </c>
+      <c r="I351" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" ht="15">
+      <c r="A352" t="s">
+        <v>263</v>
+      </c>
+      <c r="B352" t="s">
+        <v>64</v>
+      </c>
+      <c r="C352" t="s">
+        <v>30</v>
+      </c>
+      <c r="D352" t="s">
+        <v>90</v>
+      </c>
+      <c r="E352" t="s">
+        <v>32</v>
+      </c>
+      <c r="F352" t="s">
+        <v>33</v>
+      </c>
+      <c r="G352" t="s">
+        <v>27</v>
+      </c>
+      <c r="H352" t="s">
+        <v>18</v>
+      </c>
+      <c r="I352" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" ht="15">
+      <c r="A353" t="s">
+        <v>263</v>
+      </c>
+      <c r="B353" t="s">
+        <v>64</v>
+      </c>
+      <c r="C353" t="s">
+        <v>265</v>
+      </c>
+      <c r="D353" t="s">
+        <v>269</v>
+      </c>
+      <c r="E353" t="s">
+        <v>75</v>
+      </c>
+      <c r="F353" t="s">
+        <v>161</v>
+      </c>
+      <c r="G353" t="s">
+        <v>27</v>
+      </c>
+      <c r="H353" t="s">
+        <v>18</v>
+      </c>
+      <c r="I353" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" ht="15">
+      <c r="A354" t="s">
+        <v>263</v>
+      </c>
+      <c r="B354" t="s">
+        <v>64</v>
+      </c>
+      <c r="C354" t="s">
+        <v>53</v>
+      </c>
+      <c r="D354" t="s">
+        <v>258</v>
+      </c>
+      <c r="E354" t="s">
+        <v>32</v>
+      </c>
+      <c r="F354" t="s">
+        <v>52</v>
+      </c>
+      <c r="G354" t="s">
+        <v>27</v>
+      </c>
+      <c r="H354" t="s">
+        <v>18</v>
+      </c>
+      <c r="I354" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" ht="15">
+      <c r="A355" t="s">
+        <v>263</v>
+      </c>
+      <c r="B355" t="s">
+        <v>64</v>
+      </c>
+      <c r="C355" t="s">
+        <v>147</v>
+      </c>
+      <c r="D355" t="s">
+        <v>165</v>
+      </c>
+      <c r="E355" t="s">
+        <v>148</v>
+      </c>
+      <c r="F355" t="s">
+        <v>94</v>
+      </c>
+      <c r="G355" t="s">
+        <v>27</v>
+      </c>
+      <c r="H355" t="s">
+        <v>18</v>
+      </c>
+      <c r="I355" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" ht="15">
+      <c r="A356" t="s">
+        <v>263</v>
+      </c>
+      <c r="B356" t="s">
+        <v>71</v>
+      </c>
+      <c r="C356" t="s">
+        <v>30</v>
+      </c>
+      <c r="D356" t="s">
+        <v>90</v>
+      </c>
+      <c r="E356" t="s">
+        <v>32</v>
+      </c>
+      <c r="F356" t="s">
+        <v>33</v>
+      </c>
+      <c r="G356" t="s">
+        <v>27</v>
+      </c>
+      <c r="H356" t="s">
+        <v>18</v>
+      </c>
+      <c r="I356" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" ht="15">
+      <c r="A357" t="s">
+        <v>263</v>
+      </c>
+      <c r="B357" t="s">
+        <v>71</v>
+      </c>
+      <c r="C357" t="s">
+        <v>267</v>
+      </c>
+      <c r="D357" t="s">
+        <v>270</v>
+      </c>
+      <c r="E357" t="s">
+        <v>140</v>
+      </c>
+      <c r="F357" t="s">
+        <v>157</v>
+      </c>
+      <c r="G357" t="s">
+        <v>27</v>
+      </c>
+      <c r="H357" t="s">
+        <v>18</v>
+      </c>
+      <c r="I357" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" ht="15">
+      <c r="A358" t="s">
+        <v>263</v>
+      </c>
+      <c r="B358" t="s">
+        <v>71</v>
+      </c>
+      <c r="C358" t="s">
+        <v>147</v>
+      </c>
+      <c r="D358" t="s">
+        <v>128</v>
+      </c>
+      <c r="E358" t="s">
+        <v>148</v>
+      </c>
+      <c r="F358" t="s">
+        <v>94</v>
+      </c>
+      <c r="G358" t="s">
+        <v>27</v>
+      </c>
+      <c r="H358" t="s">
+        <v>18</v>
+      </c>
+      <c r="I358" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10561,7 +11809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6a288f1c-d0d3-4261-a19e-ad746eae1d31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{00c846f4-234e-4819-a718-071cf2ecb722}">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10581,16 +11829,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -10610,16 +11858,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="C2" t="s">
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E2" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="F2" t="s">
         <v>33</v>
@@ -10639,13 +11887,13 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -10668,13 +11916,13 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -10697,16 +11945,16 @@
         <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C5" t="s">
         <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E5" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -10723,19 +11971,19 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B6" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="E6" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="F6" t="s">
         <v>33</v>
@@ -10758,8 +12006,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5ae72f62-8945-4cc3-a7a4-5c3bc8ed0be2}">
-  <dimension ref="A1:F47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c0d2a9b6-7755-4929-9efe-4481356d090c}">
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -10775,13 +12023,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -10795,16 +12043,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -10815,13 +12063,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E3" t="s">
         <v>146</v>
@@ -10835,16 +12083,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -10855,13 +12103,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E5" t="s">
         <v>89</v>
@@ -10875,16 +12123,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E6" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -10895,13 +12143,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C7" t="s">
         <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
@@ -10915,13 +12163,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -10935,13 +12183,13 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C9" t="s">
         <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E9" t="s">
         <v>142</v>
@@ -10955,16 +12203,16 @@
         <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
         <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -10975,16 +12223,16 @@
         <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C11" t="s">
         <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E11" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -10995,16 +12243,16 @@
         <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="C12" t="s">
         <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E12" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -11015,16 +12263,16 @@
         <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -11035,13 +12283,13 @@
         <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C14" t="s">
         <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E14" t="s">
         <v>127</v>
@@ -11055,13 +12303,13 @@
         <v>110</v>
       </c>
       <c r="B15" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C15" t="s">
         <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
@@ -11075,16 +12323,16 @@
         <v>110</v>
       </c>
       <c r="B16" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C16" t="s">
         <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -11095,16 +12343,16 @@
         <v>110</v>
       </c>
       <c r="B17" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E17" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -11115,13 +12363,13 @@
         <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C18" t="s">
         <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E18" t="s">
         <v>155</v>
@@ -11135,13 +12383,13 @@
         <v>110</v>
       </c>
       <c r="B19" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="C19" t="s">
         <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E19" t="s">
         <v>132</v>
@@ -11155,13 +12403,13 @@
         <v>110</v>
       </c>
       <c r="B20" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C20" t="s">
         <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E20" t="s">
         <v>106</v>
@@ -11175,13 +12423,13 @@
         <v>110</v>
       </c>
       <c r="B21" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C21" t="s">
         <v>155</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E21" t="s">
         <v>147</v>
@@ -11195,13 +12443,13 @@
         <v>143</v>
       </c>
       <c r="B22" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E22" t="s">
         <v>43</v>
@@ -11215,16 +12463,16 @@
         <v>143</v>
       </c>
       <c r="B23" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C23" t="s">
         <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -11235,13 +12483,13 @@
         <v>143</v>
       </c>
       <c r="B24" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C24" t="s">
         <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E24" t="s">
         <v>88</v>
@@ -11252,19 +12500,19 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C25" t="s">
         <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E25" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -11272,19 +12520,19 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C26" t="s">
         <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E26" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -11292,16 +12540,16 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B27" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D27" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E27" t="s">
         <v>77</v>
@@ -11312,16 +12560,16 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B28" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C28" t="s">
         <v>146</v>
       </c>
       <c r="D28" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E28" t="s">
         <v>13</v>
@@ -11332,19 +12580,19 @@
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B29" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C29" t="s">
         <v>146</v>
       </c>
       <c r="D29" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E29" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -11352,16 +12600,16 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B30" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C30" t="s">
         <v>53</v>
       </c>
       <c r="D30" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -11372,16 +12620,16 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B31" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C31" t="s">
         <v>83</v>
       </c>
       <c r="D31" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E31" t="s">
         <v>101</v>
@@ -11392,16 +12640,16 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B32" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C32" t="s">
         <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E32" t="s">
         <v>60</v>
@@ -11412,16 +12660,16 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B33" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C33" t="s">
         <v>53</v>
       </c>
       <c r="D33" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -11432,16 +12680,16 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B34" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="C34" t="s">
         <v>53</v>
       </c>
       <c r="D34" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -11452,16 +12700,16 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B35" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C35" t="s">
         <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
@@ -11472,16 +12720,16 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B36" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C36" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="D36" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -11492,16 +12740,16 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B37" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C37" t="s">
         <v>53</v>
       </c>
       <c r="D37" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -11512,16 +12760,16 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B38" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="C38" t="s">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -11532,16 +12780,16 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B39" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="D39" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -11552,16 +12800,16 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B40" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C40" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -11572,16 +12820,16 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B41" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C41" t="s">
-        <v>252</v>
+        <v>53</v>
       </c>
       <c r="D41" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
@@ -11592,16 +12840,16 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B42" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
@@ -11612,16 +12860,16 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B43" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -11632,16 +12880,16 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B44" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D44" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
@@ -11652,16 +12900,16 @@
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B45" t="s">
+        <v>301</v>
+      </c>
+      <c r="C45" t="s">
+        <v>261</v>
+      </c>
+      <c r="D45" t="s">
         <v>293</v>
-      </c>
-      <c r="C45" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" t="s">
-        <v>274</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
@@ -11672,16 +12920,16 @@
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B46" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>146</v>
       </c>
       <c r="D46" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
@@ -11692,21 +12940,221 @@
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B47" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C47" t="s">
-        <v>256</v>
+        <v>89</v>
       </c>
       <c r="D47" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15">
+      <c r="A48" t="s">
+        <v>263</v>
+      </c>
+      <c r="B48" t="s">
+        <v>286</v>
+      </c>
+      <c r="C48" t="s">
+        <v>147</v>
+      </c>
+      <c r="D48" t="s">
+        <v>293</v>
+      </c>
+      <c r="E48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15">
+      <c r="A49" t="s">
+        <v>263</v>
+      </c>
+      <c r="B49" t="s">
+        <v>298</v>
+      </c>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" t="s">
+        <v>287</v>
+      </c>
+      <c r="E49" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15">
+      <c r="A50" t="s">
+        <v>263</v>
+      </c>
+      <c r="B50" t="s">
+        <v>298</v>
+      </c>
+      <c r="C50" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" t="s">
+        <v>299</v>
+      </c>
+      <c r="E50" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15">
+      <c r="A51" t="s">
+        <v>263</v>
+      </c>
+      <c r="B51" t="s">
+        <v>295</v>
+      </c>
+      <c r="C51" t="s">
+        <v>47</v>
+      </c>
+      <c r="D51" t="s">
+        <v>299</v>
+      </c>
+      <c r="E51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15">
+      <c r="A52" t="s">
+        <v>263</v>
+      </c>
+      <c r="B52" t="s">
+        <v>289</v>
+      </c>
+      <c r="C52" t="s">
+        <v>146</v>
+      </c>
+      <c r="D52" t="s">
+        <v>285</v>
+      </c>
+      <c r="E52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15">
+      <c r="A53" t="s">
+        <v>263</v>
+      </c>
+      <c r="B53" t="s">
+        <v>300</v>
+      </c>
+      <c r="C53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53" t="s">
+        <v>299</v>
+      </c>
+      <c r="E53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15">
+      <c r="A54" t="s">
+        <v>263</v>
+      </c>
+      <c r="B54" t="s">
+        <v>303</v>
+      </c>
+      <c r="C54" t="s">
+        <v>265</v>
+      </c>
+      <c r="D54" t="s">
+        <v>296</v>
+      </c>
+      <c r="E54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15">
+      <c r="A55" t="s">
+        <v>263</v>
+      </c>
+      <c r="B55" t="s">
+        <v>303</v>
+      </c>
+      <c r="C55" t="s">
+        <v>53</v>
+      </c>
+      <c r="D55" t="s">
+        <v>285</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15">
+      <c r="A56" t="s">
+        <v>263</v>
+      </c>
+      <c r="B56" t="s">
+        <v>301</v>
+      </c>
+      <c r="C56" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56" t="s">
+        <v>287</v>
+      </c>
+      <c r="E56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15">
+      <c r="A57" t="s">
+        <v>263</v>
+      </c>
+      <c r="B57" t="s">
+        <v>301</v>
+      </c>
+      <c r="C57" t="s">
+        <v>267</v>
+      </c>
+      <c r="D57" t="s">
+        <v>293</v>
+      </c>
+      <c r="E57" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -12125,7 +12125,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bezpłatne</t>
         </is>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -580,7 +580,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>-</t>
@@ -623,7 +622,6 @@
           <t>Wrzeszcz Barbara</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -713,7 +711,6 @@
           <t>Filipiak Wiesław</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -756,7 +753,6 @@
           <t>Wrzeszcz Barbara</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -799,7 +795,6 @@
           <t>Wrzeszcz Barbara</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -842,7 +837,6 @@
           <t>Filipiak Wiesław</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -885,7 +879,6 @@
           <t>Kaczorowski Waldemar</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -928,7 +921,6 @@
           <t>Granatowska Mariola</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -971,7 +963,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1014,7 +1005,6 @@
           <t>Nowak Magdalena</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1057,7 +1047,6 @@
           <t>Wrzeszcz Barbara</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -1100,7 +1089,6 @@
           <t>Galert Anna</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1143,7 +1131,6 @@
           <t>Wojciechowski Łukasz</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -1186,7 +1173,6 @@
           <t>Filipek Anna</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1229,7 +1215,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1272,7 +1257,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>-</t>
@@ -1315,7 +1299,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>-</t>
@@ -1358,7 +1341,6 @@
           <t>Zając Ewa</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -1401,7 +1383,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>-</t>
@@ -1444,7 +1425,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1487,7 +1467,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>-</t>
@@ -1530,7 +1509,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>-</t>
@@ -1573,7 +1551,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1616,7 +1593,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>-</t>
@@ -1659,7 +1635,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>-</t>
@@ -1702,7 +1677,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1745,7 +1719,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1788,7 +1761,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1831,7 +1803,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1874,7 +1845,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>-</t>
@@ -1917,7 +1887,6 @@
           <t>Leńczowska Iwona</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -1960,7 +1929,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>-</t>
@@ -2003,7 +1971,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2046,7 +2013,6 @@
           <t>Wojciechowski Łukasz</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2089,7 +2055,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>-</t>
@@ -2132,7 +2097,6 @@
           <t>Zając Ewa</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2222,7 +2186,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2265,7 +2228,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>-</t>
@@ -2308,7 +2270,6 @@
           <t>Dalach Krystyna</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2351,7 +2312,6 @@
           <t>Sałdyka Karolina</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2394,7 +2354,6 @@
           <t>Zając Ewa</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -2437,7 +2396,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>-</t>
@@ -2480,7 +2438,6 @@
           <t>Płatek Krzysztof</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2570,7 +2527,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2613,7 +2569,6 @@
           <t>Płatek Krzysztof</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2656,7 +2611,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>-</t>
@@ -2699,7 +2653,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>-</t>
@@ -2742,7 +2695,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>-</t>
@@ -2785,7 +2737,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>-</t>
@@ -2828,7 +2779,6 @@
           <t>Dalach Krystyna</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -2871,7 +2821,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>-</t>
@@ -2914,7 +2863,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>-</t>
@@ -2957,7 +2905,6 @@
           <t>Dalach Krystyna</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3000,7 +2947,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>-</t>
@@ -3043,7 +2989,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>-</t>
@@ -3086,7 +3031,6 @@
           <t>Dalach Krystyna</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3176,7 +3120,6 @@
           <t>Wrzeszcz Barbara</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -3219,7 +3162,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>-</t>
@@ -3262,7 +3204,6 @@
           <t>Marzec Renata</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3305,7 +3246,6 @@
           <t>Dalach Krystyna</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3348,7 +3288,6 @@
           <t>Wojciechowski Łukasz</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3391,7 +3330,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>-</t>
@@ -3434,7 +3372,6 @@
           <t>Marzec Renata</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3477,7 +3414,6 @@
           <t>Nestoruk Lidia</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3520,7 +3456,6 @@
           <t>Marzec Renata</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3563,7 +3498,6 @@
           <t>Kruk Marcin</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3606,7 +3540,6 @@
           <t>Wrzeszcz Barbara</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -3639,13 +3572,11 @@
           <t>Język polski</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>-</t>
@@ -3688,7 +3619,6 @@
           <t>Krzemińska Beata</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3731,7 +3661,6 @@
           <t>Nestoruk Lidia</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3774,7 +3703,6 @@
           <t>Marzec Renata</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3817,7 +3745,6 @@
           <t>Mucha Anna</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3860,7 +3787,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>-</t>
@@ -3903,7 +3829,6 @@
           <t>Galert Anna</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -3946,7 +3871,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>-</t>
@@ -3989,7 +3913,6 @@
           <t>Misiąg Anna</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -4032,7 +3955,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>-</t>
@@ -4075,7 +3997,6 @@
           <t>Kosin Anna</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -4118,7 +4039,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -4161,7 +4081,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>-</t>
@@ -4204,7 +4123,6 @@
           <t>Zając Ewa</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -4247,7 +4165,6 @@
           <t>Wójcik Kamil</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -4290,7 +4207,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -4427,7 +4343,6 @@
           <t>Hudziec Agnieszka</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -4564,7 +4479,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -4607,7 +4521,6 @@
           <t>Piątek-Pawłowska Bożena</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -4650,7 +4563,6 @@
           <t>Wójcik Kamil</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -4693,7 +4605,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -4736,7 +4647,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>-</t>
@@ -4826,7 +4736,6 @@
           <t>Sobczak Anna</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -4869,7 +4778,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -4912,7 +4820,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>-</t>
@@ -5002,7 +4909,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -5045,7 +4951,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>-</t>
@@ -5088,7 +4993,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>-</t>
@@ -5131,7 +5035,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -5268,7 +5171,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>-</t>
@@ -5311,7 +5213,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>-</t>
@@ -5354,7 +5255,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -5397,7 +5297,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>-</t>
@@ -5487,7 +5386,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>-</t>
@@ -5530,7 +5428,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>-</t>
@@ -5573,7 +5470,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -5616,7 +5512,6 @@
           <t>Nestoruk Lidia</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -5706,7 +5601,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>-</t>
@@ -5749,7 +5643,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>-</t>
@@ -5792,7 +5685,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>-</t>
@@ -5835,7 +5727,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -5878,7 +5769,6 @@
           <t>Hudziec Agnieszka</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -5968,7 +5858,6 @@
           <t>Biczysko Wojciech</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -5998,7 +5887,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Biznes i zarządzanie</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6008,10 +5897,9 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Kaczorowski Waldemar</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
+          <t>Smirnow-Zechman Eleonora</t>
+        </is>
+      </c>
       <c r="I127" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -6054,7 +5942,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -6097,7 +5984,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -6140,7 +6026,6 @@
           <t>Sałdyka Karolina</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -6371,7 +6256,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>-</t>
@@ -6461,7 +6345,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -6504,7 +6387,6 @@
           <t>Pietrycha Małgorzata</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -6547,7 +6429,6 @@
           <t>Taszycka Magdalena</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -6778,7 +6659,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>-</t>
@@ -6868,7 +6748,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>-</t>
@@ -6911,7 +6790,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>-</t>
@@ -6954,7 +6832,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>-</t>
@@ -6997,7 +6874,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>-</t>
@@ -7040,7 +6916,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>-</t>
@@ -7083,7 +6958,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>-</t>
@@ -7126,7 +7000,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>-</t>
@@ -7169,7 +7042,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>-</t>
@@ -7212,7 +7084,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>-</t>
@@ -7255,7 +7126,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>-</t>
@@ -7298,7 +7168,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>-</t>
@@ -7341,7 +7210,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>-</t>
@@ -7384,7 +7252,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>-</t>
@@ -7427,7 +7294,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>-</t>
@@ -7470,7 +7336,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>-</t>
@@ -7513,7 +7378,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>-</t>
@@ -7556,7 +7420,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>-</t>
@@ -7599,7 +7462,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>-</t>
@@ -7642,7 +7504,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>-</t>
@@ -7685,7 +7546,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>-</t>
@@ -7728,7 +7588,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>-</t>
@@ -7771,7 +7630,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>-</t>
@@ -7814,7 +7672,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>-</t>
@@ -7857,7 +7714,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>-</t>
@@ -7900,7 +7756,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>-</t>
@@ -7943,7 +7798,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>-</t>
@@ -7986,7 +7840,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>-</t>
@@ -8029,7 +7882,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>-</t>
@@ -8072,7 +7924,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>-</t>
@@ -8115,7 +7966,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>-</t>
@@ -8158,7 +8008,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>-</t>
@@ -8201,7 +8050,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>-</t>
@@ -8244,7 +8092,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>-</t>
@@ -8287,7 +8134,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>-</t>
@@ -8330,7 +8176,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>-</t>
@@ -8373,7 +8218,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>-</t>
@@ -8416,7 +8260,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>-</t>
@@ -8459,7 +8302,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>-</t>
@@ -8502,7 +8344,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>-</t>
@@ -8545,7 +8386,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>-</t>
@@ -8588,7 +8428,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>-</t>
@@ -8631,7 +8470,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>-</t>
@@ -8674,7 +8512,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>-</t>
@@ -8717,7 +8554,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>-</t>
@@ -8760,7 +8596,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>-</t>
@@ -8803,7 +8638,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>-</t>
@@ -8846,7 +8680,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>-</t>
@@ -8889,7 +8722,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>-</t>
@@ -8932,7 +8764,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>-</t>
@@ -8975,7 +8806,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>-</t>
@@ -9018,7 +8848,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>-</t>
@@ -9061,7 +8890,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>-</t>
@@ -9104,7 +8932,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>-</t>
@@ -9147,7 +8974,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>-</t>
@@ -9190,7 +9016,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>-</t>
@@ -9233,7 +9058,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>-</t>
@@ -9276,7 +9100,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>-</t>
@@ -9319,7 +9142,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>-</t>
@@ -9362,7 +9184,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>-</t>
@@ -9405,7 +9226,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>-</t>
@@ -9448,7 +9268,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>-</t>
@@ -9491,7 +9310,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>-</t>
@@ -9534,7 +9352,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>-</t>
@@ -9577,7 +9394,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>-</t>
@@ -9620,7 +9436,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>-</t>
@@ -9663,7 +9478,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>-</t>
@@ -9706,7 +9520,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>-</t>
@@ -9749,7 +9562,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>-</t>
@@ -9792,7 +9604,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>-</t>
@@ -9835,7 +9646,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>-</t>
@@ -9878,7 +9688,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>-</t>
@@ -9921,7 +9730,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>-</t>
@@ -9964,7 +9772,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>-</t>
@@ -10007,7 +9814,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>-</t>
@@ -10050,7 +9856,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>-</t>
@@ -10093,7 +9898,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>-</t>
@@ -10136,7 +9940,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>-</t>
@@ -10179,7 +9982,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>-</t>
@@ -10222,7 +10024,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>-</t>
@@ -10265,7 +10066,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>-</t>
@@ -10308,7 +10108,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>-</t>
@@ -10351,7 +10150,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
           <t>-</t>
@@ -10394,7 +10192,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
           <t>-</t>
@@ -10437,7 +10234,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>-</t>
@@ -10480,7 +10276,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>-</t>
@@ -10523,7 +10318,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
           <t>-</t>
@@ -10566,7 +10360,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
           <t>-</t>
@@ -10609,7 +10402,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
           <t>-</t>
@@ -10652,7 +10444,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>-</t>
@@ -10695,7 +10486,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>-</t>
@@ -10738,7 +10528,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>-</t>
@@ -10781,7 +10570,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>-</t>
@@ -10824,7 +10612,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
           <t>-</t>
@@ -10867,7 +10654,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>-</t>
@@ -10910,7 +10696,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
           <t>-</t>
@@ -10953,7 +10738,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
           <t>-</t>
@@ -10996,7 +10780,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>-</t>
@@ -11039,7 +10822,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
           <t>-</t>
@@ -11082,7 +10864,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>-</t>
@@ -11125,7 +10906,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>-</t>
@@ -11168,7 +10948,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
           <t>-</t>
@@ -11211,7 +10990,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>-</t>
@@ -11254,7 +11032,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>-</t>
@@ -11297,7 +11074,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
           <t>-</t>
@@ -11340,7 +11116,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>-</t>
@@ -11383,7 +11158,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>-</t>
@@ -11426,7 +11200,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
           <t>-</t>
@@ -11469,7 +11242,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
           <t>-</t>
@@ -11512,7 +11284,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
           <t>-</t>
@@ -11555,7 +11326,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
           <t>-</t>
@@ -11598,7 +11368,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>-</t>
@@ -11641,7 +11410,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>-</t>
@@ -11684,7 +11452,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
           <t>-</t>
@@ -11727,7 +11494,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
           <t>-</t>
@@ -11770,7 +11536,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
           <t>-</t>
@@ -11813,7 +11578,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
           <t>-</t>
@@ -11856,7 +11620,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
           <t>-</t>
@@ -11899,7 +11662,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
           <t>-</t>
@@ -11942,7 +11704,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>-</t>
@@ -11985,7 +11746,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>-</t>
@@ -12028,7 +11788,6 @@
           <t>Rejno Julita</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -12165,7 +11924,6 @@
           <t>Rejno Julita</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -12302,7 +12060,6 @@
           <t>Rejno Julita</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -12345,7 +12102,6 @@
           <t>Jastrzębska-Majtyka Agnieszka</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -12388,7 +12144,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -12431,7 +12186,6 @@
           <t>Filipiak Wiesław</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -12474,7 +12228,6 @@
           <t>Rejno Julita</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -12517,7 +12270,6 @@
           <t>Jastrzębska-Majtyka Agnieszka</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -12560,7 +12312,6 @@
           <t>Kończyńska Małgorzata</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -12603,7 +12354,6 @@
           <t>Filipiak Wiesław</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -12646,7 +12396,6 @@
           <t>Rejno Julita</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -12689,7 +12438,6 @@
           <t>Jastrzębska-Majtyka Agnieszka</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -12732,7 +12480,6 @@
           <t>Rejno Julita</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -12775,7 +12522,6 @@
           <t>Jastrzębska-Majtyka Agnieszka</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -12818,7 +12564,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
           <t>-</t>
@@ -12861,7 +12606,6 @@
           <t>Jastrzębska-Majtyka Agnieszka</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -12904,7 +12648,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
           <t>-</t>
@@ -12947,7 +12690,6 @@
           <t>Krzemińska Beata</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
           <t>Dodatkowo płatne</t>
@@ -12990,7 +12732,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
           <t>-</t>
@@ -13033,7 +12774,6 @@
           <t>Jastrzębska-Majtyka Agnieszka</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -13076,7 +12816,6 @@
           <t>Uczniowie przychodzą później</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
           <t>-</t>
@@ -13119,7 +12858,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
           <t>-</t>
@@ -13162,7 +12900,6 @@
           <t>Jastrzębska-Majtyka Agnieszka</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
           <t>Bezpłatne</t>
@@ -13205,7 +12942,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
           <t>-</t>
@@ -13248,7 +12984,6 @@
           <t>Uczniowie zwolnieni do domu</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
           <t>-</t>
@@ -13291,7 +13026,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
           <t>-</t>
@@ -13334,7 +13068,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
           <t>-</t>
@@ -13377,7 +13110,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
           <t>-</t>
@@ -13420,7 +13152,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
           <t>-</t>
@@ -13463,7 +13194,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
           <t>-</t>
@@ -13506,7 +13236,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
           <t>-</t>
@@ -13549,7 +13278,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
           <t>-</t>
@@ -13592,7 +13320,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
           <t>-</t>
@@ -13635,7 +13362,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
           <t>-</t>
@@ -13678,7 +13404,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
           <t>-</t>
@@ -13721,7 +13446,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
           <t>-</t>
@@ -13764,7 +13488,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
           <t>-</t>
@@ -13807,7 +13530,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
           <t>-</t>
@@ -13850,7 +13572,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
           <t>-</t>
@@ -13893,7 +13614,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
           <t>-</t>
@@ -13936,7 +13656,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr">
         <is>
           <t>-</t>
@@ -13979,7 +13698,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
           <t>-</t>
@@ -14022,7 +13740,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
           <t>-</t>
@@ -14065,7 +13782,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr">
         <is>
           <t>-</t>
@@ -14108,7 +13824,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr">
         <is>
           <t>-</t>
@@ -14151,7 +13866,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
           <t>-</t>
@@ -14194,7 +13908,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr">
         <is>
           <t>-</t>
@@ -14237,7 +13950,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr">
         <is>
           <t>-</t>
@@ -14280,7 +13992,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr">
         <is>
           <t>-</t>
@@ -14323,7 +14034,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr">
         <is>
           <t>-</t>
@@ -14366,7 +14076,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
           <t>-</t>
@@ -14409,7 +14118,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr">
         <is>
           <t>-</t>
@@ -14452,7 +14160,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr">
         <is>
           <t>-</t>
@@ -14495,7 +14202,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr">
         <is>
           <t>-</t>
@@ -14538,7 +14244,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr">
         <is>
           <t>-</t>
@@ -14581,7 +14286,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr">
         <is>
           <t>-</t>
@@ -14624,7 +14328,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr">
         <is>
           <t>-</t>
@@ -14667,7 +14370,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr">
         <is>
           <t>-</t>
@@ -14710,7 +14412,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr">
         <is>
           <t>-</t>
@@ -14753,7 +14454,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr">
         <is>
           <t>-</t>
@@ -14796,7 +14496,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
           <t>-</t>
@@ -14839,7 +14538,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
           <t>-</t>
@@ -14882,7 +14580,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
           <t>-</t>
@@ -14925,7 +14622,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
           <t>-</t>
@@ -14968,7 +14664,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr">
         <is>
           <t>-</t>
@@ -15011,7 +14706,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
         <is>
           <t>-</t>
@@ -15054,7 +14748,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
         <is>
           <t>-</t>
@@ -15097,7 +14790,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr">
         <is>
           <t>-</t>
@@ -15140,7 +14832,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr">
         <is>
           <t>-</t>
@@ -15183,7 +14874,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr">
         <is>
           <t>-</t>
@@ -15226,7 +14916,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr">
         <is>
           <t>-</t>
@@ -15269,7 +14958,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr">
         <is>
           <t>-</t>
@@ -15312,7 +15000,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr">
         <is>
           <t>-</t>
@@ -15355,7 +15042,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr">
         <is>
           <t>-</t>
@@ -15398,7 +15084,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr">
         <is>
           <t>-</t>
@@ -15441,7 +15126,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr">
         <is>
           <t>-</t>
@@ -15484,7 +15168,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
           <t>-</t>
@@ -15527,7 +15210,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
         <is>
           <t>-</t>
@@ -15570,7 +15252,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr">
         <is>
           <t>-</t>
@@ -15613,7 +15294,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr">
         <is>
           <t>-</t>
@@ -15656,7 +15336,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr">
         <is>
           <t>-</t>
@@ -15699,7 +15378,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr">
         <is>
           <t>-</t>
@@ -15742,7 +15420,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr">
         <is>
           <t>-</t>
@@ -15785,7 +15462,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr">
         <is>
           <t>-</t>
@@ -15828,7 +15504,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr">
         <is>
           <t>-</t>
@@ -15871,7 +15546,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr">
         <is>
           <t>-</t>
@@ -15914,7 +15588,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr">
         <is>
           <t>-</t>
@@ -15957,7 +15630,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr">
         <is>
           <t>-</t>
@@ -16000,7 +15672,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr">
         <is>
           <t>-</t>
@@ -16117,7 +15788,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>-</t>
@@ -16160,7 +15830,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>-</t>
@@ -16203,7 +15872,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>-</t>
@@ -16236,13 +15904,11 @@
           <t>język polski</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>-</t>
@@ -16285,7 +15951,6 @@
           <t>Zastępstwo</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>-</t>
@@ -16374,7 +16039,6 @@
           <t>Ostrowska Ewa</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -16402,7 +16066,6 @@
           <t>Kosin Anna</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -16430,7 +16093,6 @@
           <t>Małecka Barbara</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -16458,7 +16120,6 @@
           <t>Mucha Anna</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -16486,7 +16147,6 @@
           <t>Skarupa Agnieszka</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -16514,7 +16174,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -16542,7 +16201,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -16570,7 +16228,6 @@
           <t>Misiąg Anna</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -16598,7 +16255,6 @@
           <t>Ulanowska Magdalena</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -16626,7 +16282,6 @@
           <t>Socha Dariusz</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -16654,7 +16309,6 @@
           <t>Cieśla Marcin</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -16682,7 +16336,6 @@
           <t>Małecka Barbara</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -16710,7 +16363,6 @@
           <t>Kruk Marcin</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -16738,7 +16390,6 @@
           <t>Krycia Ewelina</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -16766,7 +16417,6 @@
           <t>Danielewski Paweł</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -16794,7 +16444,6 @@
           <t>Skarupa Agnieszka</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -16822,7 +16471,6 @@
           <t>Zaleska Magdalena</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -16850,7 +16498,6 @@
           <t>Krzemińska Beata</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -16878,7 +16525,6 @@
           <t>Płatek Krzysztof</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -16906,7 +16552,6 @@
           <t>Smirnow-Zechman Eleonora</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -16934,7 +16579,6 @@
           <t>Najwer Maciej</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -16962,7 +16606,6 @@
           <t>Danielewski Paweł</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -16990,7 +16633,6 @@
           <t>Leńczowska Iwona</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
@@ -17018,7 +16660,6 @@
           <t>Smereka Alicja</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
@@ -17046,7 +16687,6 @@
           <t>Taszycka Magdalena</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -17106,7 +16746,6 @@
           <t>Krycia Ewelina</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -17134,7 +16773,6 @@
           <t>Karczmarz Aleksandra</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
@@ -17162,7 +16800,6 @@
           <t>Misiąg Anna</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
@@ -17190,7 +16827,6 @@
           <t>Dalach Krystyna</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
@@ -17218,7 +16854,6 @@
           <t>Wojciechowski Łukasz</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
@@ -17246,7 +16881,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
@@ -17274,7 +16908,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
@@ -17302,7 +16935,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
@@ -17330,7 +16962,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
@@ -17358,7 +16989,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
@@ -17386,7 +17016,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
@@ -17414,7 +17043,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
@@ -17442,7 +17070,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
@@ -17470,7 +17097,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
@@ -17498,7 +17124,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
@@ -17526,7 +17151,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
@@ -17554,7 +17178,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
@@ -17582,7 +17205,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
@@ -17610,7 +17232,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
@@ -17638,7 +17259,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
@@ -17666,7 +17286,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
@@ -17694,7 +17313,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
@@ -17722,7 +17340,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
@@ -17750,7 +17367,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
@@ -17778,7 +17394,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
@@ -17806,7 +17421,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
@@ -17834,7 +17448,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
@@ -17862,7 +17475,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
@@ -17890,7 +17502,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
@@ -17918,7 +17529,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="186">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -123,27 +123,30 @@
     <t>Zajęcia z wychowawcą</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
+    <t>zajęcia profilaktyczne - sala gimnastyczna</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Skarupa Agnieszka</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
+    <t>3, 09:40-10:25</t>
+  </si>
+  <si>
     <t>sg2</t>
   </si>
   <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
-    <t>zajęcia profilaktyczne - sala gimnastyczna</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Skarupa Agnieszka</t>
-  </si>
-  <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
-    <t>3, 09:40-10:25</t>
-  </si>
-  <si>
     <t>Smirnow-Zechman Eleonora</t>
   </si>
   <si>
@@ -207,6 +210,12 @@
     <t>8, 14:05-14:50</t>
   </si>
   <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
     <t>3TFA</t>
   </si>
   <si>
@@ -231,9 +240,24 @@
     <t>sg6</t>
   </si>
   <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>10, 15:45-16:30</t>
   </si>
   <si>
+    <t>3CA</t>
+  </si>
+  <si>
+    <t>Doradztwo zawodowe</t>
+  </si>
+  <si>
+    <t>W ramach pensum</t>
+  </si>
+  <si>
     <t>1TH</t>
   </si>
   <si>
@@ -249,9 +273,6 @@
     <t>2WA</t>
   </si>
   <si>
-    <t>Język polski</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -264,9 +285,6 @@
     <t>Zastępstwo</t>
   </si>
   <si>
-    <t>3CA</t>
-  </si>
-  <si>
     <t>Technika w produkcji cukierniczej</t>
   </si>
   <si>
@@ -276,9 +294,6 @@
     <t>Technika w produkcji gastronomicznej</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>5TFB</t>
   </si>
   <si>
@@ -294,9 +309,27 @@
     <t>Małecka Barbara</t>
   </si>
   <si>
+    <t>3CB</t>
+  </si>
+  <si>
+    <t>p. Kończyńska, lekcja przeniesiona z 8 godziny lekcyjnej</t>
+  </si>
+  <si>
     <t>2TFA</t>
   </si>
   <si>
+    <t>Podstawy fryzjerstwa</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Mikołajczak Sylwia</t>
+  </si>
+  <si>
+    <t>3FC</t>
+  </si>
+  <si>
     <t>30.09.2026</t>
   </si>
   <si>
@@ -360,6 +393,15 @@
     <t>Edukacja zdrowotna</t>
   </si>
   <si>
+    <t>Piątek-Pawłowska Bożena</t>
+  </si>
+  <si>
+    <t>4TFA</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>Fiodorów Małgorzata</t>
   </si>
   <si>
@@ -393,6 +435,9 @@
     <t>2S</t>
   </si>
   <si>
+    <t>4TFB|IND*KM</t>
+  </si>
+  <si>
     <t>1FC</t>
   </si>
   <si>
@@ -426,9 +471,6 @@
     <t>01.10.2026</t>
   </si>
   <si>
-    <t>3CB</t>
-  </si>
-  <si>
     <t>02.10.2026</t>
   </si>
   <si>
@@ -441,6 +483,9 @@
     <t>próbna ewakuacja - inspektor zewnętrzny</t>
   </si>
   <si>
+    <t>3FB</t>
+  </si>
+  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -459,9 +504,24 @@
     <t>IND</t>
   </si>
   <si>
+    <t>08:50-09:35</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matematyka </t>
   </si>
   <si>
+    <t>11:30-13:00</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>język polski</t>
+  </si>
+  <si>
     <t>Miejsce dyżuru</t>
   </si>
   <si>
@@ -483,12 +543,15 @@
     <t>piętro_1</t>
   </si>
   <si>
+    <t>piętro_3</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
+  </si>
+  <si>
     <t>15:40-15:45</t>
   </si>
   <si>
-    <t>Filusz Marzena</t>
-  </si>
-  <si>
     <t>Sałdyka Karolina</t>
   </si>
   <si>
@@ -501,9 +564,6 @@
     <t>09:35-09:40</t>
   </si>
   <si>
-    <t>piętro_3</t>
-  </si>
-  <si>
     <t>08:45-08:50</t>
   </si>
   <si>
@@ -514,6 +574,12 @@
   </si>
   <si>
     <t>13:10-13:15</t>
+  </si>
+  <si>
+    <t>16:30-16:35</t>
+  </si>
+  <si>
+    <t>bramka wejściowa</t>
   </si>
 </sst>
 </file>
@@ -963,7 +1029,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6466f1ba-5347-4a6d-92ad-0cad42877f82}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c80b4d65-d342-4837-ab53-5fcffb584c1f}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -984,18 +1050,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c8688e94-ca20-43ff-84e5-03c18c2df18d}">
-  <dimension ref="A1:I108"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{aa670ff9-0bf5-4702-9033-200baebcb9cc}">
+  <dimension ref="A1:I135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
-    <col min="4" max="4" width="12.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="13.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="37.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1219,10 +1285,10 @@
         <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
         <v>35</v>
@@ -1239,19 +1305,19 @@
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H9" t="s">
         <v>35</v>
@@ -1265,7 +1331,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>25</v>
@@ -1294,22 +1360,22 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
@@ -1323,22 +1389,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
@@ -1352,22 +1418,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s">
         <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
@@ -1381,13 +1447,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
         <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -1410,22 +1476,22 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
@@ -1439,22 +1505,22 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s">
         <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
@@ -1468,22 +1534,22 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
         <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H17" t="s">
         <v>18</v>
@@ -1497,13 +1563,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -1526,22 +1592,22 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
@@ -1555,13 +1621,13 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -1584,22 +1650,22 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
@@ -1613,22 +1679,22 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
         <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
         <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H22" t="s">
         <v>18</v>
@@ -1642,28 +1708,28 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H23" t="s">
         <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1671,28 +1737,28 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="G24" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H24" t="s">
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1700,28 +1766,28 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -1729,28 +1795,28 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" t="s">
         <v>66</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
         <v>67</v>
       </c>
-      <c r="E26" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>68</v>
       </c>
-      <c r="G26" t="s">
-        <v>59</v>
-      </c>
       <c r="H26" t="s">
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -1758,28 +1824,28 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -1787,22 +1853,22 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" t="s">
         <v>62</v>
       </c>
-      <c r="C28" t="s">
-        <v>41</v>
-      </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E28" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
@@ -1816,28 +1882,28 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G29" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
@@ -1845,28 +1911,28 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="G30" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -1874,28 +1940,28 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" t="s">
         <v>69</v>
-      </c>
-      <c r="C31" t="s">
-        <v>41</v>
       </c>
       <c r="D31" t="s">
         <v>70</v>
       </c>
       <c r="E31" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="G31" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
@@ -1903,109 +1969,109 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" t="s">
         <v>67</v>
       </c>
-      <c r="E32" t="s">
-        <v>27</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>68</v>
       </c>
-      <c r="G32" t="s">
-        <v>59</v>
-      </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="E33" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="F33" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="G33" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="G35" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
@@ -2016,25 +2082,25 @@
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" t="s">
         <v>72</v>
       </c>
-      <c r="B36" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36" t="s">
-        <v>75</v>
-      </c>
       <c r="F36" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
@@ -2045,51 +2111,51 @@
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" t="s">
         <v>72</v>
       </c>
-      <c r="B37" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" t="s">
-        <v>80</v>
-      </c>
-      <c r="E37" t="s">
-        <v>81</v>
-      </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="G37" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="E38" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="F38" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="G38" t="s">
         <v>17</v>
@@ -2103,83 +2169,83 @@
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" t="s">
         <v>72</v>
       </c>
-      <c r="B39" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>83</v>
       </c>
-      <c r="F39" t="s">
-        <v>84</v>
-      </c>
       <c r="G39" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E40" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="F40" t="s">
         <v>23</v>
       </c>
       <c r="G40" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41" t="s">
         <v>72</v>
       </c>
-      <c r="B41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" t="s">
-        <v>73</v>
-      </c>
-      <c r="D41" t="s">
-        <v>86</v>
-      </c>
-      <c r="E41" t="s">
-        <v>75</v>
-      </c>
       <c r="F41" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G41" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
@@ -2190,54 +2256,54 @@
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D42" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="E42" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="F42" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G42" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E43" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="F43" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="G43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
@@ -2248,83 +2314,83 @@
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" t="s">
         <v>72</v>
       </c>
-      <c r="B44" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" t="s">
-        <v>41</v>
-      </c>
-      <c r="D44" t="s">
-        <v>77</v>
-      </c>
-      <c r="E44" t="s">
-        <v>87</v>
-      </c>
       <c r="F44" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G44" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B45" t="s">
         <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="F45" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="G45" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D46" t="s">
         <v>90</v>
       </c>
       <c r="E46" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="F46" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="G46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
@@ -2335,25 +2401,25 @@
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
+        <v>80</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" t="s">
         <v>72</v>
       </c>
-      <c r="B47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47" t="s">
-        <v>73</v>
-      </c>
-      <c r="D47" t="s">
-        <v>78</v>
-      </c>
-      <c r="E47" t="s">
-        <v>32</v>
-      </c>
       <c r="F47" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
@@ -2364,28 +2430,28 @@
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E48" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F48" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="G48" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
@@ -2393,54 +2459,54 @@
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D49" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E49" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F49" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D50" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="E50" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F50" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G50" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
@@ -2451,54 +2517,54 @@
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="D51" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="E51" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="F51" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="G51" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D52" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E52" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F52" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
@@ -2509,54 +2575,54 @@
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E53" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F53" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="G53" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="D54" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E54" t="s">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="F54" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="G54" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
@@ -2567,54 +2633,54 @@
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D55" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E55" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F55" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="G55" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B56" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D56" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E56" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="F56" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="G56" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
@@ -2625,25 +2691,25 @@
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B57" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
+        <v>41</v>
+      </c>
+      <c r="D57" t="s">
         <v>107</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>108</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>109</v>
       </c>
-      <c r="F57" t="s">
-        <v>110</v>
-      </c>
       <c r="G57" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
@@ -2654,25 +2720,25 @@
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D58" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E58" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="F58" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="G58" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
@@ -2683,25 +2749,25 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B59" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D59" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="E59" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F59" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="G59" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
@@ -2712,25 +2778,25 @@
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B60" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
+        <v>104</v>
+      </c>
+      <c r="E60" t="s">
         <v>105</v>
       </c>
-      <c r="E60" t="s">
-        <v>52</v>
-      </c>
       <c r="F60" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G60" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
@@ -2741,25 +2807,25 @@
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D61" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="E61" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F61" t="s">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
@@ -2770,25 +2836,25 @@
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B62" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E62" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G62" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
@@ -2799,25 +2865,25 @@
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B63" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C63" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D63" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E63" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="F63" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G63" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
@@ -2828,25 +2894,25 @@
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C64" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E64" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="F64" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="G64" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
@@ -2857,25 +2923,25 @@
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C65" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="D65" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="E65" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="F65" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="G65" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
@@ -2886,25 +2952,25 @@
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B66" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C66" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E66" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F66" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G66" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
@@ -2915,25 +2981,25 @@
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D67" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="E67" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="F67" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
@@ -2944,25 +3010,25 @@
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B68" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D68" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="F68" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="G68" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
@@ -2973,25 +3039,25 @@
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B69" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D69" t="s">
         <v>116</v>
       </c>
       <c r="E69" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="F69" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G69" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
@@ -3002,25 +3068,25 @@
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C70" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D70" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="E70" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F70" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="G70" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
@@ -3031,25 +3097,25 @@
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C71" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="E71" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="F71" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="G71" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
@@ -3060,25 +3126,25 @@
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B72" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C72" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="E72" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F72" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="G72" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
@@ -3089,25 +3155,25 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="D73" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E73" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="F73" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
@@ -3118,25 +3184,25 @@
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B74" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C74" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="D74" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="E74" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F74" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G74" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
@@ -3147,25 +3213,25 @@
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B75" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C75" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D75" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="E75" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F75" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="G75" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
@@ -3176,25 +3242,25 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C76" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="D76" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E76" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="F76" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="G76" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
@@ -3205,25 +3271,25 @@
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D77" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E77" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="F77" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G77" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
@@ -3234,25 +3300,25 @@
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D78" t="s">
-        <v>61</v>
+        <v>135</v>
       </c>
       <c r="E78" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="F78" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="G78" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
@@ -3263,25 +3329,25 @@
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B79" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C79" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E79" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F79" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="G79" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
@@ -3292,25 +3358,25 @@
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C80" t="s">
+        <v>131</v>
+      </c>
+      <c r="D80" t="s">
         <v>57</v>
       </c>
-      <c r="C80" t="s">
-        <v>41</v>
-      </c>
-      <c r="D80" t="s">
-        <v>123</v>
-      </c>
       <c r="E80" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F80" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G80" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
@@ -3321,25 +3387,25 @@
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C81" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="D81" t="s">
+        <v>104</v>
+      </c>
+      <c r="E81" t="s">
+        <v>105</v>
+      </c>
+      <c r="F81" t="s">
         <v>106</v>
       </c>
-      <c r="E81" t="s">
-        <v>97</v>
-      </c>
-      <c r="F81" t="s">
-        <v>98</v>
-      </c>
       <c r="G81" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
@@ -3350,25 +3416,25 @@
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B82" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C82" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D82" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="E82" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="F82" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="G82" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
@@ -3379,25 +3445,25 @@
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B83" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="D83" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E83" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F83" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G83" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
@@ -3408,25 +3474,25 @@
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B84" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D84" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="E84" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="F84" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="G84" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
@@ -3437,25 +3503,25 @@
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C85" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="D85" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E85" t="s">
+        <v>108</v>
+      </c>
+      <c r="F85" t="s">
         <v>109</v>
       </c>
-      <c r="F85" t="s">
-        <v>110</v>
-      </c>
       <c r="G85" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
@@ -3466,25 +3532,25 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B86" t="s">
         <v>58</v>
       </c>
       <c r="C86" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D86" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="E86" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="F86" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="G86" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
@@ -3495,25 +3561,25 @@
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B87" t="s">
         <v>58</v>
       </c>
       <c r="C87" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E87" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="F87" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="G87" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
@@ -3524,25 +3590,25 @@
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B88" t="s">
         <v>58</v>
       </c>
       <c r="C88" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="D88" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="E88" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="F88" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="G88" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
@@ -3553,25 +3619,25 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B89" t="s">
         <v>58</v>
       </c>
       <c r="C89" t="s">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="E89" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F89" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="G89" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
@@ -3582,25 +3648,25 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B90" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C90" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D90" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E90" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="F90" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G90" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
@@ -3611,25 +3677,25 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B91" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C91" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="D91" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E91" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F91" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G91" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
@@ -3640,25 +3706,25 @@
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C92" t="s">
         <v>41</v>
       </c>
       <c r="D92" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="E92" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="F92" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="G92" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
@@ -3669,25 +3735,25 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B93" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C93" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="D93" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="E93" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="F93" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G93" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
@@ -3698,25 +3764,25 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B94" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C94" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="D94" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E94" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F94" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G94" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
@@ -3727,25 +3793,25 @@
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="D95" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E95" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="F95" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G95" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
@@ -3756,25 +3822,25 @@
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B96" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C96" t="s">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="D96" t="s">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="E96" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F96" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="G96" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
@@ -3785,25 +3851,25 @@
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C97" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="D97" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="E97" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="F97" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="G97" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
@@ -3814,25 +3880,25 @@
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="B98" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C98" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E98" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="F98" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G98" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
@@ -3843,25 +3909,25 @@
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C99" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D99" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="E99" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F99" t="s">
         <v>23</v>
       </c>
       <c r="G99" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
@@ -3872,25 +3938,25 @@
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="B100" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C100" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="D100" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="E100" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F100" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G100" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
@@ -3901,25 +3967,25 @@
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C101" t="s">
         <v>41</v>
       </c>
       <c r="D101" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="E101" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="F101" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="G101" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
@@ -3930,28 +3996,28 @@
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C102" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="D102" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="E102" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="F102" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G102" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H102" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="I102" t="s">
         <v>19</v>
@@ -3959,25 +4025,25 @@
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C103" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="D103" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="E103" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F103" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G103" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
@@ -3988,25 +4054,25 @@
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B104" t="s">
+        <v>61</v>
+      </c>
+      <c r="C104" t="s">
+        <v>42</v>
+      </c>
+      <c r="D104" t="s">
         <v>57</v>
       </c>
-      <c r="C104" t="s">
-        <v>41</v>
-      </c>
-      <c r="D104" t="s">
-        <v>31</v>
-      </c>
       <c r="E104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F104" t="s">
         <v>23</v>
       </c>
       <c r="G104" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H104" t="s">
         <v>18</v>
@@ -4017,25 +4083,25 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C105" t="s">
         <v>41</v>
       </c>
       <c r="D105" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E105" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="F105" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="G105" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
@@ -4046,25 +4112,25 @@
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C106" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="D106" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="E106" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F106" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="G106" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
@@ -4075,25 +4141,25 @@
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B107" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C107" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="D107" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="E107" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="F107" t="s">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="G107" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
@@ -4104,30 +4170,813 @@
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B108" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C108" t="s">
         <v>41</v>
       </c>
       <c r="D108" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="E108" t="s">
+        <v>108</v>
+      </c>
+      <c r="F108" t="s">
+        <v>109</v>
+      </c>
+      <c r="G108" t="s">
+        <v>86</v>
+      </c>
+      <c r="H108" t="s">
+        <v>18</v>
+      </c>
+      <c r="I108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15">
+      <c r="A109" t="s">
+        <v>148</v>
+      </c>
+      <c r="B109" t="s">
+        <v>44</v>
+      </c>
+      <c r="C109" t="s">
+        <v>42</v>
+      </c>
+      <c r="D109" t="s">
+        <v>78</v>
+      </c>
+      <c r="E109" t="s">
+        <v>53</v>
+      </c>
+      <c r="F109" t="s">
+        <v>23</v>
+      </c>
+      <c r="G109" t="s">
+        <v>86</v>
+      </c>
+      <c r="H109" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15">
+      <c r="A110" t="s">
+        <v>148</v>
+      </c>
+      <c r="B110" t="s">
+        <v>44</v>
+      </c>
+      <c r="C110" t="s">
+        <v>123</v>
+      </c>
+      <c r="D110" t="s">
+        <v>107</v>
+      </c>
+      <c r="E110" t="s">
+        <v>72</v>
+      </c>
+      <c r="F110" t="s">
+        <v>125</v>
+      </c>
+      <c r="G110" t="s">
+        <v>86</v>
+      </c>
+      <c r="H110" t="s">
+        <v>18</v>
+      </c>
+      <c r="I110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="15">
+      <c r="A111" t="s">
+        <v>148</v>
+      </c>
+      <c r="B111" t="s">
+        <v>55</v>
+      </c>
+      <c r="C111" t="s">
+        <v>42</v>
+      </c>
+      <c r="D111" t="s">
+        <v>95</v>
+      </c>
+      <c r="E111" t="s">
+        <v>53</v>
+      </c>
+      <c r="F111" t="s">
+        <v>23</v>
+      </c>
+      <c r="G111" t="s">
+        <v>86</v>
+      </c>
+      <c r="H111" t="s">
+        <v>18</v>
+      </c>
+      <c r="I111" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="15">
+      <c r="A112" t="s">
+        <v>148</v>
+      </c>
+      <c r="B112" t="s">
+        <v>55</v>
+      </c>
+      <c r="C112" t="s">
+        <v>123</v>
+      </c>
+      <c r="D112" t="s">
+        <v>107</v>
+      </c>
+      <c r="E112" t="s">
+        <v>72</v>
+      </c>
+      <c r="F112" t="s">
+        <v>125</v>
+      </c>
+      <c r="G112" t="s">
+        <v>86</v>
+      </c>
+      <c r="H112" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15">
+      <c r="A113" t="s">
+        <v>148</v>
+      </c>
+      <c r="B113" t="s">
+        <v>58</v>
+      </c>
+      <c r="C113" t="s">
+        <v>42</v>
+      </c>
+      <c r="D113" t="s">
+        <v>97</v>
+      </c>
+      <c r="E113" t="s">
+        <v>53</v>
+      </c>
+      <c r="F113" t="s">
+        <v>23</v>
+      </c>
+      <c r="G113" t="s">
+        <v>86</v>
+      </c>
+      <c r="H113" t="s">
+        <v>18</v>
+      </c>
+      <c r="I113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="15">
+      <c r="A114" t="s">
+        <v>148</v>
+      </c>
+      <c r="B114" t="s">
+        <v>58</v>
+      </c>
+      <c r="C114" t="s">
+        <v>123</v>
+      </c>
+      <c r="D114" t="s">
+        <v>144</v>
+      </c>
+      <c r="E114" t="s">
+        <v>72</v>
+      </c>
+      <c r="F114" t="s">
+        <v>125</v>
+      </c>
+      <c r="G114" t="s">
+        <v>86</v>
+      </c>
+      <c r="H114" t="s">
+        <v>18</v>
+      </c>
+      <c r="I114" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="15">
+      <c r="A115" t="s">
+        <v>148</v>
+      </c>
+      <c r="B115" t="s">
+        <v>59</v>
+      </c>
+      <c r="C115" t="s">
+        <v>42</v>
+      </c>
+      <c r="D115" t="s">
+        <v>97</v>
+      </c>
+      <c r="E115" t="s">
+        <v>53</v>
+      </c>
+      <c r="F115" t="s">
+        <v>23</v>
+      </c>
+      <c r="G115" t="s">
+        <v>86</v>
+      </c>
+      <c r="H115" t="s">
+        <v>18</v>
+      </c>
+      <c r="I115" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15">
+      <c r="A116" t="s">
+        <v>148</v>
+      </c>
+      <c r="B116" t="s">
+        <v>59</v>
+      </c>
+      <c r="C116" t="s">
+        <v>123</v>
+      </c>
+      <c r="D116" t="s">
+        <v>66</v>
+      </c>
+      <c r="E116" t="s">
+        <v>72</v>
+      </c>
+      <c r="F116" t="s">
+        <v>125</v>
+      </c>
+      <c r="G116" t="s">
+        <v>86</v>
+      </c>
+      <c r="H116" t="s">
+        <v>18</v>
+      </c>
+      <c r="I116" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15">
+      <c r="A117" t="s">
+        <v>148</v>
+      </c>
+      <c r="B117" t="s">
+        <v>61</v>
+      </c>
+      <c r="C117" t="s">
+        <v>123</v>
+      </c>
+      <c r="D117" t="s">
+        <v>66</v>
+      </c>
+      <c r="E117" t="s">
+        <v>72</v>
+      </c>
+      <c r="F117" t="s">
+        <v>125</v>
+      </c>
+      <c r="G117" t="s">
+        <v>86</v>
+      </c>
+      <c r="H117" t="s">
+        <v>18</v>
+      </c>
+      <c r="I117" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="15">
+      <c r="A118" t="s">
+        <v>148</v>
+      </c>
+      <c r="B118" t="s">
+        <v>65</v>
+      </c>
+      <c r="C118" t="s">
+        <v>123</v>
+      </c>
+      <c r="D118" t="s">
+        <v>145</v>
+      </c>
+      <c r="E118" t="s">
+        <v>72</v>
+      </c>
+      <c r="F118" t="s">
+        <v>125</v>
+      </c>
+      <c r="G118" t="s">
+        <v>86</v>
+      </c>
+      <c r="H118" t="s">
+        <v>18</v>
+      </c>
+      <c r="I118" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="15">
+      <c r="A119" t="s">
+        <v>148</v>
+      </c>
+      <c r="B119" t="s">
+        <v>74</v>
+      </c>
+      <c r="C119" t="s">
+        <v>123</v>
+      </c>
+      <c r="D119" t="s">
+        <v>145</v>
+      </c>
+      <c r="E119" t="s">
+        <v>72</v>
+      </c>
+      <c r="F119" t="s">
+        <v>125</v>
+      </c>
+      <c r="G119" t="s">
+        <v>86</v>
+      </c>
+      <c r="H119" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="15">
+      <c r="A120" t="s">
+        <v>149</v>
+      </c>
+      <c r="B120" t="s">
+        <v>39</v>
+      </c>
+      <c r="C120" t="s">
+        <v>42</v>
+      </c>
+      <c r="D120" t="s">
+        <v>136</v>
+      </c>
+      <c r="E120" t="s">
+        <v>53</v>
+      </c>
+      <c r="F120" t="s">
+        <v>23</v>
+      </c>
+      <c r="G120" t="s">
+        <v>86</v>
+      </c>
+      <c r="H120" t="s">
+        <v>18</v>
+      </c>
+      <c r="I120" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="15">
+      <c r="A121" t="s">
+        <v>149</v>
+      </c>
+      <c r="B121" t="s">
+        <v>39</v>
+      </c>
+      <c r="C121" t="s">
+        <v>123</v>
+      </c>
+      <c r="D121" t="s">
+        <v>144</v>
+      </c>
+      <c r="E121" t="s">
+        <v>72</v>
+      </c>
+      <c r="F121" t="s">
+        <v>125</v>
+      </c>
+      <c r="G121" t="s">
+        <v>86</v>
+      </c>
+      <c r="H121" t="s">
+        <v>18</v>
+      </c>
+      <c r="I121" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15">
+      <c r="A122" t="s">
+        <v>149</v>
+      </c>
+      <c r="B122" t="s">
+        <v>39</v>
+      </c>
+      <c r="C122" t="s">
+        <v>150</v>
+      </c>
+      <c r="D122" t="s">
+        <v>138</v>
+      </c>
+      <c r="E122" t="s">
+        <v>151</v>
+      </c>
+      <c r="F122" t="s">
+        <v>109</v>
+      </c>
+      <c r="G122" t="s">
+        <v>86</v>
+      </c>
+      <c r="H122" t="s">
+        <v>152</v>
+      </c>
+      <c r="I122" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15">
+      <c r="A123" t="s">
+        <v>149</v>
+      </c>
+      <c r="B123" t="s">
+        <v>44</v>
+      </c>
+      <c r="C123" t="s">
+        <v>42</v>
+      </c>
+      <c r="D123" t="s">
+        <v>84</v>
+      </c>
+      <c r="E123" t="s">
+        <v>53</v>
+      </c>
+      <c r="F123" t="s">
+        <v>23</v>
+      </c>
+      <c r="G123" t="s">
+        <v>86</v>
+      </c>
+      <c r="H123" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15">
+      <c r="A124" t="s">
+        <v>149</v>
+      </c>
+      <c r="B124" t="s">
+        <v>44</v>
+      </c>
+      <c r="C124" t="s">
+        <v>123</v>
+      </c>
+      <c r="D124" t="s">
+        <v>144</v>
+      </c>
+      <c r="E124" t="s">
+        <v>72</v>
+      </c>
+      <c r="F124" t="s">
+        <v>125</v>
+      </c>
+      <c r="G124" t="s">
+        <v>86</v>
+      </c>
+      <c r="H124" t="s">
+        <v>18</v>
+      </c>
+      <c r="I124" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15">
+      <c r="A125" t="s">
+        <v>149</v>
+      </c>
+      <c r="B125" t="s">
+        <v>55</v>
+      </c>
+      <c r="C125" t="s">
+        <v>123</v>
+      </c>
+      <c r="D125" t="s">
+        <v>64</v>
+      </c>
+      <c r="E125" t="s">
+        <v>72</v>
+      </c>
+      <c r="F125" t="s">
+        <v>125</v>
+      </c>
+      <c r="G125" t="s">
+        <v>86</v>
+      </c>
+      <c r="H125" t="s">
+        <v>18</v>
+      </c>
+      <c r="I125" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="15">
+      <c r="A126" t="s">
+        <v>149</v>
+      </c>
+      <c r="B126" t="s">
+        <v>58</v>
+      </c>
+      <c r="C126" t="s">
+        <v>42</v>
+      </c>
+      <c r="D126" t="s">
+        <v>31</v>
+      </c>
+      <c r="E126" t="s">
+        <v>53</v>
+      </c>
+      <c r="F126" t="s">
+        <v>23</v>
+      </c>
+      <c r="G126" t="s">
+        <v>86</v>
+      </c>
+      <c r="H126" t="s">
+        <v>18</v>
+      </c>
+      <c r="I126" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="15">
+      <c r="A127" t="s">
+        <v>149</v>
+      </c>
+      <c r="B127" t="s">
+        <v>58</v>
+      </c>
+      <c r="C127" t="s">
+        <v>123</v>
+      </c>
+      <c r="D127" t="s">
+        <v>64</v>
+      </c>
+      <c r="E127" t="s">
+        <v>72</v>
+      </c>
+      <c r="F127" t="s">
+        <v>125</v>
+      </c>
+      <c r="G127" t="s">
+        <v>86</v>
+      </c>
+      <c r="H127" t="s">
+        <v>18</v>
+      </c>
+      <c r="I127" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="15">
+      <c r="A128" t="s">
+        <v>149</v>
+      </c>
+      <c r="B128" t="s">
+        <v>59</v>
+      </c>
+      <c r="C128" t="s">
+        <v>42</v>
+      </c>
+      <c r="D128" t="s">
+        <v>138</v>
+      </c>
+      <c r="E128" t="s">
+        <v>53</v>
+      </c>
+      <c r="F128" t="s">
+        <v>23</v>
+      </c>
+      <c r="G128" t="s">
+        <v>86</v>
+      </c>
+      <c r="H128" t="s">
+        <v>18</v>
+      </c>
+      <c r="I128" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="15">
+      <c r="A129" t="s">
+        <v>149</v>
+      </c>
+      <c r="B129" t="s">
+        <v>59</v>
+      </c>
+      <c r="C129" t="s">
+        <v>123</v>
+      </c>
+      <c r="D129" t="s">
+        <v>153</v>
+      </c>
+      <c r="E129" t="s">
+        <v>72</v>
+      </c>
+      <c r="F129" t="s">
+        <v>125</v>
+      </c>
+      <c r="G129" t="s">
+        <v>86</v>
+      </c>
+      <c r="H129" t="s">
+        <v>18</v>
+      </c>
+      <c r="I129" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="15">
+      <c r="A130" t="s">
+        <v>149</v>
+      </c>
+      <c r="B130" t="s">
+        <v>61</v>
+      </c>
+      <c r="C130" t="s">
+        <v>42</v>
+      </c>
+      <c r="D130" t="s">
+        <v>132</v>
+      </c>
+      <c r="E130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F130" t="s">
+        <v>23</v>
+      </c>
+      <c r="G130" t="s">
+        <v>86</v>
+      </c>
+      <c r="H130" t="s">
+        <v>18</v>
+      </c>
+      <c r="I130" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="15">
+      <c r="A131" t="s">
+        <v>149</v>
+      </c>
+      <c r="B131" t="s">
+        <v>61</v>
+      </c>
+      <c r="C131" t="s">
+        <v>123</v>
+      </c>
+      <c r="D131" t="s">
+        <v>153</v>
+      </c>
+      <c r="E131" t="s">
+        <v>72</v>
+      </c>
+      <c r="F131" t="s">
+        <v>125</v>
+      </c>
+      <c r="G131" t="s">
+        <v>86</v>
+      </c>
+      <c r="H131" t="s">
+        <v>18</v>
+      </c>
+      <c r="I131" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="15">
+      <c r="A132" t="s">
+        <v>149</v>
+      </c>
+      <c r="B132" t="s">
+        <v>65</v>
+      </c>
+      <c r="C132" t="s">
+        <v>42</v>
+      </c>
+      <c r="D132" t="s">
+        <v>97</v>
+      </c>
+      <c r="E132" t="s">
+        <v>53</v>
+      </c>
+      <c r="F132" t="s">
+        <v>23</v>
+      </c>
+      <c r="G132" t="s">
+        <v>86</v>
+      </c>
+      <c r="H132" t="s">
+        <v>18</v>
+      </c>
+      <c r="I132" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="15">
+      <c r="A133" t="s">
+        <v>149</v>
+      </c>
+      <c r="B133" t="s">
+        <v>65</v>
+      </c>
+      <c r="C133" t="s">
+        <v>123</v>
+      </c>
+      <c r="D133" t="s">
+        <v>124</v>
+      </c>
+      <c r="E133" t="s">
+        <v>72</v>
+      </c>
+      <c r="F133" t="s">
+        <v>125</v>
+      </c>
+      <c r="G133" t="s">
+        <v>86</v>
+      </c>
+      <c r="H133" t="s">
+        <v>18</v>
+      </c>
+      <c r="I133" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="15">
+      <c r="A134" t="s">
+        <v>149</v>
+      </c>
+      <c r="B134" t="s">
+        <v>74</v>
+      </c>
+      <c r="C134" t="s">
+        <v>42</v>
+      </c>
+      <c r="D134" t="s">
         <v>52</v>
       </c>
-      <c r="F108" t="s">
+      <c r="E134" t="s">
+        <v>53</v>
+      </c>
+      <c r="F134" t="s">
         <v>23</v>
       </c>
-      <c r="G108" t="s">
-        <v>79</v>
-      </c>
-      <c r="H108" t="s">
-        <v>18</v>
-      </c>
-      <c r="I108" t="s">
+      <c r="G134" t="s">
+        <v>86</v>
+      </c>
+      <c r="H134" t="s">
+        <v>18</v>
+      </c>
+      <c r="I134" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="15">
+      <c r="A135" t="s">
+        <v>149</v>
+      </c>
+      <c r="B135" t="s">
+        <v>74</v>
+      </c>
+      <c r="C135" t="s">
+        <v>123</v>
+      </c>
+      <c r="D135" t="s">
+        <v>107</v>
+      </c>
+      <c r="E135" t="s">
+        <v>72</v>
+      </c>
+      <c r="F135" t="s">
+        <v>125</v>
+      </c>
+      <c r="G135" t="s">
+        <v>86</v>
+      </c>
+      <c r="H135" t="s">
+        <v>18</v>
+      </c>
+      <c r="I135" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4139,14 +4988,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6280f9d1-6318-4c15-86a0-ef7ffa68cd33}">
-  <dimension ref="A1:I2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ee141681-aafe-4f32-99df-d3b89bb503e3}">
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="17.7142857142857" customWidth="1"/>
-    <col min="4" max="4" width="22.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="24.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="28.8571428571429" customWidth="1"/>
     <col min="5" max="5" width="12.7142857142857" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
@@ -4159,16 +5008,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -4185,30 +5034,117 @@
     </row>
     <row r="2" spans="1:9" ht="15">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
       </c>
       <c r="I2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4220,8 +5156,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4f2c19b9-2766-46fe-8a92-5340540f2a12}">
-  <dimension ref="A1:F27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d535eff7-55a3-4b87-9f2a-43f343c03bda}">
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -4237,13 +5173,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -4257,16 +5193,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -4277,16 +5213,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -4297,16 +5233,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -4317,16 +5253,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="E5" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -4337,16 +5273,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -4357,16 +5293,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="E7" t="s">
-        <v>156</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -4374,19 +5310,19 @@
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -4394,19 +5330,19 @@
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -4414,16 +5350,16 @@
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -4434,16 +5370,16 @@
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
@@ -4454,16 +5390,16 @@
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -4474,16 +5410,16 @@
     </row>
     <row r="13" spans="1:6" ht="15">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -4494,16 +5430,16 @@
     </row>
     <row r="14" spans="1:6" ht="15">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -4514,16 +5450,16 @@
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B15" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -4534,16 +5470,16 @@
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
@@ -4554,16 +5490,16 @@
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
@@ -4574,16 +5510,16 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
@@ -4594,16 +5530,16 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -4614,16 +5550,16 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -4634,16 +5570,16 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -4654,16 +5590,16 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -4674,16 +5610,16 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C23" t="s">
         <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -4694,16 +5630,16 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -4714,16 +5650,16 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
@@ -4734,16 +5670,16 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
@@ -4754,21 +5690,161 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15">
+      <c r="A28" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15">
+      <c r="A29" t="s">
+        <v>148</v>
+      </c>
+      <c r="B29" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" t="s">
+        <v>172</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" t="s">
+        <v>179</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15">
+      <c r="A31" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" t="s">
+        <v>172</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15">
+      <c r="A32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15">
+      <c r="A33" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" t="s">
+        <v>169</v>
+      </c>
+      <c r="C33" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15">
+      <c r="A34" t="s">
+        <v>149</v>
+      </c>
+      <c r="B34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="192">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -471,6 +471,12 @@
     <t>01.10.2026</t>
   </si>
   <si>
+    <t>1WA</t>
+  </si>
+  <si>
+    <t>1WB</t>
+  </si>
+  <si>
     <t>02.10.2026</t>
   </si>
   <si>
@@ -561,9 +567,18 @@
     <t>07:55-08:00</t>
   </si>
   <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
     <t>09:35-09:40</t>
   </si>
   <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
+  </si>
+  <si>
     <t>08:45-08:50</t>
   </si>
   <si>
@@ -574,6 +589,9 @@
   </si>
   <si>
     <t>13:10-13:15</t>
+  </si>
+  <si>
+    <t>11:20-11:25</t>
   </si>
   <si>
     <t>16:30-16:35</t>
@@ -1029,7 +1047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c80b4d65-d342-4837-ab53-5fcffb584c1f}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{75109f0e-7138-40a5-acc9-872a91886449}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1050,8 +1068,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{aa670ff9-0bf5-4702-9033-200baebcb9cc}">
-  <dimension ref="A1:I135"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d15c40d5-0d97-40c6-a247-0c2d5babfd9f}">
+  <dimension ref="A1:I151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -3596,16 +3614,16 @@
         <v>58</v>
       </c>
       <c r="C88" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="D88" t="s">
-        <v>140</v>
+        <v>31</v>
       </c>
       <c r="E88" t="s">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="F88" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="G88" t="s">
         <v>86</v>
@@ -3625,16 +3643,16 @@
         <v>58</v>
       </c>
       <c r="C89" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D89" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="E89" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F89" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="G89" t="s">
         <v>86</v>
@@ -3654,16 +3672,16 @@
         <v>58</v>
       </c>
       <c r="C90" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D90" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="E90" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="F90" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="G90" t="s">
         <v>86</v>
@@ -3683,16 +3701,16 @@
         <v>58</v>
       </c>
       <c r="C91" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="D91" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E91" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="F91" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="G91" t="s">
         <v>86</v>
@@ -3712,16 +3730,16 @@
         <v>58</v>
       </c>
       <c r="C92" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D92" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="E92" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="F92" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="G92" t="s">
         <v>86</v>
@@ -3738,19 +3756,19 @@
         <v>102</v>
       </c>
       <c r="B93" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C93" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="D93" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="E93" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="F93" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G93" t="s">
         <v>86</v>
@@ -3770,16 +3788,16 @@
         <v>59</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D94" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="E94" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F94" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="G94" t="s">
         <v>86</v>
@@ -3799,16 +3817,16 @@
         <v>59</v>
       </c>
       <c r="C95" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D95" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E95" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="F95" t="s">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="G95" t="s">
         <v>86</v>
@@ -3828,16 +3846,16 @@
         <v>59</v>
       </c>
       <c r="C96" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D96" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="E96" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F96" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="G96" t="s">
         <v>86</v>
@@ -3857,16 +3875,16 @@
         <v>59</v>
       </c>
       <c r="C97" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D97" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E97" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="F97" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="G97" t="s">
         <v>86</v>
@@ -3886,16 +3904,16 @@
         <v>59</v>
       </c>
       <c r="C98" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D98" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E98" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="F98" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="G98" t="s">
         <v>86</v>
@@ -3915,16 +3933,16 @@
         <v>59</v>
       </c>
       <c r="C99" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E99" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="F99" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G99" t="s">
         <v>86</v>
@@ -3944,16 +3962,16 @@
         <v>59</v>
       </c>
       <c r="C100" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D100" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="E100" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F100" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="G100" t="s">
         <v>86</v>
@@ -3973,16 +3991,16 @@
         <v>59</v>
       </c>
       <c r="C101" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="D101" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="E101" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="F101" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="G101" t="s">
         <v>86</v>
@@ -3999,19 +4017,19 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C102" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="D102" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E102" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="F102" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G102" t="s">
         <v>86</v>
@@ -4031,16 +4049,16 @@
         <v>61</v>
       </c>
       <c r="C103" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D103" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E103" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F103" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="G103" t="s">
         <v>86</v>
@@ -4060,16 +4078,16 @@
         <v>61</v>
       </c>
       <c r="C104" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="D104" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="E104" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F104" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G104" t="s">
         <v>86</v>
@@ -4089,16 +4107,16 @@
         <v>61</v>
       </c>
       <c r="C105" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="D105" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E105" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="F105" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="G105" t="s">
         <v>86</v>
@@ -4115,19 +4133,19 @@
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C106" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="D106" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="E106" t="s">
         <v>53</v>
       </c>
       <c r="F106" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="G106" t="s">
         <v>86</v>
@@ -4144,19 +4162,19 @@
         <v>102</v>
       </c>
       <c r="B107" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C107" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="D107" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="E107" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="F107" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="G107" t="s">
         <v>86</v>
@@ -4176,16 +4194,16 @@
         <v>65</v>
       </c>
       <c r="C108" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="D108" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="E108" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="F108" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G108" t="s">
         <v>86</v>
@@ -4199,22 +4217,22 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="B109" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C109" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D109" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E109" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F109" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G109" t="s">
         <v>86</v>
@@ -4228,22 +4246,22 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="B110" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C110" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="E110" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="F110" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="G110" t="s">
         <v>86</v>
@@ -4257,22 +4275,22 @@
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="B111" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C111" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D111" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E111" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="F111" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="G111" t="s">
         <v>86</v>
@@ -4289,19 +4307,19 @@
         <v>148</v>
       </c>
       <c r="B112" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C112" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D112" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E112" t="s">
         <v>72</v>
       </c>
       <c r="F112" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="G112" t="s">
         <v>86</v>
@@ -4318,19 +4336,19 @@
         <v>148</v>
       </c>
       <c r="B113" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="C113" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D113" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="E113" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F113" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G113" t="s">
         <v>86</v>
@@ -4347,19 +4365,19 @@
         <v>148</v>
       </c>
       <c r="B114" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C114" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D114" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="E114" t="s">
         <v>72</v>
       </c>
       <c r="F114" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="G114" t="s">
         <v>86</v>
@@ -4376,19 +4394,19 @@
         <v>148</v>
       </c>
       <c r="B115" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C115" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D115" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="E115" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F115" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G115" t="s">
         <v>86</v>
@@ -4405,19 +4423,19 @@
         <v>148</v>
       </c>
       <c r="B116" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C116" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D116" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E116" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F116" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="G116" t="s">
         <v>86</v>
@@ -4434,13 +4452,13 @@
         <v>148</v>
       </c>
       <c r="B117" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C117" t="s">
         <v>123</v>
       </c>
       <c r="D117" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="E117" t="s">
         <v>72</v>
@@ -4463,19 +4481,19 @@
         <v>148</v>
       </c>
       <c r="B118" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C118" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E118" t="s">
         <v>72</v>
       </c>
       <c r="F118" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="G118" t="s">
         <v>86</v>
@@ -4492,19 +4510,19 @@
         <v>148</v>
       </c>
       <c r="B119" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C119" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="E119" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F119" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="G119" t="s">
         <v>86</v>
@@ -4518,22 +4536,22 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B120" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C120" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="D120" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="E120" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F120" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G120" t="s">
         <v>86</v>
@@ -4547,22 +4565,22 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B121" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C121" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D121" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="E121" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F121" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="G121" t="s">
         <v>86</v>
@@ -4576,28 +4594,28 @@
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B122" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C122" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="D122" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E122" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="F122" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="G122" t="s">
         <v>86</v>
       </c>
       <c r="H122" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="I122" t="s">
         <v>19</v>
@@ -4605,22 +4623,22 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B123" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C123" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D123" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="E123" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F123" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G123" t="s">
         <v>86</v>
@@ -4634,22 +4652,22 @@
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B124" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C124" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D124" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="E124" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F124" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="G124" t="s">
         <v>86</v>
@@ -4663,16 +4681,16 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B125" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C125" t="s">
         <v>123</v>
       </c>
       <c r="D125" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E125" t="s">
         <v>72</v>
@@ -4692,22 +4710,22 @@
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B126" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C126" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D126" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="E126" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F126" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G126" t="s">
         <v>86</v>
@@ -4721,16 +4739,16 @@
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B127" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C127" t="s">
         <v>123</v>
       </c>
       <c r="D127" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E127" t="s">
         <v>72</v>
@@ -4750,22 +4768,22 @@
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B128" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C128" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="D128" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E128" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F128" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G128" t="s">
         <v>86</v>
@@ -4779,16 +4797,16 @@
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B129" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C129" t="s">
         <v>123</v>
       </c>
       <c r="D129" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E129" t="s">
         <v>72</v>
@@ -4808,16 +4826,16 @@
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B130" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C130" t="s">
         <v>42</v>
       </c>
       <c r="D130" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E130" t="s">
         <v>53</v>
@@ -4837,16 +4855,16 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B131" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C131" t="s">
         <v>123</v>
       </c>
       <c r="D131" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E131" t="s">
         <v>72</v>
@@ -4866,28 +4884,28 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B132" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C132" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
       <c r="D132" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="E132" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="F132" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="G132" t="s">
         <v>86</v>
       </c>
       <c r="H132" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I132" t="s">
         <v>19</v>
@@ -4895,22 +4913,22 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B133" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C133" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D133" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="E133" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F133" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="G133" t="s">
         <v>86</v>
@@ -4924,22 +4942,22 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B134" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="C134" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="D134" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="E134" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F134" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G134" t="s">
         <v>86</v>
@@ -4953,30 +4971,494 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C135" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D135" t="s">
-        <v>107</v>
+        <v>31</v>
       </c>
       <c r="E135" t="s">
         <v>72</v>
       </c>
       <c r="F135" t="s">
+        <v>73</v>
+      </c>
+      <c r="G135" t="s">
+        <v>86</v>
+      </c>
+      <c r="H135" t="s">
+        <v>18</v>
+      </c>
+      <c r="I135" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="15">
+      <c r="A136" t="s">
+        <v>151</v>
+      </c>
+      <c r="B136" t="s">
+        <v>55</v>
+      </c>
+      <c r="C136" t="s">
+        <v>123</v>
+      </c>
+      <c r="D136" t="s">
+        <v>64</v>
+      </c>
+      <c r="E136" t="s">
+        <v>72</v>
+      </c>
+      <c r="F136" t="s">
         <v>125</v>
       </c>
-      <c r="G135" t="s">
-        <v>86</v>
-      </c>
-      <c r="H135" t="s">
-        <v>18</v>
-      </c>
-      <c r="I135" t="s">
+      <c r="G136" t="s">
+        <v>86</v>
+      </c>
+      <c r="H136" t="s">
+        <v>18</v>
+      </c>
+      <c r="I136" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="15">
+      <c r="A137" t="s">
+        <v>151</v>
+      </c>
+      <c r="B137" t="s">
+        <v>58</v>
+      </c>
+      <c r="C137" t="s">
+        <v>62</v>
+      </c>
+      <c r="D137" t="s">
+        <v>149</v>
+      </c>
+      <c r="E137" t="s">
+        <v>72</v>
+      </c>
+      <c r="F137" t="s">
+        <v>73</v>
+      </c>
+      <c r="G137" t="s">
+        <v>86</v>
+      </c>
+      <c r="H137" t="s">
+        <v>18</v>
+      </c>
+      <c r="I137" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="15">
+      <c r="A138" t="s">
+        <v>151</v>
+      </c>
+      <c r="B138" t="s">
+        <v>58</v>
+      </c>
+      <c r="C138" t="s">
+        <v>42</v>
+      </c>
+      <c r="D138" t="s">
+        <v>31</v>
+      </c>
+      <c r="E138" t="s">
+        <v>53</v>
+      </c>
+      <c r="F138" t="s">
+        <v>23</v>
+      </c>
+      <c r="G138" t="s">
+        <v>86</v>
+      </c>
+      <c r="H138" t="s">
+        <v>18</v>
+      </c>
+      <c r="I138" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="15">
+      <c r="A139" t="s">
+        <v>151</v>
+      </c>
+      <c r="B139" t="s">
+        <v>58</v>
+      </c>
+      <c r="C139" t="s">
+        <v>123</v>
+      </c>
+      <c r="D139" t="s">
+        <v>64</v>
+      </c>
+      <c r="E139" t="s">
+        <v>72</v>
+      </c>
+      <c r="F139" t="s">
+        <v>125</v>
+      </c>
+      <c r="G139" t="s">
+        <v>86</v>
+      </c>
+      <c r="H139" t="s">
+        <v>18</v>
+      </c>
+      <c r="I139" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="15">
+      <c r="A140" t="s">
+        <v>151</v>
+      </c>
+      <c r="B140" t="s">
+        <v>59</v>
+      </c>
+      <c r="C140" t="s">
+        <v>62</v>
+      </c>
+      <c r="D140" t="s">
+        <v>150</v>
+      </c>
+      <c r="E140" t="s">
+        <v>72</v>
+      </c>
+      <c r="F140" t="s">
+        <v>73</v>
+      </c>
+      <c r="G140" t="s">
+        <v>86</v>
+      </c>
+      <c r="H140" t="s">
+        <v>18</v>
+      </c>
+      <c r="I140" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="15">
+      <c r="A141" t="s">
+        <v>151</v>
+      </c>
+      <c r="B141" t="s">
+        <v>59</v>
+      </c>
+      <c r="C141" t="s">
+        <v>42</v>
+      </c>
+      <c r="D141" t="s">
+        <v>138</v>
+      </c>
+      <c r="E141" t="s">
+        <v>53</v>
+      </c>
+      <c r="F141" t="s">
+        <v>23</v>
+      </c>
+      <c r="G141" t="s">
+        <v>86</v>
+      </c>
+      <c r="H141" t="s">
+        <v>18</v>
+      </c>
+      <c r="I141" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="15">
+      <c r="A142" t="s">
+        <v>151</v>
+      </c>
+      <c r="B142" t="s">
+        <v>59</v>
+      </c>
+      <c r="C142" t="s">
+        <v>123</v>
+      </c>
+      <c r="D142" t="s">
+        <v>155</v>
+      </c>
+      <c r="E142" t="s">
+        <v>72</v>
+      </c>
+      <c r="F142" t="s">
+        <v>125</v>
+      </c>
+      <c r="G142" t="s">
+        <v>86</v>
+      </c>
+      <c r="H142" t="s">
+        <v>18</v>
+      </c>
+      <c r="I142" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="15">
+      <c r="A143" t="s">
+        <v>151</v>
+      </c>
+      <c r="B143" t="s">
+        <v>61</v>
+      </c>
+      <c r="C143" t="s">
+        <v>62</v>
+      </c>
+      <c r="D143" t="s">
+        <v>150</v>
+      </c>
+      <c r="E143" t="s">
+        <v>32</v>
+      </c>
+      <c r="F143" t="s">
+        <v>73</v>
+      </c>
+      <c r="G143" t="s">
+        <v>86</v>
+      </c>
+      <c r="H143" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="15">
+      <c r="A144" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" t="s">
+        <v>61</v>
+      </c>
+      <c r="C144" t="s">
+        <v>42</v>
+      </c>
+      <c r="D144" t="s">
+        <v>132</v>
+      </c>
+      <c r="E144" t="s">
+        <v>53</v>
+      </c>
+      <c r="F144" t="s">
+        <v>23</v>
+      </c>
+      <c r="G144" t="s">
+        <v>86</v>
+      </c>
+      <c r="H144" t="s">
+        <v>18</v>
+      </c>
+      <c r="I144" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="15">
+      <c r="A145" t="s">
+        <v>151</v>
+      </c>
+      <c r="B145" t="s">
+        <v>61</v>
+      </c>
+      <c r="C145" t="s">
+        <v>123</v>
+      </c>
+      <c r="D145" t="s">
+        <v>155</v>
+      </c>
+      <c r="E145" t="s">
+        <v>72</v>
+      </c>
+      <c r="F145" t="s">
+        <v>125</v>
+      </c>
+      <c r="G145" t="s">
+        <v>86</v>
+      </c>
+      <c r="H145" t="s">
+        <v>18</v>
+      </c>
+      <c r="I145" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="15">
+      <c r="A146" t="s">
+        <v>151</v>
+      </c>
+      <c r="B146" t="s">
+        <v>65</v>
+      </c>
+      <c r="C146" t="s">
+        <v>62</v>
+      </c>
+      <c r="D146" t="s">
+        <v>78</v>
+      </c>
+      <c r="E146" t="s">
+        <v>72</v>
+      </c>
+      <c r="F146" t="s">
+        <v>73</v>
+      </c>
+      <c r="G146" t="s">
+        <v>86</v>
+      </c>
+      <c r="H146" t="s">
+        <v>18</v>
+      </c>
+      <c r="I146" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="15">
+      <c r="A147" t="s">
+        <v>151</v>
+      </c>
+      <c r="B147" t="s">
+        <v>65</v>
+      </c>
+      <c r="C147" t="s">
+        <v>42</v>
+      </c>
+      <c r="D147" t="s">
+        <v>97</v>
+      </c>
+      <c r="E147" t="s">
+        <v>53</v>
+      </c>
+      <c r="F147" t="s">
+        <v>23</v>
+      </c>
+      <c r="G147" t="s">
+        <v>86</v>
+      </c>
+      <c r="H147" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="15">
+      <c r="A148" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148" t="s">
+        <v>65</v>
+      </c>
+      <c r="C148" t="s">
+        <v>123</v>
+      </c>
+      <c r="D148" t="s">
+        <v>124</v>
+      </c>
+      <c r="E148" t="s">
+        <v>72</v>
+      </c>
+      <c r="F148" t="s">
+        <v>125</v>
+      </c>
+      <c r="G148" t="s">
+        <v>86</v>
+      </c>
+      <c r="H148" t="s">
+        <v>18</v>
+      </c>
+      <c r="I148" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="15">
+      <c r="A149" t="s">
+        <v>151</v>
+      </c>
+      <c r="B149" t="s">
+        <v>74</v>
+      </c>
+      <c r="C149" t="s">
+        <v>62</v>
+      </c>
+      <c r="D149" t="s">
+        <v>78</v>
+      </c>
+      <c r="E149" t="s">
+        <v>72</v>
+      </c>
+      <c r="F149" t="s">
+        <v>73</v>
+      </c>
+      <c r="G149" t="s">
+        <v>86</v>
+      </c>
+      <c r="H149" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="15">
+      <c r="A150" t="s">
+        <v>151</v>
+      </c>
+      <c r="B150" t="s">
+        <v>74</v>
+      </c>
+      <c r="C150" t="s">
+        <v>42</v>
+      </c>
+      <c r="D150" t="s">
+        <v>52</v>
+      </c>
+      <c r="E150" t="s">
+        <v>53</v>
+      </c>
+      <c r="F150" t="s">
+        <v>23</v>
+      </c>
+      <c r="G150" t="s">
+        <v>86</v>
+      </c>
+      <c r="H150" t="s">
+        <v>18</v>
+      </c>
+      <c r="I150" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="15">
+      <c r="A151" t="s">
+        <v>151</v>
+      </c>
+      <c r="B151" t="s">
+        <v>74</v>
+      </c>
+      <c r="C151" t="s">
+        <v>123</v>
+      </c>
+      <c r="D151" t="s">
+        <v>107</v>
+      </c>
+      <c r="E151" t="s">
+        <v>72</v>
+      </c>
+      <c r="F151" t="s">
+        <v>125</v>
+      </c>
+      <c r="G151" t="s">
+        <v>86</v>
+      </c>
+      <c r="H151" t="s">
+        <v>18</v>
+      </c>
+      <c r="I151" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4988,7 +5470,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ee141681-aafe-4f32-99df-d3b89bb503e3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8e2ad2da-5ef8-4f79-a347-8e9eef3bbeda}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5008,16 +5490,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -5037,13 +5519,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
@@ -5066,13 +5548,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
         <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E3" t="s">
         <v>72</v>
@@ -5095,16 +5577,16 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
         <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F4" t="s">
         <v>111</v>
@@ -5124,16 +5606,16 @@
         <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
         <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -5156,15 +5638,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d535eff7-55a3-4b87-9f2a-43f343c03bda}">
-  <dimension ref="A1:F34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ff0eeb56-8444-41ea-a888-229a2d919efb}">
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="19.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="20.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5173,13 +5655,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -5193,13 +5675,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
@@ -5213,13 +5695,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C3" t="s">
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
         <v>131</v>
@@ -5233,13 +5715,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
         <v>126</v>
@@ -5253,16 +5735,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C5" t="s">
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -5273,13 +5755,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
         <v>110</v>
@@ -5293,13 +5775,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
@@ -5313,16 +5795,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -5333,16 +5815,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -5353,16 +5835,16 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C10" t="s">
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -5373,16 +5855,16 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -5393,16 +5875,16 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -5413,16 +5895,16 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C13" t="s">
         <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -5433,16 +5915,16 @@
         <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C14" t="s">
         <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>184</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -5453,13 +5935,13 @@
         <v>102</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C15" t="s">
         <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -5473,13 +5955,13 @@
         <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C16" t="s">
         <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
@@ -5493,13 +5975,13 @@
         <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
@@ -5513,13 +5995,13 @@
         <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C18" t="s">
         <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
@@ -5533,13 +6015,13 @@
         <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C19" t="s">
         <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -5553,13 +6035,13 @@
         <v>102</v>
       </c>
       <c r="B20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C20" t="s">
         <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -5573,13 +6055,13 @@
         <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -5593,13 +6075,13 @@
         <v>102</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -5616,10 +6098,10 @@
         <v>171</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -5633,13 +6115,13 @@
         <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -5653,13 +6135,13 @@
         <v>102</v>
       </c>
       <c r="B25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" t="s">
         <v>175</v>
-      </c>
-      <c r="C25" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" t="s">
-        <v>170</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
@@ -5673,10 +6155,10 @@
         <v>102</v>
       </c>
       <c r="B26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
         <v>172</v>
@@ -5690,16 +6172,16 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="B27" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -5713,13 +6195,13 @@
         <v>148</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -5733,13 +6215,13 @@
         <v>148</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
@@ -5750,16 +6232,16 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B30" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
@@ -5770,13 +6252,13 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B31" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s">
         <v>172</v>
@@ -5790,16 +6272,16 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C32" t="s">
         <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
@@ -5810,16 +6292,16 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B33" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -5830,21 +6312,101 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C34" t="s">
         <v>42</v>
       </c>
       <c r="D34" t="s">
+        <v>175</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15">
+      <c r="A35" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" t="s">
+        <v>186</v>
+      </c>
+      <c r="C35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15">
+      <c r="A36" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" t="s">
+        <v>169</v>
+      </c>
+      <c r="C36" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" t="s">
+        <v>191</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15">
+      <c r="A37" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" t="s">
+        <v>172</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15">
+      <c r="A38" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" t="s">
         <v>173</v>
       </c>
-      <c r="E34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="C38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" t="s">
+        <v>175</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="230">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -285,7 +285,7 @@
     <t>Zastępstwo</t>
   </si>
   <si>
-    <t>Technika w produkcji cukierniczej</t>
+    <t>Technologie produkcji cukierniczej</t>
   </si>
   <si>
     <t>2FB</t>
@@ -309,12 +309,33 @@
     <t>Małecka Barbara</t>
   </si>
   <si>
+    <t>Smereka Alicja</t>
+  </si>
+  <si>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Godzina do zliczenia</t>
+  </si>
+  <si>
     <t>3CB</t>
   </si>
   <si>
     <t>p. Kończyńska, lekcja przeniesiona z 8 godziny lekcyjnej</t>
   </si>
   <si>
+    <t>3WA</t>
+  </si>
+  <si>
+    <t>Geografia</t>
+  </si>
+  <si>
     <t>2TFA</t>
   </si>
   <si>
@@ -327,18 +348,24 @@
     <t>Mikołajczak Sylwia</t>
   </si>
   <si>
+    <t>2TH</t>
+  </si>
+  <si>
     <t>3FC</t>
   </si>
   <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>3TFB|t.hand.</t>
+  </si>
+  <si>
     <t>30.09.2026</t>
   </si>
   <si>
     <t>Kosin Anna</t>
   </si>
   <si>
-    <t>3TFB|t.hand.</t>
-  </si>
-  <si>
     <t>Pracownia sprzedaży</t>
   </si>
   <si>
@@ -348,64 +375,133 @@
     <t>1TFB</t>
   </si>
   <si>
-    <t>Biznes i zarządzanie</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
     <t>Bujanowska Iwona</t>
   </si>
   <si>
+    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>Cieśla Marcin</t>
+  </si>
+  <si>
+    <t>1TFB|CH</t>
+  </si>
+  <si>
+    <t>Mucha Anna</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>prs</t>
+  </si>
+  <si>
+    <t>Marzec Renata</t>
+  </si>
+  <si>
+    <t>1S</t>
+  </si>
+  <si>
     <t>29</t>
   </si>
   <si>
-    <t>Cieśla Marcin</t>
-  </si>
-  <si>
-    <t>1TFB|CH</t>
-  </si>
-  <si>
-    <t>Mucha Anna</t>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>2K|gr2</t>
+  </si>
+  <si>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>Wrzeszcz Barbara</t>
+  </si>
+  <si>
+    <t>Piątek-Pawłowska Bożena</t>
+  </si>
+  <si>
+    <t>4TFA</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Zaleska Magdalena</t>
+  </si>
+  <si>
+    <t>Bez konsekwencji (nieobecny oddział nauczyciela)</t>
+  </si>
+  <si>
+    <t>zaplanowano zastępstwo z nauczycielem Staliś Donata [Dn]</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
+    <t>1TH|gr2</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Staliś Donata</t>
+  </si>
+  <si>
+    <t>4TH|gr2</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Krycia Ewelina</t>
+  </si>
+  <si>
+    <t>Kaczorowski Waldemar</t>
+  </si>
+  <si>
+    <t>1CB|gr1</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>1S</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>2K|gr2</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Edukacja zdrowotna</t>
-  </si>
-  <si>
-    <t>Piątek-Pawłowska Bożena</t>
-  </si>
-  <si>
-    <t>4TFA</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
-    <t>1TH|gr2</t>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>1CB|gr2</t>
+  </si>
+  <si>
+    <t>1WB|gr1</t>
   </si>
   <si>
     <t>Język niemiecki</t>
@@ -414,22 +510,10 @@
     <t>17</t>
   </si>
   <si>
-    <t>4TH|gr2</t>
-  </si>
-  <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
     <t>Chemia</t>
   </si>
   <si>
-    <t>1CB</t>
-  </si>
-  <si>
-    <t>1WB|gr1</t>
+    <t>p. Dalach, wychowanie fizyczne za lekcję 8</t>
   </si>
   <si>
     <t>2S</t>
@@ -441,22 +525,46 @@
     <t>1FC</t>
   </si>
   <si>
+    <t>p. Ulanowska, j. polski za lekcję 8</t>
+  </si>
+  <si>
     <t>2WA|ch2</t>
   </si>
   <si>
+    <t>p. Leńczowska, lekcja przeniesiona z 1 godziny lekcyjnej</t>
+  </si>
+  <si>
     <t>1TFB|gr2</t>
   </si>
   <si>
     <t>Organizacja sprzedaży</t>
   </si>
   <si>
-    <t>33</t>
+    <t>p. Kruk, techniki fryzjerskie za lekcję 1; sala 34</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>zaplanowano zastępstwo z nauczycielem Leńczowska Iwona [IL]</t>
   </si>
   <si>
     <t>2CB</t>
   </si>
   <si>
-    <t>2TH</t>
+    <t>Edukacja obywatelska</t>
+  </si>
+  <si>
+    <t>1WB</t>
+  </si>
+  <si>
+    <t>Edukacja dla bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>Płatek Krzysztof</t>
   </si>
   <si>
     <t>1K</t>
@@ -465,7 +573,7 @@
     <t>1WB|gr2</t>
   </si>
   <si>
-    <t>19</t>
+    <t>Rozwój kompetencji zawodowych - obsługa klienta</t>
   </si>
   <si>
     <t>01.10.2026</t>
@@ -474,16 +582,10 @@
     <t>1WA</t>
   </si>
   <si>
-    <t>1WB</t>
-  </si>
-  <si>
     <t>02.10.2026</t>
   </si>
   <si>
-    <t>Płatek Krzysztof</t>
-  </si>
-  <si>
-    <t>Edukacja dla bezpieczeństwa</t>
+    <t>4TFB</t>
   </si>
   <si>
     <t>próbna ewakuacja - inspektor zewnętrzny</t>
@@ -492,6 +594,9 @@
     <t>3FB</t>
   </si>
   <si>
+    <t>1TFH|t.hand.</t>
+  </si>
+  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -573,12 +678,15 @@
     <t>09:35-09:40</t>
   </si>
   <si>
-    <t>Socha Dariusz</t>
+    <t>Ostrowska Ewa</t>
   </si>
   <si>
     <t>Sobczak Anna</t>
   </si>
   <si>
+    <t>17:20-17:25</t>
+  </si>
+  <si>
     <t>08:45-08:50</t>
   </si>
   <si>
@@ -589,6 +697,12 @@
   </si>
   <si>
     <t>13:10-13:15</t>
+  </si>
+  <si>
+    <t>Taszycka Magdalena</t>
+  </si>
+  <si>
+    <t>Czukiewska Bożena</t>
   </si>
   <si>
     <t>11:20-11:25</t>
@@ -1047,7 +1161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{75109f0e-7138-40a5-acc9-872a91886449}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{eb033528-fd6d-4c09-a495-9df7ff665cd8}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1068,8 +1182,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d15c40d5-0d97-40c6-a247-0c2d5babfd9f}">
-  <dimension ref="A1:I151"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7d9cc044-5284-4fc2-ace4-841ffc3d4822}">
+  <dimension ref="A1:I178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1078,9 +1192,9 @@
     <col min="4" max="4" width="13.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
-    <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="45.5714285714286" customWidth="1"/>
+    <col min="8" max="8" width="57" customWidth="1"/>
+    <col min="9" max="9" width="19.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="56.25" customHeight="1">
@@ -2289,7 +2403,7 @@
         <v>89</v>
       </c>
       <c r="F42" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G42" t="s">
         <v>51</v>
@@ -2425,25 +2539,25 @@
         <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D47" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F47" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="G47" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
@@ -2451,25 +2565,25 @@
         <v>80</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E48" t="s">
         <v>72</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G48" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H48" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
@@ -2483,25 +2597,25 @@
         <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D49" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="E49" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="F49" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="G49" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H49" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="I49" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
@@ -2512,25 +2626,25 @@
         <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E50" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F50" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
@@ -2538,28 +2652,28 @@
         <v>80</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="E51" t="s">
+        <v>103</v>
+      </c>
+      <c r="F51" t="s">
         <v>98</v>
       </c>
-      <c r="F51" t="s">
-        <v>99</v>
-      </c>
       <c r="G51" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
@@ -2567,13 +2681,13 @@
         <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
         <v>81</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E52" t="s">
         <v>72</v>
@@ -2596,28 +2710,28 @@
         <v>80</v>
       </c>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
         <v>62</v>
       </c>
       <c r="D53" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="E53" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F53" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="G53" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
@@ -2625,22 +2739,22 @@
         <v>80</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D54" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="F54" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="G54" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
@@ -2654,51 +2768,51 @@
         <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D55" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E55" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F55" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G55" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B56" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="D56" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E56" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="F56" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="G56" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
@@ -2709,25 +2823,25 @@
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="D57" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E57" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F57" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G57" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
@@ -2738,22 +2852,22 @@
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C58" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="D58" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E58" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F58" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="G58" t="s">
         <v>86</v>
@@ -2767,25 +2881,25 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="E59" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="F59" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="G59" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
@@ -2796,25 +2910,25 @@
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C60" t="s">
+        <v>95</v>
+      </c>
+      <c r="D60" t="s">
+        <v>110</v>
+      </c>
+      <c r="E60" t="s">
         <v>103</v>
       </c>
-      <c r="D60" t="s">
-        <v>104</v>
-      </c>
-      <c r="E60" t="s">
-        <v>105</v>
-      </c>
       <c r="F60" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G60" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
@@ -2825,22 +2939,22 @@
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="D61" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="E61" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="G61" t="s">
         <v>86</v>
@@ -2854,25 +2968,25 @@
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="D62" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E62" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G62" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
@@ -2883,22 +2997,22 @@
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B63" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
+        <v>95</v>
+      </c>
+      <c r="D63" t="s">
         <v>110</v>
       </c>
-      <c r="D63" t="s">
-        <v>117</v>
-      </c>
       <c r="E63" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F63" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="G63" t="s">
         <v>86</v>
@@ -2912,25 +3026,25 @@
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B64" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="D64" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E64" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F64" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="G64" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
@@ -2941,83 +3055,83 @@
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B65" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C65" t="s">
         <v>118</v>
       </c>
       <c r="D65" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" t="s">
         <v>119</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
+        <v>36</v>
+      </c>
+      <c r="G65" t="s">
         <v>120</v>
       </c>
-      <c r="F65" t="s">
-        <v>121</v>
-      </c>
-      <c r="G65" t="s">
-        <v>86</v>
-      </c>
       <c r="H65" t="s">
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B66" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D66" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="E66" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="F66" t="s">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="G66" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B67" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C67" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" t="s">
+        <v>111</v>
+      </c>
+      <c r="E67" t="s">
         <v>114</v>
-      </c>
-      <c r="D67" t="s">
-        <v>66</v>
-      </c>
-      <c r="E67" t="s">
-        <v>122</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
       </c>
       <c r="G67" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
@@ -3028,51 +3142,51 @@
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B68" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C68" t="s">
         <v>123</v>
       </c>
       <c r="D68" t="s">
+        <v>66</v>
+      </c>
+      <c r="E68" t="s">
         <v>124</v>
-      </c>
-      <c r="E68" t="s">
-        <v>72</v>
       </c>
       <c r="F68" t="s">
         <v>125</v>
       </c>
       <c r="G68" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B69" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D69" t="s">
         <v>110</v>
       </c>
-      <c r="D69" t="s">
-        <v>116</v>
-      </c>
       <c r="E69" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F69" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="G69" t="s">
         <v>86</v>
@@ -3086,51 +3200,51 @@
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B70" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E70" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F70" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="G70" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D71" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E71" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="F71" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G71" t="s">
         <v>86</v>
@@ -3144,39 +3258,39 @@
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B72" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D72" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E72" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="F72" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="G72" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C73" t="s">
         <v>131</v>
@@ -3185,42 +3299,42 @@
         <v>132</v>
       </c>
       <c r="E73" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="F73" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="G73" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C74" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D74" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E74" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F74" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="G74" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
@@ -3231,54 +3345,54 @@
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C75" t="s">
         <v>123</v>
       </c>
       <c r="D75" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="E75" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="F75" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G75" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B76" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C76" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="D76" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E76" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="F76" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="G76" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
@@ -3289,57 +3403,57 @@
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B77" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C77" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D77" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="E77" t="s">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="F77" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="G77" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B78" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D78" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="E78" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F78" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G78" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="H78" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
@@ -3347,80 +3461,80 @@
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C79" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D79" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E79" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="F79" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="G79" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C80" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D80" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="E80" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="F80" t="s">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="G80" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B81" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C81" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="D81" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="E81" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="F81" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="G81" t="s">
         <v>86</v>
@@ -3434,54 +3548,54 @@
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C82" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="D82" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="E82" t="s">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="F82" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="G82" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B83" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C83" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="D83" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="E83" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="F83" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="G83" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
@@ -3492,13 +3606,13 @@
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B84" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D84" t="s">
         <v>137</v>
@@ -3507,10 +3621,10 @@
         <v>72</v>
       </c>
       <c r="F84" t="s">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="G84" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
@@ -3521,115 +3635,115 @@
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B85" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C85" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="D85" t="s">
+        <v>82</v>
+      </c>
+      <c r="E85" t="s">
+        <v>119</v>
+      </c>
+      <c r="F85" t="s">
         <v>138</v>
       </c>
-      <c r="E85" t="s">
-        <v>108</v>
-      </c>
-      <c r="F85" t="s">
-        <v>109</v>
-      </c>
       <c r="G85" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B86" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C86" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="D86" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="E86" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="F86" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="G86" t="s">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B87" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="D87" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="E87" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="F87" t="s">
-        <v>40</v>
+        <v>156</v>
       </c>
       <c r="G87" t="s">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B88" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="E88" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="F88" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="G88" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="H88" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="I88" t="s">
         <v>19</v>
@@ -3637,25 +3751,25 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B89" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="D89" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="E89" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="F89" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="G89" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
@@ -3666,22 +3780,22 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B90" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C90" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
-        <v>64</v>
+        <v>148</v>
       </c>
       <c r="E90" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F90" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="G90" t="s">
         <v>86</v>
@@ -3695,54 +3809,54 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B91" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="D91" t="s">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="E91" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="F91" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="G91" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B92" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C92" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="D92" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E92" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="F92" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="G92" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
@@ -3753,28 +3867,28 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B93" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C93" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="D93" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="E93" t="s">
-        <v>108</v>
+        <v>162</v>
       </c>
       <c r="F93" t="s">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="G93" t="s">
         <v>86</v>
       </c>
       <c r="H93" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
@@ -3782,51 +3896,51 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B94" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C94" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="D94" t="s">
-        <v>49</v>
+        <v>164</v>
       </c>
       <c r="E94" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="F94" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="G94" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B95" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D95" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="E95" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="F95" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G95" t="s">
         <v>86</v>
@@ -3840,25 +3954,25 @@
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B96" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C96" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="D96" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="E96" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="F96" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G96" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
@@ -3869,28 +3983,28 @@
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="D97" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="E97" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="F97" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G97" t="s">
         <v>86</v>
       </c>
       <c r="H97" t="s">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="I97" t="s">
         <v>19</v>
@@ -3898,54 +4012,54 @@
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C98" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D98" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="E98" t="s">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="F98" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="G98" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B99" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C99" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D99" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="E99" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="F99" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="G99" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
@@ -3956,28 +4070,28 @@
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B100" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C100" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D100" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F100" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G100" t="s">
         <v>86</v>
       </c>
       <c r="H100" t="s">
-        <v>18</v>
+        <v>169</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
@@ -3985,25 +4099,25 @@
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B101" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C101" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="D101" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="E101" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="F101" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="G101" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
@@ -4014,86 +4128,86 @@
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C102" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="D102" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="E102" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="F102" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G102" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B103" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C103" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D103" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="E103" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="F103" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="G103" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B104" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C104" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="D104" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="E104" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F104" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G104" t="s">
         <v>86</v>
       </c>
       <c r="H104" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="I104" t="s">
         <v>19</v>
@@ -4101,51 +4215,51 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C105" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="D105" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="E105" t="s">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="F105" t="s">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="G105" t="s">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B106" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C106" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D106" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="E106" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="F106" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="G106" t="s">
         <v>86</v>
@@ -4159,54 +4273,54 @@
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C107" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="D107" t="s">
-        <v>132</v>
+        <v>49</v>
       </c>
       <c r="E107" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="F107" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="G107" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B108" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C108" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D108" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="E108" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F108" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="G108" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
@@ -4217,28 +4331,28 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B109" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C109" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="D109" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="E109" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F109" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="G109" t="s">
         <v>86</v>
       </c>
       <c r="H109" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="I109" t="s">
         <v>19</v>
@@ -4246,83 +4360,83 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B110" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C110" t="s">
+        <v>131</v>
+      </c>
+      <c r="D110" t="s">
+        <v>176</v>
+      </c>
+      <c r="E110" t="s">
+        <v>124</v>
+      </c>
+      <c r="F110" t="s">
+        <v>106</v>
+      </c>
+      <c r="G110" t="s">
         <v>126</v>
       </c>
-      <c r="D110" t="s">
-        <v>146</v>
-      </c>
-      <c r="E110" t="s">
-        <v>128</v>
-      </c>
-      <c r="F110" t="s">
-        <v>147</v>
-      </c>
-      <c r="G110" t="s">
-        <v>86</v>
-      </c>
       <c r="H110" t="s">
         <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C111" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="D111" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="E111" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="F111" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="G111" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="C112" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="D112" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E112" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F112" t="s">
         <v>73</v>
       </c>
       <c r="G112" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
@@ -4333,25 +4447,25 @@
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C113" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D113" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E113" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F113" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G113" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
@@ -4362,112 +4476,112 @@
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C114" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="D114" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="E114" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="F114" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="G114" t="s">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B115" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C115" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="D115" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="E115" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="F115" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="G115" t="s">
-        <v>86</v>
+        <v>180</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C116" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D116" t="s">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="E116" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="F116" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="G116" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B117" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C117" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D117" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E117" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F117" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G117" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
@@ -4478,25 +4592,25 @@
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B118" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C118" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="D118" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E118" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="F118" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="G118" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
@@ -4507,25 +4621,25 @@
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B119" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C119" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D119" t="s">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="E119" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F119" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G119" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
@@ -4536,25 +4650,25 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B120" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C120" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D120" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="E120" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F120" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="G120" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
@@ -4565,25 +4679,25 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B121" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C121" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D121" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="E121" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F121" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="G121" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
@@ -4594,25 +4708,25 @@
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B122" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C122" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="D122" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E122" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F122" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G122" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
@@ -4623,25 +4737,25 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B123" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C123" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="D123" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="E123" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F123" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="G123" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
@@ -4652,25 +4766,25 @@
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B124" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C124" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D124" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="E124" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F124" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G124" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
@@ -4681,54 +4795,54 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B125" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C125" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="D125" t="s">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="E125" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="F125" t="s">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="G125" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
       </c>
       <c r="I125" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B126" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C126" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="D126" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E126" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F126" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="G126" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
@@ -4739,25 +4853,25 @@
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B127" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C127" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="D127" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="E127" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F127" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G127" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
@@ -4768,22 +4882,22 @@
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="B128" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="C128" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="E128" t="s">
         <v>72</v>
       </c>
       <c r="F128" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="G128" t="s">
         <v>86</v>
@@ -4797,22 +4911,22 @@
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="B129" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="C129" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="E129" t="s">
         <v>72</v>
       </c>
       <c r="F129" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="G129" t="s">
         <v>86</v>
@@ -4826,22 +4940,22 @@
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B130" t="s">
         <v>39</v>
       </c>
       <c r="C130" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D130" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="E130" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F130" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G130" t="s">
         <v>86</v>
@@ -4855,22 +4969,22 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B131" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C131" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D131" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="E131" t="s">
         <v>72</v>
       </c>
       <c r="F131" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="G131" t="s">
         <v>86</v>
@@ -4884,28 +4998,28 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B132" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C132" t="s">
-        <v>152</v>
+        <v>42</v>
       </c>
       <c r="D132" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="E132" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="F132" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="G132" t="s">
         <v>86</v>
       </c>
       <c r="H132" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="I132" t="s">
         <v>19</v>
@@ -4913,22 +5027,22 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B133" t="s">
         <v>44</v>
       </c>
       <c r="C133" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="D133" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="E133" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F133" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="G133" t="s">
         <v>86</v>
@@ -4942,22 +5056,22 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B134" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C134" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D134" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="E134" t="s">
         <v>72</v>
       </c>
       <c r="F134" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="G134" t="s">
         <v>86</v>
@@ -4971,22 +5085,22 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B135" t="s">
         <v>55</v>
       </c>
       <c r="C135" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D135" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="E135" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F135" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G135" t="s">
         <v>86</v>
@@ -5000,22 +5114,22 @@
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B136" t="s">
         <v>55</v>
       </c>
       <c r="C136" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D136" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="E136" t="s">
         <v>72</v>
       </c>
       <c r="F136" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G136" t="s">
         <v>86</v>
@@ -5029,22 +5143,22 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B137" t="s">
         <v>58</v>
       </c>
       <c r="C137" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D137" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="E137" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F137" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G137" t="s">
         <v>86</v>
@@ -5058,22 +5172,22 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B138" t="s">
         <v>58</v>
       </c>
       <c r="C138" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="D138" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="E138" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F138" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="G138" t="s">
         <v>86</v>
@@ -5087,22 +5201,22 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C139" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D139" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E139" t="s">
         <v>72</v>
       </c>
       <c r="F139" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="G139" t="s">
         <v>86</v>
@@ -5116,22 +5230,22 @@
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B140" t="s">
         <v>59</v>
       </c>
       <c r="C140" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D140" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="E140" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F140" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G140" t="s">
         <v>86</v>
@@ -5145,22 +5259,22 @@
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B141" t="s">
         <v>59</v>
       </c>
       <c r="C141" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="D141" t="s">
+        <v>66</v>
+      </c>
+      <c r="E141" t="s">
+        <v>72</v>
+      </c>
+      <c r="F141" t="s">
         <v>138</v>
-      </c>
-      <c r="E141" t="s">
-        <v>53</v>
-      </c>
-      <c r="F141" t="s">
-        <v>23</v>
       </c>
       <c r="G141" t="s">
         <v>86</v>
@@ -5174,22 +5288,22 @@
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B142" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C142" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D142" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="E142" t="s">
         <v>72</v>
       </c>
       <c r="F142" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="G142" t="s">
         <v>86</v>
@@ -5203,22 +5317,22 @@
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B143" t="s">
         <v>61</v>
       </c>
       <c r="C143" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="D143" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="E143" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="F143" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="G143" t="s">
         <v>86</v>
@@ -5232,22 +5346,22 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B144" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C144" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="D144" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="E144" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F144" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="G144" t="s">
         <v>86</v>
@@ -5261,22 +5375,22 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B145" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C145" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D145" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="E145" t="s">
         <v>72</v>
       </c>
       <c r="F145" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G145" t="s">
         <v>86</v>
@@ -5290,22 +5404,22 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="B146" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="C146" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="D146" t="s">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="E146" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F146" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="G146" t="s">
         <v>86</v>
@@ -5319,22 +5433,22 @@
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="B147" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C147" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D147" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E147" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F147" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="G147" t="s">
         <v>86</v>
@@ -5348,22 +5462,22 @@
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="B148" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C148" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D148" t="s">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="E148" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F148" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="G148" t="s">
         <v>86</v>
@@ -5377,22 +5491,22 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="B149" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="C149" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="D149" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E149" t="s">
         <v>72</v>
       </c>
       <c r="F149" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="G149" t="s">
         <v>86</v>
@@ -5406,28 +5520,28 @@
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="B150" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="C150" t="s">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="D150" t="s">
-        <v>52</v>
+        <v>166</v>
       </c>
       <c r="E150" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="F150" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="G150" t="s">
         <v>86</v>
       </c>
       <c r="H150" t="s">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="I150" t="s">
         <v>19</v>
@@ -5435,22 +5549,22 @@
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="B151" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="C151" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="D151" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="E151" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F151" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="G151" t="s">
         <v>86</v>
@@ -5459,6 +5573,789 @@
         <v>18</v>
       </c>
       <c r="I151" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="15">
+      <c r="A152" t="s">
+        <v>186</v>
+      </c>
+      <c r="B152" t="s">
+        <v>44</v>
+      </c>
+      <c r="C152" t="s">
+        <v>42</v>
+      </c>
+      <c r="D152" t="s">
+        <v>84</v>
+      </c>
+      <c r="E152" t="s">
+        <v>53</v>
+      </c>
+      <c r="F152" t="s">
+        <v>23</v>
+      </c>
+      <c r="G152" t="s">
+        <v>86</v>
+      </c>
+      <c r="H152" t="s">
+        <v>18</v>
+      </c>
+      <c r="I152" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="15">
+      <c r="A153" t="s">
+        <v>186</v>
+      </c>
+      <c r="B153" t="s">
+        <v>44</v>
+      </c>
+      <c r="C153" t="s">
+        <v>136</v>
+      </c>
+      <c r="D153" t="s">
+        <v>108</v>
+      </c>
+      <c r="E153" t="s">
+        <v>72</v>
+      </c>
+      <c r="F153" t="s">
+        <v>138</v>
+      </c>
+      <c r="G153" t="s">
+        <v>86</v>
+      </c>
+      <c r="H153" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="15">
+      <c r="A154" t="s">
+        <v>186</v>
+      </c>
+      <c r="B154" t="s">
+        <v>44</v>
+      </c>
+      <c r="C154" t="s">
+        <v>95</v>
+      </c>
+      <c r="D154" t="s">
+        <v>85</v>
+      </c>
+      <c r="E154" t="s">
+        <v>103</v>
+      </c>
+      <c r="F154" t="s">
+        <v>98</v>
+      </c>
+      <c r="G154" t="s">
+        <v>86</v>
+      </c>
+      <c r="H154" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="15">
+      <c r="A155" t="s">
+        <v>186</v>
+      </c>
+      <c r="B155" t="s">
+        <v>55</v>
+      </c>
+      <c r="C155" t="s">
+        <v>62</v>
+      </c>
+      <c r="D155" t="s">
+        <v>31</v>
+      </c>
+      <c r="E155" t="s">
+        <v>72</v>
+      </c>
+      <c r="F155" t="s">
+        <v>73</v>
+      </c>
+      <c r="G155" t="s">
+        <v>86</v>
+      </c>
+      <c r="H155" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="15">
+      <c r="A156" t="s">
+        <v>186</v>
+      </c>
+      <c r="B156" t="s">
+        <v>55</v>
+      </c>
+      <c r="C156" t="s">
+        <v>136</v>
+      </c>
+      <c r="D156" t="s">
+        <v>64</v>
+      </c>
+      <c r="E156" t="s">
+        <v>72</v>
+      </c>
+      <c r="F156" t="s">
+        <v>138</v>
+      </c>
+      <c r="G156" t="s">
+        <v>86</v>
+      </c>
+      <c r="H156" t="s">
+        <v>18</v>
+      </c>
+      <c r="I156" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="15">
+      <c r="A157" t="s">
+        <v>186</v>
+      </c>
+      <c r="B157" t="s">
+        <v>55</v>
+      </c>
+      <c r="C157" t="s">
+        <v>95</v>
+      </c>
+      <c r="D157" t="s">
+        <v>108</v>
+      </c>
+      <c r="E157" t="s">
+        <v>103</v>
+      </c>
+      <c r="F157" t="s">
+        <v>98</v>
+      </c>
+      <c r="G157" t="s">
+        <v>86</v>
+      </c>
+      <c r="H157" t="s">
+        <v>18</v>
+      </c>
+      <c r="I157" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="15">
+      <c r="A158" t="s">
+        <v>186</v>
+      </c>
+      <c r="B158" t="s">
+        <v>58</v>
+      </c>
+      <c r="C158" t="s">
+        <v>62</v>
+      </c>
+      <c r="D158" t="s">
+        <v>185</v>
+      </c>
+      <c r="E158" t="s">
+        <v>72</v>
+      </c>
+      <c r="F158" t="s">
+        <v>73</v>
+      </c>
+      <c r="G158" t="s">
+        <v>86</v>
+      </c>
+      <c r="H158" t="s">
+        <v>18</v>
+      </c>
+      <c r="I158" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="15">
+      <c r="A159" t="s">
+        <v>186</v>
+      </c>
+      <c r="B159" t="s">
+        <v>58</v>
+      </c>
+      <c r="C159" t="s">
+        <v>42</v>
+      </c>
+      <c r="D159" t="s">
+        <v>31</v>
+      </c>
+      <c r="E159" t="s">
+        <v>53</v>
+      </c>
+      <c r="F159" t="s">
+        <v>23</v>
+      </c>
+      <c r="G159" t="s">
+        <v>86</v>
+      </c>
+      <c r="H159" t="s">
+        <v>18</v>
+      </c>
+      <c r="I159" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="15">
+      <c r="A160" t="s">
+        <v>186</v>
+      </c>
+      <c r="B160" t="s">
+        <v>58</v>
+      </c>
+      <c r="C160" t="s">
+        <v>136</v>
+      </c>
+      <c r="D160" t="s">
+        <v>64</v>
+      </c>
+      <c r="E160" t="s">
+        <v>72</v>
+      </c>
+      <c r="F160" t="s">
+        <v>138</v>
+      </c>
+      <c r="G160" t="s">
+        <v>86</v>
+      </c>
+      <c r="H160" t="s">
+        <v>18</v>
+      </c>
+      <c r="I160" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="15">
+      <c r="A161" t="s">
+        <v>186</v>
+      </c>
+      <c r="B161" t="s">
+        <v>58</v>
+      </c>
+      <c r="C161" t="s">
+        <v>95</v>
+      </c>
+      <c r="D161" t="s">
+        <v>116</v>
+      </c>
+      <c r="E161" t="s">
+        <v>103</v>
+      </c>
+      <c r="F161" t="s">
+        <v>98</v>
+      </c>
+      <c r="G161" t="s">
+        <v>86</v>
+      </c>
+      <c r="H161" t="s">
+        <v>18</v>
+      </c>
+      <c r="I161" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="15">
+      <c r="A162" t="s">
+        <v>186</v>
+      </c>
+      <c r="B162" t="s">
+        <v>59</v>
+      </c>
+      <c r="C162" t="s">
+        <v>62</v>
+      </c>
+      <c r="D162" t="s">
+        <v>178</v>
+      </c>
+      <c r="E162" t="s">
+        <v>72</v>
+      </c>
+      <c r="F162" t="s">
+        <v>73</v>
+      </c>
+      <c r="G162" t="s">
+        <v>86</v>
+      </c>
+      <c r="H162" t="s">
+        <v>18</v>
+      </c>
+      <c r="I162" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="15">
+      <c r="A163" t="s">
+        <v>186</v>
+      </c>
+      <c r="B163" t="s">
+        <v>59</v>
+      </c>
+      <c r="C163" t="s">
+        <v>42</v>
+      </c>
+      <c r="D163" t="s">
+        <v>166</v>
+      </c>
+      <c r="E163" t="s">
+        <v>53</v>
+      </c>
+      <c r="F163" t="s">
+        <v>23</v>
+      </c>
+      <c r="G163" t="s">
+        <v>86</v>
+      </c>
+      <c r="H163" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="15">
+      <c r="A164" t="s">
+        <v>186</v>
+      </c>
+      <c r="B164" t="s">
+        <v>59</v>
+      </c>
+      <c r="C164" t="s">
+        <v>136</v>
+      </c>
+      <c r="D164" t="s">
+        <v>189</v>
+      </c>
+      <c r="E164" t="s">
+        <v>72</v>
+      </c>
+      <c r="F164" t="s">
+        <v>138</v>
+      </c>
+      <c r="G164" t="s">
+        <v>86</v>
+      </c>
+      <c r="H164" t="s">
+        <v>18</v>
+      </c>
+      <c r="I164" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="15">
+      <c r="A165" t="s">
+        <v>186</v>
+      </c>
+      <c r="B165" t="s">
+        <v>59</v>
+      </c>
+      <c r="C165" t="s">
+        <v>95</v>
+      </c>
+      <c r="D165" t="s">
+        <v>78</v>
+      </c>
+      <c r="E165" t="s">
+        <v>103</v>
+      </c>
+      <c r="F165" t="s">
+        <v>98</v>
+      </c>
+      <c r="G165" t="s">
+        <v>86</v>
+      </c>
+      <c r="H165" t="s">
+        <v>18</v>
+      </c>
+      <c r="I165" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="15">
+      <c r="A166" t="s">
+        <v>186</v>
+      </c>
+      <c r="B166" t="s">
+        <v>61</v>
+      </c>
+      <c r="C166" t="s">
+        <v>62</v>
+      </c>
+      <c r="D166" t="s">
+        <v>178</v>
+      </c>
+      <c r="E166" t="s">
+        <v>32</v>
+      </c>
+      <c r="F166" t="s">
+        <v>73</v>
+      </c>
+      <c r="G166" t="s">
+        <v>86</v>
+      </c>
+      <c r="H166" t="s">
+        <v>18</v>
+      </c>
+      <c r="I166" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="15">
+      <c r="A167" t="s">
+        <v>186</v>
+      </c>
+      <c r="B167" t="s">
+        <v>61</v>
+      </c>
+      <c r="C167" t="s">
+        <v>42</v>
+      </c>
+      <c r="D167" t="s">
+        <v>151</v>
+      </c>
+      <c r="E167" t="s">
+        <v>53</v>
+      </c>
+      <c r="F167" t="s">
+        <v>23</v>
+      </c>
+      <c r="G167" t="s">
+        <v>86</v>
+      </c>
+      <c r="H167" t="s">
+        <v>18</v>
+      </c>
+      <c r="I167" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="15">
+      <c r="A168" t="s">
+        <v>186</v>
+      </c>
+      <c r="B168" t="s">
+        <v>61</v>
+      </c>
+      <c r="C168" t="s">
+        <v>136</v>
+      </c>
+      <c r="D168" t="s">
+        <v>189</v>
+      </c>
+      <c r="E168" t="s">
+        <v>72</v>
+      </c>
+      <c r="F168" t="s">
+        <v>138</v>
+      </c>
+      <c r="G168" t="s">
+        <v>86</v>
+      </c>
+      <c r="H168" t="s">
+        <v>18</v>
+      </c>
+      <c r="I168" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="15">
+      <c r="A169" t="s">
+        <v>186</v>
+      </c>
+      <c r="B169" t="s">
+        <v>61</v>
+      </c>
+      <c r="C169" t="s">
+        <v>95</v>
+      </c>
+      <c r="D169" t="s">
+        <v>52</v>
+      </c>
+      <c r="E169" t="s">
+        <v>103</v>
+      </c>
+      <c r="F169" t="s">
+        <v>98</v>
+      </c>
+      <c r="G169" t="s">
+        <v>86</v>
+      </c>
+      <c r="H169" t="s">
+        <v>18</v>
+      </c>
+      <c r="I169" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="15">
+      <c r="A170" t="s">
+        <v>186</v>
+      </c>
+      <c r="B170" t="s">
+        <v>65</v>
+      </c>
+      <c r="C170" t="s">
+        <v>62</v>
+      </c>
+      <c r="D170" t="s">
+        <v>78</v>
+      </c>
+      <c r="E170" t="s">
+        <v>72</v>
+      </c>
+      <c r="F170" t="s">
+        <v>73</v>
+      </c>
+      <c r="G170" t="s">
+        <v>86</v>
+      </c>
+      <c r="H170" t="s">
+        <v>18</v>
+      </c>
+      <c r="I170" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="15">
+      <c r="A171" t="s">
+        <v>186</v>
+      </c>
+      <c r="B171" t="s">
+        <v>65</v>
+      </c>
+      <c r="C171" t="s">
+        <v>42</v>
+      </c>
+      <c r="D171" t="s">
+        <v>104</v>
+      </c>
+      <c r="E171" t="s">
+        <v>53</v>
+      </c>
+      <c r="F171" t="s">
+        <v>23</v>
+      </c>
+      <c r="G171" t="s">
+        <v>86</v>
+      </c>
+      <c r="H171" t="s">
+        <v>18</v>
+      </c>
+      <c r="I171" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="15">
+      <c r="A172" t="s">
+        <v>186</v>
+      </c>
+      <c r="B172" t="s">
+        <v>65</v>
+      </c>
+      <c r="C172" t="s">
+        <v>136</v>
+      </c>
+      <c r="D172" t="s">
+        <v>137</v>
+      </c>
+      <c r="E172" t="s">
+        <v>72</v>
+      </c>
+      <c r="F172" t="s">
+        <v>138</v>
+      </c>
+      <c r="G172" t="s">
+        <v>86</v>
+      </c>
+      <c r="H172" t="s">
+        <v>18</v>
+      </c>
+      <c r="I172" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="15">
+      <c r="A173" t="s">
+        <v>186</v>
+      </c>
+      <c r="B173" t="s">
+        <v>65</v>
+      </c>
+      <c r="C173" t="s">
+        <v>95</v>
+      </c>
+      <c r="D173" t="s">
+        <v>190</v>
+      </c>
+      <c r="E173" t="s">
+        <v>103</v>
+      </c>
+      <c r="F173" t="s">
+        <v>98</v>
+      </c>
+      <c r="G173" t="s">
+        <v>86</v>
+      </c>
+      <c r="H173" t="s">
+        <v>18</v>
+      </c>
+      <c r="I173" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="15">
+      <c r="A174" t="s">
+        <v>186</v>
+      </c>
+      <c r="B174" t="s">
+        <v>74</v>
+      </c>
+      <c r="C174" t="s">
+        <v>62</v>
+      </c>
+      <c r="D174" t="s">
+        <v>78</v>
+      </c>
+      <c r="E174" t="s">
+        <v>72</v>
+      </c>
+      <c r="F174" t="s">
+        <v>73</v>
+      </c>
+      <c r="G174" t="s">
+        <v>86</v>
+      </c>
+      <c r="H174" t="s">
+        <v>18</v>
+      </c>
+      <c r="I174" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="15">
+      <c r="A175" t="s">
+        <v>186</v>
+      </c>
+      <c r="B175" t="s">
+        <v>74</v>
+      </c>
+      <c r="C175" t="s">
+        <v>42</v>
+      </c>
+      <c r="D175" t="s">
+        <v>52</v>
+      </c>
+      <c r="E175" t="s">
+        <v>53</v>
+      </c>
+      <c r="F175" t="s">
+        <v>23</v>
+      </c>
+      <c r="G175" t="s">
+        <v>86</v>
+      </c>
+      <c r="H175" t="s">
+        <v>18</v>
+      </c>
+      <c r="I175" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="15">
+      <c r="A176" t="s">
+        <v>186</v>
+      </c>
+      <c r="B176" t="s">
+        <v>74</v>
+      </c>
+      <c r="C176" t="s">
+        <v>136</v>
+      </c>
+      <c r="D176" t="s">
+        <v>116</v>
+      </c>
+      <c r="E176" t="s">
+        <v>72</v>
+      </c>
+      <c r="F176" t="s">
+        <v>138</v>
+      </c>
+      <c r="G176" t="s">
+        <v>86</v>
+      </c>
+      <c r="H176" t="s">
+        <v>18</v>
+      </c>
+      <c r="I176" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="15">
+      <c r="A177" t="s">
+        <v>186</v>
+      </c>
+      <c r="B177" t="s">
+        <v>74</v>
+      </c>
+      <c r="C177" t="s">
+        <v>95</v>
+      </c>
+      <c r="D177" t="s">
+        <v>185</v>
+      </c>
+      <c r="E177" t="s">
+        <v>103</v>
+      </c>
+      <c r="F177" t="s">
+        <v>98</v>
+      </c>
+      <c r="G177" t="s">
+        <v>86</v>
+      </c>
+      <c r="H177" t="s">
+        <v>18</v>
+      </c>
+      <c r="I177" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="15">
+      <c r="A178" t="s">
+        <v>186</v>
+      </c>
+      <c r="B178" t="s">
+        <v>79</v>
+      </c>
+      <c r="C178" t="s">
+        <v>95</v>
+      </c>
+      <c r="D178" t="s">
+        <v>104</v>
+      </c>
+      <c r="E178" t="s">
+        <v>103</v>
+      </c>
+      <c r="F178" t="s">
+        <v>98</v>
+      </c>
+      <c r="G178" t="s">
+        <v>86</v>
+      </c>
+      <c r="H178" t="s">
+        <v>18</v>
+      </c>
+      <c r="I178" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5470,7 +6367,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8e2ad2da-5ef8-4f79-a347-8e9eef3bbeda}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{912be31e-d6c3-4831-8a60-1e9df761350e}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5490,16 +6387,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -5519,13 +6416,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="C2" t="s">
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
@@ -5548,13 +6445,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="C3" t="s">
         <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="E3" t="s">
         <v>72</v>
@@ -5574,22 +6471,22 @@
     </row>
     <row r="4" spans="1:9" ht="15">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="E4" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="G4" t="s">
         <v>86</v>
@@ -5603,19 +6500,19 @@
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -5638,15 +6535,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ff0eeb56-8444-41ea-a888-229a2d919efb}">
-  <dimension ref="A1:F38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{fb5f5233-bc1c-4a48-b077-988d69b3bad7}">
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="20.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="21.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5655,13 +6552,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -5675,13 +6572,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
@@ -5695,16 +6592,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="C3" t="s">
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -5715,16 +6612,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -5735,16 +6632,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s">
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="E5" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -5755,16 +6652,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -5775,13 +6672,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
@@ -5795,16 +6692,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -5815,16 +6712,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -5835,16 +6732,16 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="C10" t="s">
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -5855,16 +6752,16 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="E11" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -5875,16 +6772,16 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="E12" t="s">
-        <v>183</v>
+        <v>120</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -5895,16 +6792,16 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="C13" t="s">
         <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="E13" t="s">
-        <v>183</v>
+        <v>120</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -5915,16 +6812,16 @@
         <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -5932,19 +6829,19 @@
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -5952,19 +6849,19 @@
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -5972,19 +6869,19 @@
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
+        <v>207</v>
+      </c>
+      <c r="E17" t="s">
         <v>174</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -5992,19 +6889,19 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>216</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -6012,19 +6909,19 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -6032,19 +6929,19 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>169</v>
+        <v>222</v>
       </c>
       <c r="C20" t="s">
         <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -6052,19 +6949,19 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -6072,19 +6969,19 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -6092,19 +6989,19 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -6112,19 +7009,19 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -6132,19 +7029,19 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B25" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>225</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -6152,19 +7049,19 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B26" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -6172,19 +7069,19 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B27" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -6192,19 +7089,19 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B28" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" t="s">
+        <v>205</v>
+      </c>
+      <c r="E28" t="s">
         <v>180</v>
-      </c>
-      <c r="C28" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" t="s">
-        <v>175</v>
-      </c>
-      <c r="E28" t="s">
-        <v>19</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -6212,19 +7109,19 @@
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B29" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C29" t="s">
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>226</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -6232,19 +7129,19 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B30" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -6252,19 +7149,19 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="D31" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -6272,16 +7169,16 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
@@ -6292,16 +7189,16 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -6312,16 +7209,16 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>227</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -6332,16 +7229,16 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s">
-        <v>186</v>
+        <v>224</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D35" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
@@ -6352,16 +7249,16 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D36" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -6372,16 +7269,16 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -6392,21 +7289,141 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="B38" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="C38" t="s">
         <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
       </c>
       <c r="F38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15">
+      <c r="A39" t="s">
+        <v>186</v>
+      </c>
+      <c r="B39" t="s">
+        <v>222</v>
+      </c>
+      <c r="C39" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" t="s">
+        <v>209</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15">
+      <c r="A40" t="s">
+        <v>186</v>
+      </c>
+      <c r="B40" t="s">
+        <v>204</v>
+      </c>
+      <c r="C40" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" t="s">
+        <v>229</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15">
+      <c r="A41" t="s">
+        <v>186</v>
+      </c>
+      <c r="B41" t="s">
+        <v>204</v>
+      </c>
+      <c r="C41" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15">
+      <c r="A42" t="s">
+        <v>186</v>
+      </c>
+      <c r="B42" t="s">
+        <v>206</v>
+      </c>
+      <c r="C42" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" t="s">
+        <v>207</v>
+      </c>
+      <c r="E42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15">
+      <c r="A43" t="s">
+        <v>186</v>
+      </c>
+      <c r="B43" t="s">
+        <v>208</v>
+      </c>
+      <c r="C43" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" t="s">
+        <v>210</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15">
+      <c r="A44" t="s">
+        <v>186</v>
+      </c>
+      <c r="B44" t="s">
+        <v>220</v>
+      </c>
+      <c r="C44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" t="s">
+        <v>207</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="233">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -363,6 +363,18 @@
     <t>30.09.2026</t>
   </si>
   <si>
+    <t>Jaworska Edyta</t>
+  </si>
+  <si>
+    <t>1TFA|gr1</t>
+  </si>
+  <si>
+    <t>prf2</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
+  </si>
+  <si>
     <t>Kosin Anna</t>
   </si>
   <si>
@@ -679,9 +691,6 @@
   </si>
   <si>
     <t>Ostrowska Ewa</t>
-  </si>
-  <si>
-    <t>Sobczak Anna</t>
   </si>
   <si>
     <t>17:20-17:25</t>
@@ -1161,7 +1170,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{eb033528-fd6d-4c09-a495-9df7ff665cd8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f91a5237-8dab-4019-b7ae-a8202aa5723e}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1182,8 +1191,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7d9cc044-5284-4fc2-ace4-841ffc3d4822}">
-  <dimension ref="A1:I178"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4e09375a-26f1-40e7-a00b-4ffa06be91c6}">
+  <dimension ref="A1:I185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -2977,22 +2986,22 @@
         <v>113</v>
       </c>
       <c r="D62" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
       </c>
       <c r="G62" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
@@ -3003,19 +3012,19 @@
         <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E63" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="F63" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="G63" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
@@ -3032,19 +3041,19 @@
         <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="D64" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E64" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F64" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="G64" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
@@ -3058,28 +3067,28 @@
         <v>112</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="D65" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="E65" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="F65" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="G65" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
@@ -3090,25 +3099,25 @@
         <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D66" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="E66" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="F66" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G66" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
@@ -3119,25 +3128,25 @@
         <v>24</v>
       </c>
       <c r="C67" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D67" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="E67" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="G67" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
@@ -3148,19 +3157,19 @@
         <v>24</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D68" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="E68" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="F68" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
@@ -3177,19 +3186,19 @@
         <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D69" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E69" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="F69" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="G69" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
@@ -3206,19 +3215,19 @@
         <v>24</v>
       </c>
       <c r="C70" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="D70" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="E70" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F70" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G70" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
@@ -3232,19 +3241,19 @@
         <v>112</v>
       </c>
       <c r="B71" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C71" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="D71" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="E71" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F71" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="G71" t="s">
         <v>86</v>
@@ -3261,22 +3270,22 @@
         <v>112</v>
       </c>
       <c r="B72" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C72" t="s">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="D72" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="E72" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F72" t="s">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="G72" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
@@ -3293,25 +3302,25 @@
         <v>39</v>
       </c>
       <c r="C73" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D73" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E73" t="s">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="F73" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="G73" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
@@ -3322,25 +3331,25 @@
         <v>39</v>
       </c>
       <c r="C74" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D74" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="F74" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="G74" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
@@ -3351,25 +3360,25 @@
         <v>39</v>
       </c>
       <c r="C75" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D75" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="E75" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F75" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="G75" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
@@ -3380,25 +3389,25 @@
         <v>39</v>
       </c>
       <c r="C76" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="D76" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="E76" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="F76" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
@@ -3409,25 +3418,25 @@
         <v>39</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D77" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="E77" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="F77" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="G77" t="s">
-        <v>141</v>
+        <v>17</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
@@ -3435,28 +3444,28 @@
         <v>112</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C78" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="E78" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F78" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="G78" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H78" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
@@ -3464,28 +3473,28 @@
         <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C79" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="E79" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="F79" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="G79" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
@@ -3493,28 +3502,28 @@
         <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C80" t="s">
+        <v>95</v>
+      </c>
+      <c r="D80" t="s">
+        <v>84</v>
+      </c>
+      <c r="E80" t="s">
+        <v>143</v>
+      </c>
+      <c r="F80" t="s">
         <v>144</v>
       </c>
-      <c r="D80" t="s">
+      <c r="G80" t="s">
         <v>145</v>
       </c>
-      <c r="E80" t="s">
-        <v>124</v>
-      </c>
-      <c r="F80" t="s">
-        <v>146</v>
-      </c>
-      <c r="G80" t="s">
-        <v>147</v>
-      </c>
       <c r="H80" t="s">
         <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
@@ -3525,22 +3534,22 @@
         <v>44</v>
       </c>
       <c r="C81" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D81" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="E81" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F81" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="G81" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="H81" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="I81" t="s">
         <v>19</v>
@@ -3554,25 +3563,25 @@
         <v>44</v>
       </c>
       <c r="C82" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D82" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E82" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="F82" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
       <c r="G82" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
@@ -3583,25 +3592,25 @@
         <v>44</v>
       </c>
       <c r="C83" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="D83" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="E83" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="F83" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G83" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
@@ -3612,19 +3621,19 @@
         <v>44</v>
       </c>
       <c r="C84" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D84" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E84" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="F84" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="G84" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
@@ -3641,25 +3650,25 @@
         <v>44</v>
       </c>
       <c r="C85" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="D85" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="E85" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="F85" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="G85" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
@@ -3670,25 +3679,25 @@
         <v>44</v>
       </c>
       <c r="C86" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="D86" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E86" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="F86" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="G86" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
@@ -3699,25 +3708,25 @@
         <v>44</v>
       </c>
       <c r="C87" t="s">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="D87" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="E87" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F87" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="G87" t="s">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
@@ -3725,25 +3734,25 @@
         <v>112</v>
       </c>
       <c r="B88" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="D88" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="E88" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="F88" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="G88" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="H88" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="I88" t="s">
         <v>19</v>
@@ -3754,28 +3763,28 @@
         <v>112</v>
       </c>
       <c r="B89" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C89" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="D89" t="s">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="E89" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="F89" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="G89" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
@@ -3783,28 +3792,28 @@
         <v>112</v>
       </c>
       <c r="B90" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="D90" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E90" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F90" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="G90" t="s">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
@@ -3812,28 +3821,28 @@
         <v>112</v>
       </c>
       <c r="B91" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>41</v>
       </c>
       <c r="D91" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="E91" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F91" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="G91" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
@@ -3844,22 +3853,22 @@
         <v>55</v>
       </c>
       <c r="C92" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D92" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E92" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="F92" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="G92" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="H92" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="I92" t="s">
         <v>19</v>
@@ -3873,22 +3882,22 @@
         <v>55</v>
       </c>
       <c r="C93" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="D93" t="s">
-        <v>66</v>
+        <v>163</v>
       </c>
       <c r="E93" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F93" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G93" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H93" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
@@ -3902,25 +3911,25 @@
         <v>55</v>
       </c>
       <c r="C94" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="D94" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E94" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F94" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G94" t="s">
-        <v>147</v>
+        <v>86</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
@@ -3931,25 +3940,25 @@
         <v>55</v>
       </c>
       <c r="C95" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="D95" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="E95" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="F95" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="G95" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
@@ -3960,25 +3969,25 @@
         <v>55</v>
       </c>
       <c r="C96" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="D96" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="E96" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="F96" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="G96" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
@@ -3989,22 +3998,22 @@
         <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="D97" t="s">
-        <v>166</v>
+        <v>111</v>
       </c>
       <c r="E97" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="F97" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G97" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H97" t="s">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="I97" t="s">
         <v>19</v>
@@ -4015,28 +4024,28 @@
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C98" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D98" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E98" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="F98" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="G98" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H98" t="s">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="I98" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
@@ -4044,28 +4053,28 @@
         <v>112</v>
       </c>
       <c r="B99" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C99" t="s">
-        <v>121</v>
+        <v>42</v>
       </c>
       <c r="D99" t="s">
         <v>168</v>
       </c>
       <c r="E99" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="F99" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="G99" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
@@ -4073,25 +4082,25 @@
         <v>112</v>
       </c>
       <c r="B100" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C100" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="D100" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="E100" t="s">
         <v>72</v>
       </c>
       <c r="F100" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="G100" t="s">
         <v>86</v>
       </c>
       <c r="H100" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
@@ -4102,19 +4111,19 @@
         <v>112</v>
       </c>
       <c r="B101" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C101" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="D101" t="s">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="E101" t="s">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="F101" t="s">
-        <v>161</v>
+        <v>98</v>
       </c>
       <c r="G101" t="s">
         <v>60</v>
@@ -4131,28 +4140,28 @@
         <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C102" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="D102" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="E102" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="F102" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="G102" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="H102" t="s">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="I102" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
@@ -4163,25 +4172,25 @@
         <v>58</v>
       </c>
       <c r="C103" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D103" t="s">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="E103" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="F103" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="G103" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
@@ -4192,22 +4201,22 @@
         <v>58</v>
       </c>
       <c r="C104" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="D104" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E104" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F104" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G104" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H104" t="s">
-        <v>172</v>
+        <v>18</v>
       </c>
       <c r="I104" t="s">
         <v>19</v>
@@ -4221,25 +4230,25 @@
         <v>58</v>
       </c>
       <c r="C105" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D105" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="E105" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="F105" t="s">
+        <v>73</v>
+      </c>
+      <c r="G105" t="s">
+        <v>86</v>
+      </c>
+      <c r="H105" t="s">
         <v>173</v>
       </c>
-      <c r="G105" t="s">
-        <v>174</v>
-      </c>
-      <c r="H105" t="s">
-        <v>18</v>
-      </c>
       <c r="I105" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
@@ -4250,19 +4259,19 @@
         <v>58</v>
       </c>
       <c r="C106" t="s">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="D106" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E106" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="F106" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="G106" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
@@ -4276,22 +4285,22 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C107" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D107" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E107" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F107" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="G107" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
@@ -4305,28 +4314,28 @@
         <v>112</v>
       </c>
       <c r="B108" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C108" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D108" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="E108" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F108" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="G108" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
@@ -4334,28 +4343,28 @@
         <v>112</v>
       </c>
       <c r="B109" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C109" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="D109" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="E109" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="F109" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="G109" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="H109" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
@@ -4363,28 +4372,28 @@
         <v>112</v>
       </c>
       <c r="B110" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C110" t="s">
-        <v>131</v>
+        <v>42</v>
       </c>
       <c r="D110" t="s">
+        <v>170</v>
+      </c>
+      <c r="E110" t="s">
+        <v>53</v>
+      </c>
+      <c r="F110" t="s">
+        <v>23</v>
+      </c>
+      <c r="G110" t="s">
+        <v>86</v>
+      </c>
+      <c r="H110" t="s">
         <v>176</v>
       </c>
-      <c r="E110" t="s">
-        <v>124</v>
-      </c>
-      <c r="F110" t="s">
-        <v>106</v>
-      </c>
-      <c r="G110" t="s">
-        <v>126</v>
-      </c>
-      <c r="H110" t="s">
-        <v>18</v>
-      </c>
       <c r="I110" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
@@ -4392,22 +4401,22 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C111" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="D111" t="s">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="E111" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="F111" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="G111" t="s">
-        <v>37</v>
+        <v>178</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
@@ -4421,22 +4430,22 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C112" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="D112" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="E112" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F112" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="G112" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
@@ -4453,25 +4462,25 @@
         <v>59</v>
       </c>
       <c r="C113" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="D113" t="s">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="E113" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="F113" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G113" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
@@ -4482,25 +4491,25 @@
         <v>59</v>
       </c>
       <c r="C114" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D114" t="s">
-        <v>64</v>
+        <v>172</v>
       </c>
       <c r="E114" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="F114" t="s">
-        <v>138</v>
+        <v>40</v>
       </c>
       <c r="G114" t="s">
-        <v>174</v>
+        <v>60</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
@@ -4511,25 +4520,25 @@
         <v>59</v>
       </c>
       <c r="C115" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="D115" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="E115" t="s">
+        <v>15</v>
+      </c>
+      <c r="F115" t="s">
+        <v>156</v>
+      </c>
+      <c r="G115" t="s">
+        <v>86</v>
+      </c>
+      <c r="H115" t="s">
         <v>179</v>
       </c>
-      <c r="F115" t="s">
-        <v>117</v>
-      </c>
-      <c r="G115" t="s">
-        <v>180</v>
-      </c>
-      <c r="H115" t="s">
-        <v>18</v>
-      </c>
       <c r="I115" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
@@ -4540,19 +4549,19 @@
         <v>59</v>
       </c>
       <c r="C116" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="D116" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E116" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="F116" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G116" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
@@ -4566,28 +4575,28 @@
         <v>112</v>
       </c>
       <c r="B117" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C117" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D117" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E117" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F117" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="G117" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
@@ -4595,28 +4604,28 @@
         <v>112</v>
       </c>
       <c r="B118" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C118" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D118" t="s">
         <v>168</v>
       </c>
       <c r="E118" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="F118" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G118" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
@@ -4624,16 +4633,16 @@
         <v>112</v>
       </c>
       <c r="B119" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C119" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="D119" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="E119" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F119" t="s">
         <v>73</v>
@@ -4653,13 +4662,13 @@
         <v>112</v>
       </c>
       <c r="B120" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C120" t="s">
         <v>42</v>
       </c>
       <c r="D120" t="s">
-        <v>57</v>
+        <v>155</v>
       </c>
       <c r="E120" t="s">
         <v>53</v>
@@ -4682,28 +4691,28 @@
         <v>112</v>
       </c>
       <c r="B121" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C121" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="D121" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="E121" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="F121" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="G121" t="s">
-        <v>60</v>
+        <v>178</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
@@ -4711,28 +4720,28 @@
         <v>112</v>
       </c>
       <c r="B122" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C122" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="D122" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="E122" t="s">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="F122" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G122" t="s">
-        <v>60</v>
+        <v>184</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
@@ -4740,28 +4749,28 @@
         <v>112</v>
       </c>
       <c r="B123" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C123" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="D123" t="s">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="E123" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="F123" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="G123" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
@@ -4769,19 +4778,19 @@
         <v>112</v>
       </c>
       <c r="B124" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C124" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="D124" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="E124" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F124" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="G124" t="s">
         <v>60</v>
@@ -4798,28 +4807,28 @@
         <v>112</v>
       </c>
       <c r="B125" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C125" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D125" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E125" t="s">
-        <v>183</v>
+        <v>27</v>
       </c>
       <c r="F125" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G125" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
       </c>
       <c r="I125" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
@@ -4827,19 +4836,19 @@
         <v>112</v>
       </c>
       <c r="B126" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C126" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D126" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="E126" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F126" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G126" t="s">
         <v>60</v>
@@ -4856,19 +4865,19 @@
         <v>112</v>
       </c>
       <c r="B127" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C127" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D127" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="E127" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="F127" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="G127" t="s">
         <v>60</v>
@@ -4882,25 +4891,25 @@
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="B128" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="C128" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="D128" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="E128" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F128" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="G128" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
@@ -4911,25 +4920,25 @@
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="B129" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C129" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D129" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="E129" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F129" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="G129" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
@@ -4940,25 +4949,25 @@
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="B130" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C130" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="D130" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E130" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F130" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="G130" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
@@ -4969,16 +4978,16 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="B131" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C131" t="s">
         <v>62</v>
       </c>
       <c r="D131" t="s">
-        <v>185</v>
+        <v>57</v>
       </c>
       <c r="E131" t="s">
         <v>72</v>
@@ -4987,7 +4996,7 @@
         <v>73</v>
       </c>
       <c r="G131" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
@@ -4998,54 +5007,54 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="B132" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C132" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="D132" t="s">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="E132" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="F132" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G132" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="B133" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C133" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="D133" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E133" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F133" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="G133" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
@@ -5056,25 +5065,25 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="B134" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C134" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D134" t="s">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="E134" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F134" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="G134" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H134" t="s">
         <v>18</v>
@@ -5085,22 +5094,22 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B135" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C135" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D135" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="E135" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F135" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G135" t="s">
         <v>86</v>
@@ -5114,22 +5123,22 @@
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B136" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="C136" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="D136" t="s">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="E136" t="s">
         <v>72</v>
       </c>
       <c r="F136" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="G136" t="s">
         <v>86</v>
@@ -5143,22 +5152,22 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B137" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C137" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D137" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E137" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F137" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G137" t="s">
         <v>86</v>
@@ -5172,22 +5181,22 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B138" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C138" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="D138" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="E138" t="s">
         <v>72</v>
       </c>
       <c r="F138" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="G138" t="s">
         <v>86</v>
@@ -5201,22 +5210,22 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B139" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C139" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D139" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E139" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F139" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G139" t="s">
         <v>86</v>
@@ -5230,22 +5239,22 @@
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B140" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C140" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D140" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="E140" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F140" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G140" t="s">
         <v>86</v>
@@ -5259,22 +5268,22 @@
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B141" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C141" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="D141" t="s">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="E141" t="s">
         <v>72</v>
       </c>
       <c r="F141" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="G141" t="s">
         <v>86</v>
@@ -5288,22 +5297,22 @@
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B142" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C142" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D142" t="s">
         <v>100</v>
       </c>
       <c r="E142" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F142" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G142" t="s">
         <v>86</v>
@@ -5317,22 +5326,22 @@
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B143" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C143" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D143" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="E143" t="s">
         <v>72</v>
       </c>
       <c r="F143" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G143" t="s">
         <v>86</v>
@@ -5346,22 +5355,22 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B144" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C144" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="D144" t="s">
-        <v>181</v>
+        <v>104</v>
       </c>
       <c r="E144" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F144" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="G144" t="s">
         <v>86</v>
@@ -5375,22 +5384,22 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B145" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C145" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D145" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="E145" t="s">
         <v>72</v>
       </c>
       <c r="F145" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G145" t="s">
         <v>86</v>
@@ -5404,22 +5413,22 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="C146" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D146" t="s">
-        <v>187</v>
+        <v>57</v>
       </c>
       <c r="E146" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F146" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G146" t="s">
         <v>86</v>
@@ -5433,22 +5442,22 @@
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B147" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C147" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="D147" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E147" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F147" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="G147" t="s">
         <v>86</v>
@@ -5462,22 +5471,22 @@
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B148" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C148" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D148" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="E148" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F148" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G148" t="s">
         <v>86</v>
@@ -5491,22 +5500,22 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B149" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C149" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="D149" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E149" t="s">
         <v>72</v>
       </c>
       <c r="F149" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="G149" t="s">
         <v>86</v>
@@ -5520,28 +5529,28 @@
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B150" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C150" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="D150" t="s">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="E150" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="F150" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="G150" t="s">
         <v>86</v>
       </c>
       <c r="H150" t="s">
-        <v>188</v>
+        <v>18</v>
       </c>
       <c r="I150" t="s">
         <v>19</v>
@@ -5549,22 +5558,22 @@
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B151" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C151" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="D151" t="s">
-        <v>64</v>
+        <v>185</v>
       </c>
       <c r="E151" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F151" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="G151" t="s">
         <v>86</v>
@@ -5578,22 +5587,22 @@
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B152" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C152" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D152" t="s">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="E152" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F152" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G152" t="s">
         <v>86</v>
@@ -5607,22 +5616,22 @@
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B153" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C153" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="D153" t="s">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="E153" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F153" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="G153" t="s">
         <v>86</v>
@@ -5636,19 +5645,19 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B154" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C154" t="s">
         <v>95</v>
       </c>
       <c r="D154" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E154" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="F154" t="s">
         <v>98</v>
@@ -5665,22 +5674,22 @@
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B155" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C155" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D155" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="E155" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F155" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G155" t="s">
         <v>86</v>
@@ -5694,22 +5703,22 @@
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B156" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C156" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D156" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="E156" t="s">
         <v>72</v>
       </c>
       <c r="F156" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G156" t="s">
         <v>86</v>
@@ -5723,28 +5732,28 @@
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B157" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C157" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="D157" t="s">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="E157" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="F157" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="G157" t="s">
         <v>86</v>
       </c>
       <c r="H157" t="s">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="I157" t="s">
         <v>19</v>
@@ -5752,22 +5761,22 @@
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B158" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C158" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="D158" t="s">
-        <v>185</v>
+        <v>64</v>
       </c>
       <c r="E158" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F158" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="G158" t="s">
         <v>86</v>
@@ -5781,16 +5790,16 @@
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B159" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C159" t="s">
         <v>42</v>
       </c>
       <c r="D159" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="E159" t="s">
         <v>53</v>
@@ -5810,22 +5819,22 @@
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B160" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C160" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D160" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="E160" t="s">
         <v>72</v>
       </c>
       <c r="F160" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G160" t="s">
         <v>86</v>
@@ -5839,16 +5848,16 @@
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B161" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C161" t="s">
         <v>95</v>
       </c>
       <c r="D161" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E161" t="s">
         <v>103</v>
@@ -5868,16 +5877,16 @@
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B162" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C162" t="s">
         <v>62</v>
       </c>
       <c r="D162" t="s">
-        <v>178</v>
+        <v>31</v>
       </c>
       <c r="E162" t="s">
         <v>72</v>
@@ -5897,22 +5906,22 @@
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B163" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C163" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D163" t="s">
-        <v>166</v>
+        <v>64</v>
       </c>
       <c r="E163" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F163" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G163" t="s">
         <v>86</v>
@@ -5926,22 +5935,22 @@
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B164" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C164" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="D164" t="s">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="E164" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F164" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="G164" t="s">
         <v>86</v>
@@ -5955,22 +5964,22 @@
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B165" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C165" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D165" t="s">
-        <v>78</v>
+        <v>189</v>
       </c>
       <c r="E165" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F165" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G165" t="s">
         <v>86</v>
@@ -5984,22 +5993,22 @@
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B166" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C166" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D166" t="s">
-        <v>178</v>
+        <v>31</v>
       </c>
       <c r="E166" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F166" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G166" t="s">
         <v>86</v>
@@ -6013,22 +6022,22 @@
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B167" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C167" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D167" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="E167" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F167" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G167" t="s">
         <v>86</v>
@@ -6042,22 +6051,22 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B168" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C168" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="D168" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="E168" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F168" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="G168" t="s">
         <v>86</v>
@@ -6071,22 +6080,22 @@
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B169" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C169" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D169" t="s">
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="E169" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F169" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G169" t="s">
         <v>86</v>
@@ -6100,22 +6109,22 @@
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B170" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C170" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D170" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="E170" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F170" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G170" t="s">
         <v>86</v>
@@ -6129,22 +6138,22 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B171" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C171" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D171" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="E171" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F171" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G171" t="s">
         <v>86</v>
@@ -6158,22 +6167,22 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B172" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C172" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="D172" t="s">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="E172" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F172" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="G172" t="s">
         <v>86</v>
@@ -6187,22 +6196,22 @@
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B173" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C173" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D173" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E173" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="F173" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G173" t="s">
         <v>86</v>
@@ -6216,22 +6225,22 @@
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B174" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C174" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D174" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="E174" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F174" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G174" t="s">
         <v>86</v>
@@ -6245,22 +6254,22 @@
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B175" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C175" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D175" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="E175" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F175" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G175" t="s">
         <v>86</v>
@@ -6274,22 +6283,22 @@
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B176" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C176" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="D176" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="E176" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F176" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="G176" t="s">
         <v>86</v>
@@ -6303,22 +6312,22 @@
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B177" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C177" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D177" t="s">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="E177" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F177" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G177" t="s">
         <v>86</v>
@@ -6332,22 +6341,22 @@
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B178" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C178" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="D178" t="s">
         <v>104</v>
       </c>
       <c r="E178" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="F178" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="G178" t="s">
         <v>86</v>
@@ -6356,6 +6365,209 @@
         <v>18</v>
       </c>
       <c r="I178" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="15">
+      <c r="A179" t="s">
+        <v>190</v>
+      </c>
+      <c r="B179" t="s">
+        <v>65</v>
+      </c>
+      <c r="C179" t="s">
+        <v>140</v>
+      </c>
+      <c r="D179" t="s">
+        <v>141</v>
+      </c>
+      <c r="E179" t="s">
+        <v>72</v>
+      </c>
+      <c r="F179" t="s">
+        <v>142</v>
+      </c>
+      <c r="G179" t="s">
+        <v>86</v>
+      </c>
+      <c r="H179" t="s">
+        <v>18</v>
+      </c>
+      <c r="I179" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="15">
+      <c r="A180" t="s">
+        <v>190</v>
+      </c>
+      <c r="B180" t="s">
+        <v>65</v>
+      </c>
+      <c r="C180" t="s">
+        <v>95</v>
+      </c>
+      <c r="D180" t="s">
+        <v>194</v>
+      </c>
+      <c r="E180" t="s">
+        <v>103</v>
+      </c>
+      <c r="F180" t="s">
+        <v>98</v>
+      </c>
+      <c r="G180" t="s">
+        <v>86</v>
+      </c>
+      <c r="H180" t="s">
+        <v>18</v>
+      </c>
+      <c r="I180" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="15">
+      <c r="A181" t="s">
+        <v>190</v>
+      </c>
+      <c r="B181" t="s">
+        <v>74</v>
+      </c>
+      <c r="C181" t="s">
+        <v>62</v>
+      </c>
+      <c r="D181" t="s">
+        <v>78</v>
+      </c>
+      <c r="E181" t="s">
+        <v>72</v>
+      </c>
+      <c r="F181" t="s">
+        <v>73</v>
+      </c>
+      <c r="G181" t="s">
+        <v>86</v>
+      </c>
+      <c r="H181" t="s">
+        <v>18</v>
+      </c>
+      <c r="I181" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="15">
+      <c r="A182" t="s">
+        <v>190</v>
+      </c>
+      <c r="B182" t="s">
+        <v>74</v>
+      </c>
+      <c r="C182" t="s">
+        <v>42</v>
+      </c>
+      <c r="D182" t="s">
+        <v>52</v>
+      </c>
+      <c r="E182" t="s">
+        <v>53</v>
+      </c>
+      <c r="F182" t="s">
+        <v>23</v>
+      </c>
+      <c r="G182" t="s">
+        <v>86</v>
+      </c>
+      <c r="H182" t="s">
+        <v>18</v>
+      </c>
+      <c r="I182" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="15">
+      <c r="A183" t="s">
+        <v>190</v>
+      </c>
+      <c r="B183" t="s">
+        <v>74</v>
+      </c>
+      <c r="C183" t="s">
+        <v>140</v>
+      </c>
+      <c r="D183" t="s">
+        <v>120</v>
+      </c>
+      <c r="E183" t="s">
+        <v>72</v>
+      </c>
+      <c r="F183" t="s">
+        <v>142</v>
+      </c>
+      <c r="G183" t="s">
+        <v>86</v>
+      </c>
+      <c r="H183" t="s">
+        <v>18</v>
+      </c>
+      <c r="I183" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="15">
+      <c r="A184" t="s">
+        <v>190</v>
+      </c>
+      <c r="B184" t="s">
+        <v>74</v>
+      </c>
+      <c r="C184" t="s">
+        <v>95</v>
+      </c>
+      <c r="D184" t="s">
+        <v>189</v>
+      </c>
+      <c r="E184" t="s">
+        <v>103</v>
+      </c>
+      <c r="F184" t="s">
+        <v>98</v>
+      </c>
+      <c r="G184" t="s">
+        <v>86</v>
+      </c>
+      <c r="H184" t="s">
+        <v>18</v>
+      </c>
+      <c r="I184" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="15">
+      <c r="A185" t="s">
+        <v>190</v>
+      </c>
+      <c r="B185" t="s">
+        <v>79</v>
+      </c>
+      <c r="C185" t="s">
+        <v>95</v>
+      </c>
+      <c r="D185" t="s">
+        <v>104</v>
+      </c>
+      <c r="E185" t="s">
+        <v>103</v>
+      </c>
+      <c r="F185" t="s">
+        <v>98</v>
+      </c>
+      <c r="G185" t="s">
+        <v>86</v>
+      </c>
+      <c r="H185" t="s">
+        <v>18</v>
+      </c>
+      <c r="I185" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6367,7 +6579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{912be31e-d6c3-4831-8a60-1e9df761350e}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e8c0c809-aa2c-4c05-99ed-cc21ba7e501c}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6387,16 +6599,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6416,13 +6628,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C2" t="s">
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
@@ -6445,13 +6657,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C3" t="s">
         <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E3" t="s">
         <v>72</v>
@@ -6474,19 +6686,19 @@
         <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G4" t="s">
         <v>86</v>
@@ -6503,16 +6715,16 @@
         <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6535,8 +6747,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{fb5f5233-bc1c-4a48-b077-988d69b3bad7}">
-  <dimension ref="A1:F44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2f3c97f6-0caf-4b74-a953-7018b5d8a6a9}">
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6552,13 +6764,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6572,13 +6784,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
@@ -6592,16 +6804,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -6612,16 +6824,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -6632,16 +6844,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C5" t="s">
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6652,16 +6864,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -6672,13 +6884,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
@@ -6692,16 +6904,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E8" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -6712,16 +6924,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -6732,16 +6944,16 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C10" t="s">
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E10" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -6752,16 +6964,16 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -6772,16 +6984,16 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E12" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -6792,16 +7004,16 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C13" t="s">
         <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E13" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -6812,16 +7024,16 @@
         <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C14" t="s">
         <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E14" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -6832,16 +7044,16 @@
         <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C15" t="s">
         <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E15" t="s">
-        <v>219</v>
+        <v>116</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -6852,16 +7064,16 @@
         <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C16" t="s">
         <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E16" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -6872,16 +7084,16 @@
         <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C17" t="s">
         <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E17" t="s">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -6892,16 +7104,16 @@
         <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E18" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -6912,16 +7124,16 @@
         <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -6932,16 +7144,16 @@
         <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E20" t="s">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -6952,16 +7164,16 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -6972,16 +7184,16 @@
         <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -6992,16 +7204,16 @@
         <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="D23" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="E23" t="s">
-        <v>214</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -7012,16 +7224,16 @@
         <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E24" t="s">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -7032,16 +7244,16 @@
         <v>112</v>
       </c>
       <c r="B25" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E25" t="s">
-        <v>225</v>
+        <v>94</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -7052,16 +7264,16 @@
         <v>112</v>
       </c>
       <c r="B26" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E26" t="s">
-        <v>126</v>
+        <v>228</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -7072,16 +7284,16 @@
         <v>112</v>
       </c>
       <c r="B27" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="E27" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -7092,16 +7304,16 @@
         <v>112</v>
       </c>
       <c r="B28" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E28" t="s">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -7112,16 +7324,16 @@
         <v>112</v>
       </c>
       <c r="B29" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D29" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E29" t="s">
-        <v>226</v>
+        <v>124</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -7135,13 +7347,13 @@
         <v>212</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E30" t="s">
-        <v>51</v>
+        <v>184</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -7155,13 +7367,13 @@
         <v>212</v>
       </c>
       <c r="C31" t="s">
-        <v>144</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E31" t="s">
-        <v>120</v>
+        <v>229</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -7169,19 +7381,19 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="B32" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -7189,19 +7401,19 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="B33" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="D33" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -7209,16 +7421,16 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C34" t="s">
         <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -7229,16 +7441,16 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
@@ -7249,16 +7461,16 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -7269,16 +7481,16 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B37" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -7289,16 +7501,16 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B38" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D38" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -7309,16 +7521,16 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -7329,16 +7541,16 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B40" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -7349,16 +7561,16 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="D41" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
@@ -7369,16 +7581,16 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B42" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D42" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
@@ -7389,16 +7601,16 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B43" t="s">
         <v>208</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -7409,21 +7621,61 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B44" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C44" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" t="s">
+        <v>211</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15">
+      <c r="A45" t="s">
+        <v>190</v>
+      </c>
+      <c r="B45" t="s">
+        <v>212</v>
+      </c>
+      <c r="C45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" t="s">
+        <v>214</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15">
+      <c r="A46" t="s">
+        <v>190</v>
+      </c>
+      <c r="B46" t="s">
+        <v>223</v>
+      </c>
+      <c r="C46" t="s">
         <v>95</v>
       </c>
-      <c r="D44" t="s">
-        <v>207</v>
-      </c>
-      <c r="E44" t="s">
-        <v>19</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="D46" t="s">
+        <v>211</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="242">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -555,9 +555,6 @@
     <t>p. Kruk, techniki fryzjerskie za lekcję 1; sala 34</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Kopij Marcin</t>
   </si>
   <si>
@@ -594,6 +591,24 @@
     <t>1WA</t>
   </si>
   <si>
+    <t>Towar jako przedmiot handlu</t>
+  </si>
+  <si>
+    <t>Wójcik Kamil</t>
+  </si>
+  <si>
+    <t>Technika w produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>Fizyka</t>
+  </si>
+  <si>
+    <t>Biczysko Wojciech</t>
+  </si>
+  <si>
+    <t>p. Czukiewska, Zajęcia z wychowawcą za lekcję 10</t>
+  </si>
+  <si>
     <t>02.10.2026</t>
   </si>
   <si>
@@ -603,6 +618,12 @@
     <t>próbna ewakuacja - inspektor zewnętrzny</t>
   </si>
   <si>
+    <t>5TH|DZ</t>
+  </si>
+  <si>
+    <t>organizacja Wrocławskiego Miasteczka Profilaktyki - opieka nad uczniami</t>
+  </si>
+  <si>
     <t>3FB</t>
   </si>
   <si>
@@ -714,10 +735,16 @@
     <t>Czukiewska Bożena</t>
   </si>
   <si>
+    <t>Misiąg Anna</t>
+  </si>
+  <si>
     <t>11:20-11:25</t>
   </si>
   <si>
     <t>16:30-16:35</t>
+  </si>
+  <si>
+    <t>Krystek Krzysztof</t>
   </si>
   <si>
     <t>bramka wejściowa</t>
@@ -1170,7 +1197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f91a5237-8dab-4019-b7ae-a8202aa5723e}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{137f1897-7d0c-4d01-9c61-95ce9d9377a5}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1191,8 +1218,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4e09375a-26f1-40e7-a00b-4ffa06be91c6}">
-  <dimension ref="A1:I185"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{51b4943e-6d1e-4ce1-950c-ad6d4d0db804}">
+  <dimension ref="A1:I188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1202,7 +1229,7 @@
     <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="45.5714285714286" customWidth="1"/>
-    <col min="8" max="8" width="57" customWidth="1"/>
+    <col min="8" max="8" width="65.2857142857143" customWidth="1"/>
     <col min="9" max="9" width="19.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4413,10 +4440,10 @@
         <v>143</v>
       </c>
       <c r="F111" t="s">
+        <v>153</v>
+      </c>
+      <c r="G111" t="s">
         <v>177</v>
-      </c>
-      <c r="G111" t="s">
-        <v>178</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
@@ -4535,7 +4562,7 @@
         <v>86</v>
       </c>
       <c r="H115" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I115" t="s">
         <v>19</v>
@@ -4552,7 +4579,7 @@
         <v>135</v>
       </c>
       <c r="D116" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E116" t="s">
         <v>128</v>
@@ -4700,13 +4727,13 @@
         <v>64</v>
       </c>
       <c r="E121" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F121" t="s">
         <v>142</v>
       </c>
       <c r="G121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
@@ -4726,16 +4753,16 @@
         <v>95</v>
       </c>
       <c r="D122" t="s">
+        <v>181</v>
+      </c>
+      <c r="E122" t="s">
         <v>182</v>
-      </c>
-      <c r="E122" t="s">
-        <v>183</v>
       </c>
       <c r="F122" t="s">
         <v>121</v>
       </c>
       <c r="G122" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
@@ -4755,7 +4782,7 @@
         <v>41</v>
       </c>
       <c r="D123" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E123" t="s">
         <v>97</v>
@@ -4842,7 +4869,7 @@
         <v>62</v>
       </c>
       <c r="D126" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E126" t="s">
         <v>72</v>
@@ -5016,10 +5043,10 @@
         <v>148</v>
       </c>
       <c r="D132" t="s">
+        <v>185</v>
+      </c>
+      <c r="E132" t="s">
         <v>186</v>
-      </c>
-      <c r="E132" t="s">
-        <v>187</v>
       </c>
       <c r="F132" t="s">
         <v>36</v>
@@ -5094,7 +5121,7 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B135" t="s">
         <v>12</v>
@@ -5112,7 +5139,7 @@
         <v>73</v>
       </c>
       <c r="G135" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H135" t="s">
         <v>18</v>
@@ -5123,7 +5150,7 @@
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B136" t="s">
         <v>24</v>
@@ -5132,7 +5159,7 @@
         <v>62</v>
       </c>
       <c r="D136" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E136" t="s">
         <v>72</v>
@@ -5141,7 +5168,7 @@
         <v>73</v>
       </c>
       <c r="G136" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H136" t="s">
         <v>18</v>
@@ -5152,7 +5179,7 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B137" t="s">
         <v>39</v>
@@ -5164,24 +5191,24 @@
         <v>109</v>
       </c>
       <c r="E137" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="F137" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="G137" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B138" t="s">
         <v>44</v>
@@ -5190,27 +5217,27 @@
         <v>62</v>
       </c>
       <c r="D138" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E138" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="F138" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G138" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B139" t="s">
         <v>44</v>
@@ -5222,24 +5249,24 @@
         <v>78</v>
       </c>
       <c r="E139" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="F139" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="G139" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B140" t="s">
         <v>44</v>
@@ -5251,24 +5278,24 @@
         <v>120</v>
       </c>
       <c r="E140" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="F140" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="G140" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B141" t="s">
         <v>55</v>
@@ -5277,27 +5304,27 @@
         <v>62</v>
       </c>
       <c r="D141" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E141" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="F141" t="s">
         <v>73</v>
       </c>
       <c r="G141" t="s">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="H141" t="s">
         <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B142" t="s">
         <v>55</v>
@@ -5309,24 +5336,24 @@
         <v>100</v>
       </c>
       <c r="E142" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="F142" t="s">
         <v>23</v>
       </c>
       <c r="G142" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="H142" t="s">
         <v>18</v>
       </c>
       <c r="I142" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B143" t="s">
         <v>55</v>
@@ -5338,24 +5365,24 @@
         <v>120</v>
       </c>
       <c r="E143" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="F143" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G143" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="H143" t="s">
         <v>18</v>
       </c>
       <c r="I143" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B144" t="s">
         <v>58</v>
@@ -5367,24 +5394,24 @@
         <v>104</v>
       </c>
       <c r="E144" t="s">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="F144" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="G144" t="s">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B145" t="s">
         <v>58</v>
@@ -5405,7 +5432,7 @@
         <v>86</v>
       </c>
       <c r="H145" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="I145" t="s">
         <v>19</v>
@@ -5413,7 +5440,7 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B146" t="s">
         <v>59</v>
@@ -5425,24 +5452,24 @@
         <v>57</v>
       </c>
       <c r="E146" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="F146" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G146" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B147" t="s">
         <v>59</v>
@@ -5454,24 +5481,24 @@
         <v>104</v>
       </c>
       <c r="E147" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="F147" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G147" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B148" t="s">
         <v>59</v>
@@ -5489,7 +5516,7 @@
         <v>142</v>
       </c>
       <c r="G148" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H148" t="s">
         <v>18</v>
@@ -5500,7 +5527,7 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B149" t="s">
         <v>61</v>
@@ -5512,24 +5539,24 @@
         <v>100</v>
       </c>
       <c r="E149" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F149" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G149" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B150" t="s">
         <v>61</v>
@@ -5547,7 +5574,7 @@
         <v>142</v>
       </c>
       <c r="G150" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H150" t="s">
         <v>18</v>
@@ -5558,7 +5585,7 @@
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B151" t="s">
         <v>65</v>
@@ -5567,27 +5594,27 @@
         <v>140</v>
       </c>
       <c r="D151" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E151" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F151" t="s">
         <v>142</v>
       </c>
       <c r="G151" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B152" t="s">
         <v>74</v>
@@ -5596,27 +5623,27 @@
         <v>140</v>
       </c>
       <c r="D152" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E152" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F152" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="G152" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B153" t="s">
         <v>12</v>
@@ -5625,7 +5652,7 @@
         <v>95</v>
       </c>
       <c r="D153" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E153" t="s">
         <v>103</v>
@@ -5645,7 +5672,7 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B154" t="s">
         <v>24</v>
@@ -5674,7 +5701,7 @@
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B155" t="s">
         <v>39</v>
@@ -5703,7 +5730,7 @@
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B156" t="s">
         <v>39</v>
@@ -5732,19 +5759,19 @@
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B157" t="s">
         <v>39</v>
       </c>
       <c r="C157" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D157" t="s">
         <v>170</v>
       </c>
       <c r="E157" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F157" t="s">
         <v>121</v>
@@ -5753,7 +5780,7 @@
         <v>86</v>
       </c>
       <c r="H157" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I157" t="s">
         <v>19</v>
@@ -5761,7 +5788,7 @@
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B158" t="s">
         <v>39</v>
@@ -5790,28 +5817,28 @@
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B159" t="s">
         <v>44</v>
       </c>
       <c r="C159" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="E159" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F159" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G159" t="s">
         <v>86</v>
       </c>
       <c r="H159" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I159" t="s">
         <v>19</v>
@@ -5819,22 +5846,22 @@
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B160" t="s">
         <v>44</v>
       </c>
       <c r="C160" t="s">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="D160" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="E160" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F160" t="s">
-        <v>142</v>
+        <v>23</v>
       </c>
       <c r="G160" t="s">
         <v>86</v>
@@ -5848,22 +5875,22 @@
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B161" t="s">
         <v>44</v>
       </c>
       <c r="C161" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="D161" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="E161" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F161" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="G161" t="s">
         <v>86</v>
@@ -5877,22 +5904,22 @@
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B162" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C162" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="D162" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="E162" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F162" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="G162" t="s">
         <v>86</v>
@@ -5906,28 +5933,28 @@
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B163" t="s">
         <v>55</v>
       </c>
       <c r="C163" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>64</v>
+        <v>198</v>
       </c>
       <c r="E163" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="F163" t="s">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="G163" t="s">
         <v>86</v>
       </c>
       <c r="H163" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I163" t="s">
         <v>19</v>
@@ -5935,22 +5962,22 @@
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B164" t="s">
         <v>55</v>
       </c>
       <c r="C164" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D164" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="E164" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F164" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G164" t="s">
         <v>86</v>
@@ -5964,22 +5991,22 @@
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B165" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C165" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="D165" t="s">
-        <v>189</v>
+        <v>64</v>
       </c>
       <c r="E165" t="s">
         <v>72</v>
       </c>
       <c r="F165" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="G165" t="s">
         <v>86</v>
@@ -5993,22 +6020,22 @@
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B166" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C166" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D166" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="E166" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F166" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="G166" t="s">
         <v>86</v>
@@ -6022,28 +6049,28 @@
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B167" t="s">
         <v>58</v>
       </c>
       <c r="C167" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="D167" t="s">
-        <v>64</v>
+        <v>198</v>
       </c>
       <c r="E167" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="F167" t="s">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="G167" t="s">
         <v>86</v>
       </c>
       <c r="H167" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I167" t="s">
         <v>19</v>
@@ -6051,22 +6078,22 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B168" t="s">
         <v>58</v>
       </c>
       <c r="C168" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D168" t="s">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="E168" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F168" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G168" t="s">
         <v>86</v>
@@ -6080,22 +6107,22 @@
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B169" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C169" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D169" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
       <c r="E169" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F169" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G169" t="s">
         <v>86</v>
@@ -6109,22 +6136,22 @@
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B170" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C170" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D170" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="E170" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F170" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G170" t="s">
         <v>86</v>
@@ -6138,22 +6165,22 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B171" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C171" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="D171" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="E171" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F171" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G171" t="s">
         <v>86</v>
@@ -6167,22 +6194,22 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B172" t="s">
         <v>59</v>
       </c>
       <c r="C172" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D172" t="s">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="E172" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F172" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G172" t="s">
         <v>86</v>
@@ -6196,22 +6223,22 @@
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B173" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C173" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D173" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="E173" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F173" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G173" t="s">
         <v>86</v>
@@ -6225,22 +6252,22 @@
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B174" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C174" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D174" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="E174" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F174" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G174" t="s">
         <v>86</v>
@@ -6254,22 +6281,22 @@
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B175" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C175" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="D175" t="s">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="E175" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F175" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G175" t="s">
         <v>86</v>
@@ -6283,22 +6310,22 @@
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B176" t="s">
         <v>61</v>
       </c>
       <c r="C176" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D176" t="s">
-        <v>52</v>
+        <v>181</v>
       </c>
       <c r="E176" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="F176" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G176" t="s">
         <v>86</v>
@@ -6312,22 +6339,22 @@
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B177" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C177" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D177" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="E177" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F177" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G177" t="s">
         <v>86</v>
@@ -6341,22 +6368,22 @@
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B178" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C178" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D178" t="s">
-        <v>104</v>
+        <v>200</v>
       </c>
       <c r="E178" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F178" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G178" t="s">
         <v>86</v>
@@ -6370,22 +6397,22 @@
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B179" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C179" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="D179" t="s">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="E179" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F179" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G179" t="s">
         <v>86</v>
@@ -6399,22 +6426,22 @@
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B180" t="s">
         <v>65</v>
       </c>
       <c r="C180" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D180" t="s">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="E180" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F180" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G180" t="s">
         <v>86</v>
@@ -6428,22 +6455,22 @@
     </row>
     <row r="181" spans="1:9" ht="15">
       <c r="A181" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B181" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C181" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D181" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="E181" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F181" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G181" t="s">
         <v>86</v>
@@ -6457,22 +6484,22 @@
     </row>
     <row r="182" spans="1:9" ht="15">
       <c r="A182" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B182" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C182" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D182" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="E182" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F182" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G182" t="s">
         <v>86</v>
@@ -6486,22 +6513,22 @@
     </row>
     <row r="183" spans="1:9" ht="15">
       <c r="A183" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B183" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C183" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="D183" t="s">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="E183" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F183" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G183" t="s">
         <v>86</v>
@@ -6515,22 +6542,22 @@
     </row>
     <row r="184" spans="1:9" ht="15">
       <c r="A184" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B184" t="s">
         <v>74</v>
       </c>
       <c r="C184" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D184" t="s">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="E184" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F184" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="G184" t="s">
         <v>86</v>
@@ -6544,22 +6571,22 @@
     </row>
     <row r="185" spans="1:9" ht="15">
       <c r="A185" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B185" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C185" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="D185" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="E185" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="F185" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="G185" t="s">
         <v>86</v>
@@ -6568,6 +6595,93 @@
         <v>18</v>
       </c>
       <c r="I185" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="15">
+      <c r="A186" t="s">
+        <v>195</v>
+      </c>
+      <c r="B186" t="s">
+        <v>74</v>
+      </c>
+      <c r="C186" t="s">
+        <v>140</v>
+      </c>
+      <c r="D186" t="s">
+        <v>120</v>
+      </c>
+      <c r="E186" t="s">
+        <v>72</v>
+      </c>
+      <c r="F186" t="s">
+        <v>142</v>
+      </c>
+      <c r="G186" t="s">
+        <v>86</v>
+      </c>
+      <c r="H186" t="s">
+        <v>18</v>
+      </c>
+      <c r="I186" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="15">
+      <c r="A187" t="s">
+        <v>195</v>
+      </c>
+      <c r="B187" t="s">
+        <v>74</v>
+      </c>
+      <c r="C187" t="s">
+        <v>95</v>
+      </c>
+      <c r="D187" t="s">
+        <v>188</v>
+      </c>
+      <c r="E187" t="s">
+        <v>103</v>
+      </c>
+      <c r="F187" t="s">
+        <v>98</v>
+      </c>
+      <c r="G187" t="s">
+        <v>86</v>
+      </c>
+      <c r="H187" t="s">
+        <v>18</v>
+      </c>
+      <c r="I187" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="15">
+      <c r="A188" t="s">
+        <v>195</v>
+      </c>
+      <c r="B188" t="s">
+        <v>79</v>
+      </c>
+      <c r="C188" t="s">
+        <v>95</v>
+      </c>
+      <c r="D188" t="s">
+        <v>104</v>
+      </c>
+      <c r="E188" t="s">
+        <v>103</v>
+      </c>
+      <c r="F188" t="s">
+        <v>98</v>
+      </c>
+      <c r="G188" t="s">
+        <v>86</v>
+      </c>
+      <c r="H188" t="s">
+        <v>18</v>
+      </c>
+      <c r="I188" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6579,7 +6693,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e8c0c809-aa2c-4c05-99ed-cc21ba7e501c}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0969d59a-0e15-4d9d-8364-324e76e8bea9}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6599,16 +6713,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6628,13 +6742,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C2" t="s">
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
@@ -6657,13 +6771,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C3" t="s">
         <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
         <v>72</v>
@@ -6686,16 +6800,16 @@
         <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C4" t="s">
         <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F4" t="s">
         <v>134</v>
@@ -6715,16 +6829,16 @@
         <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C5" t="s">
         <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E5" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6747,8 +6861,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2f3c97f6-0caf-4b74-a953-7018b5d8a6a9}">
-  <dimension ref="A1:F46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{85b2b8af-f07f-4151-a448-1bb12fae5e7b}">
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6756,7 +6870,7 @@
     <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="21.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
+    <col min="6" max="6" width="65.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="56.25" customHeight="1">
@@ -6764,13 +6878,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6784,13 +6898,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
@@ -6804,13 +6918,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C3" t="s">
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
         <v>154</v>
@@ -6824,13 +6938,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E4" t="s">
         <v>148</v>
@@ -6844,16 +6958,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C5" t="s">
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6864,13 +6978,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E6" t="s">
         <v>122</v>
@@ -6884,13 +6998,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
@@ -6904,16 +7018,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E8" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -6924,16 +7038,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -6944,16 +7058,16 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C10" t="s">
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E10" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -6964,13 +7078,13 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E11" t="s">
         <v>154</v>
@@ -6984,13 +7098,13 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E12" t="s">
         <v>124</v>
@@ -7004,13 +7118,13 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C13" t="s">
         <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E13" t="s">
         <v>124</v>
@@ -7024,16 +7138,16 @@
         <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C14" t="s">
         <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E14" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -7044,13 +7158,13 @@
         <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C15" t="s">
         <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
         <v>116</v>
@@ -7064,16 +7178,16 @@
         <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C16" t="s">
         <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E16" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -7084,13 +7198,13 @@
         <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C17" t="s">
         <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E17" t="s">
         <v>116</v>
@@ -7104,16 +7218,16 @@
         <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C18" t="s">
         <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -7124,16 +7238,16 @@
         <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C19" t="s">
         <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E19" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -7144,13 +7258,13 @@
         <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C20" t="s">
         <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E20" t="s">
         <v>81</v>
@@ -7164,13 +7278,13 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C21" t="s">
         <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E21" t="s">
         <v>157</v>
@@ -7184,13 +7298,13 @@
         <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C22" t="s">
         <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E22" t="s">
         <v>13</v>
@@ -7204,13 +7318,13 @@
         <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C23" t="s">
         <v>135</v>
       </c>
       <c r="D23" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
@@ -7224,16 +7338,16 @@
         <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C24" t="s">
         <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E24" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -7244,13 +7358,13 @@
         <v>112</v>
       </c>
       <c r="B25" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C25" t="s">
         <v>62</v>
       </c>
       <c r="D25" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E25" t="s">
         <v>94</v>
@@ -7264,16 +7378,16 @@
         <v>112</v>
       </c>
       <c r="B26" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C26" t="s">
         <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E26" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -7284,13 +7398,13 @@
         <v>112</v>
       </c>
       <c r="B27" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C27" t="s">
         <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E27" t="s">
         <v>130</v>
@@ -7304,13 +7418,13 @@
         <v>112</v>
       </c>
       <c r="B28" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C28" t="s">
         <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E28" t="s">
         <v>116</v>
@@ -7324,13 +7438,13 @@
         <v>112</v>
       </c>
       <c r="B29" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C29" t="s">
         <v>95</v>
       </c>
       <c r="D29" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E29" t="s">
         <v>124</v>
@@ -7344,16 +7458,16 @@
         <v>112</v>
       </c>
       <c r="B30" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C30" t="s">
         <v>125</v>
       </c>
       <c r="D30" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E30" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -7364,16 +7478,16 @@
         <v>112</v>
       </c>
       <c r="B31" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C31" t="s">
         <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E31" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -7384,13 +7498,13 @@
         <v>112</v>
       </c>
       <c r="B32" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C32" t="s">
         <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E32" t="s">
         <v>51</v>
@@ -7404,13 +7518,13 @@
         <v>112</v>
       </c>
       <c r="B33" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C33" t="s">
         <v>148</v>
       </c>
       <c r="D33" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E33" t="s">
         <v>124</v>
@@ -7421,19 +7535,19 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C34" t="s">
         <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
@@ -7441,19 +7555,19 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B35" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C35" t="s">
         <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>237</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
@@ -7461,19 +7575,19 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C36" t="s">
         <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
@@ -7481,19 +7595,19 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B37" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C37" t="s">
         <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>224</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -7501,19 +7615,19 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C38" t="s">
         <v>140</v>
       </c>
       <c r="D38" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -7521,19 +7635,19 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B39" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C39" t="s">
         <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
@@ -7541,16 +7655,16 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C40" t="s">
         <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -7561,16 +7675,16 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C41" t="s">
         <v>140</v>
       </c>
       <c r="D41" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
@@ -7581,16 +7695,16 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C42" t="s">
         <v>140</v>
       </c>
       <c r="D42" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
@@ -7601,16 +7715,16 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C43" t="s">
         <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -7621,36 +7735,36 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B44" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B45" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C45" t="s">
         <v>42</v>
       </c>
       <c r="D45" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
@@ -7661,21 +7775,41 @@
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B46" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15">
+      <c r="A47" t="s">
+        <v>195</v>
+      </c>
+      <c r="B47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C47" t="s">
         <v>95</v>
       </c>
-      <c r="D46" t="s">
-        <v>211</v>
-      </c>
-      <c r="E46" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="D47" t="s">
+        <v>218</v>
+      </c>
+      <c r="E47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="251">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -597,9 +597,6 @@
     <t>Wójcik Kamil</t>
   </si>
   <si>
-    <t>Technika w produkcji cukierniczej</t>
-  </si>
-  <si>
     <t>Fizyka</t>
   </si>
   <si>
@@ -615,7 +612,10 @@
     <t>4TFB</t>
   </si>
   <si>
-    <t>próbna ewakuacja - inspektor zewnętrzny</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>próbna ewakuacja - inspektor zewnętrzny /</t>
   </si>
   <si>
     <t>5TH|DZ</t>
@@ -624,12 +624,42 @@
     <t>organizacja Wrocławskiego Miasteczka Profilaktyki - opieka nad uczniami</t>
   </si>
   <si>
-    <t>3FB</t>
+    <t>Bokuniewicz Sylwia</t>
+  </si>
+  <si>
+    <t>Sałdyka Karolina</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>Kaszak Maria</t>
+  </si>
+  <si>
+    <t>3FB|CH</t>
+  </si>
+  <si>
+    <t>3FB|DZ</t>
+  </si>
+  <si>
+    <t>1TH|gr1</t>
   </si>
   <si>
     <t>1TFH|t.hand.</t>
   </si>
   <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
+    <t>1TH|CH</t>
+  </si>
+  <si>
+    <t>1TH|DZ</t>
+  </si>
+  <si>
+    <t>zaplanowano zastępstwo z nauczycielem Sobczak Anna [So]</t>
+  </si>
+  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -696,18 +726,12 @@
     <t>15:40-15:45</t>
   </si>
   <si>
-    <t>Sałdyka Karolina</t>
-  </si>
-  <si>
     <t>Galert Anna</t>
   </si>
   <si>
     <t>07:55-08:00</t>
   </si>
   <si>
-    <t>Karczmarz Aleksandra</t>
-  </si>
-  <si>
     <t>09:35-09:40</t>
   </si>
   <si>
@@ -748,6 +772,9 @@
   </si>
   <si>
     <t>bramka wejściowa</t>
+  </si>
+  <si>
+    <t>organizacja Miasteczka Profilaktyki we Wrocławiu - praca z uczniami</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{137f1897-7d0c-4d01-9c61-95ce9d9377a5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{08554a99-2908-4259-93b6-91fd89711cf1}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1218,8 +1245,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{51b4943e-6d1e-4ce1-950c-ad6d4d0db804}">
-  <dimension ref="A1:I188"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{27149f2d-c170-4b5a-a663-323085c06cdd}">
+  <dimension ref="A1:I204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -5220,7 +5247,7 @@
         <v>188</v>
       </c>
       <c r="E138" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="F138" t="s">
         <v>83</v>
@@ -5336,7 +5363,7 @@
         <v>100</v>
       </c>
       <c r="E142" t="s">
-        <v>191</v>
+        <v>87</v>
       </c>
       <c r="F142" t="s">
         <v>23</v>
@@ -5394,13 +5421,13 @@
         <v>104</v>
       </c>
       <c r="E144" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F144" t="s">
         <v>83</v>
       </c>
       <c r="G144" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
@@ -5432,7 +5459,7 @@
         <v>86</v>
       </c>
       <c r="H145" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I145" t="s">
         <v>19</v>
@@ -5452,7 +5479,7 @@
         <v>57</v>
       </c>
       <c r="E146" t="s">
-        <v>191</v>
+        <v>87</v>
       </c>
       <c r="F146" t="s">
         <v>23</v>
@@ -5643,7 +5670,7 @@
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B153" t="s">
         <v>12</v>
@@ -5652,7 +5679,7 @@
         <v>95</v>
       </c>
       <c r="D153" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E153" t="s">
         <v>103</v>
@@ -5661,7 +5688,7 @@
         <v>98</v>
       </c>
       <c r="G153" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
@@ -5672,54 +5699,54 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B154" t="s">
         <v>24</v>
       </c>
       <c r="C154" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="D154" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="E154" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="F154" t="s">
-        <v>98</v>
+        <v>196</v>
       </c>
       <c r="G154" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="H154" t="s">
         <v>18</v>
       </c>
       <c r="I154" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B155" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C155" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D155" t="s">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="E155" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F155" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="G155" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H155" t="s">
         <v>18</v>
@@ -5730,57 +5757,57 @@
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B156" t="s">
         <v>39</v>
       </c>
       <c r="C156" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="D156" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="E156" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="F156" t="s">
         <v>142</v>
       </c>
       <c r="G156" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H156" t="s">
         <v>18</v>
       </c>
       <c r="I156" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B157" t="s">
         <v>39</v>
       </c>
       <c r="C157" t="s">
-        <v>183</v>
+        <v>42</v>
       </c>
       <c r="D157" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E157" t="s">
-        <v>182</v>
+        <v>53</v>
       </c>
       <c r="F157" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="G157" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H157" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
       <c r="I157" t="s">
         <v>19</v>
@@ -5788,57 +5815,57 @@
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B158" t="s">
         <v>39</v>
       </c>
       <c r="C158" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="D158" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="E158" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F158" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G158" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B159" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C159" t="s">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="D159" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="E159" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="F159" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="G159" t="s">
         <v>86</v>
       </c>
       <c r="H159" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I159" t="s">
         <v>19</v>
@@ -5846,25 +5873,25 @@
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B160" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C160" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D160" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="E160" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F160" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="G160" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
@@ -5875,286 +5902,286 @@
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B161" t="s">
         <v>44</v>
       </c>
       <c r="C161" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="E161" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="F161" t="s">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="G161" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H161" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I161" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B162" t="s">
         <v>44</v>
       </c>
       <c r="C162" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="D162" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E162" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="F162" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="G162" t="s">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="H162" t="s">
         <v>18</v>
       </c>
       <c r="I162" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B163" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C163" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D163" t="s">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="E163" t="s">
-        <v>27</v>
+        <v>191</v>
       </c>
       <c r="F163" t="s">
-        <v>40</v>
+        <v>165</v>
       </c>
       <c r="G163" t="s">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="H163" t="s">
-        <v>199</v>
+        <v>18</v>
       </c>
       <c r="I163" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B164" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C164" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="D164" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="E164" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="F164" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="G164" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="H164" t="s">
         <v>18</v>
       </c>
       <c r="I164" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B165" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C165" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="D165" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="E165" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="F165" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="G165" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B166" t="s">
         <v>55</v>
       </c>
       <c r="C166" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="D166" t="s">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="E166" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="F166" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="G166" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H166" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I166" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B167" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C167" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="D167" t="s">
-        <v>198</v>
+        <v>31</v>
       </c>
       <c r="E167" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="F167" t="s">
-        <v>40</v>
+        <v>138</v>
       </c>
       <c r="G167" t="s">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="H167" t="s">
-        <v>199</v>
+        <v>18</v>
       </c>
       <c r="I167" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B168" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C168" t="s">
-        <v>62</v>
+        <v>177</v>
       </c>
       <c r="D168" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="E168" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="F168" t="s">
-        <v>73</v>
+        <v>196</v>
       </c>
       <c r="G168" t="s">
-        <v>86</v>
+        <v>200</v>
       </c>
       <c r="H168" t="s">
         <v>18</v>
       </c>
       <c r="I168" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B169" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C169" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D169" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E169" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="F169" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G169" t="s">
-        <v>86</v>
+        <v>201</v>
       </c>
       <c r="H169" t="s">
         <v>18</v>
       </c>
       <c r="I169" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B170" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C170" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="D170" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="E170" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F170" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G170" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H170" t="s">
         <v>18</v>
@@ -6165,83 +6192,83 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B171" t="s">
         <v>58</v>
       </c>
       <c r="C171" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>120</v>
+        <v>198</v>
       </c>
       <c r="E171" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="F171" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="G171" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H171" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="I171" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B172" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C172" t="s">
         <v>62</v>
       </c>
       <c r="D172" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E172" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="F172" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="G172" t="s">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="H172" t="s">
         <v>18</v>
       </c>
       <c r="I172" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B173" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C173" t="s">
-        <v>42</v>
+        <v>177</v>
       </c>
       <c r="D173" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="E173" t="s">
-        <v>53</v>
+        <v>180</v>
       </c>
       <c r="F173" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
       <c r="G173" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H173" t="s">
         <v>18</v>
@@ -6252,112 +6279,112 @@
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B174" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C174" t="s">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="D174" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E174" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="F174" t="s">
-        <v>142</v>
+        <v>23</v>
       </c>
       <c r="G174" t="s">
-        <v>86</v>
+        <v>202</v>
       </c>
       <c r="H174" t="s">
         <v>18</v>
       </c>
       <c r="I174" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B175" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C175" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="D175" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E175" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F175" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="G175" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H175" t="s">
         <v>18</v>
       </c>
       <c r="I175" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B176" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C176" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="D176" t="s">
-        <v>181</v>
+        <v>120</v>
       </c>
       <c r="E176" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="F176" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="G176" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="H176" t="s">
         <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B177" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C177" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D177" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="E177" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F177" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G177" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H177" t="s">
         <v>18</v>
@@ -6368,199 +6395,199 @@
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B178" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C178" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="D178" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="E178" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="F178" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="G178" t="s">
-        <v>86</v>
+        <v>203</v>
       </c>
       <c r="H178" t="s">
         <v>18</v>
       </c>
       <c r="I178" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B179" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C179" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="D179" t="s">
-        <v>52</v>
+        <v>170</v>
       </c>
       <c r="E179" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F179" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="G179" t="s">
-        <v>86</v>
+        <v>201</v>
       </c>
       <c r="H179" t="s">
         <v>18</v>
       </c>
       <c r="I179" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B180" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C180" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="D180" t="s">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="E180" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="F180" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="G180" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H180" t="s">
         <v>18</v>
       </c>
       <c r="I180" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="15">
       <c r="A181" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B181" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C181" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="D181" t="s">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="E181" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F181" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="G181" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H181" t="s">
         <v>18</v>
       </c>
       <c r="I181" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="15">
       <c r="A182" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B182" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C182" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="D182" t="s">
-        <v>141</v>
+        <v>206</v>
       </c>
       <c r="E182" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="F182" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G182" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="H182" t="s">
         <v>18</v>
       </c>
       <c r="I182" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="15">
       <c r="A183" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B183" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C183" t="s">
         <v>95</v>
       </c>
       <c r="D183" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="E183" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="F183" t="s">
         <v>98</v>
       </c>
       <c r="G183" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="H183" t="s">
         <v>18</v>
       </c>
       <c r="I183" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="15">
       <c r="A184" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B184" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C184" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="D184" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="E184" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F184" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="G184" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="H184" t="s">
         <v>18</v>
@@ -6571,117 +6598,581 @@
     </row>
     <row r="185" spans="1:9" ht="15">
       <c r="A185" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B185" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C185" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D185" t="s">
-        <v>52</v>
+        <v>181</v>
       </c>
       <c r="E185" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F185" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
       <c r="G185" t="s">
-        <v>86</v>
+        <v>203</v>
       </c>
       <c r="H185" t="s">
         <v>18</v>
       </c>
       <c r="I185" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="15">
       <c r="A186" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B186" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C186" t="s">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="D186" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="E186" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="F186" t="s">
-        <v>142</v>
+        <v>47</v>
       </c>
       <c r="G186" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="H186" t="s">
         <v>18</v>
       </c>
       <c r="I186" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="15">
       <c r="A187" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B187" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C187" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="D187" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E187" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="F187" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="G187" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H187" t="s">
         <v>18</v>
       </c>
       <c r="I187" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="15">
       <c r="A188" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B188" t="s">
+        <v>61</v>
+      </c>
+      <c r="C188" t="s">
+        <v>140</v>
+      </c>
+      <c r="D188" t="s">
+        <v>205</v>
+      </c>
+      <c r="E188" t="s">
+        <v>27</v>
+      </c>
+      <c r="F188" t="s">
+        <v>142</v>
+      </c>
+      <c r="G188" t="s">
+        <v>63</v>
+      </c>
+      <c r="H188" t="s">
+        <v>18</v>
+      </c>
+      <c r="I188" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="15">
+      <c r="A189" t="s">
+        <v>194</v>
+      </c>
+      <c r="B189" t="s">
+        <v>61</v>
+      </c>
+      <c r="C189" t="s">
+        <v>95</v>
+      </c>
+      <c r="D189" t="s">
+        <v>52</v>
+      </c>
+      <c r="E189" t="s">
+        <v>166</v>
+      </c>
+      <c r="F189" t="s">
+        <v>23</v>
+      </c>
+      <c r="G189" t="s">
+        <v>51</v>
+      </c>
+      <c r="H189" t="s">
+        <v>18</v>
+      </c>
+      <c r="I189" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="15">
+      <c r="A190" t="s">
+        <v>194</v>
+      </c>
+      <c r="B190" t="s">
+        <v>61</v>
+      </c>
+      <c r="C190" t="s">
+        <v>116</v>
+      </c>
+      <c r="D190" t="s">
+        <v>120</v>
+      </c>
+      <c r="E190" t="s">
+        <v>15</v>
+      </c>
+      <c r="F190" t="s">
+        <v>106</v>
+      </c>
+      <c r="G190" t="s">
+        <v>146</v>
+      </c>
+      <c r="H190" t="s">
+        <v>18</v>
+      </c>
+      <c r="I190" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="15">
+      <c r="A191" t="s">
+        <v>194</v>
+      </c>
+      <c r="B191" t="s">
+        <v>65</v>
+      </c>
+      <c r="C191" t="s">
+        <v>62</v>
+      </c>
+      <c r="D191" t="s">
+        <v>78</v>
+      </c>
+      <c r="E191" t="s">
+        <v>92</v>
+      </c>
+      <c r="F191" t="s">
+        <v>23</v>
+      </c>
+      <c r="G191" t="s">
+        <v>94</v>
+      </c>
+      <c r="H191" t="s">
+        <v>18</v>
+      </c>
+      <c r="I191" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="15">
+      <c r="A192" t="s">
+        <v>194</v>
+      </c>
+      <c r="B192" t="s">
+        <v>65</v>
+      </c>
+      <c r="C192" t="s">
+        <v>177</v>
+      </c>
+      <c r="D192" t="s">
+        <v>204</v>
+      </c>
+      <c r="E192" t="s">
+        <v>27</v>
+      </c>
+      <c r="F192" t="s">
+        <v>142</v>
+      </c>
+      <c r="G192" t="s">
+        <v>63</v>
+      </c>
+      <c r="H192" t="s">
+        <v>18</v>
+      </c>
+      <c r="I192" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="15">
+      <c r="A193" t="s">
+        <v>194</v>
+      </c>
+      <c r="B193" t="s">
+        <v>65</v>
+      </c>
+      <c r="C193" t="s">
+        <v>177</v>
+      </c>
+      <c r="D193" t="s">
+        <v>205</v>
+      </c>
+      <c r="E193" t="s">
+        <v>27</v>
+      </c>
+      <c r="F193" t="s">
+        <v>142</v>
+      </c>
+      <c r="G193" t="s">
+        <v>63</v>
+      </c>
+      <c r="H193" t="s">
+        <v>18</v>
+      </c>
+      <c r="I193" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="15">
+      <c r="A194" t="s">
+        <v>194</v>
+      </c>
+      <c r="B194" t="s">
+        <v>65</v>
+      </c>
+      <c r="C194" t="s">
+        <v>42</v>
+      </c>
+      <c r="D194" t="s">
+        <v>104</v>
+      </c>
+      <c r="E194" t="s">
+        <v>53</v>
+      </c>
+      <c r="F194" t="s">
+        <v>23</v>
+      </c>
+      <c r="G194" t="s">
+        <v>60</v>
+      </c>
+      <c r="H194" t="s">
+        <v>18</v>
+      </c>
+      <c r="I194" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="15">
+      <c r="A195" t="s">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>65</v>
+      </c>
+      <c r="C195" t="s">
+        <v>140</v>
+      </c>
+      <c r="D195" t="s">
+        <v>141</v>
+      </c>
+      <c r="E195" t="s">
+        <v>72</v>
+      </c>
+      <c r="F195" t="s">
+        <v>142</v>
+      </c>
+      <c r="G195" t="s">
+        <v>60</v>
+      </c>
+      <c r="H195" t="s">
+        <v>18</v>
+      </c>
+      <c r="I195" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="15">
+      <c r="A196" t="s">
+        <v>194</v>
+      </c>
+      <c r="B196" t="s">
+        <v>65</v>
+      </c>
+      <c r="C196" t="s">
+        <v>95</v>
+      </c>
+      <c r="D196" t="s">
+        <v>207</v>
+      </c>
+      <c r="E196" t="s">
+        <v>32</v>
+      </c>
+      <c r="F196" t="s">
+        <v>67</v>
+      </c>
+      <c r="G196" t="s">
+        <v>208</v>
+      </c>
+      <c r="H196" t="s">
+        <v>18</v>
+      </c>
+      <c r="I196" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="15">
+      <c r="A197" t="s">
+        <v>194</v>
+      </c>
+      <c r="B197" t="s">
+        <v>65</v>
+      </c>
+      <c r="C197" t="s">
+        <v>116</v>
+      </c>
+      <c r="D197" t="s">
+        <v>120</v>
+      </c>
+      <c r="E197" t="s">
+        <v>32</v>
+      </c>
+      <c r="F197" t="s">
+        <v>106</v>
+      </c>
+      <c r="G197" t="s">
+        <v>146</v>
+      </c>
+      <c r="H197" t="s">
+        <v>18</v>
+      </c>
+      <c r="I197" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="15">
+      <c r="A198" t="s">
+        <v>194</v>
+      </c>
+      <c r="B198" t="s">
+        <v>74</v>
+      </c>
+      <c r="C198" t="s">
+        <v>62</v>
+      </c>
+      <c r="D198" t="s">
+        <v>209</v>
+      </c>
+      <c r="E198" t="s">
+        <v>27</v>
+      </c>
+      <c r="F198" t="s">
+        <v>142</v>
+      </c>
+      <c r="G198" t="s">
+        <v>63</v>
+      </c>
+      <c r="H198" t="s">
+        <v>18</v>
+      </c>
+      <c r="I198" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="15">
+      <c r="A199" t="s">
+        <v>194</v>
+      </c>
+      <c r="B199" t="s">
+        <v>74</v>
+      </c>
+      <c r="C199" t="s">
+        <v>62</v>
+      </c>
+      <c r="D199" t="s">
+        <v>210</v>
+      </c>
+      <c r="E199" t="s">
+        <v>27</v>
+      </c>
+      <c r="F199" t="s">
+        <v>142</v>
+      </c>
+      <c r="G199" t="s">
+        <v>63</v>
+      </c>
+      <c r="H199" t="s">
+        <v>18</v>
+      </c>
+      <c r="I199" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="15">
+      <c r="A200" t="s">
+        <v>194</v>
+      </c>
+      <c r="B200" t="s">
+        <v>74</v>
+      </c>
+      <c r="C200" t="s">
+        <v>177</v>
+      </c>
+      <c r="D200" t="s">
+        <v>104</v>
+      </c>
+      <c r="E200" t="s">
+        <v>180</v>
+      </c>
+      <c r="F200" t="s">
+        <v>196</v>
+      </c>
+      <c r="G200" t="s">
+        <v>60</v>
+      </c>
+      <c r="H200" t="s">
+        <v>18</v>
+      </c>
+      <c r="I200" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="15">
+      <c r="A201" t="s">
+        <v>194</v>
+      </c>
+      <c r="B201" t="s">
+        <v>74</v>
+      </c>
+      <c r="C201" t="s">
+        <v>42</v>
+      </c>
+      <c r="D201" t="s">
+        <v>52</v>
+      </c>
+      <c r="E201" t="s">
+        <v>166</v>
+      </c>
+      <c r="F201" t="s">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
+        <v>51</v>
+      </c>
+      <c r="H201" t="s">
+        <v>18</v>
+      </c>
+      <c r="I201" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="15">
+      <c r="A202" t="s">
+        <v>194</v>
+      </c>
+      <c r="B202" t="s">
+        <v>74</v>
+      </c>
+      <c r="C202" t="s">
+        <v>140</v>
+      </c>
+      <c r="D202" t="s">
+        <v>120</v>
+      </c>
+      <c r="E202" t="s">
+        <v>15</v>
+      </c>
+      <c r="F202" t="s">
+        <v>142</v>
+      </c>
+      <c r="G202" t="s">
+        <v>86</v>
+      </c>
+      <c r="H202" t="s">
+        <v>211</v>
+      </c>
+      <c r="I202" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="15">
+      <c r="A203" t="s">
+        <v>194</v>
+      </c>
+      <c r="B203" t="s">
+        <v>74</v>
+      </c>
+      <c r="C203" t="s">
+        <v>95</v>
+      </c>
+      <c r="D203" t="s">
+        <v>188</v>
+      </c>
+      <c r="E203" t="s">
+        <v>97</v>
+      </c>
+      <c r="F203" t="s">
+        <v>121</v>
+      </c>
+      <c r="G203" t="s">
+        <v>41</v>
+      </c>
+      <c r="H203" t="s">
+        <v>18</v>
+      </c>
+      <c r="I203" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="15">
+      <c r="A204" t="s">
+        <v>194</v>
+      </c>
+      <c r="B204" t="s">
         <v>79</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C204" t="s">
         <v>95</v>
       </c>
-      <c r="D188" t="s">
+      <c r="D204" t="s">
         <v>104</v>
       </c>
-      <c r="E188" t="s">
+      <c r="E204" t="s">
         <v>103</v>
       </c>
-      <c r="F188" t="s">
+      <c r="F204" t="s">
         <v>98</v>
       </c>
-      <c r="G188" t="s">
-        <v>86</v>
-      </c>
-      <c r="H188" t="s">
-        <v>18</v>
-      </c>
-      <c r="I188" t="s">
+      <c r="G204" t="s">
+        <v>60</v>
+      </c>
+      <c r="H204" t="s">
+        <v>18</v>
+      </c>
+      <c r="I204" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6693,7 +7184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0969d59a-0e15-4d9d-8364-324e76e8bea9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{44a5d6d6-864a-4d8c-8c06-4363f5ad3523}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6713,16 +7204,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6742,13 +7233,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C2" t="s">
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
@@ -6771,13 +7262,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C3" t="s">
         <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
         <v>72</v>
@@ -6800,16 +7291,16 @@
         <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C4" t="s">
         <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F4" t="s">
         <v>134</v>
@@ -6829,16 +7320,16 @@
         <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s">
         <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E5" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6861,16 +7352,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{85b2b8af-f07f-4151-a448-1bb12fae5e7b}">
-  <dimension ref="A1:F47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{168090bc-3e0f-4334-b098-2acf4a4b70b9}">
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="21.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="65.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="60.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="56.25" customHeight="1">
@@ -6878,13 +7369,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6898,13 +7389,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
@@ -6918,13 +7409,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C3" t="s">
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E3" t="s">
         <v>154</v>
@@ -6938,13 +7429,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E4" t="s">
         <v>148</v>
@@ -6958,16 +7449,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C5" t="s">
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6978,13 +7469,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E6" t="s">
         <v>122</v>
@@ -6998,13 +7489,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
@@ -7018,16 +7509,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="E8" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -7038,16 +7529,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E9" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -7058,16 +7549,16 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C10" t="s">
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E10" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -7078,13 +7569,13 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E11" t="s">
         <v>154</v>
@@ -7098,13 +7589,13 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E12" t="s">
         <v>124</v>
@@ -7118,13 +7609,13 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C13" t="s">
         <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E13" t="s">
         <v>124</v>
@@ -7138,16 +7629,16 @@
         <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C14" t="s">
         <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E14" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -7158,13 +7649,13 @@
         <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C15" t="s">
         <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E15" t="s">
         <v>116</v>
@@ -7178,16 +7669,16 @@
         <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
         <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E16" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -7198,13 +7689,13 @@
         <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C17" t="s">
         <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="E17" t="s">
         <v>116</v>
@@ -7218,13 +7709,13 @@
         <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C18" t="s">
         <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E18" t="s">
         <v>177</v>
@@ -7238,16 +7729,16 @@
         <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C19" t="s">
         <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E19" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -7258,13 +7749,13 @@
         <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C20" t="s">
         <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E20" t="s">
         <v>81</v>
@@ -7278,13 +7769,13 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C21" t="s">
         <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E21" t="s">
         <v>157</v>
@@ -7298,13 +7789,13 @@
         <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C22" t="s">
         <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E22" t="s">
         <v>13</v>
@@ -7318,13 +7809,13 @@
         <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C23" t="s">
         <v>135</v>
       </c>
       <c r="D23" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
@@ -7338,16 +7829,16 @@
         <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C24" t="s">
         <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E24" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -7358,13 +7849,13 @@
         <v>112</v>
       </c>
       <c r="B25" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C25" t="s">
         <v>62</v>
       </c>
       <c r="D25" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E25" t="s">
         <v>94</v>
@@ -7378,16 +7869,16 @@
         <v>112</v>
       </c>
       <c r="B26" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C26" t="s">
         <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E26" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -7398,13 +7889,13 @@
         <v>112</v>
       </c>
       <c r="B27" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C27" t="s">
         <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E27" t="s">
         <v>130</v>
@@ -7418,13 +7909,13 @@
         <v>112</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C28" t="s">
         <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="E28" t="s">
         <v>116</v>
@@ -7438,13 +7929,13 @@
         <v>112</v>
       </c>
       <c r="B29" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C29" t="s">
         <v>95</v>
       </c>
       <c r="D29" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E29" t="s">
         <v>124</v>
@@ -7458,13 +7949,13 @@
         <v>112</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C30" t="s">
         <v>125</v>
       </c>
       <c r="D30" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="E30" t="s">
         <v>183</v>
@@ -7478,16 +7969,16 @@
         <v>112</v>
       </c>
       <c r="B31" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C31" t="s">
         <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E31" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -7498,13 +7989,13 @@
         <v>112</v>
       </c>
       <c r="B32" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C32" t="s">
         <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E32" t="s">
         <v>51</v>
@@ -7518,13 +8009,13 @@
         <v>112</v>
       </c>
       <c r="B33" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C33" t="s">
         <v>148</v>
       </c>
       <c r="D33" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E33" t="s">
         <v>124</v>
@@ -7538,13 +8029,13 @@
         <v>187</v>
       </c>
       <c r="B34" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C34" t="s">
         <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E34" t="s">
         <v>37</v>
@@ -7558,16 +8049,16 @@
         <v>187</v>
       </c>
       <c r="B35" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C35" t="s">
         <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E35" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
@@ -7578,13 +8069,13 @@
         <v>187</v>
       </c>
       <c r="B36" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C36" t="s">
         <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E36" t="s">
         <v>130</v>
@@ -7598,16 +8089,16 @@
         <v>187</v>
       </c>
       <c r="B37" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C37" t="s">
         <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E37" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -7618,13 +8109,13 @@
         <v>187</v>
       </c>
       <c r="B38" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C38" t="s">
         <v>140</v>
       </c>
       <c r="D38" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E38" t="s">
         <v>68</v>
@@ -7638,16 +8129,16 @@
         <v>187</v>
       </c>
       <c r="B39" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C39" t="s">
         <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E39" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
@@ -7655,19 +8146,19 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C40" t="s">
         <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>243</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
@@ -7675,19 +8166,19 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C41" t="s">
         <v>140</v>
       </c>
       <c r="D41" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="F41" t="s">
         <v>18</v>
@@ -7695,19 +8186,19 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B42" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="D42" t="s">
         <v>241</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
@@ -7715,19 +8206,19 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B43" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="D43" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -7735,59 +8226,59 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B44" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="D44" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="F44" t="s">
-        <v>199</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="F45" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B46" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C46" t="s">
         <v>42</v>
       </c>
       <c r="D46" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
@@ -7795,21 +8286,121 @@
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B47" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" t="s">
+        <v>241</v>
+      </c>
+      <c r="E47" t="s">
+        <v>208</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15">
+      <c r="A48" t="s">
+        <v>194</v>
+      </c>
+      <c r="B48" t="s">
+        <v>229</v>
+      </c>
+      <c r="C48" t="s">
+        <v>177</v>
+      </c>
+      <c r="D48" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" t="s">
+        <v>113</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15">
+      <c r="A49" t="s">
+        <v>194</v>
+      </c>
+      <c r="B49" t="s">
+        <v>229</v>
+      </c>
+      <c r="C49" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E49" t="s">
+        <v>232</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15">
+      <c r="A50" t="s">
+        <v>194</v>
+      </c>
+      <c r="B50" t="s">
+        <v>233</v>
+      </c>
+      <c r="C50" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E50" t="s">
+        <v>208</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15">
+      <c r="A51" t="s">
+        <v>194</v>
+      </c>
+      <c r="B51" t="s">
+        <v>247</v>
+      </c>
+      <c r="C51" t="s">
+        <v>177</v>
+      </c>
+      <c r="D51" t="s">
+        <v>226</v>
+      </c>
+      <c r="E51" t="s">
+        <v>48</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15">
+      <c r="A52" t="s">
+        <v>194</v>
+      </c>
+      <c r="B52" t="s">
+        <v>238</v>
+      </c>
+      <c r="C52" t="s">
         <v>95</v>
       </c>
-      <c r="D47" t="s">
-        <v>218</v>
-      </c>
-      <c r="E47" t="s">
-        <v>19</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="D52" t="s">
+        <v>228</v>
+      </c>
+      <c r="E52" t="s">
+        <v>151</v>
+      </c>
+      <c r="F52" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="128">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
   <si>
-    <t>Okres: 05.10.2026 (pon.) - 05.10.2026 (pon.)</t>
+    <t>Okres: 05.10.2026 (pon.) - 11.10.2026 (niedz.)</t>
   </si>
   <si>
     <t>Dzień</t>
@@ -82,6 +82,18 @@
     <t>-</t>
   </si>
   <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>2, 08:50-09:35</t>
   </si>
   <si>
@@ -103,6 +115,21 @@
     <t>Dodatkowo płatne</t>
   </si>
   <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>Wrzeszcz Barbara</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
     <t>3, 09:40-10:25</t>
   </si>
   <si>
@@ -112,70 +139,70 @@
     <t>3K</t>
   </si>
   <si>
+    <t>4, 10:35-11:20</t>
+  </si>
+  <si>
+    <t>2K|gr1</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>2K|gr2</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t>Filipiak Wiesław</t>
+  </si>
+  <si>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>Technika w produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>5, 11:25-12:10</t>
+  </si>
+  <si>
+    <t>4TFB|DZ</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Kaczorowski Waldemar</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>1TH</t>
+  </si>
+  <si>
+    <t>6, 12:25-13:10</t>
+  </si>
+  <si>
+    <t>1WA</t>
+  </si>
+  <si>
     <t>Zajęcia z wychowawcą</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Smirnow-Zechman Eleonora</t>
-  </si>
-  <si>
-    <t>4, 10:35-11:20</t>
-  </si>
-  <si>
-    <t>2K|gr1</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>Biezmienow Małgorzata</t>
-  </si>
-  <si>
-    <t>2K|gr2</t>
-  </si>
-  <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>Filipiak Wiesław</t>
-  </si>
-  <si>
-    <t>5, 11:25-12:10</t>
-  </si>
-  <si>
-    <t>4TFB|DZ</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Kaczorowski Waldemar</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>Technika w produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
-    <t>6, 12:25-13:10</t>
+    <t>Galert Anna</t>
   </si>
   <si>
     <t>7, 13:15-14:00</t>
@@ -205,9 +232,6 @@
     <t>8, 14:05-14:50</t>
   </si>
   <si>
-    <t>1WA</t>
-  </si>
-  <si>
     <t>Edukacja dla bezpieczeństwa</t>
   </si>
   <si>
@@ -250,12 +274,81 @@
     <t>Sałdyka Karolina</t>
   </si>
   <si>
-    <t>1TH</t>
-  </si>
-  <si>
     <t>11, 16:35-17:20</t>
   </si>
   <si>
+    <t>06.10.2026</t>
+  </si>
+  <si>
+    <t>Technika w produkcji gastronomicznej</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>07.10.2026</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>1S</t>
+  </si>
+  <si>
+    <t>Obsługa klientów</t>
+  </si>
+  <si>
+    <t>Misiąg Anna</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>2WA|gr1</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - kompetencje zawodowe</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1TFB|gr1</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>3TFB|gr1</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>09.10.2026</t>
+  </si>
+  <si>
+    <t>Piątek-Pawłowska Bożena</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>Okienko dla uczniów</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
+    <t>4TFA</t>
+  </si>
+  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -265,6 +358,21 @@
     <t>Miejsce dyżuru</t>
   </si>
   <si>
+    <t>08:45-08:50</t>
+  </si>
+  <si>
+    <t>piętro_1</t>
+  </si>
+  <si>
+    <t>Ulanowska Magdalena</t>
+  </si>
+  <si>
+    <t>11:20-11:25</t>
+  </si>
+  <si>
+    <t>Zaleska Magdalena</t>
+  </si>
+  <si>
     <t>14:00-14:05</t>
   </si>
   <si>
@@ -277,22 +385,25 @@
     <t>14:50-14:55</t>
   </si>
   <si>
-    <t>piętro_1</t>
-  </si>
-  <si>
     <t>Fiodorów Małgorzata</t>
   </si>
   <si>
     <t>15:40-15:45</t>
   </si>
   <si>
-    <t>Galert Anna</t>
-  </si>
-  <si>
     <t>16:30-16:35</t>
   </si>
   <si>
     <t>Bujanowska Iwona</t>
+  </si>
+  <si>
+    <t>10:25-10:35</t>
+  </si>
+  <si>
+    <t>12:10-12:25</t>
+  </si>
+  <si>
+    <t>bramka wejściowa</t>
   </si>
 </sst>
 </file>
@@ -742,7 +853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{42338ebe-0f60-4c0c-91fa-69d729a3ad29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f4ebc4f6-2fc1-4cab-b980-759ce17ffb8d}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -763,15 +874,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7f5c8871-f820-49c3-90c0-c4b43e814d38}">
-  <dimension ref="A1:I28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0471a07e-a6de-43e1-8069-e1ffbadce27a}">
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="11.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="44.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="54.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="27.8571428571429" customWidth="1"/>
     <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
@@ -841,28 +952,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
@@ -870,28 +981,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
@@ -899,28 +1010,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -928,28 +1039,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -957,28 +1068,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -986,28 +1097,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
         <v>33</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="G8" t="s">
         <v>34</v>
       </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
         <v>35</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
@@ -1015,28 +1126,28 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
@@ -1044,28 +1155,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -1073,28 +1184,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
         <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1102,28 +1213,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
         <v>44</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="s">
         <v>45</v>
       </c>
-      <c r="F12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
       <c r="H12" t="s">
         <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1131,28 +1242,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" t="s">
         <v>48</v>
       </c>
-      <c r="E13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" t="s">
-        <v>50</v>
-      </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1160,28 +1271,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1189,28 +1300,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" t="s">
         <v>52</v>
       </c>
-      <c r="C15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1218,28 +1329,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1247,22 +1358,22 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
         <v>18</v>
@@ -1276,28 +1387,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="H18" t="s">
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1305,28 +1416,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" t="s">
         <v>60</v>
       </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" t="s">
-        <v>41</v>
-      </c>
       <c r="H19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1334,28 +1445,28 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" t="s">
         <v>30</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1363,22 +1474,22 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" t="s">
         <v>65</v>
       </c>
-      <c r="C21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" t="s">
-        <v>70</v>
-      </c>
       <c r="G21" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
@@ -1392,22 +1503,22 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="H22" t="s">
         <v>18</v>
@@ -1421,22 +1532,22 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="G23" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H23" t="s">
         <v>18</v>
@@ -1450,28 +1561,28 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="H24" t="s">
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1479,28 +1590,28 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -1508,22 +1619,22 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E26" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
@@ -1537,22 +1648,22 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E27" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="F27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
@@ -1566,27 +1677,694 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" t="s">
+        <v>68</v>
+      </c>
+      <c r="H28" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" t="s">
         <v>77</v>
       </c>
-      <c r="C28" t="s">
+      <c r="E29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" t="s">
+        <v>68</v>
+      </c>
+      <c r="H31" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" t="s">
+        <v>78</v>
+      </c>
+      <c r="G32" t="s">
+        <v>68</v>
+      </c>
+      <c r="H32" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15">
+      <c r="A34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" t="s">
+        <v>87</v>
+      </c>
+      <c r="G34" t="s">
+        <v>66</v>
+      </c>
+      <c r="H34" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15">
+      <c r="A35" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" t="s">
+        <v>66</v>
+      </c>
+      <c r="H35" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15">
+      <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" t="s">
+        <v>93</v>
+      </c>
+      <c r="F36" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" t="s">
+        <v>66</v>
+      </c>
+      <c r="H36" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15">
+      <c r="A37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" t="s">
+        <v>71</v>
+      </c>
+      <c r="G37" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15">
+      <c r="A38" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" t="s">
+        <v>66</v>
+      </c>
+      <c r="H38" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15">
+      <c r="A39" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" t="s">
+        <v>97</v>
+      </c>
+      <c r="F39" t="s">
+        <v>98</v>
+      </c>
+      <c r="G39" t="s">
+        <v>66</v>
+      </c>
+      <c r="H39" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" t="s">
+        <v>97</v>
+      </c>
+      <c r="F40" t="s">
+        <v>98</v>
+      </c>
+      <c r="G40" t="s">
+        <v>66</v>
+      </c>
+      <c r="H40" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15">
+      <c r="A41" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" t="s">
+        <v>99</v>
+      </c>
+      <c r="E41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F41" t="s">
+        <v>94</v>
+      </c>
+      <c r="G41" t="s">
+        <v>66</v>
+      </c>
+      <c r="H41" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15">
+      <c r="A42" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" t="s">
+        <v>97</v>
+      </c>
+      <c r="F42" t="s">
+        <v>98</v>
+      </c>
+      <c r="G42" t="s">
+        <v>66</v>
+      </c>
+      <c r="H42" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15">
+      <c r="A43" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" t="s">
+        <v>100</v>
+      </c>
+      <c r="E43" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43" t="s">
+        <v>94</v>
+      </c>
+      <c r="G43" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="15">
+      <c r="A44" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" t="s">
+        <v>101</v>
+      </c>
+      <c r="E44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F44" t="s">
+        <v>94</v>
+      </c>
+      <c r="G44" t="s">
+        <v>66</v>
+      </c>
+      <c r="H44" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15">
+      <c r="A45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" t="s">
+        <v>91</v>
+      </c>
+      <c r="F45" t="s">
+        <v>102</v>
+      </c>
+      <c r="G45" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15">
+      <c r="A46" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" t="s">
+        <v>91</v>
+      </c>
+      <c r="F46" t="s">
+        <v>102</v>
+      </c>
+      <c r="G46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H46" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15">
+      <c r="A47" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" t="s">
+        <v>104</v>
+      </c>
+      <c r="D47" t="s">
+        <v>72</v>
+      </c>
+      <c r="E47" t="s">
+        <v>105</v>
+      </c>
+      <c r="F47" t="s">
         <v>53</v>
       </c>
-      <c r="D28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" t="s">
-        <v>62</v>
-      </c>
-      <c r="F28" t="s">
-        <v>63</v>
-      </c>
-      <c r="G28" t="s">
-        <v>59</v>
-      </c>
-      <c r="H28" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="G47" t="s">
+        <v>106</v>
+      </c>
+      <c r="H47" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15">
+      <c r="A48" t="s">
+        <v>103</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" t="s">
+        <v>105</v>
+      </c>
+      <c r="F48" t="s">
+        <v>53</v>
+      </c>
+      <c r="G48" t="s">
+        <v>106</v>
+      </c>
+      <c r="H48" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15">
+      <c r="A49" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" t="s">
+        <v>107</v>
+      </c>
+      <c r="E49" t="s">
+        <v>105</v>
+      </c>
+      <c r="F49" t="s">
+        <v>53</v>
+      </c>
+      <c r="G49" t="s">
+        <v>106</v>
+      </c>
+      <c r="H49" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15">
+      <c r="A50" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E50" t="s">
+        <v>105</v>
+      </c>
+      <c r="F50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G50" t="s">
+        <v>106</v>
+      </c>
+      <c r="H50" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15">
+      <c r="A51" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" t="s">
+        <v>105</v>
+      </c>
+      <c r="F51" t="s">
+        <v>53</v>
+      </c>
+      <c r="G51" t="s">
+        <v>68</v>
+      </c>
+      <c r="H51" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1598,15 +2376,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5d69ac15-95ae-4463-8635-0ab231f4a5d7}">
-  <dimension ref="A1:F6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{32e6ccfb-b4e6-4427-93eb-23d732c2301c}">
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="17.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="17.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="19.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="17.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1615,13 +2393,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -1635,16 +2413,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -1655,16 +2433,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -1675,16 +2453,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -1695,16 +2473,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -1715,18 +2493,138 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" t="s">
         <v>89</v>
       </c>
-      <c r="C6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="D9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15">
+      <c r="A10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15">
+      <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -9,18 +9,20 @@
   <sheets>
     <sheet name="Opis parametrów" sheetId="2" r:id="rId2"/>
     <sheet name="Oddziały" sheetId="3" r:id="rId3"/>
-    <sheet name="Dyżury" sheetId="4" r:id="rId4"/>
+    <sheet name="Dzienniki zajeć innych" sheetId="4" r:id="rId4"/>
+    <sheet name="Dyżury" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Oddziały!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Dyżury!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dzienniki zajeć innych'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dyżury!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="192">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -61,6 +63,27 @@
     <t>1, 08:00-08:45</t>
   </si>
   <si>
+    <t>Jastrzębska-Majtyka Agnieszka</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
+    <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Uczniowie przychodzą później</t>
+  </si>
+  <si>
+    <t>Erasmus+</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>Mocarski Arkadiusz</t>
   </si>
   <si>
@@ -73,15 +96,9 @@
     <t>34</t>
   </si>
   <si>
-    <t>Uczniowie przychodzą później</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Smirnow-Zechman Eleonora</t>
   </si>
   <si>
@@ -115,6 +132,24 @@
     <t>Dodatkowo płatne</t>
   </si>
   <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>2K|gr2</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
     <t>1FB</t>
   </si>
   <si>
@@ -127,12 +162,30 @@
     <t>Wrzeszcz Barbara</t>
   </si>
   <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
     <t>3, 09:40-10:25</t>
   </si>
   <si>
+    <t>Galert Anna</t>
+  </si>
+  <si>
+    <t>1FB|gr1</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>Fizyka</t>
+  </si>
+  <si>
+    <t>Biczysko Wojciech</t>
+  </si>
+  <si>
     <t>Nowak Magdalena</t>
   </si>
   <si>
@@ -142,18 +195,33 @@
     <t>4, 10:35-11:20</t>
   </si>
   <si>
+    <t>1TFB|gr1</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>1TFB|gr2</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>2TFA|gr1</t>
+  </si>
+  <si>
+    <t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</t>
+  </si>
+  <si>
+    <t>prf2</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
     <t>2K|gr1</t>
   </si>
   <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>Biezmienow Małgorzata</t>
-  </si>
-  <si>
-    <t>2K|gr2</t>
-  </si>
-  <si>
     <t>Matematyka</t>
   </si>
   <si>
@@ -175,6 +243,9 @@
     <t>4TFB|DZ</t>
   </si>
   <si>
+    <t>1TFA|gr2</t>
+  </si>
+  <si>
     <t>2K</t>
   </si>
   <si>
@@ -199,54 +270,57 @@
     <t>1WA</t>
   </si>
   <si>
+    <t>7, 13:15-14:00</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
+  </si>
+  <si>
+    <t>1WA|gr2</t>
+  </si>
+  <si>
+    <t>Informatyka</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>2FC</t>
+  </si>
+  <si>
+    <t>Uczniowie zwolnieni do domu</t>
+  </si>
+  <si>
+    <t>8, 14:05-14:50</t>
+  </si>
+  <si>
+    <t>1CA|gr1</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>Edukacja dla bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>9, 14:55-15:40</t>
+  </si>
+  <si>
+    <t>2FA</t>
+  </si>
+  <si>
     <t>Zajęcia z wychowawcą</t>
   </si>
   <si>
-    <t>Galert Anna</t>
-  </si>
-  <si>
-    <t>7, 13:15-14:00</t>
-  </si>
-  <si>
-    <t>Młynarczyk Paweł</t>
-  </si>
-  <si>
-    <t>1WA|gr2</t>
-  </si>
-  <si>
-    <t>Informatyka</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
-    <t>2FC</t>
-  </si>
-  <si>
-    <t>Uczniowie zwolnieni do domu</t>
-  </si>
-  <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>Edukacja dla bezpieczeństwa</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>3TFA</t>
-  </si>
-  <si>
-    <t>9, 14:55-15:40</t>
-  </si>
-  <si>
-    <t>2FA</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -259,9 +333,21 @@
     <t>sg6</t>
   </si>
   <si>
+    <t>3TFB|gr1</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
     <t>10, 15:45-16:30</t>
   </si>
   <si>
+    <t>4TFA</t>
+  </si>
+  <si>
     <t>1TFB</t>
   </si>
   <si>
@@ -286,6 +372,27 @@
     <t>30</t>
   </si>
   <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>4TH|gr2</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - fryzjerstwo wellness</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
     <t>07.10.2026</t>
   </si>
   <si>
@@ -301,12 +408,6 @@
     <t>Misiąg Anna</t>
   </si>
   <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
     <t>2WA|gr1</t>
   </si>
   <si>
@@ -316,21 +417,48 @@
     <t>Rozwój kompetencji zawodowych - kompetencje zawodowe</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1TFB|gr1</t>
+    <t>1CB|gr1</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>1FA|gr2</t>
   </si>
   <si>
     <t>2TFA</t>
   </si>
   <si>
-    <t>3TFB|gr1</t>
-  </si>
-  <si>
     <t>42</t>
   </si>
   <si>
+    <t>08.10.2026</t>
+  </si>
+  <si>
+    <t>1K|gr1</t>
+  </si>
+  <si>
+    <t>1FC|gr1</t>
+  </si>
+  <si>
+    <t>1S|gr2</t>
+  </si>
+  <si>
+    <t>1TH|gr2</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>3TFB|gr2</t>
+  </si>
+  <si>
+    <t>1B|gr1</t>
+  </si>
+  <si>
     <t>09.10.2026</t>
   </si>
   <si>
@@ -346,15 +474,66 @@
     <t>3FB</t>
   </si>
   <si>
-    <t>4TFA</t>
-  </si>
-  <si>
     <t>Godzina</t>
   </si>
   <si>
     <t>Nauczyciel</t>
   </si>
   <si>
+    <t>Dziennik zajęć innych</t>
+  </si>
+  <si>
+    <t>Opis zajęć</t>
+  </si>
+  <si>
+    <t>08:00-08:45</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Język angielski zawodowy</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Język angielski </t>
+  </si>
+  <si>
+    <t>08:50-09:35</t>
+  </si>
+  <si>
+    <t>09:40-10:25</t>
+  </si>
+  <si>
+    <t>10:35-11:20</t>
+  </si>
+  <si>
+    <t>14:55-15:40</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur -T</t>
+  </si>
+  <si>
+    <t>07:15-08:00</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur za 29.09.26</t>
+  </si>
+  <si>
+    <t>08:00-11:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projektowanie i wykonywanie fryzur-zaj.prakt. </t>
+  </si>
+  <si>
+    <t>Proj.fryz. za tydzień : 05.09.26-09.10.26</t>
+  </si>
+  <si>
+    <t>11:25-12:10</t>
+  </si>
+  <si>
     <t>Miejsce dyżuru</t>
   </si>
   <si>
@@ -376,6 +555,12 @@
     <t>14:00-14:05</t>
   </si>
   <si>
+    <t>parter</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
+  </si>
+  <si>
     <t>piętro_2</t>
   </si>
   <si>
@@ -385,25 +570,34 @@
     <t>14:50-14:55</t>
   </si>
   <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
     <t>15:40-15:45</t>
   </si>
   <si>
     <t>16:30-16:35</t>
   </si>
   <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
     <t>Bujanowska Iwona</t>
   </si>
   <si>
+    <t>12:10-12:25</t>
+  </si>
+  <si>
+    <t>13:10-13:15</t>
+  </si>
+  <si>
     <t>10:25-10:35</t>
   </si>
   <si>
-    <t>12:10-12:25</t>
-  </si>
-  <si>
     <t>bramka wejściowa</t>
+  </si>
+  <si>
+    <t>07:55-08:00</t>
+  </si>
+  <si>
+    <t>boisko - dziedziniec wejściowy/boisko</t>
   </si>
 </sst>
 </file>
@@ -853,7 +1047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f4ebc4f6-2fc1-4cab-b980-759ce17ffb8d}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8aa18952-91d5-4fea-986a-287b44f5de5f}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -874,18 +1068,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0471a07e-a6de-43e1-8069-e1ffbadce27a}">
-  <dimension ref="A1:I51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8bdcfde0-3736-4733-baab-9412d2fad7e3}">
+  <dimension ref="A1:I125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="28.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="11.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="54.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="27.8571428571429" customWidth="1"/>
-    <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
+    <col min="8" max="8" width="9.57142857142857" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -970,7 +1164,7 @@
         <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
@@ -981,7 +1175,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
@@ -996,13 +1190,13 @@
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
@@ -1010,28 +1204,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1039,28 +1233,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1068,28 +1262,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1097,28 +1291,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
@@ -1126,28 +1320,28 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
@@ -1155,28 +1349,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -1184,28 +1378,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
         <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1213,28 +1407,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" t="s">
         <v>39</v>
       </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1242,28 +1436,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1271,28 +1465,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I14" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1300,28 +1494,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1329,28 +1523,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1358,19 +1552,19 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G17" t="s">
         <v>17</v>
@@ -1387,28 +1581,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G18" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="H18" t="s">
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1416,28 +1610,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
         <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H19" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I19" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1445,28 +1639,28 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" t="s">
         <v>50</v>
       </c>
-      <c r="E20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" t="s">
-        <v>29</v>
-      </c>
       <c r="H20" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I20" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1474,28 +1668,28 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
@@ -1503,28 +1697,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H22" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
@@ -1532,28 +1726,28 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="H23" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1561,19 +1755,19 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" t="s">
         <v>44</v>
-      </c>
-      <c r="F24" t="s">
-        <v>16</v>
       </c>
       <c r="G24" t="s">
         <v>45</v>
@@ -1582,7 +1776,7 @@
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1590,28 +1784,28 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F25" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G25" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -1619,28 +1813,28 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" t="s">
         <v>76</v>
       </c>
-      <c r="D26" t="s">
+      <c r="G26" t="s">
         <v>77</v>
       </c>
-      <c r="E26" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" t="s">
-        <v>68</v>
-      </c>
       <c r="H26" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -1648,28 +1842,28 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="G27" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H27" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -1677,25 +1871,25 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G28" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I28" t="s">
         <v>19</v>
@@ -1706,28 +1900,28 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="G29" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="H29" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
@@ -1735,28 +1929,28 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" t="s">
         <v>62</v>
       </c>
-      <c r="D30" t="s">
-        <v>80</v>
-      </c>
-      <c r="E30" t="s">
-        <v>81</v>
-      </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="G30" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -1764,28 +1958,28 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" t="s">
         <v>44</v>
       </c>
-      <c r="F31" t="s">
-        <v>16</v>
-      </c>
       <c r="G31" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H31" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
@@ -1793,28 +1987,28 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F32" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="G32" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="H32" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -1822,54 +2016,54 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" t="s">
         <v>62</v>
       </c>
-      <c r="D33" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" t="s">
-        <v>70</v>
-      </c>
       <c r="F33" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G33" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" t="s">
         <v>85</v>
       </c>
-      <c r="B34" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>86</v>
       </c>
-      <c r="F34" t="s">
-        <v>87</v>
-      </c>
       <c r="G34" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I34" t="s">
         <v>19</v>
@@ -1877,28 +2071,28 @@
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" t="s">
         <v>88</v>
       </c>
-      <c r="B35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="E35" t="s">
+        <v>66</v>
+      </c>
+      <c r="F35" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
       </c>
-      <c r="D35" t="s">
-        <v>90</v>
-      </c>
-      <c r="E35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F35" t="s">
-        <v>71</v>
-      </c>
-      <c r="G35" t="s">
-        <v>66</v>
-      </c>
       <c r="H35" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I35" t="s">
         <v>19</v>
@@ -1906,86 +2100,86 @@
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" t="s">
+        <v>91</v>
+      </c>
+      <c r="E36" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" t="s">
         <v>92</v>
       </c>
-      <c r="D36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>93</v>
       </c>
-      <c r="F36" t="s">
-        <v>94</v>
-      </c>
-      <c r="G36" t="s">
-        <v>66</v>
-      </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="F37" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
+        <v>81</v>
+      </c>
+      <c r="E38" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" t="s">
         <v>95</v>
       </c>
-      <c r="E38" t="s">
-        <v>93</v>
-      </c>
-      <c r="F38" t="s">
-        <v>94</v>
-      </c>
       <c r="G38" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I38" t="s">
         <v>19</v>
@@ -1993,86 +2187,86 @@
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="D39" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F39" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="G39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H39" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G40" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="H40" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D41" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E41" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G41" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I41" t="s">
         <v>19</v>
@@ -2080,86 +2274,86 @@
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E42" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="G42" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="E43" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="F43" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="G43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D44" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="E44" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G44" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I44" t="s">
         <v>19</v>
@@ -2167,28 +2361,28 @@
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C45" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" t="s">
+        <v>51</v>
+      </c>
+      <c r="E45" t="s">
+        <v>66</v>
+      </c>
+      <c r="F45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G45" t="s">
         <v>89</v>
       </c>
-      <c r="D45" t="s">
-        <v>96</v>
-      </c>
-      <c r="E45" t="s">
-        <v>91</v>
-      </c>
-      <c r="F45" t="s">
-        <v>102</v>
-      </c>
-      <c r="G45" t="s">
-        <v>66</v>
-      </c>
       <c r="H45" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
@@ -2196,28 +2390,28 @@
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="F46" t="s">
         <v>102</v>
       </c>
       <c r="G46" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
@@ -2225,25 +2419,25 @@
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="C47" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="D47" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="E47" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="F47" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G47" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
@@ -2254,86 +2448,86 @@
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="C48" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E48" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="F48" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G48" t="s">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="C49" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E49" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="G49" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H49" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E50" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="F50" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
@@ -2341,30 +2535,2176 @@
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" t="s">
+        <v>112</v>
+      </c>
+      <c r="C51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" t="s">
+        <v>101</v>
+      </c>
+      <c r="E51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" t="s">
+        <v>102</v>
+      </c>
+      <c r="G51" t="s">
+        <v>89</v>
+      </c>
+      <c r="H51" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" t="s">
+        <v>83</v>
+      </c>
+      <c r="D52" t="s">
+        <v>79</v>
+      </c>
+      <c r="E52" t="s">
+        <v>94</v>
+      </c>
+      <c r="F52" t="s">
+        <v>95</v>
+      </c>
+      <c r="G52" t="s">
+        <v>89</v>
+      </c>
+      <c r="H52" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="15">
+      <c r="A53" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" t="s">
+        <v>87</v>
+      </c>
+      <c r="H53" t="s">
+        <v>18</v>
+      </c>
+      <c r="I53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="15">
+      <c r="A54" t="s">
+        <v>113</v>
+      </c>
+      <c r="B54" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" t="s">
+        <v>87</v>
+      </c>
+      <c r="H54" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="15">
+      <c r="A55" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" t="s">
+        <v>87</v>
+      </c>
+      <c r="H55" t="s">
+        <v>18</v>
+      </c>
+      <c r="I55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="15">
+      <c r="A56" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56" t="s">
+        <v>71</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" t="s">
+        <v>87</v>
+      </c>
+      <c r="H56" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="15">
+      <c r="A57" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" t="s">
+        <v>115</v>
+      </c>
+      <c r="G57" t="s">
+        <v>87</v>
+      </c>
+      <c r="H57" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="15">
+      <c r="A58" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" t="s">
+        <v>36</v>
+      </c>
+      <c r="D58" t="s">
+        <v>116</v>
+      </c>
+      <c r="E58" t="s">
+        <v>38</v>
+      </c>
+      <c r="F58" t="s">
+        <v>60</v>
+      </c>
+      <c r="G58" t="s">
+        <v>87</v>
+      </c>
+      <c r="H58" t="s">
+        <v>18</v>
+      </c>
+      <c r="I58" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="15">
+      <c r="A59" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F59" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" t="s">
+        <v>87</v>
+      </c>
+      <c r="H59" t="s">
+        <v>18</v>
+      </c>
+      <c r="I59" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="15">
+      <c r="A60" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" t="s">
+        <v>82</v>
+      </c>
+      <c r="C60" t="s">
+        <v>47</v>
+      </c>
+      <c r="D60" t="s">
+        <v>42</v>
+      </c>
+      <c r="E60" t="s">
+        <v>98</v>
+      </c>
+      <c r="F60" t="s">
+        <v>118</v>
+      </c>
+      <c r="G60" t="s">
+        <v>87</v>
+      </c>
+      <c r="H60" t="s">
+        <v>18</v>
+      </c>
+      <c r="I60" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15">
+      <c r="A61" t="s">
+        <v>113</v>
+      </c>
+      <c r="B61" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61" t="s">
+        <v>116</v>
+      </c>
+      <c r="E61" t="s">
+        <v>98</v>
+      </c>
+      <c r="F61" t="s">
+        <v>60</v>
+      </c>
+      <c r="G61" t="s">
+        <v>87</v>
+      </c>
+      <c r="H61" t="s">
+        <v>18</v>
+      </c>
+      <c r="I61" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15">
+      <c r="A62" t="s">
+        <v>113</v>
+      </c>
+      <c r="B62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" t="s">
+        <v>117</v>
+      </c>
+      <c r="F62" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H62" t="s">
+        <v>18</v>
+      </c>
+      <c r="I62" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15">
+      <c r="A63" t="s">
+        <v>113</v>
+      </c>
+      <c r="B63" t="s">
+        <v>90</v>
+      </c>
+      <c r="C63" t="s">
+        <v>47</v>
+      </c>
+      <c r="D63" t="s">
+        <v>91</v>
+      </c>
+      <c r="E63" t="s">
+        <v>38</v>
+      </c>
+      <c r="F63" t="s">
+        <v>118</v>
+      </c>
+      <c r="G63" t="s">
+        <v>87</v>
+      </c>
+      <c r="H63" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15">
+      <c r="A64" t="s">
+        <v>113</v>
+      </c>
+      <c r="B64" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64" t="s">
+        <v>119</v>
+      </c>
+      <c r="E64" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64" t="s">
+        <v>60</v>
+      </c>
+      <c r="G64" t="s">
+        <v>87</v>
+      </c>
+      <c r="H64" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15">
+      <c r="A65" t="s">
+        <v>113</v>
+      </c>
+      <c r="B65" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s">
+        <v>120</v>
+      </c>
+      <c r="E65" t="s">
+        <v>121</v>
+      </c>
+      <c r="F65" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" t="s">
+        <v>87</v>
+      </c>
+      <c r="H65" t="s">
+        <v>18</v>
+      </c>
+      <c r="I65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="15">
+      <c r="A66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B66" t="s">
+        <v>96</v>
+      </c>
+      <c r="C66" t="s">
+        <v>36</v>
+      </c>
+      <c r="D66" t="s">
+        <v>122</v>
+      </c>
+      <c r="E66" t="s">
+        <v>38</v>
+      </c>
+      <c r="F66" t="s">
+        <v>60</v>
+      </c>
+      <c r="G66" t="s">
+        <v>87</v>
+      </c>
+      <c r="H66" t="s">
+        <v>18</v>
+      </c>
+      <c r="I66" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="15">
+      <c r="A67" t="s">
+        <v>113</v>
+      </c>
+      <c r="B67" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" t="s">
+        <v>36</v>
+      </c>
+      <c r="D67" t="s">
+        <v>122</v>
+      </c>
+      <c r="E67" t="s">
+        <v>38</v>
+      </c>
+      <c r="F67" t="s">
+        <v>60</v>
+      </c>
+      <c r="G67" t="s">
+        <v>87</v>
+      </c>
+      <c r="H67" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="15">
+      <c r="A68" t="s">
+        <v>123</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" t="s">
+        <v>124</v>
+      </c>
+      <c r="D68" t="s">
+        <v>125</v>
+      </c>
+      <c r="E68" t="s">
+        <v>126</v>
+      </c>
+      <c r="F68" t="s">
+        <v>95</v>
+      </c>
+      <c r="G68" t="s">
+        <v>87</v>
+      </c>
+      <c r="H68" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="15">
+      <c r="A69" t="s">
+        <v>123</v>
+      </c>
+      <c r="B69" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" t="s">
+        <v>127</v>
+      </c>
+      <c r="D69" t="s">
+        <v>51</v>
+      </c>
+      <c r="E69" t="s">
+        <v>104</v>
+      </c>
+      <c r="F69" t="s">
+        <v>92</v>
+      </c>
+      <c r="G69" t="s">
+        <v>87</v>
+      </c>
+      <c r="H69" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="15">
+      <c r="A70" t="s">
+        <v>123</v>
+      </c>
+      <c r="B70" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" t="s">
+        <v>124</v>
+      </c>
+      <c r="D70" t="s">
+        <v>125</v>
+      </c>
+      <c r="E70" t="s">
+        <v>126</v>
+      </c>
+      <c r="F70" t="s">
+        <v>95</v>
+      </c>
+      <c r="G70" t="s">
+        <v>87</v>
+      </c>
+      <c r="H70" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="15">
+      <c r="A71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B71" t="s">
+        <v>46</v>
+      </c>
+      <c r="C71" t="s">
+        <v>36</v>
+      </c>
+      <c r="D71" t="s">
+        <v>37</v>
+      </c>
+      <c r="E71" t="s">
+        <v>38</v>
+      </c>
+      <c r="F71" t="s">
+        <v>118</v>
+      </c>
+      <c r="G71" t="s">
+        <v>87</v>
+      </c>
+      <c r="H71" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="15">
+      <c r="A72" t="s">
+        <v>123</v>
+      </c>
+      <c r="B72" t="s">
+        <v>46</v>
+      </c>
+      <c r="C72" t="s">
+        <v>127</v>
+      </c>
+      <c r="D72" t="s">
+        <v>128</v>
+      </c>
+      <c r="E72" t="s">
+        <v>104</v>
+      </c>
+      <c r="F72" t="s">
+        <v>92</v>
+      </c>
+      <c r="G72" t="s">
+        <v>87</v>
+      </c>
+      <c r="H72" t="s">
+        <v>24</v>
+      </c>
+      <c r="I72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="15">
+      <c r="A73" t="s">
+        <v>123</v>
+      </c>
+      <c r="B73" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" t="s">
+        <v>124</v>
+      </c>
+      <c r="D73" t="s">
+        <v>129</v>
+      </c>
+      <c r="E73" t="s">
+        <v>130</v>
+      </c>
+      <c r="F73" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" t="s">
+        <v>87</v>
+      </c>
+      <c r="H73" t="s">
+        <v>24</v>
+      </c>
+      <c r="I73" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="15">
+      <c r="A74" t="s">
+        <v>123</v>
+      </c>
+      <c r="B74" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" t="s">
+        <v>36</v>
+      </c>
+      <c r="D74" t="s">
+        <v>119</v>
+      </c>
+      <c r="E74" t="s">
+        <v>38</v>
+      </c>
+      <c r="F74" t="s">
+        <v>118</v>
+      </c>
+      <c r="G74" t="s">
+        <v>87</v>
+      </c>
+      <c r="H74" t="s">
+        <v>18</v>
+      </c>
+      <c r="I74" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="15">
+      <c r="A75" t="s">
+        <v>123</v>
+      </c>
+      <c r="B75" t="s">
+        <v>56</v>
+      </c>
+      <c r="C75" t="s">
+        <v>124</v>
+      </c>
+      <c r="D75" t="s">
+        <v>129</v>
+      </c>
+      <c r="E75" t="s">
+        <v>130</v>
+      </c>
+      <c r="F75" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" t="s">
+        <v>87</v>
+      </c>
+      <c r="H75" t="s">
+        <v>24</v>
+      </c>
+      <c r="I75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="15">
+      <c r="A76" t="s">
+        <v>123</v>
+      </c>
+      <c r="B76" t="s">
+        <v>71</v>
+      </c>
+      <c r="C76" t="s">
+        <v>47</v>
+      </c>
+      <c r="D76" t="s">
+        <v>131</v>
+      </c>
+      <c r="E76" t="s">
+        <v>38</v>
+      </c>
+      <c r="F76" t="s">
+        <v>132</v>
+      </c>
+      <c r="G76" t="s">
+        <v>87</v>
+      </c>
+      <c r="H76" t="s">
+        <v>18</v>
+      </c>
+      <c r="I76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="15">
+      <c r="A77" t="s">
+        <v>123</v>
+      </c>
+      <c r="B77" t="s">
+        <v>71</v>
+      </c>
+      <c r="C77" t="s">
+        <v>36</v>
+      </c>
+      <c r="D77" t="s">
+        <v>119</v>
+      </c>
+      <c r="E77" t="s">
+        <v>38</v>
+      </c>
+      <c r="F77" t="s">
+        <v>118</v>
+      </c>
+      <c r="G77" t="s">
+        <v>87</v>
+      </c>
+      <c r="H77" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="15">
+      <c r="A78" t="s">
+        <v>123</v>
+      </c>
+      <c r="B78" t="s">
+        <v>71</v>
+      </c>
+      <c r="C78" t="s">
+        <v>127</v>
+      </c>
+      <c r="D78" t="s">
+        <v>57</v>
+      </c>
+      <c r="E78" t="s">
+        <v>104</v>
+      </c>
+      <c r="F78" t="s">
+        <v>92</v>
+      </c>
+      <c r="G78" t="s">
+        <v>87</v>
+      </c>
+      <c r="H78" t="s">
+        <v>24</v>
+      </c>
+      <c r="I78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="15">
+      <c r="A79" t="s">
+        <v>123</v>
+      </c>
+      <c r="B79" t="s">
+        <v>71</v>
+      </c>
+      <c r="C79" t="s">
+        <v>124</v>
+      </c>
+      <c r="D79" t="s">
+        <v>125</v>
+      </c>
+      <c r="E79" t="s">
+        <v>130</v>
+      </c>
+      <c r="F79" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" t="s">
+        <v>87</v>
+      </c>
+      <c r="H79" t="s">
+        <v>24</v>
+      </c>
+      <c r="I79" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="15">
+      <c r="A80" t="s">
+        <v>123</v>
+      </c>
+      <c r="B80" t="s">
+        <v>80</v>
+      </c>
+      <c r="C80" t="s">
+        <v>47</v>
+      </c>
+      <c r="D80" t="s">
+        <v>133</v>
+      </c>
+      <c r="E80" t="s">
+        <v>38</v>
+      </c>
+      <c r="F80" t="s">
+        <v>132</v>
+      </c>
+      <c r="G80" t="s">
+        <v>87</v>
+      </c>
+      <c r="H80" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="15">
+      <c r="A81" t="s">
+        <v>123</v>
+      </c>
+      <c r="B81" t="s">
+        <v>80</v>
+      </c>
+      <c r="C81" t="s">
+        <v>36</v>
+      </c>
+      <c r="D81" t="s">
+        <v>51</v>
+      </c>
+      <c r="E81" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" t="s">
+        <v>118</v>
+      </c>
+      <c r="G81" t="s">
+        <v>87</v>
+      </c>
+      <c r="H81" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="15">
+      <c r="A82" t="s">
+        <v>123</v>
+      </c>
+      <c r="B82" t="s">
+        <v>80</v>
+      </c>
+      <c r="C82" t="s">
+        <v>127</v>
+      </c>
+      <c r="D82" t="s">
+        <v>134</v>
+      </c>
+      <c r="E82" t="s">
+        <v>104</v>
+      </c>
+      <c r="F82" t="s">
+        <v>92</v>
+      </c>
+      <c r="G82" t="s">
+        <v>87</v>
+      </c>
+      <c r="H82" t="s">
+        <v>24</v>
+      </c>
+      <c r="I82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="15">
+      <c r="A83" t="s">
+        <v>123</v>
+      </c>
+      <c r="B83" t="s">
+        <v>82</v>
+      </c>
+      <c r="C83" t="s">
+        <v>36</v>
+      </c>
+      <c r="D83" t="s">
+        <v>116</v>
+      </c>
+      <c r="E83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F83" t="s">
+        <v>118</v>
+      </c>
+      <c r="G83" t="s">
+        <v>87</v>
+      </c>
+      <c r="H83" t="s">
+        <v>18</v>
+      </c>
+      <c r="I83" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="15">
+      <c r="A84" t="s">
+        <v>123</v>
+      </c>
+      <c r="B84" t="s">
+        <v>82</v>
+      </c>
+      <c r="C84" t="s">
+        <v>127</v>
+      </c>
+      <c r="D84" t="s">
         <v>103</v>
       </c>
-      <c r="B51" t="s">
+      <c r="E84" t="s">
+        <v>104</v>
+      </c>
+      <c r="F84" t="s">
+        <v>92</v>
+      </c>
+      <c r="G84" t="s">
+        <v>87</v>
+      </c>
+      <c r="H84" t="s">
+        <v>24</v>
+      </c>
+      <c r="I84" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="15">
+      <c r="A85" t="s">
+        <v>123</v>
+      </c>
+      <c r="B85" t="s">
+        <v>90</v>
+      </c>
+      <c r="C85" t="s">
+        <v>124</v>
+      </c>
+      <c r="D85" t="s">
+        <v>129</v>
+      </c>
+      <c r="E85" t="s">
+        <v>126</v>
+      </c>
+      <c r="F85" t="s">
+        <v>135</v>
+      </c>
+      <c r="G85" t="s">
+        <v>87</v>
+      </c>
+      <c r="H85" t="s">
+        <v>24</v>
+      </c>
+      <c r="I85" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="15">
+      <c r="A86" t="s">
+        <v>123</v>
+      </c>
+      <c r="B86" t="s">
+        <v>96</v>
+      </c>
+      <c r="C86" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" t="s">
+        <v>129</v>
+      </c>
+      <c r="E86" t="s">
+        <v>126</v>
+      </c>
+      <c r="F86" t="s">
+        <v>135</v>
+      </c>
+      <c r="G86" t="s">
+        <v>87</v>
+      </c>
+      <c r="H86" t="s">
+        <v>24</v>
+      </c>
+      <c r="I86" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="15">
+      <c r="A87" t="s">
+        <v>136</v>
+      </c>
+      <c r="B87" t="s">
+        <v>46</v>
+      </c>
+      <c r="C87" t="s">
+        <v>47</v>
+      </c>
+      <c r="D87" t="s">
+        <v>133</v>
+      </c>
+      <c r="E87" t="s">
+        <v>38</v>
+      </c>
+      <c r="F87" t="s">
+        <v>118</v>
+      </c>
+      <c r="G87" t="s">
+        <v>87</v>
+      </c>
+      <c r="H87" t="s">
+        <v>18</v>
+      </c>
+      <c r="I87" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="15">
+      <c r="A88" t="s">
+        <v>136</v>
+      </c>
+      <c r="B88" t="s">
+        <v>56</v>
+      </c>
+      <c r="C88" t="s">
+        <v>47</v>
+      </c>
+      <c r="D88" t="s">
+        <v>137</v>
+      </c>
+      <c r="E88" t="s">
+        <v>38</v>
+      </c>
+      <c r="F88" t="s">
+        <v>118</v>
+      </c>
+      <c r="G88" t="s">
+        <v>87</v>
+      </c>
+      <c r="H88" t="s">
+        <v>18</v>
+      </c>
+      <c r="I88" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="15">
+      <c r="A89" t="s">
+        <v>136</v>
+      </c>
+      <c r="B89" t="s">
+        <v>71</v>
+      </c>
+      <c r="C89" t="s">
+        <v>47</v>
+      </c>
+      <c r="D89" t="s">
+        <v>138</v>
+      </c>
+      <c r="E89" t="s">
+        <v>38</v>
+      </c>
+      <c r="F89" t="s">
+        <v>118</v>
+      </c>
+      <c r="G89" t="s">
+        <v>87</v>
+      </c>
+      <c r="H89" t="s">
+        <v>18</v>
+      </c>
+      <c r="I89" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="15">
+      <c r="A90" t="s">
+        <v>136</v>
+      </c>
+      <c r="B90" t="s">
+        <v>80</v>
+      </c>
+      <c r="C90" t="s">
+        <v>47</v>
+      </c>
+      <c r="D90" t="s">
         <v>73</v>
       </c>
-      <c r="C51" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" t="s">
-        <v>108</v>
-      </c>
-      <c r="E51" t="s">
-        <v>105</v>
-      </c>
-      <c r="F51" t="s">
-        <v>53</v>
-      </c>
-      <c r="G51" t="s">
-        <v>68</v>
-      </c>
-      <c r="H51" t="s">
-        <v>18</v>
-      </c>
-      <c r="I51" t="s">
+      <c r="E90" t="s">
+        <v>38</v>
+      </c>
+      <c r="F90" t="s">
+        <v>118</v>
+      </c>
+      <c r="G90" t="s">
+        <v>87</v>
+      </c>
+      <c r="H90" t="s">
+        <v>18</v>
+      </c>
+      <c r="I90" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="15">
+      <c r="A91" t="s">
+        <v>136</v>
+      </c>
+      <c r="B91" t="s">
+        <v>82</v>
+      </c>
+      <c r="C91" t="s">
+        <v>47</v>
+      </c>
+      <c r="D91" t="s">
+        <v>139</v>
+      </c>
+      <c r="E91" t="s">
+        <v>38</v>
+      </c>
+      <c r="F91" t="s">
+        <v>118</v>
+      </c>
+      <c r="G91" t="s">
+        <v>87</v>
+      </c>
+      <c r="H91" t="s">
+        <v>18</v>
+      </c>
+      <c r="I91" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="15">
+      <c r="A92" t="s">
+        <v>136</v>
+      </c>
+      <c r="B92" t="s">
+        <v>82</v>
+      </c>
+      <c r="C92" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" t="s">
+        <v>140</v>
+      </c>
+      <c r="E92" t="s">
+        <v>38</v>
+      </c>
+      <c r="F92" t="s">
+        <v>60</v>
+      </c>
+      <c r="G92" t="s">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="15">
+      <c r="A93" t="s">
+        <v>136</v>
+      </c>
+      <c r="B93" t="s">
+        <v>82</v>
+      </c>
+      <c r="C93" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" t="s">
+        <v>141</v>
+      </c>
+      <c r="E93" t="s">
+        <v>142</v>
+      </c>
+      <c r="F93" t="s">
+        <v>16</v>
+      </c>
+      <c r="G93" t="s">
+        <v>87</v>
+      </c>
+      <c r="H93" t="s">
+        <v>18</v>
+      </c>
+      <c r="I93" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="15">
+      <c r="A94" t="s">
+        <v>136</v>
+      </c>
+      <c r="B94" t="s">
+        <v>90</v>
+      </c>
+      <c r="C94" t="s">
+        <v>36</v>
+      </c>
+      <c r="D94" t="s">
+        <v>143</v>
+      </c>
+      <c r="E94" t="s">
+        <v>38</v>
+      </c>
+      <c r="F94" t="s">
+        <v>60</v>
+      </c>
+      <c r="G94" t="s">
+        <v>87</v>
+      </c>
+      <c r="H94" t="s">
+        <v>18</v>
+      </c>
+      <c r="I94" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="15">
+      <c r="A95" t="s">
+        <v>136</v>
+      </c>
+      <c r="B95" t="s">
+        <v>90</v>
+      </c>
+      <c r="C95" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" t="s">
+        <v>141</v>
+      </c>
+      <c r="E95" t="s">
+        <v>142</v>
+      </c>
+      <c r="F95" t="s">
+        <v>16</v>
+      </c>
+      <c r="G95" t="s">
+        <v>87</v>
+      </c>
+      <c r="H95" t="s">
+        <v>18</v>
+      </c>
+      <c r="I95" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="15">
+      <c r="A96" t="s">
+        <v>136</v>
+      </c>
+      <c r="B96" t="s">
+        <v>96</v>
+      </c>
+      <c r="C96" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96" t="s">
+        <v>117</v>
+      </c>
+      <c r="F96" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" t="s">
+        <v>87</v>
+      </c>
+      <c r="H96" t="s">
+        <v>18</v>
+      </c>
+      <c r="I96" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="15">
+      <c r="A97" t="s">
+        <v>136</v>
+      </c>
+      <c r="B97" t="s">
+        <v>106</v>
+      </c>
+      <c r="C97" t="s">
+        <v>36</v>
+      </c>
+      <c r="D97" t="s">
+        <v>144</v>
+      </c>
+      <c r="E97" t="s">
+        <v>38</v>
+      </c>
+      <c r="F97" t="s">
+        <v>60</v>
+      </c>
+      <c r="G97" t="s">
+        <v>87</v>
+      </c>
+      <c r="H97" t="s">
+        <v>18</v>
+      </c>
+      <c r="I97" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15">
+      <c r="A98" t="s">
+        <v>136</v>
+      </c>
+      <c r="B98" t="s">
+        <v>106</v>
+      </c>
+      <c r="C98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98" t="s">
+        <v>117</v>
+      </c>
+      <c r="F98" t="s">
+        <v>16</v>
+      </c>
+      <c r="G98" t="s">
+        <v>87</v>
+      </c>
+      <c r="H98" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15">
+      <c r="A99" t="s">
+        <v>145</v>
+      </c>
+      <c r="B99" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99" t="s">
+        <v>120</v>
+      </c>
+      <c r="E99" t="s">
+        <v>121</v>
+      </c>
+      <c r="F99" t="s">
+        <v>16</v>
+      </c>
+      <c r="G99" t="s">
+        <v>87</v>
+      </c>
+      <c r="H99" t="s">
+        <v>18</v>
+      </c>
+      <c r="I99" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15">
+      <c r="A100" t="s">
+        <v>145</v>
+      </c>
+      <c r="B100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" t="s">
+        <v>47</v>
+      </c>
+      <c r="D100" t="s">
+        <v>107</v>
+      </c>
+      <c r="E100" t="s">
+        <v>38</v>
+      </c>
+      <c r="F100" t="s">
+        <v>118</v>
+      </c>
+      <c r="G100" t="s">
+        <v>87</v>
+      </c>
+      <c r="H100" t="s">
+        <v>18</v>
+      </c>
+      <c r="I100" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="15">
+      <c r="A101" t="s">
+        <v>145</v>
+      </c>
+      <c r="B101" t="s">
+        <v>46</v>
+      </c>
+      <c r="C101" t="s">
+        <v>47</v>
+      </c>
+      <c r="D101" t="s">
+        <v>107</v>
+      </c>
+      <c r="E101" t="s">
+        <v>38</v>
+      </c>
+      <c r="F101" t="s">
+        <v>118</v>
+      </c>
+      <c r="G101" t="s">
+        <v>87</v>
+      </c>
+      <c r="H101" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="15">
+      <c r="A102" t="s">
+        <v>145</v>
+      </c>
+      <c r="B102" t="s">
+        <v>46</v>
+      </c>
+      <c r="C102" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" t="s">
+        <v>98</v>
+      </c>
+      <c r="F102" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" t="s">
+        <v>87</v>
+      </c>
+      <c r="H102" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="15">
+      <c r="A103" t="s">
+        <v>145</v>
+      </c>
+      <c r="B103" t="s">
+        <v>56</v>
+      </c>
+      <c r="C103" t="s">
+        <v>47</v>
+      </c>
+      <c r="D103" t="s">
+        <v>139</v>
+      </c>
+      <c r="E103" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" t="s">
+        <v>118</v>
+      </c>
+      <c r="G103" t="s">
+        <v>87</v>
+      </c>
+      <c r="H103" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15">
+      <c r="A104" t="s">
+        <v>145</v>
+      </c>
+      <c r="B104" t="s">
+        <v>71</v>
+      </c>
+      <c r="C104" t="s">
+        <v>47</v>
+      </c>
+      <c r="D104" t="s">
+        <v>57</v>
+      </c>
+      <c r="E104" t="s">
+        <v>38</v>
+      </c>
+      <c r="F104" t="s">
+        <v>118</v>
+      </c>
+      <c r="G104" t="s">
+        <v>87</v>
+      </c>
+      <c r="H104" t="s">
+        <v>18</v>
+      </c>
+      <c r="I104" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="15">
+      <c r="A105" t="s">
+        <v>145</v>
+      </c>
+      <c r="B105" t="s">
+        <v>71</v>
+      </c>
+      <c r="C105" t="s">
+        <v>36</v>
+      </c>
+      <c r="D105" t="s">
+        <v>59</v>
+      </c>
+      <c r="E105" t="s">
+        <v>38</v>
+      </c>
+      <c r="F105" t="s">
+        <v>58</v>
+      </c>
+      <c r="G105" t="s">
+        <v>87</v>
+      </c>
+      <c r="H105" t="s">
+        <v>18</v>
+      </c>
+      <c r="I105" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15">
+      <c r="A106" t="s">
+        <v>145</v>
+      </c>
+      <c r="B106" t="s">
+        <v>71</v>
+      </c>
+      <c r="C106" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" t="s">
+        <v>120</v>
+      </c>
+      <c r="E106" t="s">
+        <v>142</v>
+      </c>
+      <c r="F106" t="s">
+        <v>16</v>
+      </c>
+      <c r="G106" t="s">
+        <v>87</v>
+      </c>
+      <c r="H106" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15">
+      <c r="A107" t="s">
+        <v>145</v>
+      </c>
+      <c r="B107" t="s">
+        <v>71</v>
+      </c>
+      <c r="C107" t="s">
+        <v>146</v>
+      </c>
+      <c r="D107" t="s">
+        <v>51</v>
+      </c>
+      <c r="E107" t="s">
+        <v>147</v>
+      </c>
+      <c r="F107" t="s">
+        <v>76</v>
+      </c>
+      <c r="G107" t="s">
+        <v>148</v>
+      </c>
+      <c r="H107" t="s">
+        <v>24</v>
+      </c>
+      <c r="I107" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15">
+      <c r="A108" t="s">
+        <v>145</v>
+      </c>
+      <c r="B108" t="s">
+        <v>80</v>
+      </c>
+      <c r="C108" t="s">
+        <v>47</v>
+      </c>
+      <c r="D108" t="s">
+        <v>103</v>
+      </c>
+      <c r="E108" t="s">
+        <v>38</v>
+      </c>
+      <c r="F108" t="s">
+        <v>118</v>
+      </c>
+      <c r="G108" t="s">
+        <v>87</v>
+      </c>
+      <c r="H108" t="s">
+        <v>18</v>
+      </c>
+      <c r="I108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15">
+      <c r="A109" t="s">
+        <v>145</v>
+      </c>
+      <c r="B109" t="s">
+        <v>80</v>
+      </c>
+      <c r="C109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D109" t="s">
+        <v>143</v>
+      </c>
+      <c r="E109" t="s">
+        <v>38</v>
+      </c>
+      <c r="F109" t="s">
+        <v>58</v>
+      </c>
+      <c r="G109" t="s">
+        <v>87</v>
+      </c>
+      <c r="H109" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15">
+      <c r="A110" t="s">
+        <v>145</v>
+      </c>
+      <c r="B110" t="s">
+        <v>80</v>
+      </c>
+      <c r="C110" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" t="s">
+        <v>120</v>
+      </c>
+      <c r="E110" t="s">
+        <v>142</v>
+      </c>
+      <c r="F110" t="s">
+        <v>16</v>
+      </c>
+      <c r="G110" t="s">
+        <v>87</v>
+      </c>
+      <c r="H110" t="s">
+        <v>18</v>
+      </c>
+      <c r="I110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="15">
+      <c r="A111" t="s">
+        <v>145</v>
+      </c>
+      <c r="B111" t="s">
+        <v>80</v>
+      </c>
+      <c r="C111" t="s">
+        <v>146</v>
+      </c>
+      <c r="D111" t="s">
+        <v>51</v>
+      </c>
+      <c r="E111" t="s">
+        <v>147</v>
+      </c>
+      <c r="F111" t="s">
+        <v>76</v>
+      </c>
+      <c r="G111" t="s">
+        <v>148</v>
+      </c>
+      <c r="H111" t="s">
+        <v>24</v>
+      </c>
+      <c r="I111" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="15">
+      <c r="A112" t="s">
+        <v>145</v>
+      </c>
+      <c r="B112" t="s">
+        <v>82</v>
+      </c>
+      <c r="C112" t="s">
+        <v>47</v>
+      </c>
+      <c r="D112" t="s">
+        <v>131</v>
+      </c>
+      <c r="E112" t="s">
+        <v>38</v>
+      </c>
+      <c r="F112" t="s">
+        <v>118</v>
+      </c>
+      <c r="G112" t="s">
+        <v>87</v>
+      </c>
+      <c r="H112" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15">
+      <c r="A113" t="s">
+        <v>145</v>
+      </c>
+      <c r="B113" t="s">
+        <v>82</v>
+      </c>
+      <c r="C113" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" t="s">
+        <v>120</v>
+      </c>
+      <c r="E113" t="s">
+        <v>142</v>
+      </c>
+      <c r="F113" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" t="s">
+        <v>87</v>
+      </c>
+      <c r="H113" t="s">
+        <v>18</v>
+      </c>
+      <c r="I113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="15">
+      <c r="A114" t="s">
+        <v>145</v>
+      </c>
+      <c r="B114" t="s">
+        <v>82</v>
+      </c>
+      <c r="C114" t="s">
+        <v>146</v>
+      </c>
+      <c r="D114" t="s">
+        <v>149</v>
+      </c>
+      <c r="E114" t="s">
+        <v>147</v>
+      </c>
+      <c r="F114" t="s">
+        <v>76</v>
+      </c>
+      <c r="G114" t="s">
+        <v>148</v>
+      </c>
+      <c r="H114" t="s">
+        <v>24</v>
+      </c>
+      <c r="I114" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="15">
+      <c r="A115" t="s">
+        <v>145</v>
+      </c>
+      <c r="B115" t="s">
+        <v>90</v>
+      </c>
+      <c r="C115" t="s">
+        <v>47</v>
+      </c>
+      <c r="D115" t="s">
+        <v>137</v>
+      </c>
+      <c r="E115" t="s">
+        <v>38</v>
+      </c>
+      <c r="F115" t="s">
+        <v>118</v>
+      </c>
+      <c r="G115" t="s">
+        <v>87</v>
+      </c>
+      <c r="H115" t="s">
+        <v>18</v>
+      </c>
+      <c r="I115" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15">
+      <c r="A116" t="s">
+        <v>145</v>
+      </c>
+      <c r="B116" t="s">
+        <v>90</v>
+      </c>
+      <c r="C116" t="s">
+        <v>36</v>
+      </c>
+      <c r="D116" t="s">
+        <v>140</v>
+      </c>
+      <c r="E116" t="s">
+        <v>38</v>
+      </c>
+      <c r="F116" t="s">
+        <v>58</v>
+      </c>
+      <c r="G116" t="s">
+        <v>87</v>
+      </c>
+      <c r="H116" t="s">
+        <v>18</v>
+      </c>
+      <c r="I116" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15">
+      <c r="A117" t="s">
+        <v>145</v>
+      </c>
+      <c r="B117" t="s">
+        <v>90</v>
+      </c>
+      <c r="C117" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" t="s">
+        <v>120</v>
+      </c>
+      <c r="E117" t="s">
+        <v>142</v>
+      </c>
+      <c r="F117" t="s">
+        <v>16</v>
+      </c>
+      <c r="G117" t="s">
+        <v>87</v>
+      </c>
+      <c r="H117" t="s">
+        <v>18</v>
+      </c>
+      <c r="I117" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="15">
+      <c r="A118" t="s">
+        <v>145</v>
+      </c>
+      <c r="B118" t="s">
+        <v>90</v>
+      </c>
+      <c r="C118" t="s">
+        <v>146</v>
+      </c>
+      <c r="D118" t="s">
+        <v>149</v>
+      </c>
+      <c r="E118" t="s">
+        <v>147</v>
+      </c>
+      <c r="F118" t="s">
+        <v>76</v>
+      </c>
+      <c r="G118" t="s">
+        <v>148</v>
+      </c>
+      <c r="H118" t="s">
+        <v>24</v>
+      </c>
+      <c r="I118" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="15">
+      <c r="A119" t="s">
+        <v>145</v>
+      </c>
+      <c r="B119" t="s">
+        <v>96</v>
+      </c>
+      <c r="C119" t="s">
+        <v>47</v>
+      </c>
+      <c r="D119" t="s">
+        <v>138</v>
+      </c>
+      <c r="E119" t="s">
+        <v>38</v>
+      </c>
+      <c r="F119" t="s">
+        <v>118</v>
+      </c>
+      <c r="G119" t="s">
+        <v>87</v>
+      </c>
+      <c r="H119" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="15">
+      <c r="A120" t="s">
+        <v>145</v>
+      </c>
+      <c r="B120" t="s">
+        <v>96</v>
+      </c>
+      <c r="C120" t="s">
+        <v>36</v>
+      </c>
+      <c r="D120" t="s">
+        <v>144</v>
+      </c>
+      <c r="E120" t="s">
+        <v>38</v>
+      </c>
+      <c r="F120" t="s">
+        <v>58</v>
+      </c>
+      <c r="G120" t="s">
+        <v>87</v>
+      </c>
+      <c r="H120" t="s">
+        <v>18</v>
+      </c>
+      <c r="I120" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="15">
+      <c r="A121" t="s">
+        <v>145</v>
+      </c>
+      <c r="B121" t="s">
+        <v>96</v>
+      </c>
+      <c r="C121" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" t="s">
+        <v>141</v>
+      </c>
+      <c r="E121" t="s">
+        <v>142</v>
+      </c>
+      <c r="F121" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" t="s">
+        <v>87</v>
+      </c>
+      <c r="H121" t="s">
+        <v>18</v>
+      </c>
+      <c r="I121" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15">
+      <c r="A122" t="s">
+        <v>145</v>
+      </c>
+      <c r="B122" t="s">
+        <v>96</v>
+      </c>
+      <c r="C122" t="s">
+        <v>146</v>
+      </c>
+      <c r="D122" t="s">
+        <v>107</v>
+      </c>
+      <c r="E122" t="s">
+        <v>147</v>
+      </c>
+      <c r="F122" t="s">
+        <v>76</v>
+      </c>
+      <c r="G122" t="s">
+        <v>89</v>
+      </c>
+      <c r="H122" t="s">
+        <v>24</v>
+      </c>
+      <c r="I122" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15">
+      <c r="A123" t="s">
+        <v>145</v>
+      </c>
+      <c r="B123" t="s">
+        <v>106</v>
+      </c>
+      <c r="C123" t="s">
+        <v>47</v>
+      </c>
+      <c r="D123" t="s">
+        <v>48</v>
+      </c>
+      <c r="E123" t="s">
+        <v>38</v>
+      </c>
+      <c r="F123" t="s">
+        <v>118</v>
+      </c>
+      <c r="G123" t="s">
+        <v>87</v>
+      </c>
+      <c r="H123" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15">
+      <c r="A124" t="s">
+        <v>145</v>
+      </c>
+      <c r="B124" t="s">
+        <v>106</v>
+      </c>
+      <c r="C124" t="s">
+        <v>36</v>
+      </c>
+      <c r="D124" t="s">
+        <v>144</v>
+      </c>
+      <c r="E124" t="s">
+        <v>38</v>
+      </c>
+      <c r="F124" t="s">
+        <v>58</v>
+      </c>
+      <c r="G124" t="s">
+        <v>87</v>
+      </c>
+      <c r="H124" t="s">
+        <v>18</v>
+      </c>
+      <c r="I124" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15">
+      <c r="A125" t="s">
+        <v>145</v>
+      </c>
+      <c r="B125" t="s">
+        <v>106</v>
+      </c>
+      <c r="C125" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" t="s">
+        <v>141</v>
+      </c>
+      <c r="E125" t="s">
+        <v>142</v>
+      </c>
+      <c r="F125" t="s">
+        <v>16</v>
+      </c>
+      <c r="G125" t="s">
+        <v>87</v>
+      </c>
+      <c r="H125" t="s">
+        <v>18</v>
+      </c>
+      <c r="I125" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2376,16 +4716,445 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{32e6ccfb-b4e6-4427-93eb-23d732c2301c}">
-  <dimension ref="A1:F12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1e6bdb72-d120-4d1b-90d7-29f17b33ac0e}">
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
-    <col min="4" max="4" width="17.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="28.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="28.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="42.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
+    <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
+    <col min="8" max="8" width="9.57142857142857" customWidth="1"/>
+    <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="56.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15">
+      <c r="A3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
+      <c r="A4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15">
+      <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15">
+      <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15">
+      <c r="A8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" t="s">
+        <v>165</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15">
+      <c r="A9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15">
+      <c r="A10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15">
+      <c r="A11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15">
+      <c r="A12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" t="s">
+        <v>168</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15">
+      <c r="A13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" t="s">
+        <v>168</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15">
+      <c r="A14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" t="s">
+        <v>168</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{dc245a11-a53c-4c26-a1a8-d94eef1f3e34}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="28.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="9.28571428571429" customWidth="1"/>
+    <col min="6" max="6" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="56.25" customHeight="1">
@@ -2393,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -2413,19 +5182,19 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15">
@@ -2433,19 +5202,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
@@ -2453,16 +5222,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>177</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -2473,19 +5242,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
@@ -2493,19 +5262,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
@@ -2513,19 +5282,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
@@ -2533,36 +5302,36 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>184</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -2570,36 +5339,36 @@
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
@@ -2610,21 +5379,381 @@
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15">
+      <c r="A13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15">
+      <c r="A14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15">
+      <c r="A15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15">
+      <c r="A16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15">
+      <c r="A17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15">
+      <c r="A19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15">
+      <c r="A20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s">
+        <v>177</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15">
+      <c r="A21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" t="s">
         <v>127</v>
       </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="D21" t="s">
+        <v>179</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15">
+      <c r="A22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" t="s">
+        <v>188</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" t="s">
+        <v>177</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15">
+      <c r="A23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15">
+      <c r="A24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15">
+      <c r="A25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15">
+      <c r="A26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15">
+      <c r="A27" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" t="s">
+        <v>188</v>
+      </c>
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15">
+      <c r="A28" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" t="s">
+        <v>189</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15">
+      <c r="A29" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>191</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="194">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -222,96 +222,96 @@
     <t>2K|gr1</t>
   </si>
   <si>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>Technologie produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>5, 11:25-12:10</t>
+  </si>
+  <si>
+    <t>4TFB|DZ</t>
+  </si>
+  <si>
+    <t>1TFA|gr2</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Kaczorowski Waldemar</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>1TH</t>
+  </si>
+  <si>
+    <t>6, 12:25-13:10</t>
+  </si>
+  <si>
+    <t>1WA</t>
+  </si>
+  <si>
+    <t>7, 13:15-14:00</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
+  </si>
+  <si>
+    <t>1WA|gr2</t>
+  </si>
+  <si>
+    <t>Informatyka</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>2FC</t>
+  </si>
+  <si>
     <t>Matematyka</t>
   </si>
   <si>
+    <t>Uczniowie zwolnieni do domu</t>
+  </si>
+  <si>
+    <t>8, 14:05-14:50</t>
+  </si>
+  <si>
+    <t>1CA|gr1</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>Edukacja dla bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
     <t>Filipiak Wiesław</t>
   </si>
   <si>
-    <t>1CA</t>
-  </si>
-  <si>
-    <t>Technika w produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
-    <t>5, 11:25-12:10</t>
-  </si>
-  <si>
-    <t>4TFB|DZ</t>
-  </si>
-  <si>
-    <t>1TFA|gr2</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Kaczorowski Waldemar</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>6, 12:25-13:10</t>
-  </si>
-  <si>
-    <t>1WA</t>
-  </si>
-  <si>
-    <t>7, 13:15-14:00</t>
-  </si>
-  <si>
-    <t>Młynarczyk Paweł</t>
-  </si>
-  <si>
-    <t>1WA|gr2</t>
-  </si>
-  <si>
-    <t>Informatyka</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
-    <t>2FC</t>
-  </si>
-  <si>
-    <t>Uczniowie zwolnieni do domu</t>
-  </si>
-  <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>1CA|gr1</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>Wojciechowski Łukasz</t>
-  </si>
-  <si>
-    <t>Edukacja dla bezpieczeństwa</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>9, 14:55-15:40</t>
   </si>
   <si>
@@ -546,6 +546,18 @@
     <t>Ulanowska Magdalena</t>
   </si>
   <si>
+    <t>10:25-10:35</t>
+  </si>
+  <si>
+    <t>Stępień Krystyna</t>
+  </si>
+  <si>
+    <t>boisko - dziedziniec wejściowy/boisko</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
     <t>11:20-11:25</t>
   </si>
   <si>
@@ -588,16 +600,10 @@
     <t>13:10-13:15</t>
   </si>
   <si>
-    <t>10:25-10:35</t>
-  </si>
-  <si>
     <t>bramka wejściowa</t>
   </si>
   <si>
     <t>07:55-08:00</t>
-  </si>
-  <si>
-    <t>boisko - dziedziniec wejściowy/boisko</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1053,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8aa18952-91d5-4fea-986a-287b44f5de5f}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c3a39568-118a-471e-8c64-c8c790e513db}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1068,7 +1074,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8bdcfde0-3736-4733-baab-9412d2fad7e3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{43d1a943-5e2f-4651-9491-1f0878988cda}">
   <dimension ref="A1:I125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1677,19 +1683,19 @@
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G21" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="H21" t="s">
         <v>24</v>
       </c>
       <c r="I21" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
@@ -1703,16 +1709,16 @@
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
       </c>
       <c r="G22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H22" t="s">
         <v>24</v>
@@ -1726,13 +1732,13 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
         <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s">
         <v>32</v>
@@ -1755,13 +1761,13 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
         <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E24" t="s">
         <v>43</v>
@@ -1784,7 +1790,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -1813,22 +1819,22 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
         <v>20</v>
       </c>
       <c r="D26" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" t="s">
         <v>74</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="F26" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" t="s">
-        <v>77</v>
       </c>
       <c r="H26" t="s">
         <v>24</v>
@@ -1842,22 +1848,22 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
         <v>54</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F27" t="s">
         <v>23</v>
       </c>
       <c r="G27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H27" t="s">
         <v>24</v>
@@ -1871,13 +1877,13 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -1900,13 +1906,13 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
         <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E29" t="s">
         <v>32</v>
@@ -1929,7 +1935,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
@@ -1958,13 +1964,13 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E31" t="s">
         <v>43</v>
@@ -1987,13 +1993,13 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
         <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E32" t="s">
         <v>32</v>
@@ -2016,7 +2022,7 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
@@ -2045,22 +2051,22 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" t="s">
         <v>82</v>
       </c>
-      <c r="C34" t="s">
+      <c r="E34" t="s">
         <v>83</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
         <v>84</v>
       </c>
-      <c r="E34" t="s">
-        <v>85</v>
-      </c>
-      <c r="F34" t="s">
-        <v>86</v>
-      </c>
       <c r="G34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H34" t="s">
         <v>24</v>
@@ -2074,22 +2080,22 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
         <v>54</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E35" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F35" t="s">
         <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s">
         <v>24</v>
@@ -2103,22 +2109,22 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
         <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E36" t="s">
         <v>38</v>
       </c>
       <c r="F36" t="s">
+        <v>91</v>
+      </c>
+      <c r="G36" t="s">
         <v>92</v>
-      </c>
-      <c r="G36" t="s">
-        <v>93</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
@@ -2132,7 +2138,7 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
@@ -2161,22 +2167,22 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D38" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E38" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" t="s">
         <v>94</v>
       </c>
-      <c r="F38" t="s">
-        <v>95</v>
-      </c>
       <c r="G38" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s">
         <v>24</v>
@@ -2190,7 +2196,7 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
         <v>54</v>
@@ -2199,13 +2205,13 @@
         <v>51</v>
       </c>
       <c r="E39" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F39" t="s">
         <v>23</v>
       </c>
       <c r="G39" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="H39" t="s">
         <v>24</v>
@@ -2263,7 +2269,7 @@
         <v>102</v>
       </c>
       <c r="G41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s">
         <v>24</v>
@@ -2338,19 +2344,19 @@
         <v>96</v>
       </c>
       <c r="C44" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E44" t="s">
         <v>98</v>
       </c>
       <c r="F44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s">
         <v>24</v>
@@ -2373,13 +2379,13 @@
         <v>51</v>
       </c>
       <c r="E45" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F45" t="s">
         <v>23</v>
       </c>
       <c r="G45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s">
         <v>24</v>
@@ -2408,7 +2414,7 @@
         <v>102</v>
       </c>
       <c r="G46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s">
         <v>24</v>
@@ -2437,7 +2443,7 @@
         <v>60</v>
       </c>
       <c r="G47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
@@ -2483,7 +2489,7 @@
         <v>106</v>
       </c>
       <c r="C49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D49" t="s">
         <v>108</v>
@@ -2515,16 +2521,16 @@
         <v>54</v>
       </c>
       <c r="D50" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E50" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F50" t="s">
         <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s">
         <v>24</v>
@@ -2553,7 +2559,7 @@
         <v>102</v>
       </c>
       <c r="G51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s">
         <v>24</v>
@@ -2570,19 +2576,19 @@
         <v>112</v>
       </c>
       <c r="C52" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E52" t="s">
+        <v>93</v>
+      </c>
+      <c r="F52" t="s">
         <v>94</v>
       </c>
-      <c r="F52" t="s">
-        <v>95</v>
-      </c>
       <c r="G52" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s">
         <v>24</v>
@@ -2611,7 +2617,7 @@
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
@@ -2640,7 +2646,7 @@
         <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
@@ -2669,7 +2675,7 @@
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
@@ -2683,7 +2689,7 @@
         <v>113</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -2698,7 +2704,7 @@
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
@@ -2712,7 +2718,7 @@
         <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C57" t="s">
         <v>20</v>
@@ -2727,7 +2733,7 @@
         <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H57" t="s">
         <v>24</v>
@@ -2741,7 +2747,7 @@
         <v>113</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
         <v>36</v>
@@ -2756,7 +2762,7 @@
         <v>60</v>
       </c>
       <c r="G58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
@@ -2770,7 +2776,7 @@
         <v>113</v>
       </c>
       <c r="B59" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
         <v>13</v>
@@ -2785,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
@@ -2799,7 +2805,7 @@
         <v>113</v>
       </c>
       <c r="B60" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C60" t="s">
         <v>47</v>
@@ -2814,7 +2820,7 @@
         <v>118</v>
       </c>
       <c r="G60" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
@@ -2828,7 +2834,7 @@
         <v>113</v>
       </c>
       <c r="B61" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C61" t="s">
         <v>36</v>
@@ -2843,7 +2849,7 @@
         <v>60</v>
       </c>
       <c r="G61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
@@ -2857,7 +2863,7 @@
         <v>113</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C62" t="s">
         <v>13</v>
@@ -2872,7 +2878,7 @@
         <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
@@ -2886,13 +2892,13 @@
         <v>113</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C63" t="s">
         <v>47</v>
       </c>
       <c r="D63" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E63" t="s">
         <v>38</v>
@@ -2901,7 +2907,7 @@
         <v>118</v>
       </c>
       <c r="G63" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
@@ -2915,7 +2921,7 @@
         <v>113</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C64" t="s">
         <v>36</v>
@@ -2930,7 +2936,7 @@
         <v>60</v>
       </c>
       <c r="G64" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
@@ -2944,7 +2950,7 @@
         <v>113</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
@@ -2959,7 +2965,7 @@
         <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
@@ -2988,7 +2994,7 @@
         <v>60</v>
       </c>
       <c r="G66" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
@@ -3017,7 +3023,7 @@
         <v>60</v>
       </c>
       <c r="G67" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
@@ -3043,10 +3049,10 @@
         <v>126</v>
       </c>
       <c r="F68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G68" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H68" t="s">
         <v>24</v>
@@ -3072,10 +3078,10 @@
         <v>104</v>
       </c>
       <c r="F69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G69" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H69" t="s">
         <v>24</v>
@@ -3101,10 +3107,10 @@
         <v>126</v>
       </c>
       <c r="F70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G70" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H70" t="s">
         <v>24</v>
@@ -3133,7 +3139,7 @@
         <v>118</v>
       </c>
       <c r="G71" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
@@ -3159,10 +3165,10 @@
         <v>104</v>
       </c>
       <c r="F72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G72" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H72" t="s">
         <v>24</v>
@@ -3191,7 +3197,7 @@
         <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H73" t="s">
         <v>24</v>
@@ -3220,7 +3226,7 @@
         <v>118</v>
       </c>
       <c r="G74" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
@@ -3249,7 +3255,7 @@
         <v>16</v>
       </c>
       <c r="G75" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H75" t="s">
         <v>24</v>
@@ -3263,7 +3269,7 @@
         <v>123</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C76" t="s">
         <v>47</v>
@@ -3278,7 +3284,7 @@
         <v>132</v>
       </c>
       <c r="G76" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
@@ -3292,7 +3298,7 @@
         <v>123</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C77" t="s">
         <v>36</v>
@@ -3307,7 +3313,7 @@
         <v>118</v>
       </c>
       <c r="G77" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
@@ -3321,7 +3327,7 @@
         <v>123</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C78" t="s">
         <v>127</v>
@@ -3333,10 +3339,10 @@
         <v>104</v>
       </c>
       <c r="F78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G78" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H78" t="s">
         <v>24</v>
@@ -3350,7 +3356,7 @@
         <v>123</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C79" t="s">
         <v>124</v>
@@ -3365,7 +3371,7 @@
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H79" t="s">
         <v>24</v>
@@ -3379,7 +3385,7 @@
         <v>123</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C80" t="s">
         <v>47</v>
@@ -3394,7 +3400,7 @@
         <v>132</v>
       </c>
       <c r="G80" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
@@ -3408,7 +3414,7 @@
         <v>123</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C81" t="s">
         <v>36</v>
@@ -3423,7 +3429,7 @@
         <v>118</v>
       </c>
       <c r="G81" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
@@ -3437,7 +3443,7 @@
         <v>123</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C82" t="s">
         <v>127</v>
@@ -3449,10 +3455,10 @@
         <v>104</v>
       </c>
       <c r="F82" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G82" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H82" t="s">
         <v>24</v>
@@ -3466,7 +3472,7 @@
         <v>123</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C83" t="s">
         <v>36</v>
@@ -3481,7 +3487,7 @@
         <v>118</v>
       </c>
       <c r="G83" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
@@ -3495,7 +3501,7 @@
         <v>123</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C84" t="s">
         <v>127</v>
@@ -3507,10 +3513,10 @@
         <v>104</v>
       </c>
       <c r="F84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G84" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H84" t="s">
         <v>24</v>
@@ -3524,7 +3530,7 @@
         <v>123</v>
       </c>
       <c r="B85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C85" t="s">
         <v>124</v>
@@ -3539,7 +3545,7 @@
         <v>135</v>
       </c>
       <c r="G85" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H85" t="s">
         <v>24</v>
@@ -3568,7 +3574,7 @@
         <v>135</v>
       </c>
       <c r="G86" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H86" t="s">
         <v>24</v>
@@ -3597,7 +3603,7 @@
         <v>118</v>
       </c>
       <c r="G87" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
@@ -3626,7 +3632,7 @@
         <v>118</v>
       </c>
       <c r="G88" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
@@ -3640,7 +3646,7 @@
         <v>136</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C89" t="s">
         <v>47</v>
@@ -3655,7 +3661,7 @@
         <v>118</v>
       </c>
       <c r="G89" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
@@ -3669,13 +3675,13 @@
         <v>136</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C90" t="s">
         <v>47</v>
       </c>
       <c r="D90" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E90" t="s">
         <v>38</v>
@@ -3684,7 +3690,7 @@
         <v>118</v>
       </c>
       <c r="G90" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
@@ -3698,7 +3704,7 @@
         <v>136</v>
       </c>
       <c r="B91" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C91" t="s">
         <v>47</v>
@@ -3713,7 +3719,7 @@
         <v>118</v>
       </c>
       <c r="G91" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
@@ -3727,7 +3733,7 @@
         <v>136</v>
       </c>
       <c r="B92" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C92" t="s">
         <v>36</v>
@@ -3742,7 +3748,7 @@
         <v>60</v>
       </c>
       <c r="G92" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
@@ -3756,7 +3762,7 @@
         <v>136</v>
       </c>
       <c r="B93" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C93" t="s">
         <v>13</v>
@@ -3771,7 +3777,7 @@
         <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
@@ -3785,7 +3791,7 @@
         <v>136</v>
       </c>
       <c r="B94" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C94" t="s">
         <v>36</v>
@@ -3800,7 +3806,7 @@
         <v>60</v>
       </c>
       <c r="G94" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
@@ -3814,7 +3820,7 @@
         <v>136</v>
       </c>
       <c r="B95" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C95" t="s">
         <v>13</v>
@@ -3829,7 +3835,7 @@
         <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
@@ -3858,7 +3864,7 @@
         <v>16</v>
       </c>
       <c r="G96" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
@@ -3887,7 +3893,7 @@
         <v>60</v>
       </c>
       <c r="G97" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
@@ -3916,7 +3922,7 @@
         <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
@@ -3945,7 +3951,7 @@
         <v>16</v>
       </c>
       <c r="G99" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
@@ -3974,7 +3980,7 @@
         <v>118</v>
       </c>
       <c r="G100" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
@@ -4003,7 +4009,7 @@
         <v>118</v>
       </c>
       <c r="G101" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
@@ -4032,7 +4038,7 @@
         <v>16</v>
       </c>
       <c r="G102" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
@@ -4061,7 +4067,7 @@
         <v>118</v>
       </c>
       <c r="G103" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
@@ -4075,7 +4081,7 @@
         <v>145</v>
       </c>
       <c r="B104" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C104" t="s">
         <v>47</v>
@@ -4090,7 +4096,7 @@
         <v>118</v>
       </c>
       <c r="G104" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H104" t="s">
         <v>18</v>
@@ -4104,7 +4110,7 @@
         <v>145</v>
       </c>
       <c r="B105" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C105" t="s">
         <v>36</v>
@@ -4119,7 +4125,7 @@
         <v>58</v>
       </c>
       <c r="G105" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
@@ -4133,7 +4139,7 @@
         <v>145</v>
       </c>
       <c r="B106" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C106" t="s">
         <v>13</v>
@@ -4148,7 +4154,7 @@
         <v>16</v>
       </c>
       <c r="G106" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
@@ -4162,7 +4168,7 @@
         <v>145</v>
       </c>
       <c r="B107" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C107" t="s">
         <v>146</v>
@@ -4174,7 +4180,7 @@
         <v>147</v>
       </c>
       <c r="F107" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G107" t="s">
         <v>148</v>
@@ -4191,7 +4197,7 @@
         <v>145</v>
       </c>
       <c r="B108" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C108" t="s">
         <v>47</v>
@@ -4206,7 +4212,7 @@
         <v>118</v>
       </c>
       <c r="G108" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
@@ -4220,7 +4226,7 @@
         <v>145</v>
       </c>
       <c r="B109" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C109" t="s">
         <v>36</v>
@@ -4235,7 +4241,7 @@
         <v>58</v>
       </c>
       <c r="G109" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
@@ -4249,7 +4255,7 @@
         <v>145</v>
       </c>
       <c r="B110" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C110" t="s">
         <v>13</v>
@@ -4264,7 +4270,7 @@
         <v>16</v>
       </c>
       <c r="G110" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H110" t="s">
         <v>18</v>
@@ -4278,7 +4284,7 @@
         <v>145</v>
       </c>
       <c r="B111" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C111" t="s">
         <v>146</v>
@@ -4290,7 +4296,7 @@
         <v>147</v>
       </c>
       <c r="F111" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G111" t="s">
         <v>148</v>
@@ -4307,7 +4313,7 @@
         <v>145</v>
       </c>
       <c r="B112" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C112" t="s">
         <v>47</v>
@@ -4322,7 +4328,7 @@
         <v>118</v>
       </c>
       <c r="G112" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
@@ -4336,7 +4342,7 @@
         <v>145</v>
       </c>
       <c r="B113" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C113" t="s">
         <v>13</v>
@@ -4351,7 +4357,7 @@
         <v>16</v>
       </c>
       <c r="G113" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
@@ -4365,7 +4371,7 @@
         <v>145</v>
       </c>
       <c r="B114" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C114" t="s">
         <v>146</v>
@@ -4377,7 +4383,7 @@
         <v>147</v>
       </c>
       <c r="F114" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G114" t="s">
         <v>148</v>
@@ -4394,7 +4400,7 @@
         <v>145</v>
       </c>
       <c r="B115" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C115" t="s">
         <v>47</v>
@@ -4409,7 +4415,7 @@
         <v>118</v>
       </c>
       <c r="G115" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
@@ -4423,7 +4429,7 @@
         <v>145</v>
       </c>
       <c r="B116" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C116" t="s">
         <v>36</v>
@@ -4438,7 +4444,7 @@
         <v>58</v>
       </c>
       <c r="G116" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
@@ -4452,7 +4458,7 @@
         <v>145</v>
       </c>
       <c r="B117" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C117" t="s">
         <v>13</v>
@@ -4467,7 +4473,7 @@
         <v>16</v>
       </c>
       <c r="G117" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
@@ -4481,7 +4487,7 @@
         <v>145</v>
       </c>
       <c r="B118" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C118" t="s">
         <v>146</v>
@@ -4493,7 +4499,7 @@
         <v>147</v>
       </c>
       <c r="F118" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G118" t="s">
         <v>148</v>
@@ -4525,7 +4531,7 @@
         <v>118</v>
       </c>
       <c r="G119" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
@@ -4554,7 +4560,7 @@
         <v>58</v>
       </c>
       <c r="G120" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
@@ -4583,7 +4589,7 @@
         <v>16</v>
       </c>
       <c r="G121" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
@@ -4609,10 +4615,10 @@
         <v>147</v>
       </c>
       <c r="F122" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G122" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H122" t="s">
         <v>24</v>
@@ -4641,7 +4647,7 @@
         <v>118</v>
       </c>
       <c r="G123" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
@@ -4670,7 +4676,7 @@
         <v>58</v>
       </c>
       <c r="G124" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
@@ -4699,7 +4705,7 @@
         <v>16</v>
       </c>
       <c r="G125" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
@@ -4716,7 +4722,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1e6bdb72-d120-4d1b-90d7-29f17b33ac0e}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d5756b5f-3811-4d3a-a440-b3ddb7be54da}">
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4780,7 +4786,7 @@
         <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
@@ -4809,7 +4815,7 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -4838,7 +4844,7 @@
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
@@ -4867,7 +4873,7 @@
         <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
@@ -4896,7 +4902,7 @@
         <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -4925,7 +4931,7 @@
         <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
@@ -4954,7 +4960,7 @@
         <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
@@ -4983,7 +4989,7 @@
         <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
@@ -5012,7 +5018,7 @@
         <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
@@ -5041,7 +5047,7 @@
         <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
@@ -5070,7 +5076,7 @@
         <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
@@ -5099,7 +5105,7 @@
         <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
@@ -5128,7 +5134,7 @@
         <v>24</v>
       </c>
       <c r="G14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
@@ -5145,8 +5151,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{dc245a11-a53c-4c26-a1a8-d94eef1f3e34}">
-  <dimension ref="A1:F30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0abb702e-7a04-4d7a-9945-7bfeda0c48e5}">
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -5205,13 +5211,13 @@
         <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F3" t="s">
         <v>24</v>
@@ -5222,19 +5228,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
@@ -5242,19 +5248,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
@@ -5262,16 +5268,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>184</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -5282,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -5291,7 +5297,7 @@
         <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="F7" t="s">
         <v>24</v>
@@ -5302,16 +5308,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
@@ -5322,19 +5328,19 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
         <v>183</v>
       </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>177</v>
-      </c>
       <c r="E9" t="s">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15">
@@ -5342,39 +5348,39 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15">
@@ -5382,13 +5388,13 @@
         <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -5402,13 +5408,13 @@
         <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -5422,13 +5428,13 @@
         <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C14" t="s">
         <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -5442,13 +5448,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
         <v>181</v>
-      </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>179</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -5459,16 +5465,16 @@
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
@@ -5482,19 +5488,19 @@
         <v>123</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15">
@@ -5502,19 +5508,19 @@
         <v>123</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15">
@@ -5522,19 +5528,19 @@
         <v>123</v>
       </c>
       <c r="B19" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15">
@@ -5542,19 +5548,19 @@
         <v>123</v>
       </c>
       <c r="B20" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
@@ -5562,39 +5568,39 @@
         <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B22" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15">
@@ -5602,13 +5608,13 @@
         <v>136</v>
       </c>
       <c r="B23" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C23" t="s">
         <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -5622,13 +5628,13 @@
         <v>136</v>
       </c>
       <c r="B24" t="s">
+        <v>191</v>
+      </c>
+      <c r="C24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" t="s">
         <v>181</v>
-      </c>
-      <c r="C24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" t="s">
-        <v>177</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -5642,13 +5648,13 @@
         <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
@@ -5659,16 +5665,16 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B26" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
@@ -5682,13 +5688,13 @@
         <v>145</v>
       </c>
       <c r="B27" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -5702,19 +5708,19 @@
         <v>145</v>
       </c>
       <c r="B28" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="C28" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
@@ -5722,19 +5728,19 @@
         <v>145</v>
       </c>
       <c r="B29" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>146</v>
       </c>
       <c r="D29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
@@ -5742,18 +5748,38 @@
         <v>145</v>
       </c>
       <c r="B30" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>176</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15">
+      <c r="A31" t="s">
+        <v>145</v>
+      </c>
+      <c r="B31" t="s">
+        <v>187</v>
+      </c>
+      <c r="C31" t="s">
         <v>47</v>
       </c>
-      <c r="D30" t="s">
-        <v>177</v>
-      </c>
-      <c r="E30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="D31" t="s">
+        <v>181</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="222">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -366,9 +366,24 @@
     <t>06.10.2026</t>
   </si>
   <si>
+    <t>3FA</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Wójcik Kamil</t>
+  </si>
+  <si>
     <t>29</t>
   </si>
   <si>
+    <t>Antoszewska Joanna</t>
+  </si>
+  <si>
     <t>Język angielski zawodowy</t>
   </si>
   <si>
@@ -447,6 +462,18 @@
     <t>33</t>
   </si>
   <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>spotkanie COVE Polska - bez uczniów</t>
+  </si>
+  <si>
     <t>1FC</t>
   </si>
   <si>
@@ -456,12 +483,12 @@
     <t>1FA|gr2</t>
   </si>
   <si>
-    <t>2TFA</t>
-  </si>
-  <si>
     <t>1TH|gr1</t>
   </si>
   <si>
+    <t>3TFB|gr2</t>
+  </si>
+  <si>
     <t>1K</t>
   </si>
   <si>
@@ -486,12 +513,6 @@
     <t>1TH|gr2</t>
   </si>
   <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>3TFB|gr2</t>
-  </si>
-  <si>
     <t>1B|gr1</t>
   </si>
   <si>
@@ -606,9 +627,6 @@
     <t>boisko - dziedziniec wejściowy/boisko</t>
   </si>
   <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
     <t>11:20-11:25</t>
   </si>
   <si>
@@ -648,6 +666,12 @@
     <t>12:10-12:25</t>
   </si>
   <si>
+    <t>bramka wejściowa</t>
+  </si>
+  <si>
+    <t>Cieśla Marcin</t>
+  </si>
+  <si>
     <t>13:10-13:15</t>
   </si>
   <si>
@@ -661,9 +685,6 @@
   </si>
   <si>
     <t>piętro_3</t>
-  </si>
-  <si>
-    <t>bramka wejściowa</t>
   </si>
   <si>
     <t>07:55-08:00</t>
@@ -1116,7 +1137,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c718b666-1f71-4e13-9ab1-0f2f85d6e7d3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8c82d4d3-8525-4a94-90a5-b9ab132dfbe0}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1137,8 +1158,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{dba2c121-fe82-4d94-9917-b54ce3f82765}">
-  <dimension ref="A1:I138"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{46b0994c-5577-4276-b01c-2fac70620afc}">
+  <dimension ref="A1:I147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1148,7 +1169,7 @@
     <col min="5" max="5" width="54.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="27.8571428571429" customWidth="1"/>
-    <col min="8" max="8" width="9.57142857142857" customWidth="1"/>
+    <col min="8" max="8" width="33.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2697,22 +2718,22 @@
         <v>46</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="E54" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="F54" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G54" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="H54" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I54" t="s">
         <v>35</v>
@@ -2723,7 +2744,7 @@
         <v>113</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C55" t="s">
         <v>13</v>
@@ -2735,10 +2756,10 @@
         <v>38</v>
       </c>
       <c r="F55" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="G55" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
@@ -2752,28 +2773,28 @@
         <v>113</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="E56" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F56" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="G56" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="H56" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
@@ -2781,28 +2802,28 @@
         <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C57" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="F57" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G57" t="s">
         <v>93</v>
       </c>
       <c r="H57" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
@@ -2810,25 +2831,25 @@
         <v>113</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C58" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D58" t="s">
+        <v>114</v>
+      </c>
+      <c r="E58" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" t="s">
         <v>116</v>
       </c>
-      <c r="E58" t="s">
-        <v>117</v>
-      </c>
-      <c r="F58" t="s">
-        <v>118</v>
-      </c>
       <c r="G58" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H58" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I58" t="s">
         <v>35</v>
@@ -2839,7 +2860,7 @@
         <v>113</v>
       </c>
       <c r="B59" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C59" t="s">
         <v>13</v>
@@ -2848,7 +2869,7 @@
         <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
@@ -2868,28 +2889,28 @@
         <v>113</v>
       </c>
       <c r="B60" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C60" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E60" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="F60" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="G60" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I60" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
@@ -2897,22 +2918,22 @@
         <v>113</v>
       </c>
       <c r="B61" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C61" t="s">
         <v>36</v>
       </c>
       <c r="D61" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E61" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F61" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="G61" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
@@ -2926,7 +2947,7 @@
         <v>113</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C62" t="s">
         <v>13</v>
@@ -2935,7 +2956,7 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
@@ -2955,28 +2976,28 @@
         <v>113</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D63" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E63" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F63" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G63" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I63" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
@@ -2984,28 +3005,28 @@
         <v>113</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C64" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D64" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E64" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F64" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="G64" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
@@ -3013,22 +3034,22 @@
         <v>113</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E65" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="F65" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
@@ -3042,22 +3063,22 @@
         <v>113</v>
       </c>
       <c r="B66" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C66" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>125</v>
+        <v>14</v>
       </c>
       <c r="E66" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="F66" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
@@ -3071,25 +3092,25 @@
         <v>113</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D67" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="E67" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F67" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="G67" t="s">
         <v>89</v>
       </c>
       <c r="H67" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
@@ -3097,112 +3118,112 @@
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D68" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="E68" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F68" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G68" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="H68" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="C69" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="D69" t="s">
         <v>128</v>
       </c>
       <c r="E69" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="F69" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="G69" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H69" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="C70" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E70" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="F70" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="G70" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="H70" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B71" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="C71" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="D71" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="E71" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="F71" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="G71" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s">
         <v>24</v>
@@ -3213,28 +3234,28 @@
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="C72" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D72" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E72" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F72" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="G72" t="s">
         <v>87</v>
       </c>
       <c r="H72" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I72" t="s">
         <v>19</v>
@@ -3242,28 +3263,28 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B73" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="D73" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E73" t="s">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="F73" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="G73" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I73" t="s">
         <v>19</v>
@@ -3271,22 +3292,22 @@
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="E74" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F74" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="G74" t="s">
         <v>87</v>
@@ -3300,28 +3321,28 @@
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B75" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="D75" t="s">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="E75" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="F75" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="G75" t="s">
         <v>87</v>
       </c>
       <c r="H75" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I75" t="s">
         <v>19</v>
@@ -3329,22 +3350,22 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B76" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C76" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="D76" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E76" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="F76" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="G76" t="s">
         <v>87</v>
@@ -3358,22 +3379,22 @@
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B77" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D77" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="E77" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="F77" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="G77" t="s">
         <v>87</v>
@@ -3387,28 +3408,28 @@
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="E78" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F78" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="G78" t="s">
         <v>87</v>
       </c>
       <c r="H78" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
@@ -3416,22 +3437,22 @@
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B79" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C79" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="D79" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E79" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="F79" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="G79" t="s">
         <v>87</v>
@@ -3445,22 +3466,22 @@
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B80" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C80" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="D80" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E80" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="F80" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G80" t="s">
         <v>87</v>
@@ -3474,28 +3495,28 @@
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C81" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D81" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="E81" t="s">
         <v>38</v>
       </c>
       <c r="F81" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="G81" t="s">
         <v>87</v>
       </c>
       <c r="H81" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I81" t="s">
         <v>19</v>
@@ -3503,28 +3524,28 @@
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C82" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="D82" t="s">
         <v>139</v>
       </c>
       <c r="E82" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="F82" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="G82" t="s">
         <v>87</v>
       </c>
       <c r="H82" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I82" t="s">
         <v>19</v>
@@ -3532,28 +3553,28 @@
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C83" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="D83" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="E83" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="F83" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="G83" t="s">
         <v>87</v>
       </c>
       <c r="H83" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I83" t="s">
         <v>19</v>
@@ -3561,28 +3582,28 @@
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B84" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C84" t="s">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="D84" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="E84" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="F84" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="G84" t="s">
         <v>87</v>
       </c>
       <c r="H84" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I84" t="s">
         <v>19</v>
@@ -3590,16 +3611,16 @@
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C85" t="s">
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E85" t="s">
         <v>27</v>
@@ -3619,19 +3640,19 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C86" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D86" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E86" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F86" t="s">
         <v>16</v>
@@ -3648,22 +3669,22 @@
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C87" t="s">
         <v>50</v>
       </c>
       <c r="D87" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E87" t="s">
         <v>38</v>
       </c>
       <c r="F87" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G87" t="s">
         <v>87</v>
@@ -3677,22 +3698,22 @@
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C88" t="s">
         <v>47</v>
       </c>
       <c r="D88" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E88" t="s">
         <v>38</v>
       </c>
       <c r="F88" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G88" t="s">
         <v>87</v>
@@ -3706,22 +3727,22 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B89" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C89" t="s">
         <v>36</v>
       </c>
       <c r="D89" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="E89" t="s">
         <v>38</v>
       </c>
       <c r="F89" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G89" t="s">
         <v>87</v>
@@ -3735,16 +3756,16 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D90" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="E90" t="s">
         <v>104</v>
@@ -3764,28 +3785,28 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B91" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="D91" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="E91" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="F91" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="G91" t="s">
         <v>87</v>
       </c>
       <c r="H91" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="I91" t="s">
         <v>19</v>
@@ -3793,22 +3814,22 @@
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B92" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C92" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E92" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F92" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="G92" t="s">
         <v>87</v>
@@ -3822,28 +3843,28 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B93" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C93" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="D93" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="E93" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="F93" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="G93" t="s">
         <v>87</v>
       </c>
       <c r="H93" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
@@ -3851,22 +3872,22 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="D94" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="E94" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="F94" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="G94" t="s">
         <v>87</v>
@@ -3880,28 +3901,28 @@
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B95" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D95" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E95" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F95" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="G95" t="s">
         <v>87</v>
       </c>
       <c r="H95" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I95" t="s">
         <v>19</v>
@@ -3909,28 +3930,28 @@
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B96" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C96" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D96" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="E96" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F96" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="G96" t="s">
         <v>87</v>
       </c>
       <c r="H96" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I96" t="s">
         <v>19</v>
@@ -3938,22 +3959,22 @@
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B97" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C97" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D97" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E97" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="F97" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="G97" t="s">
         <v>87</v>
@@ -3967,28 +3988,28 @@
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B98" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C98" t="s">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="D98" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="E98" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="F98" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="G98" t="s">
         <v>87</v>
       </c>
       <c r="H98" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="I98" t="s">
         <v>19</v>
@@ -3996,22 +4017,22 @@
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B99" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C99" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E99" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="F99" t="s">
-        <v>148</v>
+        <v>28</v>
       </c>
       <c r="G99" t="s">
         <v>87</v>
@@ -4025,28 +4046,28 @@
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B100" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C100" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D100" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E100" t="s">
         <v>38</v>
       </c>
       <c r="F100" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="G100" t="s">
         <v>87</v>
       </c>
       <c r="H100" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
@@ -4054,22 +4075,22 @@
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B101" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C101" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D101" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="E101" t="s">
         <v>38</v>
       </c>
       <c r="F101" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G101" t="s">
         <v>87</v>
@@ -4083,28 +4104,28 @@
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B102" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C102" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="D102" t="s">
-        <v>151</v>
+        <v>103</v>
       </c>
       <c r="E102" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="F102" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="G102" t="s">
         <v>87</v>
       </c>
       <c r="H102" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I102" t="s">
         <v>19</v>
@@ -4112,28 +4133,28 @@
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
+        <v>131</v>
+      </c>
+      <c r="B103" t="s">
+        <v>82</v>
+      </c>
+      <c r="C103" t="s">
+        <v>146</v>
+      </c>
+      <c r="D103" t="s">
+        <v>154</v>
+      </c>
+      <c r="E103" t="s">
+        <v>85</v>
+      </c>
+      <c r="F103" t="s">
+        <v>148</v>
+      </c>
+      <c r="G103" t="s">
+        <v>87</v>
+      </c>
+      <c r="H103" t="s">
         <v>149</v>
-      </c>
-      <c r="B103" t="s">
-        <v>80</v>
-      </c>
-      <c r="C103" t="s">
-        <v>47</v>
-      </c>
-      <c r="D103" t="s">
-        <v>73</v>
-      </c>
-      <c r="E103" t="s">
-        <v>38</v>
-      </c>
-      <c r="F103" t="s">
-        <v>133</v>
-      </c>
-      <c r="G103" t="s">
-        <v>87</v>
-      </c>
-      <c r="H103" t="s">
-        <v>18</v>
       </c>
       <c r="I103" t="s">
         <v>19</v>
@@ -4141,28 +4162,28 @@
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B104" t="s">
         <v>82</v>
       </c>
       <c r="C104" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E104" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F104" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="G104" t="s">
         <v>87</v>
       </c>
       <c r="H104" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I104" t="s">
         <v>19</v>
@@ -4170,28 +4191,28 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B105" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C105" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E105" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F105" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="G105" t="s">
         <v>87</v>
       </c>
       <c r="H105" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I105" t="s">
         <v>19</v>
@@ -4199,28 +4220,28 @@
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B106" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C106" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="D106" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E106" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="F106" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="G106" t="s">
         <v>87</v>
       </c>
       <c r="H106" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I106" t="s">
         <v>19</v>
@@ -4228,28 +4249,28 @@
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B107" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C107" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E107" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F107" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="G107" t="s">
         <v>87</v>
       </c>
       <c r="H107" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I107" t="s">
         <v>19</v>
@@ -4257,28 +4278,28 @@
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B108" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C108" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="D108" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E108" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="F108" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="G108" t="s">
         <v>87</v>
       </c>
       <c r="H108" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I108" t="s">
         <v>19</v>
@@ -4286,22 +4307,22 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B109" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="C109" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D109" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="E109" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="F109" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="G109" t="s">
         <v>87</v>
@@ -4315,22 +4336,22 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B110" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="C110" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D110" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E110" t="s">
         <v>38</v>
       </c>
       <c r="F110" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="G110" t="s">
         <v>87</v>
@@ -4344,22 +4365,22 @@
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B111" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="C111" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D111" t="s">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="E111" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="F111" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="G111" t="s">
         <v>87</v>
@@ -4373,22 +4394,22 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C112" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D112" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="E112" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="F112" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="G112" t="s">
         <v>87</v>
@@ -4402,22 +4423,22 @@
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B113" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C113" t="s">
         <v>47</v>
       </c>
       <c r="D113" t="s">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="E113" t="s">
         <v>38</v>
       </c>
       <c r="F113" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G113" t="s">
         <v>87</v>
@@ -4431,22 +4452,22 @@
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B114" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C114" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D114" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="E114" t="s">
         <v>38</v>
       </c>
       <c r="F114" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="G114" t="s">
         <v>87</v>
@@ -4460,19 +4481,19 @@
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B115" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C115" t="s">
         <v>13</v>
       </c>
       <c r="D115" t="s">
-        <v>14</v>
+        <v>156</v>
       </c>
       <c r="E115" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="F115" t="s">
         <v>16</v>
@@ -4489,22 +4510,22 @@
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B116" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="C116" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D116" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E116" t="s">
         <v>38</v>
       </c>
       <c r="F116" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="G116" t="s">
         <v>87</v>
@@ -4518,22 +4539,22 @@
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B117" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C117" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D117" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="E117" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="F117" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="G117" t="s">
         <v>87</v>
@@ -4547,22 +4568,22 @@
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B118" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C118" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D118" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="E118" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="F118" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G118" t="s">
         <v>87</v>
@@ -4576,22 +4597,22 @@
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B119" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="C119" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D119" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="E119" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="F119" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="G119" t="s">
         <v>87</v>
@@ -4605,28 +4626,28 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B120" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="C120" t="s">
-        <v>159</v>
+        <v>13</v>
       </c>
       <c r="D120" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E120" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="F120" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="G120" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="H120" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I120" t="s">
         <v>19</v>
@@ -4634,22 +4655,22 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B121" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D121" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="E121" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="F121" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="G121" t="s">
         <v>87</v>
@@ -4663,22 +4684,22 @@
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B122" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C122" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D122" t="s">
-        <v>155</v>
+        <v>107</v>
       </c>
       <c r="E122" t="s">
         <v>38</v>
       </c>
       <c r="F122" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="G122" t="s">
         <v>87</v>
@@ -4692,22 +4713,22 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B123" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C123" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D123" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E123" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="F123" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="G123" t="s">
         <v>87</v>
@@ -4721,28 +4742,28 @@
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B124" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C124" t="s">
-        <v>159</v>
+        <v>13</v>
       </c>
       <c r="D124" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E124" t="s">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="F124" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="G124" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="H124" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I124" t="s">
         <v>19</v>
@@ -4750,22 +4771,22 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B125" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C125" t="s">
         <v>47</v>
       </c>
       <c r="D125" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="E125" t="s">
         <v>38</v>
       </c>
       <c r="F125" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G125" t="s">
         <v>87</v>
@@ -4779,22 +4800,22 @@
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B126" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C126" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D126" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="E126" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="F126" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="G126" t="s">
         <v>87</v>
@@ -4808,28 +4829,28 @@
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B127" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C127" t="s">
-        <v>159</v>
+        <v>36</v>
       </c>
       <c r="D127" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="E127" t="s">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="F127" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="G127" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="H127" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I127" t="s">
         <v>19</v>
@@ -4837,22 +4858,22 @@
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B128" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C128" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D128" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="E128" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="F128" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="G128" t="s">
         <v>87</v>
@@ -4866,28 +4887,28 @@
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B129" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C129" t="s">
-        <v>36</v>
+        <v>166</v>
       </c>
       <c r="D129" t="s">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="E129" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="F129" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G129" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="H129" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I129" t="s">
         <v>19</v>
@@ -4895,22 +4916,22 @@
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B130" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C130" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D130" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="E130" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="F130" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="G130" t="s">
         <v>87</v>
@@ -4924,28 +4945,28 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B131" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C131" t="s">
-        <v>159</v>
+        <v>36</v>
       </c>
       <c r="D131" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E131" t="s">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="F131" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="G131" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="H131" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I131" t="s">
         <v>19</v>
@@ -4953,22 +4974,22 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B132" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C132" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D132" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="E132" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="F132" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="G132" t="s">
         <v>87</v>
@@ -4982,28 +5003,28 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B133" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C133" t="s">
-        <v>36</v>
+        <v>166</v>
       </c>
       <c r="D133" t="s">
-        <v>156</v>
+        <v>51</v>
       </c>
       <c r="E133" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="F133" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G133" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="H133" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I133" t="s">
         <v>19</v>
@@ -5011,22 +5032,22 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B134" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C134" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D134" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E134" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="F134" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="G134" t="s">
         <v>87</v>
@@ -5040,28 +5061,28 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B135" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C135" t="s">
-        <v>159</v>
+        <v>13</v>
       </c>
       <c r="D135" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="E135" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="F135" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="G135" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H135" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I135" t="s">
         <v>19</v>
@@ -5069,28 +5090,28 @@
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B136" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C136" t="s">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="D136" t="s">
-        <v>48</v>
+        <v>169</v>
       </c>
       <c r="E136" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="F136" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="G136" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="H136" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I136" t="s">
         <v>19</v>
@@ -5098,22 +5119,22 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B137" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C137" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D137" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E137" t="s">
         <v>38</v>
       </c>
       <c r="F137" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="G137" t="s">
         <v>87</v>
@@ -5127,30 +5148,291 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B138" t="s">
+        <v>90</v>
+      </c>
+      <c r="C138" t="s">
+        <v>36</v>
+      </c>
+      <c r="D138" t="s">
+        <v>162</v>
+      </c>
+      <c r="E138" t="s">
+        <v>38</v>
+      </c>
+      <c r="F138" t="s">
+        <v>58</v>
+      </c>
+      <c r="G138" t="s">
+        <v>87</v>
+      </c>
+      <c r="H138" t="s">
+        <v>18</v>
+      </c>
+      <c r="I138" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="15">
+      <c r="A139" t="s">
+        <v>164</v>
+      </c>
+      <c r="B139" t="s">
+        <v>90</v>
+      </c>
+      <c r="C139" t="s">
+        <v>13</v>
+      </c>
+      <c r="D139" t="s">
+        <v>129</v>
+      </c>
+      <c r="E139" t="s">
+        <v>115</v>
+      </c>
+      <c r="F139" t="s">
+        <v>16</v>
+      </c>
+      <c r="G139" t="s">
+        <v>87</v>
+      </c>
+      <c r="H139" t="s">
+        <v>18</v>
+      </c>
+      <c r="I139" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="15">
+      <c r="A140" t="s">
+        <v>164</v>
+      </c>
+      <c r="B140" t="s">
+        <v>90</v>
+      </c>
+      <c r="C140" t="s">
+        <v>166</v>
+      </c>
+      <c r="D140" t="s">
+        <v>169</v>
+      </c>
+      <c r="E140" t="s">
+        <v>167</v>
+      </c>
+      <c r="F140" t="s">
+        <v>76</v>
+      </c>
+      <c r="G140" t="s">
+        <v>168</v>
+      </c>
+      <c r="H140" t="s">
+        <v>24</v>
+      </c>
+      <c r="I140" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="15">
+      <c r="A141" t="s">
+        <v>164</v>
+      </c>
+      <c r="B141" t="s">
+        <v>96</v>
+      </c>
+      <c r="C141" t="s">
+        <v>47</v>
+      </c>
+      <c r="D141" t="s">
+        <v>160</v>
+      </c>
+      <c r="E141" t="s">
+        <v>38</v>
+      </c>
+      <c r="F141" t="s">
+        <v>138</v>
+      </c>
+      <c r="G141" t="s">
+        <v>87</v>
+      </c>
+      <c r="H141" t="s">
+        <v>18</v>
+      </c>
+      <c r="I141" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="15">
+      <c r="A142" t="s">
+        <v>164</v>
+      </c>
+      <c r="B142" t="s">
+        <v>96</v>
+      </c>
+      <c r="C142" t="s">
+        <v>36</v>
+      </c>
+      <c r="D142" t="s">
+        <v>163</v>
+      </c>
+      <c r="E142" t="s">
+        <v>38</v>
+      </c>
+      <c r="F142" t="s">
+        <v>58</v>
+      </c>
+      <c r="G142" t="s">
+        <v>87</v>
+      </c>
+      <c r="H142" t="s">
+        <v>18</v>
+      </c>
+      <c r="I142" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="15">
+      <c r="A143" t="s">
+        <v>164</v>
+      </c>
+      <c r="B143" t="s">
+        <v>96</v>
+      </c>
+      <c r="C143" t="s">
+        <v>13</v>
+      </c>
+      <c r="D143" t="s">
+        <v>156</v>
+      </c>
+      <c r="E143" t="s">
+        <v>115</v>
+      </c>
+      <c r="F143" t="s">
+        <v>16</v>
+      </c>
+      <c r="G143" t="s">
+        <v>87</v>
+      </c>
+      <c r="H143" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="15">
+      <c r="A144" t="s">
+        <v>164</v>
+      </c>
+      <c r="B144" t="s">
+        <v>96</v>
+      </c>
+      <c r="C144" t="s">
+        <v>166</v>
+      </c>
+      <c r="D144" t="s">
+        <v>107</v>
+      </c>
+      <c r="E144" t="s">
+        <v>167</v>
+      </c>
+      <c r="F144" t="s">
+        <v>76</v>
+      </c>
+      <c r="G144" t="s">
+        <v>89</v>
+      </c>
+      <c r="H144" t="s">
+        <v>24</v>
+      </c>
+      <c r="I144" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="15">
+      <c r="A145" t="s">
+        <v>164</v>
+      </c>
+      <c r="B145" t="s">
         <v>106</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C145" t="s">
+        <v>47</v>
+      </c>
+      <c r="D145" t="s">
+        <v>48</v>
+      </c>
+      <c r="E145" t="s">
+        <v>38</v>
+      </c>
+      <c r="F145" t="s">
+        <v>138</v>
+      </c>
+      <c r="G145" t="s">
+        <v>87</v>
+      </c>
+      <c r="H145" t="s">
+        <v>18</v>
+      </c>
+      <c r="I145" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="15">
+      <c r="A146" t="s">
+        <v>164</v>
+      </c>
+      <c r="B146" t="s">
+        <v>106</v>
+      </c>
+      <c r="C146" t="s">
+        <v>36</v>
+      </c>
+      <c r="D146" t="s">
+        <v>163</v>
+      </c>
+      <c r="E146" t="s">
+        <v>38</v>
+      </c>
+      <c r="F146" t="s">
+        <v>58</v>
+      </c>
+      <c r="G146" t="s">
+        <v>87</v>
+      </c>
+      <c r="H146" t="s">
+        <v>18</v>
+      </c>
+      <c r="I146" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="15">
+      <c r="A147" t="s">
+        <v>164</v>
+      </c>
+      <c r="B147" t="s">
+        <v>106</v>
+      </c>
+      <c r="C147" t="s">
         <v>13</v>
       </c>
-      <c r="D138" t="s">
-        <v>147</v>
-      </c>
-      <c r="E138" t="s">
-        <v>154</v>
-      </c>
-      <c r="F138" t="s">
+      <c r="D147" t="s">
+        <v>156</v>
+      </c>
+      <c r="E147" t="s">
+        <v>115</v>
+      </c>
+      <c r="F147" t="s">
         <v>16</v>
       </c>
-      <c r="G138" t="s">
-        <v>87</v>
-      </c>
-      <c r="H138" t="s">
-        <v>18</v>
-      </c>
-      <c r="I138" t="s">
+      <c r="G147" t="s">
+        <v>87</v>
+      </c>
+      <c r="H147" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5162,7 +5444,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4575bc9f-3dc6-4748-a1ad-be5b5b9fdc77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{878ba8c3-4d36-4042-8cb8-a6913cd92a77}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5182,16 +5464,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -5211,16 +5493,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s">
         <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
@@ -5240,13 +5522,13 @@
         <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C3" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E3" t="s">
         <v>109</v>
@@ -5255,7 +5537,7 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -5269,16 +5551,16 @@
         <v>113</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
         <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -5298,16 +5580,16 @@
         <v>113</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C5" t="s">
         <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F5" t="s">
         <v>24</v>
@@ -5327,16 +5609,16 @@
         <v>113</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C6" t="s">
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -5356,16 +5638,16 @@
         <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
         <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F7" t="s">
         <v>24</v>
@@ -5385,16 +5667,16 @@
         <v>113</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
@@ -5411,25 +5693,25 @@
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D9" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E9" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -5440,19 +5722,19 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E10" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="F10" t="s">
         <v>24</v>
@@ -5469,19 +5751,19 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -5498,16 +5780,16 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E12" t="s">
         <v>109</v>
@@ -5516,7 +5798,7 @@
         <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
@@ -5527,19 +5809,19 @@
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E13" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F13" t="s">
         <v>24</v>
@@ -5556,19 +5838,19 @@
     </row>
     <row r="14" spans="1:9" ht="15">
       <c r="A14" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F14" t="s">
         <v>24</v>
@@ -5585,19 +5867,19 @@
     </row>
     <row r="15" spans="1:9" ht="15">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B15" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F15" t="s">
         <v>24</v>
@@ -5614,19 +5896,19 @@
     </row>
     <row r="16" spans="1:9" ht="15">
       <c r="A16" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B16" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F16" t="s">
         <v>24</v>
@@ -5643,19 +5925,19 @@
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B17" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E17" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F17" t="s">
         <v>24</v>
@@ -5678,8 +5960,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{74f372fa-0145-4a88-96ab-45fec92c5fc9}">
-  <dimension ref="A1:F33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{eb070e0f-1e6f-4ef1-9e39-e34cf7bf0514}">
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -5695,13 +5977,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -5715,16 +5997,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
@@ -5735,16 +6017,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E3" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="F3" t="s">
         <v>24</v>
@@ -5755,16 +6037,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -5775,16 +6057,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E5" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -5795,16 +6077,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C6" t="s">
         <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -5815,13 +6097,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E7" t="s">
         <v>105</v>
@@ -5835,13 +6117,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E8" t="s">
         <v>34</v>
@@ -5855,13 +6137,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C9" t="s">
         <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E9" t="s">
         <v>47</v>
@@ -5875,16 +6157,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E10" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -5895,16 +6177,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E11" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -5915,19 +6197,19 @@
         <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>215</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15">
@@ -5935,16 +6217,16 @@
         <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E13" t="s">
-        <v>199</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -5955,16 +6237,16 @@
         <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E14" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -5975,16 +6257,16 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C15" t="s">
         <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E15" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -5995,16 +6277,16 @@
         <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -6012,56 +6294,56 @@
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B19" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -6072,56 +6354,56 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B22" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -6132,16 +6414,16 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C23" t="s">
         <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -6152,16 +6434,16 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B24" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -6172,16 +6454,16 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
@@ -6192,36 +6474,36 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="D26" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -6232,16 +6514,16 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -6252,16 +6534,16 @@
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C29" t="s">
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
@@ -6272,16 +6554,16 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B30" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
@@ -6292,36 +6574,36 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C31" t="s">
-        <v>159</v>
+        <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B32" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
@@ -6332,21 +6614,61 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B33" t="s">
+        <v>213</v>
+      </c>
+      <c r="C33" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" t="s">
+        <v>214</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15">
+      <c r="A34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>200</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15">
+      <c r="A35" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" t="s">
         <v>204</v>
       </c>
-      <c r="C33" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" t="s">
-        <v>198</v>
-      </c>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="251">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -432,58 +432,106 @@
     <t>1TFH|gr2</t>
   </si>
   <si>
+    <t>p. Najwer, informatyka za lekcję 1</t>
+  </si>
+  <si>
     <t>Misiąg Anna</t>
   </si>
   <si>
     <t>2TFB</t>
   </si>
   <si>
+    <t>p. Zaleska, historia za lekcję 8</t>
+  </si>
+  <si>
+    <t>2WA|gr1</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>1CB</t>
+  </si>
+  <si>
+    <t>Mucha Anna</t>
+  </si>
+  <si>
+    <t>1CB|gr2</t>
+  </si>
+  <si>
+    <t>p. Kończyńska, technologie produkcji cukierniczej za lekcję 9</t>
+  </si>
+  <si>
+    <t>1CB|gr1</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Przeniesiona</t>
+  </si>
+  <si>
+    <t>Erasmus+ / p. Kończyńska, technologie produkcji cukierniczej za lekcję 9</t>
+  </si>
+  <si>
+    <t>Staliś Donata</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
+    <t>spotkanie COVE Polska - bez uczniów</t>
+  </si>
+  <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>p. Ulanowska, j. polski za lekcję 8</t>
+  </si>
+  <si>
+    <t>Cieśla Marcin</t>
+  </si>
+  <si>
+    <t>1K|gr2</t>
+  </si>
+  <si>
+    <t>sg5</t>
+  </si>
+  <si>
+    <t>1FA|gr2</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>1TH|gr1</t>
+  </si>
+  <si>
     <t>05</t>
   </si>
   <si>
-    <t>2WA|gr1</t>
-  </si>
-  <si>
-    <t>2S</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - kompetencje zawodowe</t>
-  </si>
-  <si>
-    <t>1CB</t>
-  </si>
-  <si>
-    <t>1CB|gr2</t>
-  </si>
-  <si>
-    <t>1CB|gr1</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>spotkanie COVE Polska - bez uczniów</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>1K|gr2</t>
-  </si>
-  <si>
-    <t>1FA|gr2</t>
-  </si>
-  <si>
-    <t>1TH|gr1</t>
+    <t>Erasmus+ / p. Filipek, j. polski za lekcję 8</t>
+  </si>
+  <si>
+    <t>Zaleska Magdalena</t>
   </si>
   <si>
     <t>3TFB|gr2</t>
@@ -495,24 +543,51 @@
     <t>1FA</t>
   </si>
   <si>
+    <t>Doradztwo zawodowe</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
+  </si>
+  <si>
+    <t>W ramach pensum</t>
+  </si>
+  <si>
     <t>42</t>
   </si>
   <si>
     <t>08.10.2026</t>
   </si>
   <si>
+    <t>1FC|gr2</t>
+  </si>
+  <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
     <t>1K|gr1</t>
   </si>
   <si>
     <t>1FC|gr1</t>
   </si>
   <si>
+    <t>Erasmus+ / p. Nestoruk, wychowanie fizyczne za lekcję 2</t>
+  </si>
+  <si>
+    <t>p. Filusz, matematyka za lekcję 9</t>
+  </si>
+  <si>
     <t>1S|gr2</t>
   </si>
   <si>
     <t>1TH|gr2</t>
   </si>
   <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
     <t>1B|gr1</t>
   </si>
   <si>
@@ -522,6 +597,18 @@
     <t>Rozwój kompetencji zawodowych - fryzjerstwo wellness</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Małecka Barbara</t>
+  </si>
+  <si>
+    <t>5TH|DZ</t>
+  </si>
+  <si>
+    <t>sg2</t>
+  </si>
+  <si>
     <t>Piątek-Pawłowska Bożena</t>
   </si>
   <si>
@@ -531,6 +618,12 @@
     <t>Okienko dla uczniów</t>
   </si>
   <si>
+    <t>Erasmus+ / p. Małecka biologia za lekcję 7</t>
+  </si>
+  <si>
+    <t>Godzina do zliczenia</t>
+  </si>
+  <si>
     <t>3FB</t>
   </si>
   <si>
@@ -630,24 +723,15 @@
     <t>11:20-11:25</t>
   </si>
   <si>
-    <t>Zaleska Magdalena</t>
-  </si>
-  <si>
     <t>14:00-14:05</t>
   </si>
   <si>
     <t>parter</t>
   </si>
   <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
     <t>piętro_2</t>
   </si>
   <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
     <t>14:50-14:55</t>
   </si>
   <si>
@@ -657,9 +741,6 @@
     <t>16:30-16:35</t>
   </si>
   <si>
-    <t>Kruk Marcin</t>
-  </si>
-  <si>
     <t>Bujanowska Iwona</t>
   </si>
   <si>
@@ -669,9 +750,6 @@
     <t>bramka wejściowa</t>
   </si>
   <si>
-    <t>Cieśla Marcin</t>
-  </si>
-  <si>
     <t>13:10-13:15</t>
   </si>
   <si>
@@ -685,6 +763,15 @@
   </si>
   <si>
     <t>piętro_3</t>
+  </si>
+  <si>
+    <t>Taszycka Magdalena</t>
+  </si>
+  <si>
+    <t>Jaworska Edyta</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
   </si>
   <si>
     <t>07:55-08:00</t>
@@ -1137,7 +1224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8c82d4d3-8525-4a94-90a5-b9ab132dfbe0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{666deb5b-5827-4626-b6ff-ea87ea166c1d}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1158,19 +1245,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{46b0994c-5577-4276-b01c-2fac70620afc}">
-  <dimension ref="A1:I147"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b8567b33-96dd-4b22-b9e8-96324e20b4b9}">
+  <dimension ref="A1:I159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="28.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="11.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="54.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="51.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="27.8571428571429" customWidth="1"/>
-    <col min="8" max="8" width="33.8571428571429" customWidth="1"/>
-    <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="64.1428571428571" customWidth="1"/>
+    <col min="9" max="9" width="19.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="56.25" customHeight="1">
@@ -3310,7 +3397,7 @@
         <v>28</v>
       </c>
       <c r="G74" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H74" t="s">
         <v>24</v>
@@ -3339,7 +3426,7 @@
         <v>95</v>
       </c>
       <c r="G75" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H75" t="s">
         <v>24</v>
@@ -3371,7 +3458,7 @@
         <v>87</v>
       </c>
       <c r="H76" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="I76" t="s">
         <v>19</v>
@@ -3385,7 +3472,7 @@
         <v>29</v>
       </c>
       <c r="C77" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D77" t="s">
         <v>51</v>
@@ -3397,7 +3484,7 @@
         <v>92</v>
       </c>
       <c r="G77" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H77" t="s">
         <v>24</v>
@@ -3417,22 +3504,22 @@
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E78" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="F78" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="G78" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H78" t="s">
         <v>24</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
@@ -3455,7 +3542,7 @@
         <v>95</v>
       </c>
       <c r="G79" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H79" t="s">
         <v>24</v>
@@ -3475,7 +3562,7 @@
         <v>50</v>
       </c>
       <c r="D80" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E80" t="s">
         <v>38</v>
@@ -3487,7 +3574,7 @@
         <v>87</v>
       </c>
       <c r="H80" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="I80" t="s">
         <v>19</v>
@@ -3507,19 +3594,19 @@
         <v>37</v>
       </c>
       <c r="E81" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F81" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="G81" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
@@ -3530,25 +3617,25 @@
         <v>46</v>
       </c>
       <c r="C82" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D82" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E82" t="s">
         <v>104</v>
       </c>
       <c r="F82" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="G82" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H82" t="s">
         <v>24</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
@@ -3562,22 +3649,22 @@
         <v>132</v>
       </c>
       <c r="D83" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E83" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F83" t="s">
         <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="H83" t="s">
         <v>24</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
@@ -3597,16 +3684,16 @@
         <v>38</v>
       </c>
       <c r="F84" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="G84" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
@@ -3620,22 +3707,22 @@
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E85" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
       </c>
       <c r="G85" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H85" t="s">
         <v>24</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
@@ -3649,22 +3736,22 @@
         <v>132</v>
       </c>
       <c r="D86" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E86" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F86" t="s">
         <v>16</v>
       </c>
       <c r="G86" t="s">
-        <v>87</v>
+        <v>145</v>
       </c>
       <c r="H86" t="s">
         <v>24</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
@@ -3678,7 +3765,7 @@
         <v>50</v>
       </c>
       <c r="D87" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E87" t="s">
         <v>38</v>
@@ -3690,7 +3777,7 @@
         <v>87</v>
       </c>
       <c r="H87" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
@@ -3707,19 +3794,19 @@
         <v>47</v>
       </c>
       <c r="D88" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E88" t="s">
         <v>38</v>
       </c>
       <c r="F88" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G88" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="H88" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
       <c r="I88" t="s">
         <v>19</v>
@@ -3742,16 +3829,16 @@
         <v>38</v>
       </c>
       <c r="F89" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="G89" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
@@ -3762,7 +3849,7 @@
         <v>71</v>
       </c>
       <c r="C90" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D90" t="s">
         <v>57</v>
@@ -3774,7 +3861,7 @@
         <v>92</v>
       </c>
       <c r="G90" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H90" t="s">
         <v>24</v>
@@ -3791,25 +3878,25 @@
         <v>71</v>
       </c>
       <c r="C91" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D91" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E91" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="F91" t="s">
-        <v>148</v>
+        <v>28</v>
       </c>
       <c r="G91" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="H91" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
@@ -3823,7 +3910,7 @@
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E92" t="s">
         <v>27</v>
@@ -3835,7 +3922,7 @@
         <v>87</v>
       </c>
       <c r="H92" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="I92" t="s">
         <v>19</v>
@@ -3855,19 +3942,19 @@
         <v>133</v>
       </c>
       <c r="E93" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="F93" t="s">
         <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="H93" t="s">
         <v>24</v>
       </c>
       <c r="I93" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
@@ -3881,7 +3968,7 @@
         <v>50</v>
       </c>
       <c r="D94" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E94" t="s">
         <v>38</v>
@@ -3890,7 +3977,7 @@
         <v>123</v>
       </c>
       <c r="G94" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H94" t="s">
         <v>24</v>
@@ -3907,22 +3994,22 @@
         <v>80</v>
       </c>
       <c r="C95" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D95" t="s">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="E95" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F95" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="G95" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H95" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I95" t="s">
         <v>19</v>
@@ -3936,25 +4023,25 @@
         <v>80</v>
       </c>
       <c r="C96" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D96" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="E96" t="s">
         <v>38</v>
       </c>
       <c r="F96" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="G96" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
@@ -3965,25 +4052,25 @@
         <v>80</v>
       </c>
       <c r="C97" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="D97" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="E97" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="F97" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="G97" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="H97" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
@@ -3994,25 +4081,25 @@
         <v>80</v>
       </c>
       <c r="C98" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D98" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="E98" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="F98" t="s">
-        <v>148</v>
+        <v>28</v>
       </c>
       <c r="G98" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="H98" t="s">
-        <v>149</v>
+        <v>24</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
@@ -4023,22 +4110,22 @@
         <v>80</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="D99" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="E99" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="F99" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
       <c r="G99" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H99" t="s">
-        <v>24</v>
+        <v>156</v>
       </c>
       <c r="I99" t="s">
         <v>19</v>
@@ -4049,28 +4136,28 @@
         <v>131</v>
       </c>
       <c r="B100" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C100" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="E100" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="F100" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="G100" t="s">
-        <v>87</v>
+        <v>145</v>
       </c>
       <c r="H100" t="s">
         <v>24</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
@@ -4081,22 +4168,22 @@
         <v>82</v>
       </c>
       <c r="C101" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D101" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E101" t="s">
         <v>38</v>
       </c>
       <c r="F101" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="G101" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H101" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I101" t="s">
         <v>19</v>
@@ -4110,19 +4197,19 @@
         <v>82</v>
       </c>
       <c r="C102" t="s">
-        <v>136</v>
+        <v>30</v>
       </c>
       <c r="D102" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E102" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="F102" t="s">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="G102" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H102" t="s">
         <v>24</v>
@@ -4139,22 +4226,22 @@
         <v>82</v>
       </c>
       <c r="C103" t="s">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="D103" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="E103" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F103" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="G103" t="s">
         <v>87</v>
       </c>
       <c r="H103" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="I103" t="s">
         <v>19</v>
@@ -4168,25 +4255,25 @@
         <v>82</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="D104" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="E104" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="F104" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G104" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="H104" t="s">
         <v>24</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
@@ -4194,28 +4281,28 @@
         <v>131</v>
       </c>
       <c r="B105" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="D105" t="s">
+        <v>170</v>
+      </c>
+      <c r="E105" t="s">
+        <v>75</v>
+      </c>
+      <c r="F105" t="s">
+        <v>39</v>
+      </c>
+      <c r="G105" t="s">
+        <v>169</v>
+      </c>
+      <c r="H105" t="s">
         <v>156</v>
       </c>
-      <c r="E105" t="s">
-        <v>27</v>
-      </c>
-      <c r="F105" t="s">
-        <v>28</v>
-      </c>
-      <c r="G105" t="s">
-        <v>87</v>
-      </c>
-      <c r="H105" t="s">
-        <v>24</v>
-      </c>
       <c r="I105" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
@@ -4223,22 +4310,22 @@
         <v>131</v>
       </c>
       <c r="B106" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C106" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="E106" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="F106" t="s">
-        <v>157</v>
+        <v>28</v>
       </c>
       <c r="G106" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H106" t="s">
         <v>24</v>
@@ -4252,22 +4339,22 @@
         <v>131</v>
       </c>
       <c r="B107" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D107" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="E107" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F107" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
       <c r="G107" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H107" t="s">
         <v>24</v>
@@ -4281,54 +4368,54 @@
         <v>131</v>
       </c>
       <c r="B108" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C108" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="E108" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="F108" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="G108" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="H108" t="s">
         <v>24</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
+        <v>176</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="B109" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="C109" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="D109" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E109" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="F109" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="G109" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H109" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I109" t="s">
         <v>19</v>
@@ -4336,28 +4423,28 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="B110" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C110" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E110" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F110" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="G110" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H110" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I110" t="s">
         <v>19</v>
@@ -4365,28 +4452,28 @@
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="B111" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C111" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="D111" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E111" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="F111" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="G111" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H111" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I111" t="s">
         <v>19</v>
@@ -4394,112 +4481,112 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B112" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C112" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D112" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="E112" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F112" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="G112" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="H112" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B113" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="C113" t="s">
         <v>47</v>
       </c>
       <c r="D113" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E113" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F113" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="G113" t="s">
-        <v>87</v>
+        <v>180</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B114" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C114" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D114" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="E114" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F114" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="G114" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="H114" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I114" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B115" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C115" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D115" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="E115" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="F115" t="s">
-        <v>16</v>
+        <v>167</v>
       </c>
       <c r="G115" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
@@ -4510,57 +4597,57 @@
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B116" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C116" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D116" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="E116" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F116" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="G116" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="H116" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B117" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C117" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D117" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="E117" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="F117" t="s">
-        <v>16</v>
+        <v>167</v>
       </c>
       <c r="G117" t="s">
         <v>87</v>
       </c>
       <c r="H117" t="s">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="I117" t="s">
         <v>19</v>
@@ -4568,28 +4655,28 @@
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B118" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C118" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D118" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="E118" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="F118" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="G118" t="s">
         <v>87</v>
       </c>
       <c r="H118" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="I118" t="s">
         <v>19</v>
@@ -4597,25 +4684,25 @@
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B119" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C119" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D119" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="E119" t="s">
         <v>38</v>
       </c>
       <c r="F119" t="s">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="G119" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
@@ -4626,28 +4713,28 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B120" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C120" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D120" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="E120" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="F120" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="G120" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H120" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I120" t="s">
         <v>19</v>
@@ -4655,25 +4742,25 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B121" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C121" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D121" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="E121" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
       <c r="F121" t="s">
-        <v>16</v>
+        <v>167</v>
       </c>
       <c r="G121" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
@@ -4684,25 +4771,25 @@
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B122" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C122" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D122" t="s">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="E122" t="s">
         <v>38</v>
       </c>
       <c r="F122" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="G122" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
@@ -4713,57 +4800,57 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B123" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C123" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D123" t="s">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="E123" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="F123" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="G123" t="s">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B124" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="C124" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D124" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="E124" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="F124" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="G124" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H124" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I124" t="s">
         <v>19</v>
@@ -4771,112 +4858,112 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B125" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="C125" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D125" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="E125" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F125" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="G125" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
       </c>
       <c r="I125" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B126" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C126" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D126" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="E126" t="s">
-        <v>38</v>
+        <v>173</v>
       </c>
       <c r="F126" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="G126" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>19</v>
+        <v>176</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B127" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C127" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D127" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="E127" t="s">
-        <v>38</v>
+        <v>173</v>
       </c>
       <c r="F127" t="s">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="G127" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>19</v>
+        <v>176</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B128" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="C128" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D128" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="E128" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="F128" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="G128" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
@@ -4887,54 +4974,54 @@
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B129" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="C129" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D129" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F129" t="s">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="G129" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H129" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>19</v>
+        <v>176</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B130" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="C130" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D130" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="E130" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="F130" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="G130" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
@@ -4945,25 +5032,25 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B131" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C131" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D131" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="E131" t="s">
         <v>38</v>
       </c>
       <c r="F131" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="G131" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
@@ -4974,25 +5061,25 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B132" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C132" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D132" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="E132" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="F132" t="s">
-        <v>16</v>
+        <v>167</v>
       </c>
       <c r="G132" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
@@ -5003,57 +5090,57 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B133" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C133" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D133" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E133" t="s">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="F133" t="s">
-        <v>76</v>
+        <v>191</v>
       </c>
       <c r="G133" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="H133" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B134" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C134" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D134" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="E134" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F134" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="G134" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H134" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I134" t="s">
         <v>19</v>
@@ -5061,54 +5148,54 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B135" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C135" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D135" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="E135" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="F135" t="s">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="G135" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H135" t="s">
         <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B136" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C136" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="D136" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="E136" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
       <c r="F136" t="s">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="G136" t="s">
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="H136" t="s">
         <v>24</v>
@@ -5119,25 +5206,25 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B137" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C137" t="s">
         <v>47</v>
       </c>
       <c r="D137" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
       <c r="E137" t="s">
         <v>38</v>
       </c>
       <c r="F137" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="G137" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
@@ -5148,16 +5235,16 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B138" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C138" t="s">
         <v>36</v>
       </c>
       <c r="D138" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="E138" t="s">
         <v>38</v>
@@ -5166,7 +5253,7 @@
         <v>58</v>
       </c>
       <c r="G138" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
@@ -5177,10 +5264,10 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B139" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C139" t="s">
         <v>13</v>
@@ -5189,42 +5276,42 @@
         <v>129</v>
       </c>
       <c r="E139" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F139" t="s">
         <v>16</v>
       </c>
       <c r="G139" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B140" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C140" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="D140" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="E140" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="F140" t="s">
         <v>76</v>
       </c>
       <c r="G140" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="H140" t="s">
         <v>24</v>
@@ -5235,28 +5322,28 @@
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B141" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C141" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D141" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="E141" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F141" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="G141" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H141" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I141" t="s">
         <v>19</v>
@@ -5264,28 +5351,28 @@
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B142" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C142" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D142" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="E142" t="s">
         <v>38</v>
       </c>
       <c r="F142" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="G142" t="s">
         <v>87</v>
       </c>
       <c r="H142" t="s">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="I142" t="s">
         <v>19</v>
@@ -5293,28 +5380,28 @@
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B143" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C143" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D143" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="E143" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="F143" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G143" t="s">
         <v>87</v>
       </c>
       <c r="H143" t="s">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="I143" t="s">
         <v>19</v>
@@ -5322,28 +5409,28 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B144" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C144" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D144" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="E144" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="F144" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="G144" t="s">
         <v>89</v>
       </c>
       <c r="H144" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I144" t="s">
         <v>19</v>
@@ -5351,28 +5438,28 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B145" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C145" t="s">
-        <v>47</v>
+        <v>195</v>
       </c>
       <c r="D145" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E145" t="s">
-        <v>38</v>
+        <v>196</v>
       </c>
       <c r="F145" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="G145" t="s">
-        <v>87</v>
+        <v>197</v>
       </c>
       <c r="H145" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I145" t="s">
         <v>19</v>
@@ -5380,45 +5467,45 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B146" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C146" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D146" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="E146" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F146" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="G146" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>19</v>
+        <v>199</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B147" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C147" t="s">
         <v>13</v>
       </c>
       <c r="D147" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="E147" t="s">
         <v>115</v>
@@ -5427,12 +5514,360 @@
         <v>16</v>
       </c>
       <c r="G147" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
       </c>
       <c r="I147" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="15">
+      <c r="A148" t="s">
+        <v>189</v>
+      </c>
+      <c r="B148" t="s">
+        <v>82</v>
+      </c>
+      <c r="C148" t="s">
+        <v>195</v>
+      </c>
+      <c r="D148" t="s">
+        <v>200</v>
+      </c>
+      <c r="E148" t="s">
+        <v>109</v>
+      </c>
+      <c r="F148" t="s">
+        <v>16</v>
+      </c>
+      <c r="G148" t="s">
+        <v>111</v>
+      </c>
+      <c r="H148" t="s">
+        <v>24</v>
+      </c>
+      <c r="I148" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="15">
+      <c r="A149" t="s">
+        <v>189</v>
+      </c>
+      <c r="B149" t="s">
+        <v>90</v>
+      </c>
+      <c r="C149" t="s">
+        <v>47</v>
+      </c>
+      <c r="D149" t="s">
+        <v>181</v>
+      </c>
+      <c r="E149" t="s">
+        <v>32</v>
+      </c>
+      <c r="F149" t="s">
+        <v>167</v>
+      </c>
+      <c r="G149" t="s">
+        <v>34</v>
+      </c>
+      <c r="H149" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="15">
+      <c r="A150" t="s">
+        <v>189</v>
+      </c>
+      <c r="B150" t="s">
+        <v>90</v>
+      </c>
+      <c r="C150" t="s">
+        <v>36</v>
+      </c>
+      <c r="D150" t="s">
+        <v>186</v>
+      </c>
+      <c r="E150" t="s">
+        <v>104</v>
+      </c>
+      <c r="F150" t="s">
+        <v>92</v>
+      </c>
+      <c r="G150" t="s">
+        <v>137</v>
+      </c>
+      <c r="H150" t="s">
+        <v>18</v>
+      </c>
+      <c r="I150" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="15">
+      <c r="A151" t="s">
+        <v>189</v>
+      </c>
+      <c r="B151" t="s">
+        <v>90</v>
+      </c>
+      <c r="C151" t="s">
+        <v>13</v>
+      </c>
+      <c r="D151" t="s">
+        <v>129</v>
+      </c>
+      <c r="E151" t="s">
+        <v>115</v>
+      </c>
+      <c r="F151" t="s">
+        <v>16</v>
+      </c>
+      <c r="G151" t="s">
+        <v>89</v>
+      </c>
+      <c r="H151" t="s">
+        <v>18</v>
+      </c>
+      <c r="I151" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="15">
+      <c r="A152" t="s">
+        <v>189</v>
+      </c>
+      <c r="B152" t="s">
+        <v>90</v>
+      </c>
+      <c r="C152" t="s">
+        <v>195</v>
+      </c>
+      <c r="D152" t="s">
+        <v>200</v>
+      </c>
+      <c r="E152" t="s">
+        <v>173</v>
+      </c>
+      <c r="F152" t="s">
+        <v>16</v>
+      </c>
+      <c r="G152" t="s">
+        <v>175</v>
+      </c>
+      <c r="H152" t="s">
+        <v>24</v>
+      </c>
+      <c r="I152" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="15">
+      <c r="A153" t="s">
+        <v>189</v>
+      </c>
+      <c r="B153" t="s">
+        <v>96</v>
+      </c>
+      <c r="C153" t="s">
+        <v>47</v>
+      </c>
+      <c r="D153" t="s">
+        <v>182</v>
+      </c>
+      <c r="E153" t="s">
+        <v>32</v>
+      </c>
+      <c r="F153" t="s">
+        <v>167</v>
+      </c>
+      <c r="G153" t="s">
+        <v>34</v>
+      </c>
+      <c r="H153" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="15">
+      <c r="A154" t="s">
+        <v>189</v>
+      </c>
+      <c r="B154" t="s">
+        <v>96</v>
+      </c>
+      <c r="C154" t="s">
+        <v>36</v>
+      </c>
+      <c r="D154" t="s">
+        <v>188</v>
+      </c>
+      <c r="E154" t="s">
+        <v>38</v>
+      </c>
+      <c r="F154" t="s">
+        <v>92</v>
+      </c>
+      <c r="G154" t="s">
+        <v>152</v>
+      </c>
+      <c r="H154" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="15">
+      <c r="A155" t="s">
+        <v>189</v>
+      </c>
+      <c r="B155" t="s">
+        <v>96</v>
+      </c>
+      <c r="C155" t="s">
+        <v>13</v>
+      </c>
+      <c r="D155" t="s">
+        <v>172</v>
+      </c>
+      <c r="E155" t="s">
+        <v>115</v>
+      </c>
+      <c r="F155" t="s">
+        <v>16</v>
+      </c>
+      <c r="G155" t="s">
+        <v>89</v>
+      </c>
+      <c r="H155" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="15">
+      <c r="A156" t="s">
+        <v>189</v>
+      </c>
+      <c r="B156" t="s">
+        <v>96</v>
+      </c>
+      <c r="C156" t="s">
+        <v>195</v>
+      </c>
+      <c r="D156" t="s">
+        <v>107</v>
+      </c>
+      <c r="E156" t="s">
+        <v>196</v>
+      </c>
+      <c r="F156" t="s">
+        <v>76</v>
+      </c>
+      <c r="G156" t="s">
+        <v>89</v>
+      </c>
+      <c r="H156" t="s">
+        <v>24</v>
+      </c>
+      <c r="I156" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="15">
+      <c r="A157" t="s">
+        <v>189</v>
+      </c>
+      <c r="B157" t="s">
+        <v>106</v>
+      </c>
+      <c r="C157" t="s">
+        <v>47</v>
+      </c>
+      <c r="D157" t="s">
+        <v>48</v>
+      </c>
+      <c r="E157" t="s">
+        <v>32</v>
+      </c>
+      <c r="F157" t="s">
+        <v>167</v>
+      </c>
+      <c r="G157" t="s">
+        <v>34</v>
+      </c>
+      <c r="H157" t="s">
+        <v>18</v>
+      </c>
+      <c r="I157" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="15">
+      <c r="A158" t="s">
+        <v>189</v>
+      </c>
+      <c r="B158" t="s">
+        <v>106</v>
+      </c>
+      <c r="C158" t="s">
+        <v>36</v>
+      </c>
+      <c r="D158" t="s">
+        <v>188</v>
+      </c>
+      <c r="E158" t="s">
+        <v>38</v>
+      </c>
+      <c r="F158" t="s">
+        <v>92</v>
+      </c>
+      <c r="G158" t="s">
+        <v>152</v>
+      </c>
+      <c r="H158" t="s">
+        <v>18</v>
+      </c>
+      <c r="I158" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="15">
+      <c r="A159" t="s">
+        <v>189</v>
+      </c>
+      <c r="B159" t="s">
+        <v>106</v>
+      </c>
+      <c r="C159" t="s">
+        <v>13</v>
+      </c>
+      <c r="D159" t="s">
+        <v>172</v>
+      </c>
+      <c r="E159" t="s">
+        <v>115</v>
+      </c>
+      <c r="F159" t="s">
+        <v>16</v>
+      </c>
+      <c r="G159" t="s">
+        <v>89</v>
+      </c>
+      <c r="H159" t="s">
+        <v>18</v>
+      </c>
+      <c r="I159" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5444,7 +5879,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{878ba8c3-4d36-4042-8cb8-a6913cd92a77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8ee6f30a-8b08-4fdf-973b-6a2081a8c121}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5464,16 +5899,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -5493,13 +5928,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
         <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E2" t="s">
         <v>120</v>
@@ -5522,13 +5957,13 @@
         <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E3" t="s">
         <v>109</v>
@@ -5537,7 +5972,7 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -5551,16 +5986,16 @@
         <v>113</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="C4" t="s">
         <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -5580,13 +6015,13 @@
         <v>113</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="C5" t="s">
         <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="E5" t="s">
         <v>120</v>
@@ -5609,16 +6044,16 @@
         <v>113</v>
       </c>
       <c r="B6" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="C6" t="s">
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E6" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -5638,13 +6073,13 @@
         <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="C7" t="s">
         <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E7" t="s">
         <v>120</v>
@@ -5667,16 +6102,16 @@
         <v>113</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E8" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
@@ -5696,22 +6131,22 @@
         <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E9" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -5725,16 +6160,16 @@
         <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E10" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="F10" t="s">
         <v>24</v>
@@ -5754,16 +6189,16 @@
         <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E11" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -5780,16 +6215,16 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="C12" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E12" t="s">
         <v>109</v>
@@ -5798,7 +6233,7 @@
         <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
@@ -5809,19 +6244,19 @@
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B13" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E13" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="F13" t="s">
         <v>24</v>
@@ -5838,19 +6273,19 @@
     </row>
     <row r="14" spans="1:9" ht="15">
       <c r="A14" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E14" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="F14" t="s">
         <v>24</v>
@@ -5867,19 +6302,19 @@
     </row>
     <row r="15" spans="1:9" ht="15">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E15" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="F15" t="s">
         <v>24</v>
@@ -5896,19 +6331,19 @@
     </row>
     <row r="16" spans="1:9" ht="15">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E16" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="F16" t="s">
         <v>24</v>
@@ -5925,19 +6360,19 @@
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E17" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="F17" t="s">
         <v>24</v>
@@ -5960,15 +6395,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{eb070e0f-1e6f-4ef1-9e39-e34cf7bf0514}">
-  <dimension ref="A1:F35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a6f880fc-2bfa-4cd4-ab9f-4160e5246153}">
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="28.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="5" max="5" width="24.2857142857143" customWidth="1"/>
     <col min="6" max="6" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5977,13 +6412,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -5997,16 +6432,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
@@ -6017,16 +6452,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="E3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F3" t="s">
         <v>24</v>
@@ -6037,16 +6472,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="E4" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -6057,16 +6492,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E5" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -6077,16 +6512,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="C6" t="s">
         <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="E6" t="s">
-        <v>207</v>
+        <v>143</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -6097,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
         <v>105</v>
@@ -6117,13 +6552,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
         <v>34</v>
@@ -6137,13 +6572,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C9" t="s">
         <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
         <v>47</v>
@@ -6157,16 +6592,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E10" t="s">
-        <v>211</v>
+        <v>155</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -6177,16 +6612,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="E11" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -6197,16 +6632,16 @@
         <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="F12" t="s">
         <v>24</v>
@@ -6217,13 +6652,13 @@
         <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="E13" t="s">
         <v>53</v>
@@ -6237,16 +6672,16 @@
         <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E14" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -6257,16 +6692,16 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="C15" t="s">
         <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E15" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -6277,16 +6712,16 @@
         <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="C16" t="s">
         <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E16" t="s">
-        <v>211</v>
+        <v>155</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -6297,16 +6732,16 @@
         <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="E17" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -6317,13 +6752,13 @@
         <v>113</v>
       </c>
       <c r="B18" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="E18" t="s">
         <v>34</v>
@@ -6337,16 +6772,16 @@
         <v>131</v>
       </c>
       <c r="B19" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="C19" t="s">
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>228</v>
       </c>
       <c r="F19" t="s">
         <v>24</v>
@@ -6357,16 +6792,16 @@
         <v>131</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -6377,16 +6812,16 @@
         <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="C21" t="s">
         <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>195</v>
       </c>
       <c r="F21" t="s">
         <v>24</v>
@@ -6397,16 +6832,16 @@
         <v>131</v>
       </c>
       <c r="B22" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="C22" t="s">
         <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>247</v>
       </c>
       <c r="F22" t="s">
         <v>24</v>
@@ -6417,16 +6852,16 @@
         <v>131</v>
       </c>
       <c r="B23" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C23" t="s">
         <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>187</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -6437,16 +6872,16 @@
         <v>131</v>
       </c>
       <c r="B24" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C24" t="s">
         <v>132</v>
       </c>
       <c r="D24" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="F24" t="s">
         <v>24</v>
@@ -6457,16 +6892,16 @@
         <v>131</v>
       </c>
       <c r="B25" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="C25" t="s">
         <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -6477,16 +6912,16 @@
         <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="F26" t="s">
         <v>24</v>
@@ -6494,39 +6929,39 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B28" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="C28" t="s">
         <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -6534,19 +6969,19 @@
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -6554,19 +6989,19 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B30" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -6574,19 +7009,19 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B31" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>195</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -6594,19 +7029,19 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -6614,61 +7049,101 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="C33" t="s">
-        <v>166</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B34" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>195</v>
       </c>
       <c r="D34" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="F34" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="C35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" t="s">
+        <v>231</v>
+      </c>
+      <c r="E35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15">
+      <c r="A36" t="s">
+        <v>189</v>
+      </c>
+      <c r="B36" t="s">
+        <v>236</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>231</v>
+      </c>
+      <c r="E36" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15">
+      <c r="A37" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" t="s">
+        <v>238</v>
+      </c>
+      <c r="C37" t="s">
         <v>47</v>
       </c>
-      <c r="D35" t="s">
-        <v>204</v>
-      </c>
-      <c r="E35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="D37" t="s">
+        <v>234</v>
+      </c>
+      <c r="E37" t="s">
+        <v>187</v>
+      </c>
+      <c r="F37" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="252">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -78,75 +78,78 @@
     <t>Uczniowie przychodzą później</t>
   </si>
   <si>
+    <t>wyjazd w ramach projektu FERS</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Mocarski Arkadiusz</t>
+  </si>
+  <si>
+    <t>3K|kucharz</t>
+  </si>
+  <si>
+    <t>Technologia gastronomiczna z towaroznawstwem</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>2, 08:50-09:35</t>
+  </si>
+  <si>
+    <t>Dalach Krystyna</t>
+  </si>
+  <si>
+    <t>2TFB|DZ</t>
+  </si>
+  <si>
+    <t>Wychowanie fizyczne</t>
+  </si>
+  <si>
+    <t>sg1</t>
+  </si>
+  <si>
+    <t>Nestoruk Lidia</t>
+  </si>
+  <si>
+    <t>Dodatkowo płatne</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>2K|gr2</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
     <t>Erasmus+</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Mocarski Arkadiusz</t>
-  </si>
-  <si>
-    <t>3K|kucharz</t>
-  </si>
-  <si>
-    <t>Technologia gastronomiczna z towaroznawstwem</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Smirnow-Zechman Eleonora</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
-    <t>Biznes i zarządzanie</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>2, 08:50-09:35</t>
-  </si>
-  <si>
-    <t>Dalach Krystyna</t>
-  </si>
-  <si>
-    <t>2TFB|DZ</t>
-  </si>
-  <si>
-    <t>Wychowanie fizyczne</t>
-  </si>
-  <si>
-    <t>sg1</t>
-  </si>
-  <si>
-    <t>Nestoruk Lidia</t>
-  </si>
-  <si>
-    <t>Dodatkowo płatne</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>2K|gr2</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Karczmarz Aleksandra</t>
-  </si>
-  <si>
     <t>Bezpłatne</t>
   </si>
   <si>
@@ -450,15 +453,21 @@
     <t>2S</t>
   </si>
   <si>
+    <t>Staliś Donata</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>1CB</t>
+  </si>
+  <si>
     <t>Chemia</t>
   </si>
   <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>1CB</t>
-  </si>
-  <si>
     <t>Mucha Anna</t>
   </si>
   <si>
@@ -480,7 +489,10 @@
     <t>Erasmus+ / p. Kończyńska, technologie produkcji cukierniczej za lekcję 9</t>
   </si>
   <si>
-    <t>Staliś Donata</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>p. Filipek, j. polski za lekcję 9</t>
   </si>
   <si>
     <t>Najwer Maciej</t>
@@ -540,9 +552,6 @@
     <t>1K</t>
   </si>
   <si>
-    <t>1FA</t>
-  </si>
-  <si>
     <t>Doradztwo zawodowe</t>
   </si>
   <si>
@@ -691,12 +700,6 @@
   </si>
   <si>
     <t xml:space="preserve">Projektowanie i wykonywanie fryzur-zaj.prakt. </t>
-  </si>
-  <si>
-    <t>Proj.fryz. za tydzień : 05.09.26-09.10.26</t>
-  </si>
-  <si>
-    <t>11:25-12:10</t>
   </si>
   <si>
     <t>Miejsce dyżuru</t>
@@ -1224,7 +1227,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{666deb5b-5827-4626-b6ff-ea87ea166c1d}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c8c43a2e-3d8c-46ea-be3c-77a45be146c9}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1245,8 +1248,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b8567b33-96dd-4b22-b9e8-96324e20b4b9}">
-  <dimension ref="A1:I159"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a1c45121-e8a4-4edf-bd82-a0a61dfb6950}">
+  <dimension ref="A1:I161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1428,10 +1431,10 @@
         <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1503,22 +1506,22 @@
         <v>25</v>
       </c>
       <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
         <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
@@ -1526,7 +1529,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
         <v>30</v>
@@ -1555,28 +1558,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1584,25 +1587,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I12" t="s">
         <v>35</v>
@@ -1613,7 +1616,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -1642,28 +1645,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" t="s">
         <v>46</v>
       </c>
-      <c r="C14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" t="s">
-        <v>45</v>
-      </c>
       <c r="H14" t="s">
         <v>24</v>
       </c>
       <c r="I14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1671,7 +1674,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
@@ -1700,25 +1703,25 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
         <v>38</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G16" t="s">
         <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I16" t="s">
         <v>19</v>
@@ -1729,25 +1732,25 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
         <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G17" t="s">
         <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I17" t="s">
         <v>19</v>
@@ -1758,28 +1761,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1787,13 +1790,13 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
         <v>38</v>
@@ -1802,7 +1805,7 @@
         <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H19" t="s">
         <v>24</v>
@@ -1816,7 +1819,7 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
@@ -1831,13 +1834,13 @@
         <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H20" t="s">
         <v>24</v>
       </c>
       <c r="I20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1845,22 +1848,22 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H21" t="s">
         <v>24</v>
@@ -1874,22 +1877,22 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
       </c>
       <c r="G22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H22" t="s">
         <v>24</v>
@@ -1903,13 +1906,13 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
         <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
         <v>32</v>
@@ -1932,28 +1935,28 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1961,28 +1964,28 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H25" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -1990,22 +1993,22 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s">
         <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s">
         <v>24</v>
@@ -2019,22 +2022,22 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F27" t="s">
         <v>23</v>
       </c>
       <c r="G27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H27" t="s">
         <v>24</v>
@@ -2048,13 +2051,13 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -2077,13 +2080,13 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
         <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E29" t="s">
         <v>32</v>
@@ -2106,28 +2109,28 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H30" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -2135,28 +2138,28 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H31" t="s">
         <v>24</v>
       </c>
       <c r="I31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
@@ -2164,13 +2167,13 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" t="s">
         <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s">
         <v>32</v>
@@ -2193,28 +2196,28 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H33" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -2222,22 +2225,22 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s">
         <v>24</v>
@@ -2251,22 +2254,22 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F35" t="s">
         <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s">
         <v>24</v>
@@ -2280,28 +2283,28 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E36" t="s">
         <v>38</v>
       </c>
       <c r="F36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -2309,28 +2312,28 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H37" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
@@ -2338,22 +2341,22 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s">
         <v>24</v>
@@ -2367,22 +2370,22 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F39" t="s">
         <v>23</v>
       </c>
       <c r="G39" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H39" t="s">
         <v>24</v>
@@ -2396,19 +2399,19 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C40" t="s">
         <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G40" t="s">
         <v>34</v>
@@ -2425,22 +2428,22 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E41" t="s">
         <v>32</v>
       </c>
       <c r="F41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s">
         <v>24</v>
@@ -2454,28 +2457,28 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E42" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
       </c>
       <c r="G42" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H42" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
@@ -2483,28 +2486,28 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H43" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
@@ -2512,22 +2515,22 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" t="s">
+        <v>99</v>
+      </c>
+      <c r="F44" t="s">
         <v>96</v>
       </c>
-      <c r="C44" t="s">
-        <v>83</v>
-      </c>
-      <c r="D44" t="s">
-        <v>81</v>
-      </c>
-      <c r="E44" t="s">
-        <v>98</v>
-      </c>
-      <c r="F44" t="s">
-        <v>95</v>
-      </c>
       <c r="G44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s">
         <v>24</v>
@@ -2541,22 +2544,22 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F45" t="s">
         <v>23</v>
       </c>
       <c r="G45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s">
         <v>24</v>
@@ -2570,22 +2573,22 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E46" t="s">
         <v>32</v>
       </c>
       <c r="F46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s">
         <v>24</v>
@@ -2599,25 +2602,25 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E47" t="s">
         <v>38</v>
       </c>
       <c r="F47" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G47" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
@@ -2628,28 +2631,28 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C48" t="s">
         <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E48" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H48" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I48" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
@@ -2657,22 +2660,22 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E49" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F49" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G49" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H49" t="s">
         <v>24</v>
@@ -2686,22 +2689,22 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F50" t="s">
         <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s">
         <v>24</v>
@@ -2715,22 +2718,22 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E51" t="s">
         <v>32</v>
       </c>
       <c r="F51" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s">
         <v>24</v>
@@ -2744,22 +2747,22 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C52" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E52" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F52" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G52" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s">
         <v>24</v>
@@ -2770,7 +2773,7 @@
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B53" t="s">
         <v>29</v>
@@ -2785,13 +2788,13 @@
         <v>38</v>
       </c>
       <c r="F53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H53" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I53" t="s">
         <v>35</v>
@@ -2799,25 +2802,25 @@
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C54" t="s">
         <v>30</v>
       </c>
       <c r="D54" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E54" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F54" t="s">
         <v>39</v>
       </c>
       <c r="G54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H54" t="s">
         <v>24</v>
@@ -2828,10 +2831,10 @@
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C55" t="s">
         <v>13</v>
@@ -2843,13 +2846,13 @@
         <v>38</v>
       </c>
       <c r="F55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G55" t="s">
         <v>40</v>
       </c>
       <c r="H55" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I55" t="s">
         <v>35</v>
@@ -2857,25 +2860,25 @@
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C56" t="s">
         <v>30</v>
       </c>
       <c r="D56" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E56" t="s">
         <v>32</v>
       </c>
       <c r="F56" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G56" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H56" t="s">
         <v>24</v>
@@ -2886,10 +2889,10 @@
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
@@ -2901,13 +2904,13 @@
         <v>38</v>
       </c>
       <c r="F57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G57" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I57" t="s">
         <v>35</v>
@@ -2915,25 +2918,25 @@
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C58" t="s">
         <v>30</v>
       </c>
       <c r="D58" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E58" t="s">
         <v>32</v>
       </c>
       <c r="F58" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H58" t="s">
         <v>24</v>
@@ -2944,10 +2947,10 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" t="s">
         <v>13</v>
@@ -2962,7 +2965,7 @@
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
@@ -2973,10 +2976,10 @@
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" t="s">
         <v>20</v>
@@ -2985,45 +2988,45 @@
         <v>21</v>
       </c>
       <c r="E60" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s">
         <v>24</v>
       </c>
       <c r="I60" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C61" t="s">
         <v>36</v>
       </c>
       <c r="D61" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E61" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G61" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H61" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I61" t="s">
         <v>35</v>
@@ -3031,10 +3034,10 @@
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B62" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C62" t="s">
         <v>13</v>
@@ -3043,13 +3046,13 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
@@ -3060,16 +3063,16 @@
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C63" t="s">
         <v>30</v>
       </c>
       <c r="D63" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E63" t="s">
         <v>32</v>
@@ -3078,7 +3081,7 @@
         <v>33</v>
       </c>
       <c r="G63" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s">
         <v>24</v>
@@ -3089,28 +3092,28 @@
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D64" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E64" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G64" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H64" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I64" t="s">
         <v>35</v>
@@ -3118,28 +3121,28 @@
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B65" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C65" t="s">
         <v>36</v>
       </c>
       <c r="D65" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E65" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F65" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G65" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H65" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I65" t="s">
         <v>35</v>
@@ -3147,10 +3150,10 @@
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C66" t="s">
         <v>13</v>
@@ -3159,13 +3162,13 @@
         <v>14</v>
       </c>
       <c r="E66" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
         <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
@@ -3176,16 +3179,16 @@
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C67" t="s">
         <v>30</v>
       </c>
       <c r="D67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E67" t="s">
         <v>32</v>
@@ -3194,7 +3197,7 @@
         <v>33</v>
       </c>
       <c r="G67" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s">
         <v>24</v>
@@ -3205,86 +3208,86 @@
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B68" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D68" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E68" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F68" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G68" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H68" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I68" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C69" t="s">
         <v>36</v>
       </c>
       <c r="D69" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E69" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F69" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G69" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H69" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I69" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B70" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C70" t="s">
         <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E70" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F70" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G70" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H70" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I70" t="s">
         <v>35</v>
@@ -3292,16 +3295,16 @@
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B71" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C71" t="s">
         <v>30</v>
       </c>
       <c r="D71" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E71" t="s">
         <v>32</v>
@@ -3310,7 +3313,7 @@
         <v>33</v>
       </c>
       <c r="G71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s">
         <v>24</v>
@@ -3321,28 +3324,28 @@
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C72" t="s">
         <v>36</v>
       </c>
       <c r="D72" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E72" t="s">
         <v>38</v>
       </c>
       <c r="F72" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G72" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I72" t="s">
         <v>19</v>
@@ -3350,28 +3353,28 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C73" t="s">
         <v>36</v>
       </c>
       <c r="D73" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E73" t="s">
         <v>38</v>
       </c>
       <c r="F73" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G73" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I73" t="s">
         <v>19</v>
@@ -3379,7 +3382,7 @@
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
@@ -3388,7 +3391,7 @@
         <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E74" t="s">
         <v>27</v>
@@ -3408,22 +3411,22 @@
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D75" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E75" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F75" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G75" t="s">
         <v>17</v>
@@ -3437,28 +3440,28 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B76" t="s">
         <v>29</v>
       </c>
       <c r="C76" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D76" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E76" t="s">
         <v>38</v>
       </c>
       <c r="F76" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G76" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I76" t="s">
         <v>19</v>
@@ -3466,22 +3469,22 @@
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B77" t="s">
         <v>29</v>
       </c>
       <c r="C77" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D77" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F77" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G77" t="s">
         <v>17</v>
@@ -3495,7 +3498,7 @@
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B78" t="s">
         <v>29</v>
@@ -3504,42 +3507,42 @@
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E78" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="F78" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G78" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="H78" t="s">
         <v>24</v>
       </c>
       <c r="I78" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B79" t="s">
         <v>29</v>
       </c>
       <c r="C79" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E79" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F79" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G79" t="s">
         <v>17</v>
@@ -3553,28 +3556,28 @@
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C80" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D80" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E80" t="s">
         <v>38</v>
       </c>
       <c r="F80" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G80" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H80" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I80" t="s">
         <v>19</v>
@@ -3582,10 +3585,10 @@
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B81" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C81" t="s">
         <v>36</v>
@@ -3594,68 +3597,68 @@
         <v>37</v>
       </c>
       <c r="E81" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F81" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G81" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H81" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I81" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C82" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D82" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E82" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F82" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G82" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H82" t="s">
         <v>24</v>
       </c>
       <c r="I82" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B83" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C83" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D83" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E83" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="F83" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="G83" t="s">
         <v>143</v>
@@ -3669,28 +3672,28 @@
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C84" t="s">
         <v>36</v>
       </c>
       <c r="D84" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E84" t="s">
         <v>38</v>
       </c>
       <c r="F84" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G84" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H84" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I84" t="s">
         <v>35</v>
@@ -3698,54 +3701,54 @@
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B85" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="D85" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E85" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="F85" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G85" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="H85" t="s">
         <v>24</v>
       </c>
       <c r="I85" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B86" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C86" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E86" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="F86" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G86" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="H86" t="s">
         <v>24</v>
@@ -3756,57 +3759,57 @@
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B87" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C87" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E87" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="F87" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G87" t="s">
-        <v>87</v>
+        <v>148</v>
       </c>
       <c r="H87" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B88" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C88" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D88" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E88" t="s">
         <v>38</v>
       </c>
       <c r="F88" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="G88" t="s">
+        <v>88</v>
+      </c>
+      <c r="H88" t="s">
         <v>150</v>
-      </c>
-      <c r="H88" t="s">
-        <v>151</v>
       </c>
       <c r="I88" t="s">
         <v>19</v>
@@ -3814,115 +3817,115 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C89" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D89" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="E89" t="s">
         <v>38</v>
       </c>
       <c r="F89" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="G89" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H89" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I89" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B90" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C90" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="D90" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="E90" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="F90" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="G90" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="H90" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C91" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D91" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="E91" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F91" t="s">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="G91" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="H91" t="s">
         <v>156</v>
       </c>
       <c r="I91" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="D92" t="s">
-        <v>157</v>
+        <v>58</v>
       </c>
       <c r="E92" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="F92" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="G92" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H92" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
       <c r="I92" t="s">
         <v>19</v>
@@ -3930,28 +3933,28 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C93" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="D93" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="E93" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="F93" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G93" t="s">
         <v>159</v>
       </c>
       <c r="H93" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="I93" t="s">
         <v>35</v>
@@ -3959,28 +3962,28 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C94" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E94" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F94" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="G94" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H94" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="I94" t="s">
         <v>19</v>
@@ -3988,115 +3991,115 @@
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C95" t="s">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="D95" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="E95" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="F95" t="s">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="H95" t="s">
         <v>24</v>
       </c>
       <c r="I95" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C96" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D96" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E96" t="s">
         <v>38</v>
       </c>
       <c r="F96" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="G96" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H96" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I96" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C97" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D97" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="E97" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="F97" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G97" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="H97" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I97" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C98" t="s">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="D98" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E98" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="F98" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G98" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
       <c r="H98" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I98" t="s">
         <v>35</v>
@@ -4104,54 +4107,54 @@
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C99" t="s">
-        <v>153</v>
+        <v>36</v>
       </c>
       <c r="D99" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E99" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="F99" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G99" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H99" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B100" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="D100" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="E100" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F100" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="G100" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="H100" t="s">
         <v>24</v>
@@ -4162,28 +4165,28 @@
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B101" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C101" t="s">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="D101" t="s">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="E101" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="F101" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="G101" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H101" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="I101" t="s">
         <v>19</v>
@@ -4191,57 +4194,57 @@
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B102" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C102" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="E102" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="F102" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G102" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="H102" t="s">
         <v>24</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B103" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D103" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E103" t="s">
         <v>38</v>
       </c>
       <c r="F103" t="s">
-        <v>167</v>
+        <v>124</v>
       </c>
       <c r="G103" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H103" t="s">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="I103" t="s">
         <v>19</v>
@@ -4249,170 +4252,170 @@
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B104" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="D104" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E104" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="F104" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="G104" t="s">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s">
         <v>24</v>
       </c>
       <c r="I104" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B105" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>153</v>
+        <v>36</v>
       </c>
       <c r="D105" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="E105" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F105" t="s">
-        <v>39</v>
+        <v>171</v>
       </c>
       <c r="G105" t="s">
-        <v>169</v>
+        <v>88</v>
       </c>
       <c r="H105" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="I105" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B106" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="D106" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="E106" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="F106" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G106" t="s">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="H106" t="s">
         <v>24</v>
       </c>
       <c r="I106" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B107" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c r="D107" t="s">
-        <v>97</v>
+        <v>174</v>
       </c>
       <c r="E107" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="F107" t="s">
-        <v>161</v>
+        <v>39</v>
       </c>
       <c r="G107" t="s">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="H107" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B108" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C108" t="s">
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E108" t="s">
-        <v>173</v>
+        <v>27</v>
       </c>
       <c r="F108" t="s">
-        <v>174</v>
+        <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="H108" t="s">
         <v>24</v>
       </c>
       <c r="I108" t="s">
-        <v>176</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B109" t="s">
+        <v>91</v>
+      </c>
+      <c r="C109" t="s">
+        <v>30</v>
+      </c>
+      <c r="D109" t="s">
+        <v>98</v>
+      </c>
+      <c r="E109" t="s">
+        <v>32</v>
+      </c>
+      <c r="F109" t="s">
+        <v>165</v>
+      </c>
+      <c r="G109" t="s">
         <v>90</v>
-      </c>
-      <c r="C109" t="s">
-        <v>132</v>
-      </c>
-      <c r="D109" t="s">
-        <v>141</v>
-      </c>
-      <c r="E109" t="s">
-        <v>134</v>
-      </c>
-      <c r="F109" t="s">
-        <v>177</v>
-      </c>
-      <c r="G109" t="s">
-        <v>89</v>
       </c>
       <c r="H109" t="s">
         <v>24</v>
@@ -4423,54 +4426,54 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B110" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C110" t="s">
         <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E110" t="s">
-        <v>27</v>
+        <v>176</v>
       </c>
       <c r="F110" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="G110" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="H110" t="s">
         <v>24</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B111" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C111" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D111" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E111" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F111" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G111" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H111" t="s">
         <v>24</v>
@@ -4481,83 +4484,83 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="B112" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C112" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="E112" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F112" t="s">
-        <v>161</v>
+        <v>28</v>
       </c>
       <c r="G112" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="H112" t="s">
         <v>24</v>
       </c>
       <c r="I112" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="B113" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C113" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="D113" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="E113" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="F113" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="G113" t="s">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="H113" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I113" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B114" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C114" t="s">
         <v>30</v>
       </c>
       <c r="D114" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E114" t="s">
         <v>32</v>
       </c>
       <c r="F114" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G114" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H114" t="s">
         <v>24</v>
@@ -4568,54 +4571,54 @@
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C115" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D115" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E115" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F115" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G115" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="H115" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B116" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C116" t="s">
         <v>30</v>
       </c>
       <c r="D116" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E116" t="s">
         <v>32</v>
       </c>
       <c r="F116" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G116" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H116" t="s">
         <v>24</v>
@@ -4626,28 +4629,28 @@
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B117" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C117" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D117" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E117" t="s">
         <v>38</v>
       </c>
       <c r="F117" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G117" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H117" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="I117" t="s">
         <v>19</v>
@@ -4655,57 +4658,57 @@
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B118" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C118" t="s">
         <v>30</v>
       </c>
       <c r="D118" t="s">
-        <v>107</v>
+        <v>182</v>
       </c>
       <c r="E118" t="s">
         <v>32</v>
       </c>
       <c r="F118" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G118" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="H118" t="s">
-        <v>184</v>
+        <v>24</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B119" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C119" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D119" t="s">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="E119" t="s">
         <v>38</v>
       </c>
       <c r="F119" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G119" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H119" t="s">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="I119" t="s">
         <v>19</v>
@@ -4713,28 +4716,28 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B120" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C120" t="s">
         <v>30</v>
       </c>
       <c r="D120" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E120" t="s">
         <v>32</v>
       </c>
       <c r="F120" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G120" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H120" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="I120" t="s">
         <v>19</v>
@@ -4742,28 +4745,28 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B121" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C121" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D121" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="E121" t="s">
         <v>38</v>
       </c>
       <c r="F121" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G121" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H121" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I121" t="s">
         <v>19</v>
@@ -4771,28 +4774,28 @@
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B122" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C122" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D122" t="s">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="E122" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F122" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="G122" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H122" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I122" t="s">
         <v>19</v>
@@ -4800,57 +4803,57 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B123" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C123" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D123" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="E123" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="F123" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="G123" t="s">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="H123" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I123" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B124" t="s">
+        <v>83</v>
+      </c>
+      <c r="C124" t="s">
+        <v>36</v>
+      </c>
+      <c r="D124" t="s">
+        <v>189</v>
+      </c>
+      <c r="E124" t="s">
+        <v>38</v>
+      </c>
+      <c r="F124" t="s">
+        <v>61</v>
+      </c>
+      <c r="G124" t="s">
         <v>90</v>
       </c>
-      <c r="C124" t="s">
-        <v>30</v>
-      </c>
-      <c r="D124" t="s">
-        <v>107</v>
-      </c>
-      <c r="E124" t="s">
-        <v>32</v>
-      </c>
-      <c r="F124" t="s">
-        <v>161</v>
-      </c>
-      <c r="G124" t="s">
-        <v>89</v>
-      </c>
       <c r="H124" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I124" t="s">
         <v>19</v>
@@ -4858,126 +4861,126 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B125" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C125" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D125" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="E125" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="F125" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="G125" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="H125" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I125" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B126" t="s">
+        <v>91</v>
+      </c>
+      <c r="C126" t="s">
+        <v>30</v>
+      </c>
+      <c r="D126" t="s">
+        <v>108</v>
+      </c>
+      <c r="E126" t="s">
+        <v>32</v>
+      </c>
+      <c r="F126" t="s">
+        <v>165</v>
+      </c>
+      <c r="G126" t="s">
         <v>90</v>
       </c>
-      <c r="C126" t="s">
-        <v>13</v>
-      </c>
-      <c r="D126" t="s">
-        <v>172</v>
-      </c>
-      <c r="E126" t="s">
-        <v>173</v>
-      </c>
-      <c r="F126" t="s">
-        <v>174</v>
-      </c>
-      <c r="G126" t="s">
-        <v>175</v>
-      </c>
       <c r="H126" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I126" t="s">
-        <v>176</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B127" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C127" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D127" t="s">
-        <v>14</v>
+        <v>174</v>
       </c>
       <c r="E127" t="s">
-        <v>173</v>
+        <v>44</v>
       </c>
       <c r="F127" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="G127" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="H127" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I127" t="s">
-        <v>176</v>
+        <v>42</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
+        <v>181</v>
+      </c>
+      <c r="B128" t="s">
+        <v>91</v>
+      </c>
+      <c r="C128" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" t="s">
+        <v>145</v>
+      </c>
+      <c r="E128" t="s">
+        <v>176</v>
+      </c>
+      <c r="F128" t="s">
+        <v>177</v>
+      </c>
+      <c r="G128" t="s">
         <v>178</v>
       </c>
-      <c r="B128" t="s">
-        <v>106</v>
-      </c>
-      <c r="C128" t="s">
-        <v>36</v>
-      </c>
-      <c r="D128" t="s">
-        <v>188</v>
-      </c>
-      <c r="E128" t="s">
-        <v>38</v>
-      </c>
-      <c r="F128" t="s">
-        <v>60</v>
-      </c>
-      <c r="G128" t="s">
-        <v>17</v>
-      </c>
       <c r="H128" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I128" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B129" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C129" t="s">
         <v>13</v>
@@ -4986,45 +4989,45 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F129" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G129" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H129" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I129" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B130" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="C130" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D130" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="E130" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="F130" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="G130" t="s">
         <v>17</v>
       </c>
       <c r="H130" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I130" t="s">
         <v>19</v>
@@ -5032,51 +5035,51 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B131" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="C131" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D131" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="E131" t="s">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="F131" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G131" t="s">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="H131" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I131" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B132" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C132" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D132" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="E132" t="s">
-        <v>38</v>
+        <v>193</v>
       </c>
       <c r="F132" t="s">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="G132" t="s">
         <v>17</v>
@@ -5090,57 +5093,57 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B133" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C133" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D133" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="E133" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F133" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="G133" t="s">
-        <v>192</v>
+        <v>17</v>
       </c>
       <c r="H133" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I133" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B134" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C134" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D134" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="E134" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F134" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="G134" t="s">
         <v>17</v>
       </c>
       <c r="H134" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I134" t="s">
         <v>19</v>
@@ -5148,28 +5151,28 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B135" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C135" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D135" t="s">
-        <v>185</v>
+        <v>14</v>
       </c>
       <c r="E135" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="F135" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="G135" t="s">
-        <v>93</v>
+        <v>195</v>
       </c>
       <c r="H135" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I135" t="s">
         <v>35</v>
@@ -5177,22 +5180,22 @@
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B136" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C136" t="s">
         <v>30</v>
       </c>
       <c r="D136" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E136" t="s">
         <v>32</v>
       </c>
       <c r="F136" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G136" t="s">
         <v>17</v>
@@ -5206,57 +5209,57 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B137" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C137" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D137" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="E137" t="s">
         <v>38</v>
       </c>
       <c r="F137" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="G137" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="H137" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I137" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B138" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C138" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D138" t="s">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="E138" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F138" t="s">
-        <v>58</v>
+        <v>197</v>
       </c>
       <c r="G138" t="s">
         <v>17</v>
       </c>
       <c r="H138" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I138" t="s">
         <v>19</v>
@@ -5264,57 +5267,57 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B139" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C139" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D139" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="E139" t="s">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="F139" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="G139" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="H139" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I139" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B140" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C140" t="s">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="D140" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E140" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="F140" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="G140" t="s">
-        <v>197</v>
+        <v>17</v>
       </c>
       <c r="H140" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I140" t="s">
         <v>19</v>
@@ -5322,57 +5325,57 @@
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B141" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C141" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D141" t="s">
-        <v>193</v>
+        <v>130</v>
       </c>
       <c r="E141" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="F141" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="G141" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="H141" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I141" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B142" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C142" t="s">
-        <v>47</v>
+        <v>198</v>
       </c>
       <c r="D142" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="E142" t="s">
-        <v>38</v>
+        <v>199</v>
       </c>
       <c r="F142" t="s">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="G142" t="s">
-        <v>87</v>
+        <v>200</v>
       </c>
       <c r="H142" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="I142" t="s">
         <v>19</v>
@@ -5380,28 +5383,28 @@
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B143" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C143" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D143" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="E143" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F143" t="s">
-        <v>58</v>
+        <v>197</v>
       </c>
       <c r="G143" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H143" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="I143" t="s">
         <v>19</v>
@@ -5409,28 +5412,28 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B144" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C144" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D144" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="E144" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="F144" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="G144" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H144" t="s">
-        <v>18</v>
+        <v>201</v>
       </c>
       <c r="I144" t="s">
         <v>19</v>
@@ -5438,28 +5441,28 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B145" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C145" t="s">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="D145" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="E145" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="F145" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="G145" t="s">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="H145" t="s">
-        <v>24</v>
+        <v>201</v>
       </c>
       <c r="I145" t="s">
         <v>19</v>
@@ -5467,57 +5470,57 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B146" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C146" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D146" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="E146" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="F146" t="s">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="G146" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>199</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B147" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C147" t="s">
-        <v>13</v>
+        <v>198</v>
       </c>
       <c r="D147" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="E147" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="F147" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="G147" t="s">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="H147" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I147" t="s">
         <v>19</v>
@@ -5525,349 +5528,407 @@
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B148" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C148" t="s">
-        <v>195</v>
+        <v>48</v>
       </c>
       <c r="D148" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="E148" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="F148" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="G148" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="H148" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I148" t="s">
-        <v>35</v>
+        <v>202</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B149" t="s">
+        <v>83</v>
+      </c>
+      <c r="C149" t="s">
+        <v>13</v>
+      </c>
+      <c r="D149" t="s">
+        <v>130</v>
+      </c>
+      <c r="E149" t="s">
+        <v>116</v>
+      </c>
+      <c r="F149" t="s">
+        <v>16</v>
+      </c>
+      <c r="G149" t="s">
         <v>90</v>
-      </c>
-      <c r="C149" t="s">
-        <v>47</v>
-      </c>
-      <c r="D149" t="s">
-        <v>181</v>
-      </c>
-      <c r="E149" t="s">
-        <v>32</v>
-      </c>
-      <c r="F149" t="s">
-        <v>167</v>
-      </c>
-      <c r="G149" t="s">
-        <v>34</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>199</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B150" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C150" t="s">
-        <v>36</v>
+        <v>198</v>
       </c>
       <c r="D150" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E150" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F150" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="G150" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="H150" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I150" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B151" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C151" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D151" t="s">
-        <v>129</v>
+        <v>184</v>
       </c>
       <c r="E151" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="F151" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="G151" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="H151" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I151" t="s">
-        <v>19</v>
+        <v>202</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
+        <v>192</v>
+      </c>
+      <c r="B152" t="s">
+        <v>91</v>
+      </c>
+      <c r="C152" t="s">
+        <v>36</v>
+      </c>
+      <c r="D152" t="s">
         <v>189</v>
       </c>
-      <c r="B152" t="s">
-        <v>90</v>
-      </c>
-      <c r="C152" t="s">
-        <v>195</v>
-      </c>
-      <c r="D152" t="s">
-        <v>200</v>
-      </c>
       <c r="E152" t="s">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="F152" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="G152" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="H152" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I152" t="s">
-        <v>176</v>
+        <v>42</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B153" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C153" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D153" t="s">
-        <v>182</v>
+        <v>130</v>
       </c>
       <c r="E153" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="F153" t="s">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="G153" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
       </c>
       <c r="I153" t="s">
-        <v>199</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B154" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C154" t="s">
-        <v>36</v>
+        <v>198</v>
       </c>
       <c r="D154" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E154" t="s">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="F154" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="G154" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="H154" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I154" t="s">
-        <v>41</v>
+        <v>179</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B155" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C155" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D155" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E155" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="F155" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="G155" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="H155" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I155" t="s">
-        <v>19</v>
+        <v>202</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B156" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C156" t="s">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="D156" t="s">
-        <v>107</v>
+        <v>191</v>
       </c>
       <c r="E156" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="F156" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="G156" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="H156" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I156" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B157" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C157" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D157" t="s">
-        <v>48</v>
+        <v>145</v>
       </c>
       <c r="E157" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="F157" t="s">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="G157" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
       </c>
       <c r="I157" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B158" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C158" t="s">
-        <v>36</v>
+        <v>198</v>
       </c>
       <c r="D158" t="s">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="E158" t="s">
-        <v>38</v>
+        <v>199</v>
       </c>
       <c r="F158" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G158" t="s">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="H158" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I158" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B159" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C159" t="s">
+        <v>48</v>
+      </c>
+      <c r="D159" t="s">
+        <v>49</v>
+      </c>
+      <c r="E159" t="s">
+        <v>32</v>
+      </c>
+      <c r="F159" t="s">
+        <v>171</v>
+      </c>
+      <c r="G159" t="s">
+        <v>34</v>
+      </c>
+      <c r="H159" t="s">
+        <v>41</v>
+      </c>
+      <c r="I159" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="15">
+      <c r="A160" t="s">
+        <v>192</v>
+      </c>
+      <c r="B160" t="s">
+        <v>107</v>
+      </c>
+      <c r="C160" t="s">
+        <v>36</v>
+      </c>
+      <c r="D160" t="s">
+        <v>191</v>
+      </c>
+      <c r="E160" t="s">
+        <v>38</v>
+      </c>
+      <c r="F160" t="s">
+        <v>93</v>
+      </c>
+      <c r="G160" t="s">
+        <v>143</v>
+      </c>
+      <c r="H160" t="s">
+        <v>41</v>
+      </c>
+      <c r="I160" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="15">
+      <c r="A161" t="s">
+        <v>192</v>
+      </c>
+      <c r="B161" t="s">
+        <v>107</v>
+      </c>
+      <c r="C161" t="s">
         <v>13</v>
       </c>
-      <c r="D159" t="s">
-        <v>172</v>
-      </c>
-      <c r="E159" t="s">
-        <v>115</v>
-      </c>
-      <c r="F159" t="s">
+      <c r="D161" t="s">
+        <v>145</v>
+      </c>
+      <c r="E161" t="s">
+        <v>116</v>
+      </c>
+      <c r="F161" t="s">
         <v>16</v>
       </c>
-      <c r="G159" t="s">
-        <v>89</v>
-      </c>
-      <c r="H159" t="s">
+      <c r="G161" t="s">
+        <v>90</v>
+      </c>
+      <c r="H161" t="s">
         <v>18</v>
       </c>
-      <c r="I159" t="s">
+      <c r="I161" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5879,8 +5940,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8ee6f30a-8b08-4fdf-973b-6a2081a8c121}">
-  <dimension ref="A1:I17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4fe58967-a8c2-4fcd-9e91-e3dc9858a676}">
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -5890,7 +5951,7 @@
     <col min="5" max="5" width="42.8571428571429" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="15.5714285714286" customWidth="1"/>
-    <col min="8" max="8" width="9.57142857142857" customWidth="1"/>
+    <col min="8" max="8" width="28.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5899,16 +5960,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -5928,25 +5989,25 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
@@ -5954,25 +6015,25 @@
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F3" t="s">
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -5983,28 +6044,28 @@
     </row>
     <row r="4" spans="1:9" ht="15">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I4" t="s">
         <v>19</v>
@@ -6012,28 +6073,28 @@
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F5" t="s">
         <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
@@ -6041,28 +6102,28 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
         <v>19</v>
@@ -6070,28 +6131,28 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F7" t="s">
         <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
         <v>19</v>
@@ -6099,25 +6160,25 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
@@ -6128,25 +6189,25 @@
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -6157,25 +6218,25 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E10" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F10" t="s">
         <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
@@ -6186,25 +6247,25 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E11" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
@@ -6215,175 +6276,30 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D12" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F12" t="s">
         <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15">
-      <c r="A13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B13" t="s">
-        <v>205</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>206</v>
-      </c>
-      <c r="E13" t="s">
-        <v>223</v>
-      </c>
-      <c r="F13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15">
-      <c r="A14" t="s">
-        <v>178</v>
-      </c>
-      <c r="B14" t="s">
-        <v>212</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
-        <v>206</v>
-      </c>
-      <c r="E14" t="s">
-        <v>223</v>
-      </c>
-      <c r="F14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15">
-      <c r="A15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B15" t="s">
-        <v>213</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s">
-        <v>206</v>
-      </c>
-      <c r="E15" t="s">
-        <v>223</v>
-      </c>
-      <c r="F15" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15">
-      <c r="A16" t="s">
-        <v>178</v>
-      </c>
-      <c r="B16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>206</v>
-      </c>
-      <c r="E16" t="s">
-        <v>223</v>
-      </c>
-      <c r="F16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15">
-      <c r="A17" t="s">
-        <v>178</v>
-      </c>
-      <c r="B17" t="s">
-        <v>224</v>
-      </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s">
-        <v>206</v>
-      </c>
-      <c r="E17" t="s">
-        <v>223</v>
-      </c>
-      <c r="F17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" t="s">
-        <v>87</v>
-      </c>
-      <c r="H17" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6395,7 +6311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a6f880fc-2bfa-4cd4-ab9f-4160e5246153}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bd020053-c577-46aa-b57b-ee90f5d9b509}">
   <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6412,13 +6328,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6432,16 +6348,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
@@ -6452,16 +6368,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F3" t="s">
         <v>24</v>
@@ -6472,16 +6388,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -6492,19 +6408,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
@@ -6512,16 +6428,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -6532,16 +6448,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F7" t="s">
         <v>24</v>
@@ -6552,13 +6468,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E8" t="s">
         <v>34</v>
@@ -6572,16 +6488,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
@@ -6592,19 +6508,19 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
@@ -6612,16 +6528,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -6629,19 +6545,19 @@
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F12" t="s">
         <v>24</v>
@@ -6649,116 +6565,116 @@
     </row>
     <row r="13" spans="1:6" ht="15">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E14" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E16" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E18" t="s">
         <v>34</v>
@@ -6769,19 +6685,19 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C19" t="s">
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F19" t="s">
         <v>24</v>
@@ -6789,39 +6705,39 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E21" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F21" t="s">
         <v>24</v>
@@ -6829,19 +6745,19 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F22" t="s">
         <v>24</v>
@@ -6849,39 +6765,39 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B23" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C23" t="s">
         <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E23" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F24" t="s">
         <v>24</v>
@@ -6889,39 +6805,39 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C25" t="s">
         <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E26" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F26" t="s">
         <v>24</v>
@@ -6929,19 +6845,19 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B27" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E27" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F27" t="s">
         <v>24</v>
@@ -6949,139 +6865,139 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
+        <v>181</v>
+      </c>
+      <c r="B28" t="s">
+        <v>230</v>
+      </c>
+      <c r="C28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28" t="s">
         <v>178</v>
       </c>
-      <c r="B28" t="s">
-        <v>229</v>
-      </c>
-      <c r="C28" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" t="s">
-        <v>234</v>
-      </c>
-      <c r="E28" t="s">
-        <v>175</v>
-      </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E29" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E30" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B31" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E31" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F31" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B32" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E32" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B33" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C34" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E34" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F34" t="s">
         <v>24</v>
@@ -7089,16 +7005,16 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B35" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C35" t="s">
         <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E35" t="s">
         <v>34</v>
@@ -7109,42 +7025,42 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B36" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E36" t="s">
         <v>34</v>
       </c>
       <c r="F36" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E37" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F37" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="261">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -570,6 +570,9 @@
     <t>08.10.2026</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>1FC|gr2</t>
   </si>
   <si>
@@ -579,6 +582,12 @@
     <t>1K|gr1</t>
   </si>
   <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>p. Karczmarz, j. angielski za lekcję 3</t>
+  </si>
+  <si>
     <t>1FC|gr1</t>
   </si>
   <si>
@@ -588,6 +597,12 @@
     <t>p. Filusz, matematyka za lekcję 9</t>
   </si>
   <si>
+    <t>1WB</t>
+  </si>
+  <si>
+    <t>p. Biczysko, fizyka za lekcję 8</t>
+  </si>
+  <si>
     <t>1S|gr2</t>
   </si>
   <si>
@@ -597,6 +612,9 @@
     <t>Danielewski Paweł</t>
   </si>
   <si>
+    <t>Erasmus + / Wyjazd FERS</t>
+  </si>
+  <si>
     <t>1B|gr1</t>
   </si>
   <si>
@@ -634,6 +652,15 @@
   </si>
   <si>
     <t>3FB</t>
+  </si>
+  <si>
+    <t>Technika w produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>1TFH</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>Godzina</t>
@@ -1227,7 +1254,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c8c43a2e-3d8c-46ea-be3c-77a45be146c9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{49730d5d-3bab-47fc-851c-76609f23a735}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1248,8 +1275,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a1c45121-e8a4-4edf-bd82-a0a61dfb6950}">
-  <dimension ref="A1:I161"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e1f78c2c-2331-4e66-a197-67bd70021d8f}">
+  <dimension ref="A1:I173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -3948,7 +3975,7 @@
         <v>116</v>
       </c>
       <c r="F93" t="s">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="G93" t="s">
         <v>159</v>
@@ -4545,28 +4572,28 @@
         <v>181</v>
       </c>
       <c r="B114" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="E114" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F114" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="G114" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H114" t="s">
         <v>24</v>
       </c>
       <c r="I114" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
@@ -4574,25 +4601,25 @@
         <v>181</v>
       </c>
       <c r="B115" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C115" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="E115" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="F115" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G115" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="H115" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I115" t="s">
         <v>35</v>
@@ -4603,13 +4630,13 @@
         <v>181</v>
       </c>
       <c r="B116" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C116" t="s">
         <v>30</v>
       </c>
       <c r="D116" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E116" t="s">
         <v>32</v>
@@ -4632,28 +4659,28 @@
         <v>181</v>
       </c>
       <c r="B117" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C117" t="s">
         <v>48</v>
       </c>
       <c r="D117" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="E117" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F117" t="s">
         <v>171</v>
       </c>
       <c r="G117" t="s">
-        <v>17</v>
+        <v>184</v>
       </c>
       <c r="H117" t="s">
         <v>41</v>
       </c>
       <c r="I117" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
@@ -4661,22 +4688,22 @@
         <v>181</v>
       </c>
       <c r="B118" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C118" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="E118" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="F118" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="G118" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="H118" t="s">
         <v>24</v>
@@ -4690,28 +4717,28 @@
         <v>181</v>
       </c>
       <c r="B119" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C119" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D119" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E119" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F119" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G119" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="H119" t="s">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
@@ -4719,25 +4746,25 @@
         <v>181</v>
       </c>
       <c r="B120" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C120" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D120" t="s">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="E120" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F120" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G120" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="H120" t="s">
-        <v>187</v>
+        <v>41</v>
       </c>
       <c r="I120" t="s">
         <v>19</v>
@@ -4748,25 +4775,25 @@
         <v>181</v>
       </c>
       <c r="B121" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C121" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="E121" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F121" t="s">
-        <v>171</v>
+        <v>28</v>
       </c>
       <c r="G121" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H121" t="s">
-        <v>41</v>
+        <v>187</v>
       </c>
       <c r="I121" t="s">
         <v>19</v>
@@ -4777,13 +4804,13 @@
         <v>181</v>
       </c>
       <c r="B122" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C122" t="s">
         <v>30</v>
       </c>
       <c r="D122" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="E122" t="s">
         <v>32</v>
@@ -4792,13 +4819,13 @@
         <v>165</v>
       </c>
       <c r="G122" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H122" t="s">
         <v>24</v>
       </c>
       <c r="I122" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
@@ -4806,7 +4833,7 @@
         <v>181</v>
       </c>
       <c r="B123" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C123" t="s">
         <v>48</v>
@@ -4821,10 +4848,10 @@
         <v>171</v>
       </c>
       <c r="G123" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H123" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="I123" t="s">
         <v>19</v>
@@ -4835,28 +4862,28 @@
         <v>181</v>
       </c>
       <c r="B124" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C124" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E124" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="F124" t="s">
-        <v>61</v>
+        <v>169</v>
       </c>
       <c r="G124" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="H124" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I124" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
@@ -4864,28 +4891,28 @@
         <v>181</v>
       </c>
       <c r="B125" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C125" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D125" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="E125" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="F125" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="G125" t="s">
+        <v>88</v>
+      </c>
+      <c r="H125" t="s">
         <v>190</v>
       </c>
-      <c r="H125" t="s">
-        <v>41</v>
-      </c>
       <c r="I125" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
@@ -4893,25 +4920,25 @@
         <v>181</v>
       </c>
       <c r="B126" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C126" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D126" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="E126" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F126" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G126" t="s">
         <v>90</v>
       </c>
       <c r="H126" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I126" t="s">
         <v>19</v>
@@ -4922,28 +4949,28 @@
         <v>181</v>
       </c>
       <c r="B127" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C127" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="E127" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F127" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G127" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="H127" t="s">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="I127" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
@@ -4951,28 +4978,28 @@
         <v>181</v>
       </c>
       <c r="B128" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C128" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="E128" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F128" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="G128" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="H128" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I128" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
@@ -4980,28 +5007,28 @@
         <v>181</v>
       </c>
       <c r="B129" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C129" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D129" t="s">
-        <v>14</v>
+        <v>193</v>
       </c>
       <c r="E129" t="s">
-        <v>176</v>
+        <v>38</v>
       </c>
       <c r="F129" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G129" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="H129" t="s">
         <v>41</v>
       </c>
       <c r="I129" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
@@ -5009,13 +5036,13 @@
         <v>181</v>
       </c>
       <c r="B130" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C130" t="s">
         <v>36</v>
       </c>
       <c r="D130" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E130" t="s">
         <v>38</v>
@@ -5024,7 +5051,7 @@
         <v>61</v>
       </c>
       <c r="G130" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H130" t="s">
         <v>41</v>
@@ -5038,54 +5065,54 @@
         <v>181</v>
       </c>
       <c r="B131" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C131" t="s">
         <v>13</v>
       </c>
       <c r="D131" t="s">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="E131" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="F131" t="s">
-        <v>177</v>
+        <v>16</v>
       </c>
       <c r="G131" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="H131" t="s">
         <v>41</v>
       </c>
       <c r="I131" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="C132" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="E132" t="s">
-        <v>193</v>
+        <v>27</v>
       </c>
       <c r="F132" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G132" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H132" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I132" t="s">
         <v>19</v>
@@ -5093,28 +5120,28 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B133" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="C133" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D133" t="s">
         <v>108</v>
       </c>
       <c r="E133" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F133" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G133" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H133" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I133" t="s">
         <v>19</v>
@@ -5122,28 +5149,28 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B134" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D134" t="s">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="E134" t="s">
         <v>38</v>
       </c>
       <c r="F134" t="s">
-        <v>171</v>
+        <v>61</v>
       </c>
       <c r="G134" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H134" t="s">
-        <v>41</v>
+        <v>196</v>
       </c>
       <c r="I134" t="s">
         <v>19</v>
@@ -5151,144 +5178,144 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B135" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="C135" t="s">
         <v>13</v>
       </c>
       <c r="D135" t="s">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="E135" t="s">
-        <v>99</v>
+        <v>176</v>
       </c>
       <c r="F135" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="G135" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="H135" t="s">
         <v>41</v>
       </c>
       <c r="I135" t="s">
-        <v>35</v>
+        <v>179</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B136" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="C136" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D136" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="E136" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F136" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="G136" t="s">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="H136" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I136" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B137" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="C137" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D137" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="E137" t="s">
         <v>38</v>
       </c>
       <c r="F137" t="s">
-        <v>180</v>
+        <v>61</v>
       </c>
       <c r="G137" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="H137" t="s">
         <v>41</v>
       </c>
       <c r="I137" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B138" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="C138" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D138" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F138" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="G138" t="s">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="H138" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I138" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B139" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C139" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D139" t="s">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="E139" t="s">
-        <v>38</v>
+        <v>199</v>
       </c>
       <c r="F139" t="s">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="G139" t="s">
         <v>17</v>
       </c>
       <c r="H139" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I139" t="s">
         <v>19</v>
@@ -5296,22 +5323,22 @@
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B140" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="C140" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D140" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="E140" t="s">
         <v>38</v>
       </c>
       <c r="F140" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="G140" t="s">
         <v>17</v>
@@ -5325,80 +5352,80 @@
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B141" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C141" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D141" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="E141" t="s">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="F141" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="G141" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="H141" t="s">
         <v>41</v>
       </c>
       <c r="I141" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B142" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C142" t="s">
-        <v>198</v>
+        <v>13</v>
       </c>
       <c r="D142" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="E142" t="s">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="F142" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="G142" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H142" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I142" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B143" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C143" t="s">
         <v>30</v>
       </c>
       <c r="D143" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E143" t="s">
         <v>32</v>
       </c>
       <c r="F143" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G143" t="s">
         <v>17</v>
@@ -5412,57 +5439,57 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B144" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C144" t="s">
         <v>48</v>
       </c>
       <c r="D144" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="E144" t="s">
         <v>38</v>
       </c>
       <c r="F144" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G144" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H144" t="s">
-        <v>201</v>
+        <v>41</v>
       </c>
       <c r="I144" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B145" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C145" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D145" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="E145" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F145" t="s">
-        <v>59</v>
+        <v>203</v>
       </c>
       <c r="G145" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="H145" t="s">
-        <v>201</v>
+        <v>24</v>
       </c>
       <c r="I145" t="s">
         <v>19</v>
@@ -5470,28 +5497,28 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B146" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C146" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D146" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="E146" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="F146" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="G146" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="H146" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I146" t="s">
         <v>19</v>
@@ -5499,28 +5526,28 @@
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B147" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C147" t="s">
-        <v>198</v>
+        <v>36</v>
       </c>
       <c r="D147" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E147" t="s">
-        <v>199</v>
+        <v>38</v>
       </c>
       <c r="F147" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="G147" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="H147" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I147" t="s">
         <v>19</v>
@@ -5528,57 +5555,57 @@
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B148" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C148" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D148" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="E148" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="F148" t="s">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="G148" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="H148" t="s">
         <v>41</v>
       </c>
       <c r="I148" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B149" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C149" t="s">
-        <v>13</v>
+        <v>204</v>
       </c>
       <c r="D149" t="s">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="E149" t="s">
-        <v>116</v>
+        <v>205</v>
       </c>
       <c r="F149" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="G149" t="s">
-        <v>90</v>
+        <v>206</v>
       </c>
       <c r="H149" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I149" t="s">
         <v>19</v>
@@ -5586,115 +5613,115 @@
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B150" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C150" t="s">
-        <v>198</v>
+        <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>203</v>
+        <v>161</v>
       </c>
       <c r="E150" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="F150" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G150" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="H150" t="s">
         <v>24</v>
       </c>
       <c r="I150" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B151" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C151" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D151" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E151" t="s">
         <v>32</v>
       </c>
       <c r="F151" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="G151" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H151" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I151" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B152" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C152" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D152" t="s">
-        <v>189</v>
+        <v>104</v>
       </c>
       <c r="E152" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="F152" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="G152" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="H152" t="s">
-        <v>41</v>
+        <v>207</v>
       </c>
       <c r="I152" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B153" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C153" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D153" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="E153" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="F153" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="G153" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H153" t="s">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="I153" t="s">
         <v>19</v>
@@ -5702,144 +5729,144 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B154" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C154" t="s">
-        <v>198</v>
+        <v>13</v>
       </c>
       <c r="D154" t="s">
-        <v>203</v>
+        <v>130</v>
       </c>
       <c r="E154" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="F154" t="s">
         <v>16</v>
       </c>
       <c r="G154" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="H154" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I154" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B155" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C155" t="s">
-        <v>48</v>
+        <v>204</v>
       </c>
       <c r="D155" t="s">
-        <v>185</v>
+        <v>52</v>
       </c>
       <c r="E155" t="s">
-        <v>32</v>
+        <v>205</v>
       </c>
       <c r="F155" t="s">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="G155" t="s">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="H155" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I155" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B156" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C156" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>191</v>
+        <v>43</v>
       </c>
       <c r="E156" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="F156" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="G156" t="s">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="H156" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I156" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B157" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C157" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D157" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E157" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="F157" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="G157" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="H157" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I157" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B158" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C158" t="s">
-        <v>198</v>
+        <v>13</v>
       </c>
       <c r="D158" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="E158" t="s">
-        <v>199</v>
+        <v>116</v>
       </c>
       <c r="F158" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="G158" t="s">
         <v>90</v>
       </c>
       <c r="H158" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I158" t="s">
         <v>19</v>
@@ -5847,28 +5874,28 @@
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B159" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C159" t="s">
-        <v>48</v>
+        <v>204</v>
       </c>
       <c r="D159" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="E159" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="F159" t="s">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="G159" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="H159" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I159" t="s">
         <v>35</v>
@@ -5876,59 +5903,407 @@
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B160" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C160" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>191</v>
+        <v>69</v>
       </c>
       <c r="E160" t="s">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="F160" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="G160" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="H160" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I160" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B161" t="s">
+        <v>91</v>
+      </c>
+      <c r="C161" t="s">
+        <v>48</v>
+      </c>
+      <c r="D161" t="s">
+        <v>185</v>
+      </c>
+      <c r="E161" t="s">
+        <v>32</v>
+      </c>
+      <c r="F161" t="s">
+        <v>171</v>
+      </c>
+      <c r="G161" t="s">
+        <v>34</v>
+      </c>
+      <c r="H161" t="s">
+        <v>41</v>
+      </c>
+      <c r="I161" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="15">
+      <c r="A162" t="s">
+        <v>198</v>
+      </c>
+      <c r="B162" t="s">
+        <v>91</v>
+      </c>
+      <c r="C162" t="s">
+        <v>36</v>
+      </c>
+      <c r="D162" t="s">
+        <v>194</v>
+      </c>
+      <c r="E162" t="s">
+        <v>105</v>
+      </c>
+      <c r="F162" t="s">
+        <v>93</v>
+      </c>
+      <c r="G162" t="s">
+        <v>138</v>
+      </c>
+      <c r="H162" t="s">
+        <v>41</v>
+      </c>
+      <c r="I162" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="15">
+      <c r="A163" t="s">
+        <v>198</v>
+      </c>
+      <c r="B163" t="s">
+        <v>91</v>
+      </c>
+      <c r="C163" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163" t="s">
+        <v>130</v>
+      </c>
+      <c r="E163" t="s">
+        <v>116</v>
+      </c>
+      <c r="F163" t="s">
+        <v>16</v>
+      </c>
+      <c r="G163" t="s">
+        <v>90</v>
+      </c>
+      <c r="H163" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="15">
+      <c r="A164" t="s">
+        <v>198</v>
+      </c>
+      <c r="B164" t="s">
+        <v>91</v>
+      </c>
+      <c r="C164" t="s">
+        <v>204</v>
+      </c>
+      <c r="D164" t="s">
+        <v>209</v>
+      </c>
+      <c r="E164" t="s">
+        <v>176</v>
+      </c>
+      <c r="F164" t="s">
+        <v>16</v>
+      </c>
+      <c r="G164" t="s">
+        <v>178</v>
+      </c>
+      <c r="H164" t="s">
+        <v>24</v>
+      </c>
+      <c r="I164" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="15">
+      <c r="A165" t="s">
+        <v>198</v>
+      </c>
+      <c r="B165" t="s">
+        <v>91</v>
+      </c>
+      <c r="C165" t="s">
+        <v>25</v>
+      </c>
+      <c r="D165" t="s">
+        <v>211</v>
+      </c>
+      <c r="E165" t="s">
+        <v>76</v>
+      </c>
+      <c r="F165" t="s">
+        <v>212</v>
+      </c>
+      <c r="G165" t="s">
+        <v>128</v>
+      </c>
+      <c r="H165" t="s">
+        <v>24</v>
+      </c>
+      <c r="I165" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="15">
+      <c r="A166" t="s">
+        <v>198</v>
+      </c>
+      <c r="B166" t="s">
+        <v>97</v>
+      </c>
+      <c r="C166" t="s">
+        <v>48</v>
+      </c>
+      <c r="D166" t="s">
+        <v>188</v>
+      </c>
+      <c r="E166" t="s">
+        <v>32</v>
+      </c>
+      <c r="F166" t="s">
+        <v>171</v>
+      </c>
+      <c r="G166" t="s">
+        <v>34</v>
+      </c>
+      <c r="H166" t="s">
+        <v>41</v>
+      </c>
+      <c r="I166" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="15">
+      <c r="A167" t="s">
+        <v>198</v>
+      </c>
+      <c r="B167" t="s">
+        <v>97</v>
+      </c>
+      <c r="C167" t="s">
+        <v>36</v>
+      </c>
+      <c r="D167" t="s">
+        <v>197</v>
+      </c>
+      <c r="E167" t="s">
+        <v>38</v>
+      </c>
+      <c r="F167" t="s">
+        <v>93</v>
+      </c>
+      <c r="G167" t="s">
+        <v>143</v>
+      </c>
+      <c r="H167" t="s">
+        <v>41</v>
+      </c>
+      <c r="I167" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="15">
+      <c r="A168" t="s">
+        <v>198</v>
+      </c>
+      <c r="B168" t="s">
+        <v>97</v>
+      </c>
+      <c r="C168" t="s">
+        <v>13</v>
+      </c>
+      <c r="D168" t="s">
+        <v>145</v>
+      </c>
+      <c r="E168" t="s">
+        <v>116</v>
+      </c>
+      <c r="F168" t="s">
+        <v>16</v>
+      </c>
+      <c r="G168" t="s">
+        <v>90</v>
+      </c>
+      <c r="H168" t="s">
+        <v>18</v>
+      </c>
+      <c r="I168" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="15">
+      <c r="A169" t="s">
+        <v>198</v>
+      </c>
+      <c r="B169" t="s">
+        <v>97</v>
+      </c>
+      <c r="C169" t="s">
+        <v>204</v>
+      </c>
+      <c r="D169" t="s">
+        <v>108</v>
+      </c>
+      <c r="E169" t="s">
+        <v>205</v>
+      </c>
+      <c r="F169" t="s">
+        <v>77</v>
+      </c>
+      <c r="G169" t="s">
+        <v>90</v>
+      </c>
+      <c r="H169" t="s">
+        <v>24</v>
+      </c>
+      <c r="I169" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="15">
+      <c r="A170" t="s">
+        <v>198</v>
+      </c>
+      <c r="B170" t="s">
+        <v>97</v>
+      </c>
+      <c r="C170" t="s">
+        <v>25</v>
+      </c>
+      <c r="D170" t="s">
+        <v>146</v>
+      </c>
+      <c r="E170" t="s">
+        <v>210</v>
+      </c>
+      <c r="F170" t="s">
+        <v>124</v>
+      </c>
+      <c r="G170" t="s">
+        <v>71</v>
+      </c>
+      <c r="H170" t="s">
+        <v>24</v>
+      </c>
+      <c r="I170" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="15">
+      <c r="A171" t="s">
+        <v>198</v>
+      </c>
+      <c r="B171" t="s">
         <v>107</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C171" t="s">
+        <v>48</v>
+      </c>
+      <c r="D171" t="s">
+        <v>49</v>
+      </c>
+      <c r="E171" t="s">
+        <v>32</v>
+      </c>
+      <c r="F171" t="s">
+        <v>171</v>
+      </c>
+      <c r="G171" t="s">
+        <v>34</v>
+      </c>
+      <c r="H171" t="s">
+        <v>41</v>
+      </c>
+      <c r="I171" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="15">
+      <c r="A172" t="s">
+        <v>198</v>
+      </c>
+      <c r="B172" t="s">
+        <v>107</v>
+      </c>
+      <c r="C172" t="s">
+        <v>36</v>
+      </c>
+      <c r="D172" t="s">
+        <v>197</v>
+      </c>
+      <c r="E172" t="s">
+        <v>38</v>
+      </c>
+      <c r="F172" t="s">
+        <v>93</v>
+      </c>
+      <c r="G172" t="s">
+        <v>143</v>
+      </c>
+      <c r="H172" t="s">
+        <v>41</v>
+      </c>
+      <c r="I172" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="15">
+      <c r="A173" t="s">
+        <v>198</v>
+      </c>
+      <c r="B173" t="s">
+        <v>107</v>
+      </c>
+      <c r="C173" t="s">
         <v>13</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D173" t="s">
         <v>145</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E173" t="s">
         <v>116</v>
       </c>
-      <c r="F161" t="s">
+      <c r="F173" t="s">
         <v>16</v>
       </c>
-      <c r="G161" t="s">
+      <c r="G173" t="s">
         <v>90</v>
       </c>
-      <c r="H161" t="s">
+      <c r="H173" t="s">
         <v>18</v>
       </c>
-      <c r="I161" t="s">
+      <c r="I173" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5940,7 +6315,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4fe58967-a8c2-4fcd-9e91-e3dc9858a676}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{53606715-7ab7-44aa-b488-3168f3e3a607}">
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5960,16 +6335,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -5989,13 +6364,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C2" t="s">
         <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
         <v>121</v>
@@ -6018,13 +6393,13 @@
         <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C3" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
         <v>110</v>
@@ -6033,7 +6408,7 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -6047,16 +6422,16 @@
         <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -6076,13 +6451,13 @@
         <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E5" t="s">
         <v>121</v>
@@ -6105,16 +6480,16 @@
         <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C6" t="s">
         <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E6" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -6134,13 +6509,13 @@
         <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C7" t="s">
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E7" t="s">
         <v>121</v>
@@ -6163,16 +6538,16 @@
         <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E8" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
@@ -6192,22 +6567,22 @@
         <v>132</v>
       </c>
       <c r="B9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" t="s">
         <v>220</v>
       </c>
-      <c r="C9" t="s">
-        <v>211</v>
-      </c>
       <c r="D9" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E9" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
         <v>221</v>
-      </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>212</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -6221,16 +6596,16 @@
         <v>132</v>
       </c>
       <c r="B10" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E10" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="F10" t="s">
         <v>24</v>
@@ -6250,16 +6625,16 @@
         <v>132</v>
       </c>
       <c r="B11" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E11" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -6279,13 +6654,13 @@
         <v>181</v>
       </c>
       <c r="B12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" t="s">
         <v>220</v>
       </c>
-      <c r="C12" t="s">
-        <v>211</v>
-      </c>
       <c r="D12" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E12" t="s">
         <v>110</v>
@@ -6294,7 +6669,7 @@
         <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
@@ -6311,8 +6686,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bd020053-c577-46aa-b57b-ee90f5d9b509}">
-  <dimension ref="A1:F37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0b8b47db-9b62-4233-874c-c57b4572568f}">
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6328,13 +6703,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6348,16 +6723,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
@@ -6368,13 +6743,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E3" t="s">
         <v>157</v>
@@ -6388,13 +6763,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E4" t="s">
         <v>173</v>
@@ -6408,13 +6783,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E5" t="s">
         <v>178</v>
@@ -6428,13 +6803,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E6" t="s">
         <v>144</v>
@@ -6448,13 +6823,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E7" t="s">
         <v>106</v>
@@ -6468,13 +6843,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E8" t="s">
         <v>34</v>
@@ -6488,13 +6863,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E9" t="s">
         <v>48</v>
@@ -6508,13 +6883,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E10" t="s">
         <v>159</v>
@@ -6528,16 +6903,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C11" t="s">
         <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E11" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -6548,13 +6923,13 @@
         <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="E12" t="s">
         <v>163</v>
@@ -6568,13 +6943,13 @@
         <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E13" t="s">
         <v>54</v>
@@ -6588,13 +6963,13 @@
         <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E14" t="s">
         <v>178</v>
@@ -6608,16 +6983,16 @@
         <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C15" t="s">
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E15" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F15" t="s">
         <v>41</v>
@@ -6628,13 +7003,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C16" t="s">
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E16" t="s">
         <v>159</v>
@@ -6648,16 +7023,16 @@
         <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E17" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F17" t="s">
         <v>41</v>
@@ -6668,13 +7043,13 @@
         <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E18" t="s">
         <v>34</v>
@@ -6688,16 +7063,16 @@
         <v>132</v>
       </c>
       <c r="B19" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C19" t="s">
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E19" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F19" t="s">
         <v>24</v>
@@ -6708,13 +7083,13 @@
         <v>132</v>
       </c>
       <c r="B20" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E20" t="s">
         <v>65</v>
@@ -6728,16 +7103,16 @@
         <v>132</v>
       </c>
       <c r="B21" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C21" t="s">
         <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E21" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F21" t="s">
         <v>24</v>
@@ -6748,16 +7123,16 @@
         <v>132</v>
       </c>
       <c r="B22" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C22" t="s">
         <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="E22" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F22" t="s">
         <v>24</v>
@@ -6768,16 +7143,16 @@
         <v>132</v>
       </c>
       <c r="B23" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C23" t="s">
         <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E23" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F23" t="s">
         <v>41</v>
@@ -6788,16 +7163,16 @@
         <v>132</v>
       </c>
       <c r="B24" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C24" t="s">
         <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="E24" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F24" t="s">
         <v>24</v>
@@ -6808,13 +7183,13 @@
         <v>132</v>
       </c>
       <c r="B25" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C25" t="s">
         <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E25" t="s">
         <v>126</v>
@@ -6828,16 +7203,16 @@
         <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C26" t="s">
         <v>138</v>
       </c>
       <c r="D26" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E26" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F26" t="s">
         <v>24</v>
@@ -6848,16 +7223,16 @@
         <v>181</v>
       </c>
       <c r="B27" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E27" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F27" t="s">
         <v>24</v>
@@ -6868,13 +7243,13 @@
         <v>181</v>
       </c>
       <c r="B28" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C28" t="s">
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E28" t="s">
         <v>178</v>
@@ -6888,19 +7263,19 @@
         <v>181</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E29" t="s">
-        <v>250</v>
+        <v>78</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
@@ -6908,16 +7283,16 @@
         <v>181</v>
       </c>
       <c r="B30" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E30" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="F30" t="s">
         <v>41</v>
@@ -6928,36 +7303,36 @@
         <v>181</v>
       </c>
       <c r="B31" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E31" t="s">
-        <v>198</v>
+        <v>54</v>
       </c>
       <c r="F31" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E32" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="F32" t="s">
         <v>41</v>
@@ -6965,19 +7340,19 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B33" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E33" t="s">
-        <v>128</v>
+        <v>204</v>
       </c>
       <c r="F33" t="s">
         <v>41</v>
@@ -6985,81 +7360,161 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B34" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="C34" t="s">
-        <v>198</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E34" t="s">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="F34" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="E35" t="s">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B36" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" t="s">
         <v>237</v>
       </c>
-      <c r="C36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" t="s">
-        <v>232</v>
-      </c>
       <c r="E36" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="F36" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C37" t="s">
+        <v>204</v>
+      </c>
+      <c r="D37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E37" t="s">
+        <v>258</v>
+      </c>
+      <c r="F37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15">
+      <c r="A38" t="s">
+        <v>198</v>
+      </c>
+      <c r="B38" t="s">
+        <v>252</v>
+      </c>
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" t="s">
+        <v>241</v>
+      </c>
+      <c r="E38" t="s">
+        <v>34</v>
+      </c>
+      <c r="F38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15">
+      <c r="A39" t="s">
+        <v>198</v>
+      </c>
+      <c r="B39" t="s">
+        <v>246</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" t="s">
+        <v>34</v>
+      </c>
+      <c r="F39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15">
+      <c r="A40" t="s">
+        <v>198</v>
+      </c>
+      <c r="B40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C40" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" t="s">
+        <v>237</v>
+      </c>
+      <c r="E40" t="s">
+        <v>112</v>
+      </c>
+      <c r="F40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15">
+      <c r="A41" t="s">
+        <v>198</v>
+      </c>
+      <c r="B41" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" t="s">
         <v>48</v>
       </c>
-      <c r="D37" t="s">
-        <v>235</v>
-      </c>
-      <c r="E37" t="s">
-        <v>190</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="D41" t="s">
+        <v>244</v>
+      </c>
+      <c r="E41" t="s">
+        <v>195</v>
+      </c>
+      <c r="F41" t="s">
         <v>41</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="267">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -594,6 +594,12 @@
     <t>Erasmus+ / p. Nestoruk, wychowanie fizyczne za lekcję 2</t>
   </si>
   <si>
+    <t>2WA</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>p. Filusz, matematyka za lekcję 9</t>
   </si>
   <si>
@@ -612,6 +618,9 @@
     <t>Danielewski Paweł</t>
   </si>
   <si>
+    <t>p. Sobczak, przeniesienie techniki fryzjerskie na lekcję 7</t>
+  </si>
+  <si>
     <t>Erasmus + / Wyjazd FERS</t>
   </si>
   <si>
@@ -624,9 +633,6 @@
     <t>Rozwój kompetencji zawodowych - fryzjerstwo wellness</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>Małecka Barbara</t>
   </si>
   <si>
@@ -663,6 +669,12 @@
     <t>4</t>
   </si>
   <si>
+    <t>Derezińska Katarzyna</t>
+  </si>
+  <si>
+    <t>Brak</t>
+  </si>
+  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -804,7 +816,13 @@
     <t>Sobczak Anna</t>
   </si>
   <si>
+    <t>Czukiewska Bożena</t>
+  </si>
+  <si>
     <t>07:55-08:00</t>
+  </si>
+  <si>
+    <t>17:20-17:25</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1272,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{49730d5d-3bab-47fc-851c-76609f23a735}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{95829385-fc75-4eaa-8307-ebea8736095e}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1275,8 +1293,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e1f78c2c-2331-4e66-a197-67bd70021d8f}">
-  <dimension ref="A1:I173"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8a4629d2-ecac-47f1-ab56-471c39cc8acd}">
+  <dimension ref="A1:I181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -4865,19 +4883,19 @@
         <v>72</v>
       </c>
       <c r="C124" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="D124" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="E124" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="F124" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="G124" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="H124" t="s">
         <v>24</v>
@@ -4891,28 +4909,28 @@
         <v>181</v>
       </c>
       <c r="B125" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C125" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="E125" t="s">
-        <v>32</v>
+        <v>147</v>
       </c>
       <c r="F125" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G125" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="H125" t="s">
-        <v>190</v>
+        <v>24</v>
       </c>
       <c r="I125" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
@@ -4923,22 +4941,22 @@
         <v>81</v>
       </c>
       <c r="C126" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D126" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="E126" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F126" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G126" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H126" t="s">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="I126" t="s">
         <v>19</v>
@@ -4952,22 +4970,22 @@
         <v>81</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D127" t="s">
-        <v>191</v>
+        <v>74</v>
       </c>
       <c r="E127" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F127" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="G127" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H127" t="s">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="I127" t="s">
         <v>19</v>
@@ -4978,28 +4996,28 @@
         <v>181</v>
       </c>
       <c r="B128" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C128" t="s">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="D128" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="E128" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F128" t="s">
-        <v>165</v>
+        <v>45</v>
       </c>
       <c r="G128" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="H128" t="s">
         <v>24</v>
       </c>
       <c r="I128" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
@@ -5007,25 +5025,25 @@
         <v>181</v>
       </c>
       <c r="B129" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C129" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D129" t="s">
         <v>193</v>
       </c>
       <c r="E129" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F129" t="s">
-        <v>171</v>
+        <v>28</v>
       </c>
       <c r="G129" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H129" t="s">
-        <v>41</v>
+        <v>194</v>
       </c>
       <c r="I129" t="s">
         <v>19</v>
@@ -5039,22 +5057,22 @@
         <v>83</v>
       </c>
       <c r="C130" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D130" t="s">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="E130" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F130" t="s">
-        <v>61</v>
+        <v>165</v>
       </c>
       <c r="G130" t="s">
         <v>90</v>
       </c>
       <c r="H130" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I130" t="s">
         <v>19</v>
@@ -5068,25 +5086,25 @@
         <v>83</v>
       </c>
       <c r="C131" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D131" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="E131" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="F131" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="G131" t="s">
-        <v>195</v>
+        <v>90</v>
       </c>
       <c r="H131" t="s">
         <v>41</v>
       </c>
       <c r="I131" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
@@ -5097,22 +5115,22 @@
         <v>83</v>
       </c>
       <c r="C132" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D132" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E132" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F132" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="G132" t="s">
         <v>90</v>
       </c>
       <c r="H132" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I132" t="s">
         <v>19</v>
@@ -5123,28 +5141,28 @@
         <v>181</v>
       </c>
       <c r="B133" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C133" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D133" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="E133" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="F133" t="s">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c r="G133" t="s">
-        <v>90</v>
+        <v>197</v>
       </c>
       <c r="H133" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I133" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
@@ -5152,25 +5170,25 @@
         <v>181</v>
       </c>
       <c r="B134" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C134" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="D134" t="s">
-        <v>174</v>
+        <v>109</v>
       </c>
       <c r="E134" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="F134" t="s">
-        <v>61</v>
+        <v>191</v>
       </c>
       <c r="G134" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H134" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I134" t="s">
         <v>19</v>
@@ -5181,28 +5199,28 @@
         <v>181</v>
       </c>
       <c r="B135" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C135" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="E135" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="F135" t="s">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="G135" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="H135" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I135" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
@@ -5210,28 +5228,28 @@
         <v>181</v>
       </c>
       <c r="B136" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C136" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D136" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="E136" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F136" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="G136" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="H136" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I136" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15">
@@ -5239,13 +5257,13 @@
         <v>181</v>
       </c>
       <c r="B137" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C137" t="s">
         <v>36</v>
       </c>
       <c r="D137" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="E137" t="s">
         <v>38</v>
@@ -5254,10 +5272,10 @@
         <v>61</v>
       </c>
       <c r="G137" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H137" t="s">
-        <v>41</v>
+        <v>199</v>
       </c>
       <c r="I137" t="s">
         <v>19</v>
@@ -5268,13 +5286,13 @@
         <v>181</v>
       </c>
       <c r="B138" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C138" t="s">
         <v>13</v>
       </c>
       <c r="D138" t="s">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="E138" t="s">
         <v>176</v>
@@ -5294,28 +5312,28 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="C139" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="D139" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E139" t="s">
-        <v>199</v>
+        <v>147</v>
       </c>
       <c r="F139" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="G139" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H139" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I139" t="s">
         <v>19</v>
@@ -5323,57 +5341,57 @@
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B140" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C140" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D140" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="E140" t="s">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="F140" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G140" t="s">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="H140" t="s">
         <v>41</v>
       </c>
       <c r="I140" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B141" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="C141" t="s">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="D141" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="E141" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="F141" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="G141" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H141" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I141" t="s">
         <v>19</v>
@@ -5381,115 +5399,115 @@
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B142" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="C142" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="E142" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="F142" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="G142" t="s">
-        <v>201</v>
+        <v>17</v>
       </c>
       <c r="H142" t="s">
         <v>41</v>
       </c>
       <c r="I142" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B143" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="C143" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D143" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F143" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="G143" t="s">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="H143" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I143" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B144" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C144" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D144" t="s">
-        <v>193</v>
+        <v>130</v>
       </c>
       <c r="E144" t="s">
-        <v>38</v>
+        <v>202</v>
       </c>
       <c r="F144" t="s">
-        <v>180</v>
+        <v>16</v>
       </c>
       <c r="G144" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="H144" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B145" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="C145" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D145" t="s">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="E145" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F145" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="G145" t="s">
         <v>17</v>
       </c>
       <c r="H145" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I145" t="s">
         <v>19</v>
@@ -5497,16 +5515,16 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B146" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C146" t="s">
         <v>48</v>
       </c>
       <c r="D146" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="E146" t="s">
         <v>38</v>
@@ -5526,144 +5544,144 @@
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B147" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C147" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D147" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="E147" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="F147" t="s">
-        <v>59</v>
+        <v>191</v>
       </c>
       <c r="G147" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="H147" t="s">
         <v>41</v>
       </c>
       <c r="I147" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B148" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C148" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D148" t="s">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="E148" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="F148" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="G148" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="H148" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I148" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B149" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C149" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="D149" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="E149" t="s">
-        <v>205</v>
+        <v>38</v>
       </c>
       <c r="F149" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="G149" t="s">
-        <v>206</v>
+        <v>94</v>
       </c>
       <c r="H149" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I149" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B150" t="s">
         <v>72</v>
       </c>
       <c r="C150" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D150" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="E150" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F150" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="G150" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="H150" t="s">
         <v>24</v>
       </c>
       <c r="I150" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B151" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C151" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D151" t="s">
-        <v>202</v>
+        <v>58</v>
       </c>
       <c r="E151" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F151" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="G151" t="s">
         <v>17</v>
       </c>
       <c r="H151" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I151" t="s">
         <v>19</v>
@@ -5671,28 +5689,28 @@
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B152" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C152" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D152" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="E152" t="s">
         <v>38</v>
       </c>
       <c r="F152" t="s">
-        <v>171</v>
+        <v>59</v>
       </c>
       <c r="G152" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="H152" t="s">
-        <v>207</v>
+        <v>41</v>
       </c>
       <c r="I152" t="s">
         <v>19</v>
@@ -5700,57 +5718,57 @@
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B153" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C153" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D153" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="E153" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="F153" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="G153" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="H153" t="s">
-        <v>207</v>
+        <v>41</v>
       </c>
       <c r="I153" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B154" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C154" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
       <c r="D154" t="s">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="E154" t="s">
-        <v>116</v>
+        <v>207</v>
       </c>
       <c r="F154" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="G154" t="s">
-        <v>90</v>
+        <v>208</v>
       </c>
       <c r="H154" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I154" t="s">
         <v>19</v>
@@ -5758,115 +5776,115 @@
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B155" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C155" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="D155" t="s">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="E155" t="s">
-        <v>205</v>
+        <v>44</v>
       </c>
       <c r="F155" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="G155" t="s">
-        <v>206</v>
+        <v>46</v>
       </c>
       <c r="H155" t="s">
         <v>24</v>
       </c>
       <c r="I155" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B156" t="s">
         <v>81</v>
       </c>
       <c r="C156" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D156" t="s">
-        <v>43</v>
+        <v>204</v>
       </c>
       <c r="E156" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="F156" t="s">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="G156" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H156" t="s">
         <v>24</v>
       </c>
       <c r="I156" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B157" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C157" t="s">
         <v>48</v>
       </c>
       <c r="D157" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="E157" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F157" t="s">
         <v>171</v>
       </c>
       <c r="G157" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="H157" t="s">
-        <v>41</v>
+        <v>209</v>
       </c>
       <c r="I157" t="s">
-        <v>208</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B158" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C158" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D158" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="E158" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="F158" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="G158" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H158" t="s">
-        <v>18</v>
+        <v>209</v>
       </c>
       <c r="I158" t="s">
         <v>19</v>
@@ -5874,126 +5892,126 @@
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B159" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C159" t="s">
-        <v>204</v>
+        <v>13</v>
       </c>
       <c r="D159" t="s">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="E159" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F159" t="s">
         <v>16</v>
       </c>
       <c r="G159" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="H159" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B160" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C160" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="D160" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E160" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F160" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="G160" t="s">
-        <v>71</v>
+        <v>208</v>
       </c>
       <c r="H160" t="s">
         <v>24</v>
       </c>
       <c r="I160" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B161" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C161" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="E161" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="F161" t="s">
-        <v>171</v>
+        <v>28</v>
       </c>
       <c r="G161" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H161" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I161" t="s">
-        <v>208</v>
+        <v>35</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B162" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C162" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D162" t="s">
-        <v>194</v>
+        <v>151</v>
       </c>
       <c r="E162" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="F162" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="G162" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="H162" t="s">
         <v>41</v>
       </c>
       <c r="I162" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B163" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C163" t="s">
         <v>13</v>
@@ -6019,54 +6037,54 @@
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B164" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C164" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D164" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E164" t="s">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="F164" t="s">
         <v>16</v>
       </c>
       <c r="G164" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c r="H164" t="s">
         <v>24</v>
       </c>
       <c r="I164" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B165" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C165" t="s">
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>211</v>
+        <v>69</v>
       </c>
       <c r="E165" t="s">
-        <v>76</v>
+        <v>212</v>
       </c>
       <c r="F165" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="G165" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="H165" t="s">
         <v>24</v>
@@ -6077,16 +6095,16 @@
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B166" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C166" t="s">
         <v>48</v>
       </c>
       <c r="D166" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E166" t="s">
         <v>32</v>
@@ -6101,30 +6119,30 @@
         <v>41</v>
       </c>
       <c r="I166" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B167" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C167" t="s">
         <v>36</v>
       </c>
       <c r="D167" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E167" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="F167" t="s">
         <v>93</v>
       </c>
       <c r="G167" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H167" t="s">
         <v>41</v>
@@ -6135,16 +6153,16 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B168" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C168" t="s">
         <v>13</v>
       </c>
       <c r="D168" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="E168" t="s">
         <v>116</v>
@@ -6164,54 +6182,54 @@
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B169" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C169" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D169" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="E169" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="F169" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="G169" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="H169" t="s">
         <v>24</v>
       </c>
       <c r="I169" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B170" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C170" t="s">
         <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>146</v>
+        <v>213</v>
       </c>
       <c r="E170" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="F170" t="s">
-        <v>124</v>
+        <v>214</v>
       </c>
       <c r="G170" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="H170" t="s">
         <v>24</v>
@@ -6222,88 +6240,320 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B171" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C171" t="s">
-        <v>48</v>
+        <v>215</v>
       </c>
       <c r="D171" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="E171" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="F171" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="G171" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="H171" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I171" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B172" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C172" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D172" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="E172" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F172" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="G172" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="H172" t="s">
         <v>41</v>
       </c>
       <c r="I172" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B173" t="s">
+        <v>97</v>
+      </c>
+      <c r="C173" t="s">
+        <v>36</v>
+      </c>
+      <c r="D173" t="s">
+        <v>200</v>
+      </c>
+      <c r="E173" t="s">
+        <v>38</v>
+      </c>
+      <c r="F173" t="s">
+        <v>93</v>
+      </c>
+      <c r="G173" t="s">
+        <v>143</v>
+      </c>
+      <c r="H173" t="s">
+        <v>41</v>
+      </c>
+      <c r="I173" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="15">
+      <c r="A174" t="s">
+        <v>201</v>
+      </c>
+      <c r="B174" t="s">
+        <v>97</v>
+      </c>
+      <c r="C174" t="s">
+        <v>13</v>
+      </c>
+      <c r="D174" t="s">
+        <v>145</v>
+      </c>
+      <c r="E174" t="s">
+        <v>116</v>
+      </c>
+      <c r="F174" t="s">
+        <v>16</v>
+      </c>
+      <c r="G174" t="s">
+        <v>90</v>
+      </c>
+      <c r="H174" t="s">
+        <v>18</v>
+      </c>
+      <c r="I174" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="15">
+      <c r="A175" t="s">
+        <v>201</v>
+      </c>
+      <c r="B175" t="s">
+        <v>97</v>
+      </c>
+      <c r="C175" t="s">
+        <v>206</v>
+      </c>
+      <c r="D175" t="s">
+        <v>108</v>
+      </c>
+      <c r="E175" t="s">
+        <v>207</v>
+      </c>
+      <c r="F175" t="s">
+        <v>77</v>
+      </c>
+      <c r="G175" t="s">
+        <v>90</v>
+      </c>
+      <c r="H175" t="s">
+        <v>24</v>
+      </c>
+      <c r="I175" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="15">
+      <c r="A176" t="s">
+        <v>201</v>
+      </c>
+      <c r="B176" t="s">
+        <v>97</v>
+      </c>
+      <c r="C176" t="s">
+        <v>25</v>
+      </c>
+      <c r="D176" t="s">
+        <v>146</v>
+      </c>
+      <c r="E176" t="s">
+        <v>212</v>
+      </c>
+      <c r="F176" t="s">
+        <v>124</v>
+      </c>
+      <c r="G176" t="s">
+        <v>71</v>
+      </c>
+      <c r="H176" t="s">
+        <v>24</v>
+      </c>
+      <c r="I176" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="15">
+      <c r="A177" t="s">
+        <v>201</v>
+      </c>
+      <c r="B177" t="s">
         <v>107</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C177" t="s">
+        <v>215</v>
+      </c>
+      <c r="D177" t="s">
+        <v>131</v>
+      </c>
+      <c r="E177" t="s">
+        <v>207</v>
+      </c>
+      <c r="F177" t="s">
+        <v>152</v>
+      </c>
+      <c r="G177" t="s">
+        <v>216</v>
+      </c>
+      <c r="H177" t="s">
+        <v>24</v>
+      </c>
+      <c r="I177" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="15">
+      <c r="A178" t="s">
+        <v>201</v>
+      </c>
+      <c r="B178" t="s">
+        <v>107</v>
+      </c>
+      <c r="C178" t="s">
+        <v>48</v>
+      </c>
+      <c r="D178" t="s">
+        <v>49</v>
+      </c>
+      <c r="E178" t="s">
+        <v>32</v>
+      </c>
+      <c r="F178" t="s">
+        <v>171</v>
+      </c>
+      <c r="G178" t="s">
+        <v>34</v>
+      </c>
+      <c r="H178" t="s">
+        <v>41</v>
+      </c>
+      <c r="I178" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="15">
+      <c r="A179" t="s">
+        <v>201</v>
+      </c>
+      <c r="B179" t="s">
+        <v>107</v>
+      </c>
+      <c r="C179" t="s">
+        <v>36</v>
+      </c>
+      <c r="D179" t="s">
+        <v>200</v>
+      </c>
+      <c r="E179" t="s">
+        <v>38</v>
+      </c>
+      <c r="F179" t="s">
+        <v>93</v>
+      </c>
+      <c r="G179" t="s">
+        <v>143</v>
+      </c>
+      <c r="H179" t="s">
+        <v>41</v>
+      </c>
+      <c r="I179" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="15">
+      <c r="A180" t="s">
+        <v>201</v>
+      </c>
+      <c r="B180" t="s">
+        <v>107</v>
+      </c>
+      <c r="C180" t="s">
         <v>13</v>
       </c>
-      <c r="D173" t="s">
+      <c r="D180" t="s">
         <v>145</v>
       </c>
-      <c r="E173" t="s">
+      <c r="E180" t="s">
         <v>116</v>
       </c>
-      <c r="F173" t="s">
+      <c r="F180" t="s">
         <v>16</v>
       </c>
-      <c r="G173" t="s">
+      <c r="G180" t="s">
         <v>90</v>
       </c>
-      <c r="H173" t="s">
+      <c r="H180" t="s">
         <v>18</v>
       </c>
-      <c r="I173" t="s">
+      <c r="I180" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="15">
+      <c r="A181" t="s">
+        <v>201</v>
+      </c>
+      <c r="B181" t="s">
+        <v>113</v>
+      </c>
+      <c r="C181" t="s">
+        <v>215</v>
+      </c>
+      <c r="D181" t="s">
+        <v>131</v>
+      </c>
+      <c r="E181" t="s">
+        <v>207</v>
+      </c>
+      <c r="F181" t="s">
+        <v>152</v>
+      </c>
+      <c r="G181" t="s">
+        <v>216</v>
+      </c>
+      <c r="H181" t="s">
+        <v>24</v>
+      </c>
+      <c r="I181" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6315,7 +6565,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{53606715-7ab7-44aa-b488-3168f3e3a607}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a0fb0260-0fbd-49d3-bcf9-48cf90e93b9d}">
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6335,16 +6585,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6364,13 +6614,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
         <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E2" t="s">
         <v>121</v>
@@ -6393,13 +6643,13 @@
         <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E3" t="s">
         <v>110</v>
@@ -6408,7 +6658,7 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -6422,16 +6672,16 @@
         <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -6451,13 +6701,13 @@
         <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E5" t="s">
         <v>121</v>
@@ -6480,16 +6730,16 @@
         <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C6" t="s">
         <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E6" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -6509,13 +6759,13 @@
         <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C7" t="s">
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E7" t="s">
         <v>121</v>
@@ -6538,16 +6788,16 @@
         <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E8" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
@@ -6567,22 +6817,22 @@
         <v>132</v>
       </c>
       <c r="B9" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E9" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -6596,16 +6846,16 @@
         <v>132</v>
       </c>
       <c r="B10" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F10" t="s">
         <v>24</v>
@@ -6625,16 +6875,16 @@
         <v>132</v>
       </c>
       <c r="B11" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E11" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -6654,13 +6904,13 @@
         <v>181</v>
       </c>
       <c r="B12" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E12" t="s">
         <v>110</v>
@@ -6669,7 +6919,7 @@
         <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
@@ -6686,8 +6936,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0b8b47db-9b62-4233-874c-c57b4572568f}">
-  <dimension ref="A1:F41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{56ddb128-0853-4b53-bcdf-fddfbf56cbd4}">
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6703,13 +6953,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6723,16 +6973,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
@@ -6743,13 +6993,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E3" t="s">
         <v>157</v>
@@ -6763,13 +7013,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E4" t="s">
         <v>173</v>
@@ -6783,13 +7033,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E5" t="s">
         <v>178</v>
@@ -6803,13 +7053,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E6" t="s">
         <v>144</v>
@@ -6823,13 +7073,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E7" t="s">
         <v>106</v>
@@ -6843,13 +7093,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E8" t="s">
         <v>34</v>
@@ -6863,13 +7113,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C9" t="s">
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E9" t="s">
         <v>48</v>
@@ -6883,13 +7133,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E10" t="s">
         <v>159</v>
@@ -6903,16 +7153,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C11" t="s">
         <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -6923,13 +7173,13 @@
         <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E12" t="s">
         <v>163</v>
@@ -6943,13 +7193,13 @@
         <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E13" t="s">
         <v>54</v>
@@ -6963,13 +7213,13 @@
         <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E14" t="s">
         <v>178</v>
@@ -6983,16 +7233,16 @@
         <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C15" t="s">
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E15" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F15" t="s">
         <v>41</v>
@@ -7003,13 +7253,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C16" t="s">
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E16" t="s">
         <v>159</v>
@@ -7023,16 +7273,16 @@
         <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E17" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F17" t="s">
         <v>41</v>
@@ -7043,13 +7293,13 @@
         <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E18" t="s">
         <v>34</v>
@@ -7063,16 +7313,16 @@
         <v>132</v>
       </c>
       <c r="B19" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C19" t="s">
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E19" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F19" t="s">
         <v>24</v>
@@ -7083,13 +7333,13 @@
         <v>132</v>
       </c>
       <c r="B20" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E20" t="s">
         <v>65</v>
@@ -7103,16 +7353,16 @@
         <v>132</v>
       </c>
       <c r="B21" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C21" t="s">
         <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E21" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F21" t="s">
         <v>24</v>
@@ -7123,16 +7373,16 @@
         <v>132</v>
       </c>
       <c r="B22" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C22" t="s">
         <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E22" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F22" t="s">
         <v>24</v>
@@ -7143,16 +7393,16 @@
         <v>132</v>
       </c>
       <c r="B23" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C23" t="s">
         <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F23" t="s">
         <v>41</v>
@@ -7163,16 +7413,16 @@
         <v>132</v>
       </c>
       <c r="B24" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C24" t="s">
         <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E24" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F24" t="s">
         <v>24</v>
@@ -7183,13 +7433,13 @@
         <v>132</v>
       </c>
       <c r="B25" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C25" t="s">
         <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E25" t="s">
         <v>126</v>
@@ -7203,16 +7453,16 @@
         <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C26" t="s">
         <v>138</v>
       </c>
       <c r="D26" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E26" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F26" t="s">
         <v>24</v>
@@ -7223,16 +7473,16 @@
         <v>181</v>
       </c>
       <c r="B27" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E27" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F27" t="s">
         <v>24</v>
@@ -7243,13 +7493,13 @@
         <v>181</v>
       </c>
       <c r="B28" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C28" t="s">
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E28" t="s">
         <v>178</v>
@@ -7263,13 +7513,13 @@
         <v>181</v>
       </c>
       <c r="B29" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C29" t="s">
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E29" t="s">
         <v>78</v>
@@ -7283,16 +7533,16 @@
         <v>181</v>
       </c>
       <c r="B30" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C30" t="s">
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E30" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F30" t="s">
         <v>41</v>
@@ -7303,13 +7553,13 @@
         <v>181</v>
       </c>
       <c r="B31" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C31" t="s">
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E31" t="s">
         <v>54</v>
@@ -7323,13 +7573,13 @@
         <v>181</v>
       </c>
       <c r="B32" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E32" t="s">
         <v>159</v>
@@ -7343,36 +7593,36 @@
         <v>181</v>
       </c>
       <c r="B33" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="D33" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="E33" t="s">
-        <v>204</v>
+        <v>264</v>
       </c>
       <c r="F33" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B34" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E34" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="F34" t="s">
         <v>41</v>
@@ -7380,19 +7630,19 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B35" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="C35" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="F35" t="s">
         <v>41</v>
@@ -7400,39 +7650,39 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E36" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B37" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C37" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E37" t="s">
-        <v>258</v>
+        <v>112</v>
       </c>
       <c r="F37" t="s">
         <v>24</v>
@@ -7440,19 +7690,19 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="D38" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E38" t="s">
-        <v>34</v>
+        <v>262</v>
       </c>
       <c r="F38" t="s">
         <v>24</v>
@@ -7460,62 +7710,102 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B39" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E39" t="s">
         <v>34</v>
       </c>
       <c r="F39" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="E40" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s">
+        <v>251</v>
+      </c>
+      <c r="C41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41" t="s">
+        <v>112</v>
+      </c>
+      <c r="F41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15">
+      <c r="A42" t="s">
+        <v>201</v>
+      </c>
+      <c r="B42" t="s">
+        <v>252</v>
+      </c>
+      <c r="C42" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" t="s">
         <v>248</v>
       </c>
-      <c r="C41" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" t="s">
-        <v>244</v>
-      </c>
-      <c r="E41" t="s">
-        <v>195</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="E42" t="s">
+        <v>197</v>
+      </c>
+      <c r="F42" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15">
+      <c r="A43" t="s">
+        <v>201</v>
+      </c>
+      <c r="B43" t="s">
+        <v>266</v>
+      </c>
+      <c r="C43" t="s">
+        <v>215</v>
+      </c>
+      <c r="D43" t="s">
+        <v>260</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,12 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="253">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
   <si>
-    <t>Okres: 05.10.2026 (pon.) - 11.10.2026 (niedz.)</t>
+    <t>Okres: 12.10.2026 (pon.) - 18.10.2026 (niedz.)</t>
   </si>
   <si>
     <t>Dzień</t>
@@ -57,7 +57,7 @@
     <t>Forma płatności</t>
   </si>
   <si>
-    <t>05.10.2026</t>
+    <t>12.10.2026</t>
   </si>
   <si>
     <t>1, 08:00-08:45</t>
@@ -84,742 +84,700 @@
     <t>-</t>
   </si>
   <si>
-    <t>Mocarski Arkadiusz</t>
-  </si>
-  <si>
-    <t>3K|kucharz</t>
-  </si>
-  <si>
-    <t>Technologia gastronomiczna z towaroznawstwem</t>
+    <t>2, 08:50-09:35</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>2K|gr2</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</t>
+  </si>
+  <si>
+    <t>prs</t>
+  </si>
+  <si>
+    <t>Stępień Krystyna</t>
+  </si>
+  <si>
+    <t>Erasmus+</t>
+  </si>
+  <si>
+    <t>Godzina do zliczenia</t>
+  </si>
+  <si>
+    <t>Kosin Anna</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>Towar jako przedmiot handlu</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>p. Sałdyka-Rusek, edukacja zdrowotna za lekcję 9</t>
+  </si>
+  <si>
+    <t>3, 09:40-10:25</t>
+  </si>
+  <si>
+    <t>Galert Anna</t>
+  </si>
+  <si>
+    <t>1FB|gr1</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>Fizyka</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Biczysko Wojciech</t>
+  </si>
+  <si>
+    <t>Dodatkowo płatne</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>4, 10:35-11:20</t>
+  </si>
+  <si>
+    <t>1TFB|gr1</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>1TFB|gr2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>4TFA</t>
+  </si>
+  <si>
+    <t>2TFA|gr1</t>
+  </si>
+  <si>
+    <t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Jaworska Edyta</t>
+  </si>
+  <si>
+    <t>3K|sprzed</t>
+  </si>
+  <si>
+    <t>Język angielski zawodowy</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>5, 11:25-12:10</t>
+  </si>
+  <si>
+    <t>1TFA|gr2</t>
+  </si>
+  <si>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>Wrzeszcz Barbara</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
+    <t>Nowak Magdalena</t>
+  </si>
+  <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Kaczorowski Waldemar</t>
+  </si>
+  <si>
+    <t>6, 12:25-13:10</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
+    <t>7, 13:15-14:00</t>
+  </si>
+  <si>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>8, 14:05-14:50</t>
+  </si>
+  <si>
+    <t>1CA|gr1</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Dalach Krystyna</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
+    <t>1TH</t>
+  </si>
+  <si>
+    <t>Filipiak Wiesław</t>
+  </si>
+  <si>
+    <t>9, 14:55-15:40</t>
+  </si>
+  <si>
+    <t>3TFB|gr1</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>1TFB</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Sałdyka-Rusek Karolina</t>
+  </si>
+  <si>
+    <t>10, 15:45-16:30</t>
+  </si>
+  <si>
+    <t>Uczniowie zwolnieni do domu</t>
+  </si>
+  <si>
+    <t>13.10.2026</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>3CB</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
+  </si>
+  <si>
+    <t>3FA</t>
+  </si>
+  <si>
+    <t>Edukacja obywatelska</t>
+  </si>
+  <si>
+    <t>Zaleska Magdalena</t>
+  </si>
+  <si>
+    <t>3FC</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
+    <t>3CA</t>
+  </si>
+  <si>
+    <t>Mucha Anna</t>
+  </si>
+  <si>
+    <t>Edukacja zdrowotna</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>3WA</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>Wychowanie fizyczne</t>
+  </si>
+  <si>
+    <t>sg6</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Małecka Barbara</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>Antoszewska Joanna</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>Cieśla Marcin</t>
+  </si>
+  <si>
+    <t>Mikołajczak Sylwia</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>Dalach Sławomir</t>
+  </si>
+  <si>
+    <t>4TH|gr2</t>
+  </si>
+  <si>
+    <t>Ostrowska Ewa</t>
+  </si>
+  <si>
+    <t>1TFH|t.usfryz</t>
+  </si>
+  <si>
+    <t>3FB|DZ</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>14.10.2026</t>
+  </si>
+  <si>
+    <t>1CB|gr1</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>1FA|gr2</t>
+  </si>
+  <si>
+    <t>15.10.2026</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
+  </si>
+  <si>
+    <t>1CB|fryzjer</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>1FC|gr2</t>
+  </si>
+  <si>
+    <t>sg5</t>
+  </si>
+  <si>
+    <t>1K|gr1</t>
+  </si>
+  <si>
+    <t>1FC|gr1</t>
+  </si>
+  <si>
+    <t>2FA</t>
+  </si>
+  <si>
+    <t>3TFB|t.hand.</t>
+  </si>
+  <si>
+    <t>1S|gr2</t>
+  </si>
+  <si>
+    <t>1TH|gr2</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>1S|gr1</t>
+  </si>
+  <si>
+    <t>3TFB|gr2</t>
+  </si>
+  <si>
+    <t>prF3</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>1B|gr1</t>
+  </si>
+  <si>
+    <t>16.10.2026</t>
+  </si>
+  <si>
+    <t>3TFB|DZ</t>
+  </si>
+  <si>
+    <t>sg1</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - fryzjerstwo wellness</t>
+  </si>
+  <si>
+    <t>dzień wolny za pracę w niedzielę (z uczniami wyjazd Erasmus+)</t>
+  </si>
+  <si>
+    <t>Smereka Alicja</t>
+  </si>
+  <si>
+    <t>Geografia</t>
+  </si>
+  <si>
+    <t>Taszycka Magdalena</t>
+  </si>
+  <si>
+    <t>Informatyka</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Wójcik Kamil</t>
+  </si>
+  <si>
+    <t>3TFB|CH</t>
+  </si>
+  <si>
+    <t>1TFH</t>
+  </si>
+  <si>
+    <t>Płatek Krzysztof</t>
+  </si>
+  <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>Edukacja dla bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>1TFH|gr1</t>
+  </si>
+  <si>
+    <t>5TFB|DZ</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>1WA|gr1</t>
+  </si>
+  <si>
+    <t>1FB|DZ</t>
+  </si>
+  <si>
+    <t>1FB|CH</t>
+  </si>
+  <si>
+    <t>sg2</t>
+  </si>
+  <si>
+    <t>1TFH|t.hand.</t>
+  </si>
+  <si>
+    <t>1CB</t>
+  </si>
+  <si>
+    <t>1WA</t>
+  </si>
+  <si>
+    <t>1FB|gr2</t>
+  </si>
+  <si>
+    <t>11, 16:35-17:20</t>
+  </si>
+  <si>
+    <t>Godzina</t>
+  </si>
+  <si>
+    <t>Nauczyciel</t>
+  </si>
+  <si>
+    <t>Dziennik zajęć innych</t>
+  </si>
+  <si>
+    <t>Opis zajęć</t>
+  </si>
+  <si>
+    <t>08:00-08:45</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>13:15-14:00</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Towaroznawstwo</t>
+  </si>
+  <si>
+    <t>17:25-18:10</t>
+  </si>
+  <si>
+    <t>Obsługa klienta</t>
+  </si>
+  <si>
+    <t>18:15-19:00</t>
+  </si>
+  <si>
+    <t>Organizacja sprzedaży</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Język angielski </t>
+  </si>
+  <si>
+    <t>08:00-14:40</t>
+  </si>
+  <si>
+    <t>Bokuniewicz Sylwia</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Smirnow-Zechman Eleonora</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
-    <t>Biznes i zarządzanie</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>2, 08:50-09:35</t>
-  </si>
-  <si>
-    <t>Dalach Krystyna</t>
-  </si>
-  <si>
-    <t>2TFB|DZ</t>
-  </si>
-  <si>
-    <t>Wychowanie fizyczne</t>
-  </si>
-  <si>
-    <t>sg1</t>
-  </si>
-  <si>
-    <t>Nestoruk Lidia</t>
-  </si>
-  <si>
-    <t>Dodatkowo płatne</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>2K|gr2</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Karczmarz Aleksandra</t>
-  </si>
-  <si>
-    <t>Erasmus+</t>
-  </si>
-  <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
-    <t>1FB</t>
-  </si>
-  <si>
-    <t>Zajęcia biblioteczne</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>Wrzeszcz Barbara</t>
-  </si>
-  <si>
-    <t>3, 09:40-10:25</t>
-  </si>
-  <si>
-    <t>Galert Anna</t>
-  </si>
-  <si>
-    <t>1FB|gr1</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Biezmienow Małgorzata</t>
-  </si>
-  <si>
-    <t>3TFA</t>
-  </si>
-  <si>
-    <t>Fizyka</t>
-  </si>
-  <si>
-    <t>Biczysko Wojciech</t>
-  </si>
-  <si>
-    <t>Nowak Magdalena</t>
-  </si>
-  <si>
-    <t>3K</t>
-  </si>
-  <si>
-    <t>4, 10:35-11:20</t>
-  </si>
-  <si>
-    <t>1TFB|gr1</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>1TFB|gr2</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2TFA|gr1</t>
-  </si>
-  <si>
-    <t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</t>
-  </si>
-  <si>
-    <t>prf2</t>
-  </si>
-  <si>
-    <t>Leńczowska Iwona</t>
-  </si>
-  <si>
-    <t>2K|gr1</t>
-  </si>
-  <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>Filipiak Wiesław</t>
-  </si>
-  <si>
-    <t>1CA</t>
-  </si>
-  <si>
-    <t>Technologie produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
-    <t>5, 11:25-12:10</t>
-  </si>
-  <si>
-    <t>4TFB|DZ</t>
-  </si>
-  <si>
-    <t>1TFA|gr2</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Kaczorowski Waldemar</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>6, 12:25-13:10</t>
-  </si>
-  <si>
-    <t>1WA</t>
-  </si>
-  <si>
-    <t>7, 13:15-14:00</t>
-  </si>
-  <si>
-    <t>Młynarczyk Paweł</t>
-  </si>
-  <si>
-    <t>1WA|gr2</t>
-  </si>
-  <si>
-    <t>Informatyka</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
-    <t>2FC</t>
-  </si>
-  <si>
-    <t>Uczniowie zwolnieni do domu</t>
-  </si>
-  <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>1CA|gr1</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>Wojciechowski Łukasz</t>
-  </si>
-  <si>
-    <t>Edukacja dla bezpieczeństwa</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>9, 14:55-15:40</t>
-  </si>
-  <si>
-    <t>2FA</t>
-  </si>
-  <si>
-    <t>Zajęcia z wychowawcą</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Dalach Sławomir</t>
-  </si>
-  <si>
-    <t>1CA|CH</t>
-  </si>
-  <si>
-    <t>sg6</t>
-  </si>
-  <si>
-    <t>3TFB|gr1</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
-    <t>10, 15:45-16:30</t>
-  </si>
-  <si>
-    <t>4TFA</t>
-  </si>
-  <si>
-    <t>1TFB</t>
-  </si>
-  <si>
-    <t>Biologia</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>Sałdyka Karolina</t>
-  </si>
-  <si>
-    <t>11, 16:35-17:20</t>
-  </si>
-  <si>
-    <t>06.10.2026</t>
-  </si>
-  <si>
-    <t>3FA</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Wójcik Kamil</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Antoszewska Joanna</t>
-  </si>
-  <si>
-    <t>Język angielski zawodowy</t>
-  </si>
-  <si>
-    <t>2CB</t>
-  </si>
-  <si>
-    <t>Edukacja zdrowotna</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Projektowanie fryzur</t>
-  </si>
-  <si>
-    <t>Płatek Krzysztof</t>
-  </si>
-  <si>
-    <t>Edukacja obywatelska</t>
-  </si>
-  <si>
-    <t>Kopij Marcin</t>
-  </si>
-  <si>
-    <t>4TH|gr2</t>
-  </si>
-  <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>3B</t>
-  </si>
-  <si>
-    <t>07.10.2026</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
-  </si>
-  <si>
-    <t>1S</t>
-  </si>
-  <si>
-    <t>Obsługa klientów</t>
-  </si>
-  <si>
-    <t>1TFH|gr2</t>
-  </si>
-  <si>
-    <t>p. Najwer, informatyka za lekcję 1</t>
-  </si>
-  <si>
-    <t>Misiąg Anna</t>
-  </si>
-  <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>p. Zaleska, historia za lekcję 8</t>
-  </si>
-  <si>
-    <t>2WA|gr1</t>
-  </si>
-  <si>
-    <t>2S</t>
-  </si>
-  <si>
-    <t>Staliś Donata</t>
-  </si>
-  <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>1CB</t>
-  </si>
-  <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>Mucha Anna</t>
-  </si>
-  <si>
-    <t>1CB|gr2</t>
-  </si>
-  <si>
-    <t>p. Kończyńska, technologie produkcji cukierniczej za lekcję 9</t>
-  </si>
-  <si>
-    <t>1CB|gr1</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Przeniesiona</t>
-  </si>
-  <si>
-    <t>Erasmus+ / p. Kończyńska, technologie produkcji cukierniczej za lekcję 9</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>p. Filipek, j. polski za lekcję 9</t>
-  </si>
-  <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>Kruk Marcin</t>
-  </si>
-  <si>
-    <t>spotkanie COVE Polska - bez uczniów</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>p. Ulanowska, j. polski za lekcję 8</t>
-  </si>
-  <si>
-    <t>Cieśla Marcin</t>
-  </si>
-  <si>
-    <t>1K|gr2</t>
-  </si>
-  <si>
-    <t>sg5</t>
-  </si>
-  <si>
-    <t>1FA|gr2</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>1TH|gr1</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Erasmus+ / p. Filipek, j. polski za lekcję 8</t>
-  </si>
-  <si>
-    <t>Zaleska Magdalena</t>
-  </si>
-  <si>
-    <t>3TFB|gr2</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>Doradztwo zawodowe</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
-    <t>W ramach pensum</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>08.10.2026</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>1FC|gr2</t>
-  </si>
-  <si>
-    <t>Pietrycha Małgorzata</t>
-  </si>
-  <si>
-    <t>1K|gr1</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>p. Karczmarz, j. angielski za lekcję 3</t>
-  </si>
-  <si>
-    <t>1FC|gr1</t>
-  </si>
-  <si>
-    <t>Erasmus+ / p. Nestoruk, wychowanie fizyczne za lekcję 2</t>
-  </si>
-  <si>
-    <t>2WA</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>p. Filusz, matematyka za lekcję 9</t>
-  </si>
-  <si>
-    <t>1WB</t>
-  </si>
-  <si>
-    <t>p. Biczysko, fizyka za lekcję 8</t>
-  </si>
-  <si>
-    <t>1S|gr2</t>
-  </si>
-  <si>
-    <t>1TH|gr2</t>
-  </si>
-  <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
-    <t>p. Sobczak, przeniesienie techniki fryzjerskie na lekcję 7</t>
-  </si>
-  <si>
-    <t>Erasmus + / Wyjazd FERS</t>
-  </si>
-  <si>
-    <t>1B|gr1</t>
-  </si>
-  <si>
-    <t>09.10.2026</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - fryzjerstwo wellness</t>
-  </si>
-  <si>
-    <t>Małecka Barbara</t>
-  </si>
-  <si>
-    <t>5TH|DZ</t>
-  </si>
-  <si>
-    <t>sg2</t>
-  </si>
-  <si>
-    <t>Piątek-Pawłowska Bożena</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>Okienko dla uczniów</t>
-  </si>
-  <si>
-    <t>Erasmus+ / p. Małecka biologia za lekcję 7</t>
-  </si>
-  <si>
-    <t>Godzina do zliczenia</t>
-  </si>
-  <si>
-    <t>3FB</t>
-  </si>
-  <si>
-    <t>Technika w produkcji cukierniczej</t>
-  </si>
-  <si>
-    <t>1TFH</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>dyżur pedagoga</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>08:50-09:35</t>
+  </si>
+  <si>
+    <t>09:40-10:25</t>
+  </si>
+  <si>
+    <t>10:35-11:20</t>
+  </si>
+  <si>
+    <t>12:30-17:30</t>
+  </si>
+  <si>
+    <t>Kaszak Maria</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">dyżur pedagoga specjalnego </t>
+  </si>
+  <si>
+    <t>14:55-15:40</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur -T</t>
+  </si>
+  <si>
+    <t>07:15-08:00</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur za 29.09.26</t>
+  </si>
+  <si>
+    <t>08:00-11:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projektowanie i wykonywanie fryzur-zaj.prakt. </t>
+  </si>
+  <si>
+    <t>10:00-17:00</t>
+  </si>
+  <si>
+    <t>Aszkiełowicz Aleksandra</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Dyżur psychologa szkolnego</t>
+  </si>
+  <si>
+    <t>11:00-17:30</t>
+  </si>
+  <si>
+    <t>Miejsce dyżuru</t>
+  </si>
+  <si>
+    <t>10:25-10:35</t>
+  </si>
+  <si>
+    <t>piętro_3</t>
+  </si>
+  <si>
+    <t>Skarupa Agnieszka</t>
+  </si>
+  <si>
+    <t>14:00-14:05</t>
+  </si>
+  <si>
+    <t>parter</t>
+  </si>
+  <si>
+    <t>14:50-14:55</t>
+  </si>
+  <si>
+    <t>piętro_2</t>
   </si>
   <si>
     <t>Derezińska Katarzyna</t>
   </si>
   <si>
-    <t>Brak</t>
-  </si>
-  <si>
-    <t>Godzina</t>
-  </si>
-  <si>
-    <t>Nauczyciel</t>
-  </si>
-  <si>
-    <t>Dziennik zajęć innych</t>
-  </si>
-  <si>
-    <t>Opis zajęć</t>
-  </si>
-  <si>
-    <t>08:00-08:45</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>07:00-07:45</t>
-  </si>
-  <si>
-    <t>Zych Joanna</t>
-  </si>
-  <si>
-    <t>lekcja odwołana</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Język angielski </t>
-  </si>
-  <si>
-    <t>08:50-09:35</t>
-  </si>
-  <si>
-    <t>09:40-10:25</t>
-  </si>
-  <si>
-    <t>10:35-11:20</t>
-  </si>
-  <si>
-    <t>14:55-15:40</t>
-  </si>
-  <si>
-    <t>Projektowanie fryzur -T</t>
-  </si>
-  <si>
-    <t>07:10-07:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chemia/fizyka </t>
-  </si>
-  <si>
-    <t>07:15-08:00</t>
-  </si>
-  <si>
-    <t>Projektowanie fryzur za 29.09.26</t>
-  </si>
-  <si>
-    <t>08:00-11:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projektowanie i wykonywanie fryzur-zaj.prakt. </t>
-  </si>
-  <si>
-    <t>Miejsce dyżuru</t>
+    <t>16:30-16:35</t>
+  </si>
+  <si>
+    <t>09:35-09:40</t>
+  </si>
+  <si>
+    <t>piętro_1</t>
+  </si>
+  <si>
+    <t>11:20-11:25</t>
+  </si>
+  <si>
+    <t>bramka wejściowa</t>
+  </si>
+  <si>
+    <t>12:10-12:25</t>
+  </si>
+  <si>
+    <t>13:10-13:15</t>
+  </si>
+  <si>
+    <t>boisko - dziedziniec wejściowy/boisko</t>
+  </si>
+  <si>
+    <t>07:55-08:00</t>
   </si>
   <si>
     <t>08:45-08:50</t>
   </si>
   <si>
-    <t>piętro_1</t>
-  </si>
-  <si>
-    <t>Ulanowska Magdalena</t>
-  </si>
-  <si>
-    <t>10:25-10:35</t>
-  </si>
-  <si>
-    <t>Stępień Krystyna</t>
-  </si>
-  <si>
-    <t>boisko - dziedziniec wejściowy/boisko</t>
-  </si>
-  <si>
-    <t>11:20-11:25</t>
-  </si>
-  <si>
-    <t>14:00-14:05</t>
-  </si>
-  <si>
-    <t>parter</t>
-  </si>
-  <si>
-    <t>piętro_2</t>
-  </si>
-  <si>
-    <t>14:50-14:55</t>
-  </si>
-  <si>
     <t>15:40-15:45</t>
-  </si>
-  <si>
-    <t>16:30-16:35</t>
-  </si>
-  <si>
-    <t>Bujanowska Iwona</t>
-  </si>
-  <si>
-    <t>12:10-12:25</t>
-  </si>
-  <si>
-    <t>bramka wejściowa</t>
-  </si>
-  <si>
-    <t>13:10-13:15</t>
-  </si>
-  <si>
-    <t>Mikołajczak Sylwia</t>
-  </si>
-  <si>
-    <t>Ostrowska Ewa</t>
-  </si>
-  <si>
-    <t>09:35-09:40</t>
-  </si>
-  <si>
-    <t>piętro_3</t>
-  </si>
-  <si>
-    <t>Taszycka Magdalena</t>
-  </si>
-  <si>
-    <t>Jaworska Edyta</t>
-  </si>
-  <si>
-    <t>Sobczak Anna</t>
-  </si>
-  <si>
-    <t>Czukiewska Bożena</t>
-  </si>
-  <si>
-    <t>07:55-08:00</t>
   </si>
   <si>
     <t>17:20-17:25</t>
@@ -1272,7 +1230,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{95829385-fc75-4eaa-8307-ebea8736095e}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{94519e7a-335f-43e3-90dd-14cc5ea1b819}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1293,18 +1251,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8a4629d2-ecac-47f1-ab56-471c39cc8acd}">
-  <dimension ref="A1:I181"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8507b993-b9c0-4c01-af79-a2305d0ff75e}">
+  <dimension ref="A1:I179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="28.1428571428571" customWidth="1"/>
-    <col min="4" max="4" width="11.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="51.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="13.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="27.8571428571429" customWidth="1"/>
-    <col min="8" max="8" width="64.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="56.2857142857143" customWidth="1"/>
     <col min="9" max="9" width="19.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1371,28 +1329,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
@@ -1400,25 +1358,25 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
         <v>19</v>
@@ -1429,28 +1387,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1458,28 +1416,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
         <v>36</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>39</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
         <v>40</v>
-      </c>
-      <c r="H6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1487,28 +1445,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1516,25 +1474,25 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
@@ -1545,28 +1503,28 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
@@ -1574,28 +1532,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I10" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -1603,28 +1561,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1632,28 +1590,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I12" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1661,25 +1619,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I13" t="s">
         <v>19</v>
@@ -1690,28 +1648,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" t="s">
         <v>45</v>
-      </c>
-      <c r="G14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1719,28 +1677,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H15" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1748,28 +1706,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="H16" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1777,28 +1735,28 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1806,28 +1764,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
       </c>
       <c r="D18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" t="s">
         <v>62</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>63</v>
       </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18" t="s">
-        <v>65</v>
-      </c>
       <c r="H18" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1835,28 +1793,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I19" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1864,28 +1822,28 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1893,28 +1851,28 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" t="s">
+        <v>63</v>
+      </c>
+      <c r="H21" t="s">
         <v>26</v>
       </c>
-      <c r="E21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" t="s">
-        <v>68</v>
-      </c>
-      <c r="H21" t="s">
-        <v>24</v>
-      </c>
       <c r="I21" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
@@ -1922,28 +1880,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I22" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
@@ -1951,28 +1909,28 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="G23" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I23" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1980,28 +1938,28 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F24" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" t="s">
+        <v>63</v>
+      </c>
+      <c r="H24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" t="s">
         <v>45</v>
-      </c>
-      <c r="G24" t="s">
-        <v>46</v>
-      </c>
-      <c r="H24" t="s">
-        <v>41</v>
-      </c>
-      <c r="I24" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -2009,28 +1967,28 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="H25" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I25" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -2038,28 +1996,28 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F26" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I26" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -2067,28 +2025,28 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="H27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I27" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -2096,28 +2054,28 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" t="s">
         <v>72</v>
       </c>
-      <c r="C28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E28" t="s">
-        <v>27</v>
-      </c>
       <c r="F28" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="H28" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
@@ -2125,28 +2083,28 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F29" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="G29" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="H29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I29" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
@@ -2154,28 +2112,28 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="G30" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="H30" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I30" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -2183,28 +2141,28 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E31" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F31" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H31" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" t="s">
         <v>45</v>
-      </c>
-      <c r="G31" t="s">
-        <v>46</v>
-      </c>
-      <c r="H31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
@@ -2212,28 +2170,28 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="G32" t="s">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="H32" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I32" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -2241,28 +2199,28 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E33" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="F33" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G33" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="H33" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I33" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -2270,141 +2228,141 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E34" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="H34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="G35" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="H35" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F36" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="H36" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="F37" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G37" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="H37" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I37" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="D38" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E38" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="F38" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="G38" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="H38" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I38" t="s">
         <v>19</v>
@@ -2412,86 +2370,86 @@
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D39" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="G39" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="H39" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I39" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="E40" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F40" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="H40" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D41" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="F41" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="G41" t="s">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="H41" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I41" t="s">
         <v>19</v>
@@ -2499,144 +2457,144 @@
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="D42" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="E42" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F42" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="G42" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I42" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="E43" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F43" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="G43" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="H43" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="D44" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="G44" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H44" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="E45" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="G45" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H45" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="F46" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="G46" t="s">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="H46" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
@@ -2644,28 +2602,28 @@
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="D47" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="E47" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="F47" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="G47" t="s">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="H47" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
@@ -2673,144 +2631,144 @@
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="E48" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="F48" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="G48" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="H48" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I48" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="D49" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E49" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F49" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="G49" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="H49" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I49" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="F50" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H50" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D51" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="E51" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="F51" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="G51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="E52" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="F52" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G52" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I52" t="s">
         <v>19</v>
@@ -2818,126 +2776,126 @@
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="E53" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="F53" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="G53" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H53" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I53" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="E54" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="F54" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="G54" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="H54" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I54" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="E55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F55" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G55" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H55" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I55" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="E56" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F56" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="G56" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H56" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I56" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
@@ -2946,277 +2904,277 @@
         <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F57" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="H57" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="D58" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="E58" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="F58" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G58" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H58" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I58" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B59" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="E59" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="G59" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="H59" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="D60" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="E60" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F60" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G60" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="H60" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I60" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="D61" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="E61" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="F61" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G61" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="H61" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I61" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C62" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D62" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="E62" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="F62" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G62" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="H62" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B63" t="s">
         <v>83</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D63" t="s">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="E63" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="F63" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="G63" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="H63" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B64" t="s">
         <v>83</v>
       </c>
       <c r="C64" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="F64" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H64" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B65" t="s">
         <v>83</v>
       </c>
       <c r="C65" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E65" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="F65" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="G65" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="H65" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I65" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B66" t="s">
         <v>83</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="D66" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="G66" t="s">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="H66" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I66" t="s">
         <v>19</v>
@@ -3224,173 +3182,173 @@
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B67" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="E67" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="F67" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="G67" t="s">
-        <v>90</v>
+      